--- a/outputs/marine_equipment/Контейнер_погрузка.xlsx
+++ b/outputs/marine_equipment/Контейнер_погрузка.xlsx
@@ -188,10 +188,10 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -562,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -733,7 +733,7 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>34 956 489 руб</t>
+          <t>33 276 101 руб</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>35 281 041 руб</t>
+          <t>34 819 624 руб</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>10 позиций, 201 кг</t>
+          <t>28 позиций, 521 кг</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
@@ -849,57 +849,81 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Не считаем от металла</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>50 позиций, 1 183 кг</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>электромагнитные и редукционные клапаны, клапаны Ру от 100, сталь и титан — цену согласовываем отдельно</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Что решили и по чему считаем</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>— Закупочная цена считается ОТ ЛОМА: цена приемки за килограмм, умноженная на 2,5. По бронзе это 745 * 2,5 = 1 862,50 руб за килограмм — та самая ставка, по которой посчитана спецификация.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>— Цена бронзы и латуни считается ОТ ВЕСА: 1 862,50 руб за килограмм. Уточнится вес при замере — цена пересчитается сама.</t>
+          <t>— Закупочная цена считается ОТ ЛОМА: цена приемки за килограмм, умноженная на 2,5. По бронзе это 745 * 2,5 = 1 862,50 руб за килограмм — та самая ставка, по которой посчитана спецификация.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="17" t="inlineStr">
         <is>
-          <t>— Сталь, титан и алюминий в цену по Договору по ставке не вошли, у них там «по согласованию». Закуп от лома по ним посчитан, но он низкий: по стали это 47,50 руб за кг, а стальная арматура столько не стоит. Цену согласовывать отдельно, на лом не опираться.</t>
+          <t>— Цена бронзы и латуни считается ОТ ВЕСА: 1 862,50 руб за килограмм. Уточнится вес при замере — цена пересчитается сама.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t>— Электромагнитные клапаны не считаются ни по ставке, ни от лома: там платят за привод и катушку, а не за металл.</t>
+          <t>— От металла НЕ считаются: сталь и титан, электромагнитные и редукционные клапаны, клапаны на высокое давление Ру от 100. По ним цену согласовываем отдельно: в редукторе, приводе и рабочем давлении денег больше, чем в массе корпуса.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="17" t="inlineStr">
         <is>
-          <t>— Где в договоре цена записана двойной, берем ВЕРХНЮЮ границу. Внутри диапазона конкретную цену по пункту 3.4 все равно согласовывают письменно до передачи.</t>
+          <t>— Вся остальная арматура БРОНЗОВАЯ, подтверждено собственником 25.10.2026: на море ставят бронзу, латунь идет на реки. Поэтому лом считается по бронзе 745, а не по латуни, и ставка выходит 1 862,50 руб за кг.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
         <is>
-          <t>— Веса паспортные, по бронзе: задвижка Ду350 — 212,5 кг, Ду300 — 192, Ду250 — 125, Ду200 — 76,5. Прежний наш справочник завышал их почти вдвое.</t>
+          <t>— Стаканы переборочные с маркировкой Ру100 под правило высокого давления не попадают: это не клапан, а проход через переборку.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>— Где в договоре цена записана двойной, берем ВЕРХНЮЮ границу. Внутри диапазона конкретную цену по пункту 3.4 все равно согласовывают письменно до передачи.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>— Веса паспортные, по бронзе: задвижка Ду350 — 212,5 кг, Ду300 — 192, Ду250 — 125, Ду200 — 76,5. Прежний наш справочник завышал их почти вдвое.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>— Ремонт — ориентир мастерской, а не счет. Новое не ремонтируем. Фильтров, коробок, захлопок, кингстонов и головок в прайсе ремонта нет, по ним стоимость запрашивается отдельно.</t>
         </is>
@@ -1378,10 +1402,10 @@
         <v>15692</v>
       </c>
       <c r="G14" s="19" t="n">
-        <v>30955</v>
+        <v>16762</v>
       </c>
       <c r="H14" s="19" t="n">
-        <v>30956</v>
+        <v>36763</v>
       </c>
       <c r="I14" s="19" t="n">
         <v>5000</v>
@@ -1390,7 +1414,7 @@
         <v>85000</v>
       </c>
       <c r="K14" s="19" t="n">
-        <v>1821</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="15">
@@ -1417,10 +1441,10 @@
         <v>15694</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>4098</v>
+        <v>0</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>4098</v>
+        <v>0</v>
       </c>
       <c r="I15" s="19" t="n">
         <v>0</v>
@@ -1429,7 +1453,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="19" t="n">
-        <v>2049</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1495,10 +1519,10 @@
         <v>16190</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>861257</v>
+        <v>178651</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>861252</v>
+        <v>582150</v>
       </c>
       <c r="I17" s="19" t="n">
         <v>190500</v>
@@ -1507,7 +1531,7 @@
         <v>1738000</v>
       </c>
       <c r="K17" s="19" t="n">
-        <v>1860</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="18">
@@ -1534,10 +1558,10 @@
         <v>17427</v>
       </c>
       <c r="G18" s="19" t="n">
-        <v>2306148</v>
+        <v>2026772</v>
       </c>
       <c r="H18" s="19" t="n">
-        <v>2306121</v>
+        <v>2046757</v>
       </c>
       <c r="I18" s="19" t="n">
         <v>426500</v>
@@ -1546,7 +1570,7 @@
         <v>11224000</v>
       </c>
       <c r="K18" s="19" t="n">
-        <v>1864</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="19">
@@ -1690,10 +1714,10 @@
         <v>18178</v>
       </c>
       <c r="G22" s="19" t="n">
-        <v>480525</v>
+        <v>0</v>
       </c>
       <c r="H22" s="19" t="n">
-        <v>480530</v>
+        <v>345000</v>
       </c>
       <c r="I22" s="19" t="n">
         <v>0</v>
@@ -1702,7 +1726,7 @@
         <v>1170000</v>
       </c>
       <c r="K22" s="19" t="n">
-        <v>1855</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="23">
@@ -1729,10 +1753,10 @@
         <v>18424</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>230205</v>
+        <v>26075</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>230205</v>
+        <v>441075</v>
       </c>
       <c r="I23" s="19" t="n">
         <v>0</v>
@@ -1741,7 +1765,7 @@
         <v>1070000</v>
       </c>
       <c r="K23" s="19" t="n">
-        <v>936</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="24">
@@ -1924,7 +1948,7 @@
         <v>19008</v>
       </c>
       <c r="G28" s="19" t="n">
-        <v>4009</v>
+        <v>0</v>
       </c>
       <c r="H28" s="19" t="n">
         <v>0</v>
@@ -1963,7 +1987,7 @@
         <v>19035</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>1282</v>
+        <v>0</v>
       </c>
       <c r="H29" s="19" t="n">
         <v>0</v>
@@ -2002,7 +2026,7 @@
         <v>19063</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>1330</v>
+        <v>0</v>
       </c>
       <c r="H30" s="19" t="n">
         <v>0</v>
@@ -2041,7 +2065,7 @@
         <v>19091</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>8840</v>
+        <v>0</v>
       </c>
       <c r="H31" s="19" t="n">
         <v>230000</v>
@@ -2080,10 +2104,10 @@
         <v>19091</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>34956489</v>
+        <v>33276101</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>35281041</v>
+        <v>34819624</v>
       </c>
       <c r="I32" s="21" t="n">
         <v>3267000</v>
@@ -2092,7 +2116,7 @@
         <v>58844000</v>
       </c>
       <c r="K32" s="21" t="n">
-        <v>1848</v>
+        <v>1824</v>
       </c>
     </row>
   </sheetData>
@@ -2320,7 +2344,7 @@
       </c>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2415,7 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2484,7 @@
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2555,7 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2624,7 @@
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2695,7 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2766,7 @@
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2837,7 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2908,7 @@
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2977,7 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -3022,7 +3046,7 @@
       </c>
       <c r="Q16" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3136,7 @@
       </c>
       <c r="Q18" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3203,7 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3272,7 @@
       </c>
       <c r="Q20" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3341,7 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3410,7 @@
       </c>
       <c r="Q22" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3479,7 @@
       </c>
       <c r="Q23" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3544,7 @@
       </c>
       <c r="Q24" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -3581,7 +3605,7 @@
       </c>
       <c r="Q25" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3666,7 @@
       </c>
       <c r="Q26" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3727,7 @@
       </c>
       <c r="Q27" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3796,7 @@
       </c>
       <c r="Q28" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3865,7 @@
       </c>
       <c r="Q29" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3934,7 @@
       </c>
       <c r="Q30" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -3979,7 +4003,7 @@
       </c>
       <c r="Q31" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -4044,7 +4068,7 @@
       </c>
       <c r="Q32" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -4113,7 +4137,7 @@
       </c>
       <c r="Q33" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4206,7 @@
       </c>
       <c r="Q34" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4271,7 @@
       </c>
       <c r="Q35" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -4316,7 +4340,7 @@
       </c>
       <c r="Q36" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4409,7 @@
       </c>
       <c r="Q37" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4478,7 @@
       </c>
       <c r="Q38" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4543,7 @@
       </c>
       <c r="Q39" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4608,7 @@
       </c>
       <c r="Q40" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4673,7 @@
       </c>
       <c r="Q41" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4738,7 @@
       </c>
       <c r="Q42" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4805,7 @@
       </c>
       <c r="Q43" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4874,7 @@
       </c>
       <c r="Q44" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -4915,7 +4939,7 @@
       </c>
       <c r="Q45" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -4980,7 +5004,7 @@
       </c>
       <c r="Q46" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -5051,7 +5075,7 @@
       </c>
       <c r="Q47" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5146,7 @@
       </c>
       <c r="Q48" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -5206,7 +5230,7 @@
       </c>
       <c r="Q50" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5291,7 @@
       </c>
       <c r="Q51" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5352,7 @@
       </c>
       <c r="Q52" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5413,7 @@
       </c>
       <c r="Q53" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5474,7 @@
       </c>
       <c r="Q54" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5535,7 @@
       </c>
       <c r="Q55" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5596,7 @@
       </c>
       <c r="Q56" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5684,7 @@
       </c>
       <c r="Q58" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -5725,7 +5749,7 @@
       </c>
       <c r="Q59" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5814,7 @@
       </c>
       <c r="Q60" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5883,7 @@
       </c>
       <c r="Q61" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5952,7 @@
       </c>
       <c r="Q62" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -5997,7 +6021,7 @@
       </c>
       <c r="Q63" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6086,7 @@
       </c>
       <c r="Q64" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6155,7 @@
       </c>
       <c r="Q65" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6220,7 @@
       </c>
       <c r="Q66" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6285,7 @@
       </c>
       <c r="Q67" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6346,7 @@
       </c>
       <c r="Q68" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -6387,7 +6411,7 @@
       </c>
       <c r="Q69" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6472,7 @@
       </c>
       <c r="Q70" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -6517,7 +6541,7 @@
       </c>
       <c r="Q71" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6606,7 @@
       </c>
       <c r="Q72" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -6647,7 +6671,7 @@
       </c>
       <c r="Q73" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6740,7 @@
       </c>
       <c r="Q74" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -6781,7 +6805,7 @@
       </c>
       <c r="Q75" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -6846,7 +6870,7 @@
       </c>
       <c r="Q76" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6939,7 @@
       </c>
       <c r="Q77" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -6984,7 +7008,7 @@
       </c>
       <c r="Q78" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -7049,7 +7073,7 @@
       </c>
       <c r="Q79" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -7114,7 +7138,7 @@
       </c>
       <c r="Q80" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7207,7 @@
       </c>
       <c r="Q81" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7272,7 @@
       </c>
       <c r="Q82" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7337,7 @@
       </c>
       <c r="Q83" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7406,7 @@
       </c>
       <c r="Q84" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -7447,7 +7471,7 @@
       </c>
       <c r="Q85" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -7512,7 +7536,7 @@
       </c>
       <c r="Q86" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -7600,7 +7624,7 @@
       </c>
       <c r="Q88" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -7665,7 +7689,7 @@
       </c>
       <c r="Q89" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7758,7 @@
       </c>
       <c r="Q90" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -7803,7 +7827,7 @@
       </c>
       <c r="Q91" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -7887,7 +7911,7 @@
       </c>
       <c r="Q93" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7972,7 @@
       </c>
       <c r="Q94" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -8009,7 +8033,7 @@
       </c>
       <c r="Q95" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8094,7 @@
       </c>
       <c r="Q96" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8155,7 @@
       </c>
       <c r="Q97" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8220,7 @@
       </c>
       <c r="Q98" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8281,7 @@
       </c>
       <c r="Q99" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8342,7 @@
       </c>
       <c r="Q100" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -8379,7 +8403,7 @@
       </c>
       <c r="Q101" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -8440,7 +8464,7 @@
       </c>
       <c r="Q102" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -8528,7 +8552,7 @@
       </c>
       <c r="Q104" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -8593,7 +8617,7 @@
       </c>
       <c r="Q105" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8682,7 @@
       </c>
       <c r="Q106" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -8723,7 +8747,7 @@
       </c>
       <c r="Q107" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -8788,7 +8812,7 @@
       </c>
       <c r="Q108" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -8853,7 +8877,7 @@
       </c>
       <c r="Q109" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -8918,7 +8942,7 @@
       </c>
       <c r="Q110" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -8983,7 +9007,7 @@
       </c>
       <c r="Q111" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9095,7 @@
       </c>
       <c r="Q113" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -9136,7 +9160,7 @@
       </c>
       <c r="Q114" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -9201,7 +9225,7 @@
       </c>
       <c r="Q115" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -9266,7 +9290,7 @@
       </c>
       <c r="Q116" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -9331,7 +9355,7 @@
       </c>
       <c r="Q117" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9445,7 @@
       </c>
       <c r="Q119" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -9488,7 +9512,7 @@
       </c>
       <c r="Q120" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -9555,7 +9579,7 @@
       </c>
       <c r="Q121" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -9622,7 +9646,7 @@
       </c>
       <c r="Q122" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9713,7 @@
       </c>
       <c r="Q123" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -9758,7 +9782,7 @@
       </c>
       <c r="Q124" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -9827,7 +9851,7 @@
       </c>
       <c r="Q125" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -9919,7 +9943,7 @@
       </c>
       <c r="Q127" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -9988,7 +10012,7 @@
       </c>
       <c r="Q128" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -10034,19 +10058,11 @@
           <t>коробка №5</t>
         </is>
       </c>
-      <c r="L129" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M129" s="4" t="inlineStr">
-        <is>
-          <t>6 519</t>
-        </is>
-      </c>
+      <c r="L129" s="4" t="inlineStr"/>
+      <c r="M129" s="4" t="inlineStr"/>
       <c r="N129" s="4" t="inlineStr">
         <is>
-          <t>6 519</t>
+          <t>20 000</t>
         </is>
       </c>
       <c r="O129" s="4" t="inlineStr"/>
@@ -10057,76 +10073,68 @@
       </c>
       <c r="Q129" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="18" t="n">
+      <c r="A130" s="24" t="n">
         <v>116</v>
       </c>
-      <c r="B130" s="5" t="inlineStr">
+      <c r="B130" s="15" t="inlineStr">
         <is>
           <t>Клапан предохранительный штуцерный сигнальный Ду6Ру100-250</t>
         </is>
       </c>
-      <c r="C130" s="4" t="inlineStr">
+      <c r="C130" s="14" t="inlineStr">
         <is>
           <t>524-03.188</t>
         </is>
       </c>
-      <c r="D130" s="18" t="n">
+      <c r="D130" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="E130" s="18" t="inlineStr">
+      <c r="E130" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F130" s="18" t="inlineStr">
+      <c r="F130" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G130" s="18" t="n">
+      <c r="G130" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="H130" s="18" t="n">
+      <c r="H130" s="24" t="n">
         <v>2.1</v>
       </c>
-      <c r="I130" s="18" t="n">
+      <c r="I130" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="J130" s="18" t="inlineStr"/>
-      <c r="K130" s="4" t="inlineStr">
+      <c r="J130" s="24" t="inlineStr"/>
+      <c r="K130" s="14" t="inlineStr">
         <is>
           <t>коробка №5</t>
         </is>
       </c>
-      <c r="L130" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M130" s="4" t="inlineStr">
-        <is>
-          <t>3 837</t>
-        </is>
-      </c>
-      <c r="N130" s="4" t="inlineStr">
-        <is>
-          <t>3 837</t>
-        </is>
-      </c>
-      <c r="O130" s="4" t="inlineStr"/>
-      <c r="P130" s="4" t="inlineStr">
+      <c r="L130" s="14" t="inlineStr"/>
+      <c r="M130" s="14" t="inlineStr"/>
+      <c r="N130" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="Q130" s="4" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
+      <c r="O130" s="14" t="inlineStr"/>
+      <c r="P130" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="Q130" s="14" t="inlineStr">
+        <is>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -10195,7 +10203,7 @@
       </c>
       <c r="Q131" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -10223,71 +10231,63 @@
       <c r="Q132" s="23" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="18" t="n">
+      <c r="A133" s="24" t="n">
         <v>118</v>
       </c>
-      <c r="B133" s="5" t="inlineStr">
+      <c r="B133" s="15" t="inlineStr">
         <is>
           <t>Клапан для манометра штуцерный  Ду3Ру400</t>
         </is>
       </c>
-      <c r="C133" s="4" t="inlineStr">
+      <c r="C133" s="14" t="inlineStr">
         <is>
           <t>521-03.406</t>
         </is>
       </c>
-      <c r="D133" s="18" t="n">
+      <c r="D133" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="E133" s="18" t="inlineStr">
+      <c r="E133" s="24" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="F133" s="18" t="inlineStr">
+      <c r="F133" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G133" s="18" t="n">
+      <c r="G133" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="H133" s="18" t="n">
+      <c r="H133" s="24" t="n">
         <v>1.1</v>
       </c>
-      <c r="I133" s="18" t="n">
+      <c r="I133" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J133" s="18" t="inlineStr"/>
-      <c r="K133" s="4" t="inlineStr">
+      <c r="J133" s="24" t="inlineStr"/>
+      <c r="K133" s="14" t="inlineStr">
         <is>
           <t>коробка №5</t>
         </is>
       </c>
-      <c r="L133" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M133" s="4" t="inlineStr">
-        <is>
-          <t>2 049</t>
-        </is>
-      </c>
-      <c r="N133" s="4" t="inlineStr">
-        <is>
-          <t>2 049</t>
-        </is>
-      </c>
-      <c r="O133" s="4" t="inlineStr"/>
-      <c r="P133" s="4" t="inlineStr">
+      <c r="L133" s="14" t="inlineStr"/>
+      <c r="M133" s="14" t="inlineStr"/>
+      <c r="N133" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="Q133" s="4" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
+      <c r="O133" s="14" t="inlineStr"/>
+      <c r="P133" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="Q133" s="14" t="inlineStr">
+        <is>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -10375,7 +10375,7 @@
       </c>
       <c r="Q135" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -10403,132 +10403,116 @@
       <c r="Q136" s="23" t="n"/>
     </row>
     <row r="137">
-      <c r="A137" s="18" t="n">
+      <c r="A137" s="24" t="n">
         <v>120</v>
       </c>
-      <c r="B137" s="5" t="inlineStr">
+      <c r="B137" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный угловой ДУ 32 Ру 160</t>
         </is>
       </c>
-      <c r="C137" s="4" t="inlineStr">
+      <c r="C137" s="14" t="inlineStr">
         <is>
           <t>522-03.151-01</t>
         </is>
       </c>
-      <c r="D137" s="18" t="n">
+      <c r="D137" s="24" t="n">
         <v>32</v>
       </c>
-      <c r="E137" s="18" t="inlineStr">
+      <c r="E137" s="24" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="F137" s="18" t="inlineStr">
+      <c r="F137" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G137" s="18" t="n">
+      <c r="G137" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="H137" s="18" t="n">
+      <c r="H137" s="24" t="n">
         <v>4.7</v>
       </c>
-      <c r="I137" s="18" t="n">
+      <c r="I137" s="24" t="n">
         <v>38</v>
       </c>
-      <c r="J137" s="18" t="inlineStr"/>
-      <c r="K137" s="4" t="inlineStr"/>
-      <c r="L137" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M137" s="4" t="inlineStr">
-        <is>
-          <t>8 754</t>
-        </is>
-      </c>
-      <c r="N137" s="4" t="inlineStr">
-        <is>
-          <t>8 754</t>
-        </is>
-      </c>
-      <c r="O137" s="4" t="inlineStr"/>
-      <c r="P137" s="4" t="inlineStr">
+      <c r="J137" s="24" t="inlineStr"/>
+      <c r="K137" s="14" t="inlineStr"/>
+      <c r="L137" s="14" t="inlineStr"/>
+      <c r="M137" s="14" t="inlineStr"/>
+      <c r="N137" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="Q137" s="4" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
+      <c r="O137" s="14" t="inlineStr"/>
+      <c r="P137" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="Q137" s="14" t="inlineStr">
+        <is>
+          <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="18" t="n">
+      <c r="A138" s="24" t="n">
         <v>121</v>
       </c>
-      <c r="B138" s="5" t="inlineStr">
+      <c r="B138" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный угловой ДУ 32 Ру 160</t>
         </is>
       </c>
-      <c r="C138" s="4" t="inlineStr">
+      <c r="C138" s="14" t="inlineStr">
         <is>
           <t>521-03.480</t>
         </is>
       </c>
-      <c r="D138" s="18" t="n">
+      <c r="D138" s="24" t="n">
         <v>32</v>
       </c>
-      <c r="E138" s="18" t="inlineStr">
+      <c r="E138" s="24" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="F138" s="18" t="inlineStr">
+      <c r="F138" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G138" s="18" t="n">
+      <c r="G138" s="24" t="n">
         <v>16</v>
       </c>
-      <c r="H138" s="18" t="n">
+      <c r="H138" s="24" t="n">
         <v>3.9</v>
       </c>
-      <c r="I138" s="18" t="n">
+      <c r="I138" s="24" t="n">
         <v>62</v>
       </c>
-      <c r="J138" s="18" t="inlineStr"/>
-      <c r="K138" s="4" t="inlineStr"/>
-      <c r="L138" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M138" s="4" t="inlineStr">
-        <is>
-          <t>7 264</t>
-        </is>
-      </c>
-      <c r="N138" s="4" t="inlineStr">
-        <is>
-          <t>7 264</t>
-        </is>
-      </c>
-      <c r="O138" s="4" t="inlineStr"/>
-      <c r="P138" s="4" t="inlineStr">
+      <c r="J138" s="24" t="inlineStr"/>
+      <c r="K138" s="14" t="inlineStr"/>
+      <c r="L138" s="14" t="inlineStr"/>
+      <c r="M138" s="14" t="inlineStr"/>
+      <c r="N138" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="Q138" s="4" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
+      <c r="O138" s="14" t="inlineStr"/>
+      <c r="P138" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="Q138" s="14" t="inlineStr">
+        <is>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -10576,19 +10560,11 @@
           <t>ящик №1</t>
         </is>
       </c>
-      <c r="L139" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M139" s="4" t="inlineStr">
-        <is>
-          <t>6 146</t>
-        </is>
-      </c>
+      <c r="L139" s="4" t="inlineStr"/>
+      <c r="M139" s="4" t="inlineStr"/>
       <c r="N139" s="4" t="inlineStr">
         <is>
-          <t>6 146</t>
+          <t>6 500</t>
         </is>
       </c>
       <c r="O139" s="4" t="inlineStr"/>
@@ -10599,7 +10575,7 @@
       </c>
       <c r="Q139" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -10647,19 +10623,11 @@
           <t>ящик №1</t>
         </is>
       </c>
-      <c r="L140" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M140" s="4" t="inlineStr">
-        <is>
-          <t>6 146</t>
-        </is>
-      </c>
+      <c r="L140" s="4" t="inlineStr"/>
+      <c r="M140" s="4" t="inlineStr"/>
       <c r="N140" s="4" t="inlineStr">
         <is>
-          <t>6 146</t>
+          <t>6 500</t>
         </is>
       </c>
       <c r="O140" s="4" t="inlineStr"/>
@@ -10670,7 +10638,7 @@
       </c>
       <c r="Q140" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -10716,19 +10684,11 @@
           <t>ящик №1</t>
         </is>
       </c>
-      <c r="L141" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M141" s="4" t="inlineStr">
-        <is>
-          <t>6 146</t>
-        </is>
-      </c>
+      <c r="L141" s="4" t="inlineStr"/>
+      <c r="M141" s="4" t="inlineStr"/>
       <c r="N141" s="4" t="inlineStr">
         <is>
-          <t>6 146</t>
+          <t>6 500</t>
         </is>
       </c>
       <c r="O141" s="4" t="inlineStr"/>
@@ -10739,7 +10699,7 @@
       </c>
       <c r="Q141" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -10785,19 +10745,11 @@
           <t>ящик №1</t>
         </is>
       </c>
-      <c r="L142" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M142" s="4" t="inlineStr">
-        <is>
-          <t>6 146</t>
-        </is>
-      </c>
+      <c r="L142" s="4" t="inlineStr"/>
+      <c r="M142" s="4" t="inlineStr"/>
       <c r="N142" s="4" t="inlineStr">
         <is>
-          <t>6 146</t>
+          <t>6 500</t>
         </is>
       </c>
       <c r="O142" s="4" t="inlineStr"/>
@@ -10808,7 +10760,7 @@
       </c>
       <c r="Q142" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -10873,7 +10825,7 @@
       </c>
       <c r="Q143" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -10938,7 +10890,7 @@
       </c>
       <c r="Q144" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -10984,19 +10936,11 @@
           <t>коробка №8</t>
         </is>
       </c>
-      <c r="L145" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M145" s="4" t="inlineStr">
-        <is>
-          <t>5 401</t>
-        </is>
-      </c>
+      <c r="L145" s="4" t="inlineStr"/>
+      <c r="M145" s="4" t="inlineStr"/>
       <c r="N145" s="4" t="inlineStr">
         <is>
-          <t>5 401</t>
+          <t>5 000</t>
         </is>
       </c>
       <c r="O145" s="4" t="inlineStr"/>
@@ -11007,7 +10951,7 @@
       </c>
       <c r="Q145" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -11049,19 +10993,11 @@
       </c>
       <c r="J146" s="18" t="inlineStr"/>
       <c r="K146" s="4" t="inlineStr"/>
-      <c r="L146" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M146" s="4" t="inlineStr">
-        <is>
-          <t>5 774</t>
-        </is>
-      </c>
+      <c r="L146" s="4" t="inlineStr"/>
+      <c r="M146" s="4" t="inlineStr"/>
       <c r="N146" s="4" t="inlineStr">
         <is>
-          <t>5 774</t>
+          <t>5 000</t>
         </is>
       </c>
       <c r="O146" s="4" t="inlineStr">
@@ -11076,76 +11012,68 @@
       </c>
       <c r="Q146" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="18" t="n">
+      <c r="A147" s="24" t="n">
         <v>130</v>
       </c>
-      <c r="B147" s="5" t="inlineStr">
+      <c r="B147" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный угловой Ду25 Ру 100 без маховика , без крышки корпуса</t>
         </is>
       </c>
-      <c r="C147" s="4" t="inlineStr">
+      <c r="C147" s="14" t="inlineStr">
         <is>
           <t>521-01.468-06</t>
         </is>
       </c>
-      <c r="D147" s="18" t="n">
+      <c r="D147" s="24" t="n">
         <v>25</v>
       </c>
-      <c r="E147" s="18" t="inlineStr">
+      <c r="E147" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F147" s="18" t="inlineStr">
+      <c r="F147" s="24" t="inlineStr">
         <is>
           <t>б/у</t>
         </is>
       </c>
-      <c r="G147" s="18" t="n">
+      <c r="G147" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="H147" s="18" t="n">
+      <c r="H147" s="24" t="n">
         <v>3.1</v>
       </c>
-      <c r="I147" s="18" t="n">
+      <c r="I147" s="24" t="n">
         <v>22</v>
       </c>
-      <c r="J147" s="18" t="inlineStr"/>
-      <c r="K147" s="4" t="inlineStr"/>
-      <c r="L147" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M147" s="4" t="inlineStr">
-        <is>
-          <t>5 774</t>
-        </is>
-      </c>
-      <c r="N147" s="4" t="inlineStr">
-        <is>
-          <t>5 774</t>
-        </is>
-      </c>
-      <c r="O147" s="4" t="inlineStr">
+      <c r="J147" s="24" t="inlineStr"/>
+      <c r="K147" s="14" t="inlineStr"/>
+      <c r="L147" s="14" t="inlineStr"/>
+      <c r="M147" s="14" t="inlineStr"/>
+      <c r="N147" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O147" s="14" t="inlineStr">
         <is>
           <t>4 000</t>
         </is>
       </c>
-      <c r="P147" s="4" t="inlineStr">
+      <c r="P147" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="Q147" s="4" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
+      <c r="Q147" s="14" t="inlineStr">
+        <is>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -11187,19 +11115,11 @@
       </c>
       <c r="J148" s="18" t="inlineStr"/>
       <c r="K148" s="4" t="inlineStr"/>
-      <c r="L148" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M148" s="4" t="inlineStr">
-        <is>
-          <t>5 774</t>
-        </is>
-      </c>
+      <c r="L148" s="4" t="inlineStr"/>
+      <c r="M148" s="4" t="inlineStr"/>
       <c r="N148" s="4" t="inlineStr">
         <is>
-          <t>5 774</t>
+          <t>5 000</t>
         </is>
       </c>
       <c r="O148" s="4" t="inlineStr">
@@ -11214,76 +11134,68 @@
       </c>
       <c r="Q148" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="18" t="n">
+      <c r="A149" s="24" t="n">
         <v>132</v>
       </c>
-      <c r="B149" s="5" t="inlineStr">
+      <c r="B149" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный угловой Ду25 Ру 100 без маховика , без крышки корпуса</t>
         </is>
       </c>
-      <c r="C149" s="4" t="inlineStr">
+      <c r="C149" s="14" t="inlineStr">
         <is>
           <t>522-01.500-06</t>
         </is>
       </c>
-      <c r="D149" s="18" t="n">
+      <c r="D149" s="24" t="n">
         <v>25</v>
       </c>
-      <c r="E149" s="18" t="inlineStr">
+      <c r="E149" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F149" s="18" t="inlineStr">
+      <c r="F149" s="24" t="inlineStr">
         <is>
           <t>бу</t>
         </is>
       </c>
-      <c r="G149" s="18" t="n">
+      <c r="G149" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H149" s="18" t="n">
+      <c r="H149" s="24" t="n">
         <v>3.1</v>
       </c>
-      <c r="I149" s="18" t="n">
+      <c r="I149" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J149" s="18" t="inlineStr"/>
-      <c r="K149" s="4" t="inlineStr"/>
-      <c r="L149" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M149" s="4" t="inlineStr">
-        <is>
-          <t>5 774</t>
-        </is>
-      </c>
-      <c r="N149" s="4" t="inlineStr">
-        <is>
-          <t>5 774</t>
-        </is>
-      </c>
-      <c r="O149" s="4" t="inlineStr">
+      <c r="J149" s="24" t="inlineStr"/>
+      <c r="K149" s="14" t="inlineStr"/>
+      <c r="L149" s="14" t="inlineStr"/>
+      <c r="M149" s="14" t="inlineStr"/>
+      <c r="N149" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O149" s="14" t="inlineStr">
         <is>
           <t>4 000</t>
         </is>
       </c>
-      <c r="P149" s="4" t="inlineStr">
+      <c r="P149" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="Q149" s="4" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
+      <c r="Q149" s="14" t="inlineStr">
+        <is>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -11352,7 +11264,7 @@
       </c>
       <c r="Q150" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11333,7 @@
       </c>
       <c r="Q151" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -11490,7 +11402,7 @@
       </c>
       <c r="Q152" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -11559,7 +11471,7 @@
       </c>
       <c r="Q153" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -11605,19 +11517,11 @@
           <t>коробка  № 5</t>
         </is>
       </c>
-      <c r="L154" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M154" s="4" t="inlineStr">
-        <is>
-          <t>3 352</t>
-        </is>
-      </c>
+      <c r="L154" s="4" t="inlineStr"/>
+      <c r="M154" s="4" t="inlineStr"/>
       <c r="N154" s="4" t="inlineStr">
         <is>
-          <t>3 352</t>
+          <t>4 500</t>
         </is>
       </c>
       <c r="O154" s="4" t="inlineStr"/>
@@ -11628,7 +11532,7 @@
       </c>
       <c r="Q154" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -11674,19 +11578,11 @@
           <t>коробка №5</t>
         </is>
       </c>
-      <c r="L155" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M155" s="4" t="inlineStr">
-        <is>
-          <t>1 676</t>
-        </is>
-      </c>
+      <c r="L155" s="4" t="inlineStr"/>
+      <c r="M155" s="4" t="inlineStr"/>
       <c r="N155" s="4" t="inlineStr">
         <is>
-          <t>1 676</t>
+          <t>6 500</t>
         </is>
       </c>
       <c r="O155" s="4" t="inlineStr">
@@ -11701,7 +11597,7 @@
       </c>
       <c r="Q155" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -11766,7 +11662,7 @@
       </c>
       <c r="Q156" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -11831,7 +11727,7 @@
       </c>
       <c r="Q157" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -11896,7 +11792,7 @@
       </c>
       <c r="Q158" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -11961,7 +11857,7 @@
       </c>
       <c r="Q159" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -12026,208 +11922,184 @@
       </c>
       <c r="Q160" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="18" t="n">
+      <c r="A161" s="24" t="n">
         <v>144</v>
       </c>
-      <c r="B161" s="5" t="inlineStr">
+      <c r="B161" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный угловой Ду15 Ру160</t>
         </is>
       </c>
-      <c r="C161" s="4" t="inlineStr">
+      <c r="C161" s="14" t="inlineStr">
         <is>
           <t>521-03.387</t>
         </is>
       </c>
-      <c r="D161" s="18" t="n">
+      <c r="D161" s="24" t="n">
         <v>15</v>
       </c>
-      <c r="E161" s="18" t="inlineStr">
+      <c r="E161" s="24" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="F161" s="18" t="inlineStr">
+      <c r="F161" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G161" s="18" t="n">
+      <c r="G161" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="H161" s="18" t="n">
+      <c r="H161" s="24" t="n">
         <v>4.6</v>
       </c>
-      <c r="I161" s="18" t="n">
+      <c r="I161" s="24" t="n">
         <v>18</v>
       </c>
-      <c r="J161" s="18" t="n">
+      <c r="J161" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="K161" s="4" t="inlineStr"/>
-      <c r="L161" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M161" s="4" t="inlineStr">
-        <is>
-          <t>8 568</t>
-        </is>
-      </c>
-      <c r="N161" s="4" t="inlineStr">
-        <is>
-          <t>8 568</t>
-        </is>
-      </c>
-      <c r="O161" s="4" t="inlineStr"/>
-      <c r="P161" s="4" t="inlineStr">
+      <c r="K161" s="14" t="inlineStr"/>
+      <c r="L161" s="14" t="inlineStr"/>
+      <c r="M161" s="14" t="inlineStr"/>
+      <c r="N161" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="Q161" s="4" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
+      <c r="O161" s="14" t="inlineStr"/>
+      <c r="P161" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="Q161" s="14" t="inlineStr">
+        <is>
+          <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="18" t="n">
+      <c r="A162" s="24" t="n">
         <v>145</v>
       </c>
-      <c r="B162" s="5" t="inlineStr">
+      <c r="B162" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный угловой Ду15 Ру160</t>
         </is>
       </c>
-      <c r="C162" s="4" t="inlineStr">
+      <c r="C162" s="14" t="inlineStr">
         <is>
           <t>525-03.011</t>
         </is>
       </c>
-      <c r="D162" s="18" t="n">
+      <c r="D162" s="24" t="n">
         <v>15</v>
       </c>
-      <c r="E162" s="18" t="inlineStr">
+      <c r="E162" s="24" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="F162" s="18" t="inlineStr">
+      <c r="F162" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G162" s="18" t="n">
+      <c r="G162" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="H162" s="18" t="n">
+      <c r="H162" s="24" t="n">
         <v>4.9</v>
       </c>
-      <c r="I162" s="18" t="n">
+      <c r="I162" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="J162" s="18" t="inlineStr"/>
-      <c r="K162" s="4" t="inlineStr"/>
-      <c r="L162" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M162" s="4" t="inlineStr">
-        <is>
-          <t>9 126</t>
-        </is>
-      </c>
-      <c r="N162" s="4" t="inlineStr">
-        <is>
-          <t>9 126</t>
-        </is>
-      </c>
-      <c r="O162" s="4" t="inlineStr"/>
-      <c r="P162" s="4" t="inlineStr">
+      <c r="J162" s="24" t="inlineStr"/>
+      <c r="K162" s="14" t="inlineStr"/>
+      <c r="L162" s="14" t="inlineStr"/>
+      <c r="M162" s="14" t="inlineStr"/>
+      <c r="N162" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="Q162" s="4" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
+      <c r="O162" s="14" t="inlineStr"/>
+      <c r="P162" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="Q162" s="14" t="inlineStr">
+        <is>
+          <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="18" t="n">
+      <c r="A163" s="24" t="n">
         <v>146</v>
       </c>
-      <c r="B163" s="5" t="inlineStr">
+      <c r="B163" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный угловой Ду15Ру100</t>
         </is>
       </c>
-      <c r="C163" s="4" t="inlineStr">
+      <c r="C163" s="14" t="inlineStr">
         <is>
           <t>521-01.464-01</t>
         </is>
       </c>
-      <c r="D163" s="18" t="n">
+      <c r="D163" s="24" t="n">
         <v>15</v>
       </c>
-      <c r="E163" s="18" t="inlineStr">
+      <c r="E163" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F163" s="18" t="inlineStr">
+      <c r="F163" s="24" t="inlineStr">
         <is>
           <t>б/у</t>
         </is>
       </c>
-      <c r="G163" s="18" t="n">
+      <c r="G163" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="H163" s="18" t="n">
+      <c r="H163" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="I163" s="18" t="n">
+      <c r="I163" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="J163" s="18" t="inlineStr"/>
-      <c r="K163" s="4" t="inlineStr"/>
-      <c r="L163" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M163" s="4" t="inlineStr">
-        <is>
-          <t>3 725</t>
-        </is>
-      </c>
-      <c r="N163" s="4" t="inlineStr">
-        <is>
-          <t>3 725</t>
-        </is>
-      </c>
-      <c r="O163" s="4" t="inlineStr">
+      <c r="J163" s="24" t="inlineStr"/>
+      <c r="K163" s="14" t="inlineStr"/>
+      <c r="L163" s="14" t="inlineStr"/>
+      <c r="M163" s="14" t="inlineStr"/>
+      <c r="N163" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O163" s="14" t="inlineStr">
         <is>
           <t>3 000</t>
         </is>
       </c>
-      <c r="P163" s="4" t="inlineStr">
+      <c r="P163" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="Q163" s="4" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
+      <c r="Q163" s="14" t="inlineStr">
+        <is>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12168,7 @@
       </c>
       <c r="Q164" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -12342,19 +12214,11 @@
           <t>коробка №5</t>
         </is>
       </c>
-      <c r="L165" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M165" s="4" t="inlineStr">
-        <is>
-          <t>1 304</t>
-        </is>
-      </c>
+      <c r="L165" s="4" t="inlineStr"/>
+      <c r="M165" s="4" t="inlineStr"/>
       <c r="N165" s="4" t="inlineStr">
         <is>
-          <t>1 304</t>
+          <t>3 000</t>
         </is>
       </c>
       <c r="O165" s="4" t="inlineStr"/>
@@ -12365,7 +12229,7 @@
       </c>
       <c r="Q165" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -12434,7 +12298,7 @@
       </c>
       <c r="Q166" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -12480,19 +12344,11 @@
           <t>коробка №8</t>
         </is>
       </c>
-      <c r="L167" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M167" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
+      <c r="L167" s="4" t="inlineStr"/>
+      <c r="M167" s="4" t="inlineStr"/>
       <c r="N167" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>3 000</t>
         </is>
       </c>
       <c r="O167" s="4" t="inlineStr"/>
@@ -12503,7 +12359,7 @@
       </c>
       <c r="Q167" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -12531,71 +12387,63 @@
       <c r="Q168" s="23" t="n"/>
     </row>
     <row r="169">
-      <c r="A169" s="18" t="n">
+      <c r="A169" s="24" t="n">
         <v>151</v>
       </c>
-      <c r="B169" s="5" t="inlineStr">
+      <c r="B169" s="15" t="inlineStr">
         <is>
           <t>Клапан невозвратный  штуцерный проходной Ду 32 Ру100</t>
         </is>
       </c>
-      <c r="C169" s="4" t="inlineStr">
+      <c r="C169" s="14" t="inlineStr">
         <is>
           <t>522-01.494-03</t>
         </is>
       </c>
-      <c r="D169" s="18" t="n">
+      <c r="D169" s="24" t="n">
         <v>32</v>
       </c>
-      <c r="E169" s="18" t="inlineStr">
+      <c r="E169" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F169" s="18" t="inlineStr">
+      <c r="F169" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G169" s="18" t="n">
+      <c r="G169" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="H169" s="18" t="n">
+      <c r="H169" s="24" t="n">
         <v>2.7</v>
       </c>
-      <c r="I169" s="18" t="n">
+      <c r="I169" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="J169" s="18" t="inlineStr"/>
-      <c r="K169" s="4" t="inlineStr">
+      <c r="J169" s="24" t="inlineStr"/>
+      <c r="K169" s="14" t="inlineStr">
         <is>
           <t>коробка №9</t>
         </is>
       </c>
-      <c r="L169" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M169" s="4" t="inlineStr">
-        <is>
-          <t>5 029</t>
-        </is>
-      </c>
-      <c r="N169" s="4" t="inlineStr">
-        <is>
-          <t>5 029</t>
-        </is>
-      </c>
-      <c r="O169" s="4" t="inlineStr"/>
-      <c r="P169" s="4" t="inlineStr">
+      <c r="L169" s="14" t="inlineStr"/>
+      <c r="M169" s="14" t="inlineStr"/>
+      <c r="N169" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="Q169" s="4" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
+      <c r="O169" s="14" t="inlineStr"/>
+      <c r="P169" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="Q169" s="14" t="inlineStr">
+        <is>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -12664,561 +12512,497 @@
       </c>
       <c r="Q170" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="18" t="n">
+      <c r="A171" s="24" t="n">
         <v>153</v>
       </c>
-      <c r="B171" s="5" t="inlineStr">
+      <c r="B171" s="15" t="inlineStr">
         <is>
           <t>Клапан невозвратный штуцерный проходной Ду20Ру160</t>
         </is>
       </c>
-      <c r="C171" s="4" t="inlineStr">
+      <c r="C171" s="14" t="inlineStr">
         <is>
           <t>522-03.089</t>
         </is>
       </c>
-      <c r="D171" s="18" t="n">
+      <c r="D171" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="E171" s="18" t="inlineStr">
+      <c r="E171" s="24" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="F171" s="18" t="inlineStr">
+      <c r="F171" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G171" s="18" t="n">
+      <c r="G171" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H171" s="18" t="n">
+      <c r="H171" s="24" t="n">
         <v>1.9</v>
       </c>
-      <c r="I171" s="18" t="n">
+      <c r="I171" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J171" s="18" t="inlineStr"/>
-      <c r="K171" s="4" t="inlineStr">
+      <c r="J171" s="24" t="inlineStr"/>
+      <c r="K171" s="14" t="inlineStr">
         <is>
           <t>коробка №9</t>
         </is>
       </c>
-      <c r="L171" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M171" s="4" t="inlineStr">
-        <is>
-          <t>3 539</t>
-        </is>
-      </c>
-      <c r="N171" s="4" t="inlineStr">
-        <is>
-          <t>3 539</t>
-        </is>
-      </c>
-      <c r="O171" s="4" t="inlineStr"/>
-      <c r="P171" s="4" t="inlineStr">
+      <c r="L171" s="14" t="inlineStr"/>
+      <c r="M171" s="14" t="inlineStr"/>
+      <c r="N171" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="Q171" s="4" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
+      <c r="O171" s="14" t="inlineStr"/>
+      <c r="P171" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="Q171" s="14" t="inlineStr">
+        <is>
+          <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="18" t="n">
+      <c r="A172" s="24" t="n">
         <v>154</v>
       </c>
-      <c r="B172" s="5" t="inlineStr">
+      <c r="B172" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный проходной Ду 20 Ру 100, без маховика , без крышки корпуса</t>
         </is>
       </c>
-      <c r="C172" s="4" t="inlineStr">
+      <c r="C172" s="14" t="inlineStr">
         <is>
           <t>521-01.470-02</t>
         </is>
       </c>
-      <c r="D172" s="18" t="n">
+      <c r="D172" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="E172" s="18" t="inlineStr">
+      <c r="E172" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F172" s="18" t="inlineStr">
+      <c r="F172" s="24" t="inlineStr">
         <is>
           <t>б/у</t>
         </is>
       </c>
-      <c r="G172" s="18" t="n">
+      <c r="G172" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="H172" s="18" t="n">
+      <c r="H172" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="I172" s="18" t="n">
+      <c r="I172" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="J172" s="18" t="inlineStr"/>
-      <c r="K172" s="4" t="inlineStr"/>
-      <c r="L172" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M172" s="4" t="inlineStr">
-        <is>
-          <t>3 725</t>
-        </is>
-      </c>
-      <c r="N172" s="4" t="inlineStr">
-        <is>
-          <t>3 725</t>
-        </is>
-      </c>
-      <c r="O172" s="4" t="inlineStr">
+      <c r="J172" s="24" t="inlineStr"/>
+      <c r="K172" s="14" t="inlineStr"/>
+      <c r="L172" s="14" t="inlineStr"/>
+      <c r="M172" s="14" t="inlineStr"/>
+      <c r="N172" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O172" s="14" t="inlineStr">
         <is>
           <t>3 500</t>
         </is>
       </c>
-      <c r="P172" s="4" t="inlineStr">
+      <c r="P172" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="Q172" s="4" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
+      <c r="Q172" s="14" t="inlineStr">
+        <is>
+          <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="18" t="n">
+      <c r="A173" s="24" t="n">
         <v>155</v>
       </c>
-      <c r="B173" s="5" t="inlineStr">
+      <c r="B173" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
-      <c r="C173" s="4" t="inlineStr">
+      <c r="C173" s="14" t="inlineStr">
         <is>
           <t>521-01.470-02</t>
         </is>
       </c>
-      <c r="D173" s="18" t="n">
+      <c r="D173" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="E173" s="18" t="inlineStr">
+      <c r="E173" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F173" s="18" t="inlineStr">
+      <c r="F173" s="24" t="inlineStr">
         <is>
           <t>б/у</t>
         </is>
       </c>
-      <c r="G173" s="18" t="n">
+      <c r="G173" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="H173" s="18" t="n">
+      <c r="H173" s="24" t="n">
         <v>2.1</v>
       </c>
-      <c r="I173" s="18" t="n">
+      <c r="I173" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="J173" s="18" t="inlineStr"/>
-      <c r="K173" s="4" t="inlineStr"/>
-      <c r="L173" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M173" s="4" t="inlineStr">
-        <is>
-          <t>3 911</t>
-        </is>
-      </c>
-      <c r="N173" s="4" t="inlineStr">
-        <is>
-          <t>3 911</t>
-        </is>
-      </c>
-      <c r="O173" s="4" t="inlineStr">
+      <c r="J173" s="24" t="inlineStr"/>
+      <c r="K173" s="14" t="inlineStr"/>
+      <c r="L173" s="14" t="inlineStr"/>
+      <c r="M173" s="14" t="inlineStr"/>
+      <c r="N173" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O173" s="14" t="inlineStr">
         <is>
           <t>3 500</t>
         </is>
       </c>
-      <c r="P173" s="4" t="inlineStr">
+      <c r="P173" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="Q173" s="4" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
+      <c r="Q173" s="14" t="inlineStr">
+        <is>
+          <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="18" t="n">
+      <c r="A174" s="24" t="n">
         <v>156</v>
       </c>
-      <c r="B174" s="5" t="inlineStr">
+      <c r="B174" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
-      <c r="C174" s="4" t="inlineStr">
+      <c r="C174" s="14" t="inlineStr">
         <is>
           <t>521-01.471-03</t>
         </is>
       </c>
-      <c r="D174" s="18" t="n">
+      <c r="D174" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="E174" s="18" t="inlineStr">
+      <c r="E174" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F174" s="18" t="inlineStr">
+      <c r="F174" s="24" t="inlineStr">
         <is>
           <t>б/у</t>
         </is>
       </c>
-      <c r="G174" s="18" t="n">
+      <c r="G174" s="24" t="n">
         <v>11</v>
       </c>
-      <c r="H174" s="18" t="n">
+      <c r="H174" s="24" t="n">
         <v>2.1</v>
       </c>
-      <c r="I174" s="18" t="n">
+      <c r="I174" s="24" t="n">
         <v>23</v>
       </c>
-      <c r="J174" s="18" t="inlineStr"/>
-      <c r="K174" s="4" t="inlineStr"/>
-      <c r="L174" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M174" s="4" t="inlineStr">
-        <is>
-          <t>3 911</t>
-        </is>
-      </c>
-      <c r="N174" s="4" t="inlineStr">
-        <is>
-          <t>3 911</t>
-        </is>
-      </c>
-      <c r="O174" s="4" t="inlineStr">
+      <c r="J174" s="24" t="inlineStr"/>
+      <c r="K174" s="14" t="inlineStr"/>
+      <c r="L174" s="14" t="inlineStr"/>
+      <c r="M174" s="14" t="inlineStr"/>
+      <c r="N174" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O174" s="14" t="inlineStr">
         <is>
           <t>3 500</t>
         </is>
       </c>
-      <c r="P174" s="4" t="inlineStr">
+      <c r="P174" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="Q174" s="4" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
+      <c r="Q174" s="14" t="inlineStr">
+        <is>
+          <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="18" t="n">
+      <c r="A175" s="24" t="n">
         <v>157</v>
       </c>
-      <c r="B175" s="5" t="inlineStr">
+      <c r="B175" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
-      <c r="C175" s="4" t="inlineStr">
+      <c r="C175" s="14" t="inlineStr">
         <is>
           <t>522-01.498-02</t>
         </is>
       </c>
-      <c r="D175" s="18" t="n">
+      <c r="D175" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="E175" s="18" t="inlineStr">
+      <c r="E175" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F175" s="18" t="inlineStr">
+      <c r="F175" s="24" t="inlineStr">
         <is>
           <t>б/у</t>
         </is>
       </c>
-      <c r="G175" s="18" t="n">
+      <c r="G175" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="H175" s="18" t="n">
+      <c r="H175" s="24" t="n">
         <v>1.9</v>
       </c>
-      <c r="I175" s="18" t="n">
+      <c r="I175" s="24" t="n">
         <v>15</v>
       </c>
-      <c r="J175" s="18" t="inlineStr"/>
-      <c r="K175" s="4" t="inlineStr"/>
-      <c r="L175" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M175" s="4" t="inlineStr">
-        <is>
-          <t>3 539</t>
-        </is>
-      </c>
-      <c r="N175" s="4" t="inlineStr">
-        <is>
-          <t>3 539</t>
-        </is>
-      </c>
-      <c r="O175" s="4" t="inlineStr">
+      <c r="J175" s="24" t="inlineStr"/>
+      <c r="K175" s="14" t="inlineStr"/>
+      <c r="L175" s="14" t="inlineStr"/>
+      <c r="M175" s="14" t="inlineStr"/>
+      <c r="N175" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O175" s="14" t="inlineStr">
         <is>
           <t>3 500</t>
         </is>
       </c>
-      <c r="P175" s="4" t="inlineStr">
+      <c r="P175" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="Q175" s="4" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
+      <c r="Q175" s="14" t="inlineStr">
+        <is>
+          <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="18" t="n">
+      <c r="A176" s="24" t="n">
         <v>158</v>
       </c>
-      <c r="B176" s="5" t="inlineStr">
+      <c r="B176" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
-      <c r="C176" s="4" t="inlineStr">
+      <c r="C176" s="14" t="inlineStr">
         <is>
           <t>521-01.052</t>
         </is>
       </c>
-      <c r="D176" s="18" t="n">
+      <c r="D176" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="E176" s="18" t="inlineStr">
+      <c r="E176" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F176" s="18" t="inlineStr">
+      <c r="F176" s="24" t="inlineStr">
         <is>
           <t>б/у</t>
         </is>
       </c>
-      <c r="G176" s="18" t="n">
+      <c r="G176" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="H176" s="18" t="n">
+      <c r="H176" s="24" t="n">
         <v>2.1</v>
       </c>
-      <c r="I176" s="18" t="n">
+      <c r="I176" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="J176" s="18" t="inlineStr"/>
-      <c r="K176" s="4" t="inlineStr"/>
-      <c r="L176" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M176" s="4" t="inlineStr">
-        <is>
-          <t>3 911</t>
-        </is>
-      </c>
-      <c r="N176" s="4" t="inlineStr">
-        <is>
-          <t>3 911</t>
-        </is>
-      </c>
-      <c r="O176" s="4" t="inlineStr">
+      <c r="J176" s="24" t="inlineStr"/>
+      <c r="K176" s="14" t="inlineStr"/>
+      <c r="L176" s="14" t="inlineStr"/>
+      <c r="M176" s="14" t="inlineStr"/>
+      <c r="N176" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O176" s="14" t="inlineStr">
         <is>
           <t>3 500</t>
         </is>
       </c>
-      <c r="P176" s="4" t="inlineStr">
+      <c r="P176" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="Q176" s="4" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
+      <c r="Q176" s="14" t="inlineStr">
+        <is>
+          <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="18" t="n">
+      <c r="A177" s="24" t="n">
         <v>159</v>
       </c>
-      <c r="B177" s="5" t="inlineStr">
+      <c r="B177" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
-      <c r="C177" s="4" t="inlineStr">
+      <c r="C177" s="14" t="inlineStr">
         <is>
           <t>521-01.470-03</t>
         </is>
       </c>
-      <c r="D177" s="18" t="n">
+      <c r="D177" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="E177" s="18" t="inlineStr">
+      <c r="E177" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F177" s="18" t="inlineStr">
+      <c r="F177" s="24" t="inlineStr">
         <is>
           <t>б/у</t>
         </is>
       </c>
-      <c r="G177" s="18" t="n">
+      <c r="G177" s="24" t="n">
         <v>29</v>
       </c>
-      <c r="H177" s="18" t="n">
+      <c r="H177" s="24" t="n">
         <v>2.1</v>
       </c>
-      <c r="I177" s="18" t="n">
+      <c r="I177" s="24" t="n">
         <v>61</v>
       </c>
-      <c r="J177" s="18" t="n">
+      <c r="J177" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="K177" s="4" t="inlineStr"/>
-      <c r="L177" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M177" s="4" t="inlineStr">
-        <is>
-          <t>3 911</t>
-        </is>
-      </c>
-      <c r="N177" s="4" t="inlineStr">
-        <is>
-          <t>3 911</t>
-        </is>
-      </c>
-      <c r="O177" s="4" t="inlineStr">
+      <c r="K177" s="14" t="inlineStr"/>
+      <c r="L177" s="14" t="inlineStr"/>
+      <c r="M177" s="14" t="inlineStr"/>
+      <c r="N177" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O177" s="14" t="inlineStr">
         <is>
           <t>3 500</t>
         </is>
       </c>
-      <c r="P177" s="4" t="inlineStr">
+      <c r="P177" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="Q177" s="4" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
+      <c r="Q177" s="14" t="inlineStr">
+        <is>
+          <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="18" t="n">
+      <c r="A178" s="24" t="n">
         <v>160</v>
       </c>
-      <c r="B178" s="5" t="inlineStr">
+      <c r="B178" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный проходной Ду 20 Ру 100, без маховика , без крышки корпуса</t>
         </is>
       </c>
-      <c r="C178" s="4" t="inlineStr">
+      <c r="C178" s="14" t="inlineStr">
         <is>
           <t>521-01.470-03</t>
         </is>
       </c>
-      <c r="D178" s="18" t="n">
+      <c r="D178" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="E178" s="18" t="inlineStr">
+      <c r="E178" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F178" s="18" t="inlineStr">
+      <c r="F178" s="24" t="inlineStr">
         <is>
           <t>б/у</t>
         </is>
       </c>
-      <c r="G178" s="18" t="n">
+      <c r="G178" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="H178" s="18" t="n">
+      <c r="H178" s="24" t="n">
         <v>2.1</v>
       </c>
-      <c r="I178" s="18" t="n">
+      <c r="I178" s="24" t="n">
         <v>25</v>
       </c>
-      <c r="J178" s="18" t="inlineStr"/>
-      <c r="K178" s="4" t="inlineStr"/>
-      <c r="L178" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M178" s="4" t="inlineStr">
-        <is>
-          <t>3 911</t>
-        </is>
-      </c>
-      <c r="N178" s="4" t="inlineStr">
-        <is>
-          <t>3 911</t>
-        </is>
-      </c>
-      <c r="O178" s="4" t="inlineStr">
+      <c r="J178" s="24" t="inlineStr"/>
+      <c r="K178" s="14" t="inlineStr"/>
+      <c r="L178" s="14" t="inlineStr"/>
+      <c r="M178" s="14" t="inlineStr"/>
+      <c r="N178" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O178" s="14" t="inlineStr">
         <is>
           <t>3 500</t>
         </is>
       </c>
-      <c r="P178" s="4" t="inlineStr">
+      <c r="P178" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="Q178" s="4" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
+      <c r="Q178" s="14" t="inlineStr">
+        <is>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -13287,7 +13071,7 @@
       </c>
       <c r="Q179" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -13356,7 +13140,7 @@
       </c>
       <c r="Q180" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -13425,7 +13209,7 @@
       </c>
       <c r="Q181" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13274,7 @@
       </c>
       <c r="Q182" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -13555,7 +13339,7 @@
       </c>
       <c r="Q183" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -13601,19 +13385,11 @@
           <t>коробка  № 5</t>
         </is>
       </c>
-      <c r="L184" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M184" s="4" t="inlineStr">
-        <is>
-          <t>7 078</t>
-        </is>
-      </c>
+      <c r="L184" s="4" t="inlineStr"/>
+      <c r="M184" s="4" t="inlineStr"/>
       <c r="N184" s="4" t="inlineStr">
         <is>
-          <t>7 078</t>
+          <t>20 000</t>
         </is>
       </c>
       <c r="O184" s="4" t="inlineStr"/>
@@ -13624,7 +13400,7 @@
       </c>
       <c r="Q184" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -13693,7 +13469,7 @@
       </c>
       <c r="Q185" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -13781,7 +13557,7 @@
       </c>
       <c r="Q187" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -13846,7 +13622,7 @@
       </c>
       <c r="Q188" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -13915,7 +13691,7 @@
       </c>
       <c r="Q189" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -13980,7 +13756,7 @@
       </c>
       <c r="Q190" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -14049,7 +13825,7 @@
       </c>
       <c r="Q191" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -14122,7 +13898,7 @@
       </c>
       <c r="Q192" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -14195,7 +13971,7 @@
       </c>
       <c r="Q193" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -14268,7 +14044,7 @@
       </c>
       <c r="Q194" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -14341,7 +14117,7 @@
       </c>
       <c r="Q195" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -14410,7 +14186,7 @@
       </c>
       <c r="Q196" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -14498,7 +14274,7 @@
       </c>
       <c r="Q198" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -14559,7 +14335,7 @@
       </c>
       <c r="Q199" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -14651,7 +14427,7 @@
       </c>
       <c r="Q201" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -14720,7 +14496,7 @@
       </c>
       <c r="Q202" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -14789,7 +14565,7 @@
       </c>
       <c r="Q203" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -14858,7 +14634,7 @@
       </c>
       <c r="Q204" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -14923,19 +14699,11 @@
       </c>
       <c r="J206" s="18" t="inlineStr"/>
       <c r="K206" s="4" t="inlineStr"/>
-      <c r="L206" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M206" s="4" t="inlineStr">
-        <is>
-          <t>50 288</t>
-        </is>
-      </c>
+      <c r="L206" s="4" t="inlineStr"/>
+      <c r="M206" s="4" t="inlineStr"/>
       <c r="N206" s="4" t="inlineStr">
         <is>
-          <t>50 288</t>
+          <t>35 000</t>
         </is>
       </c>
       <c r="O206" s="4" t="inlineStr"/>
@@ -14946,7 +14714,7 @@
       </c>
       <c r="Q206" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -14988,19 +14756,11 @@
       </c>
       <c r="J207" s="18" t="inlineStr"/>
       <c r="K207" s="4" t="inlineStr"/>
-      <c r="L207" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M207" s="4" t="inlineStr">
-        <is>
-          <t>50 288</t>
-        </is>
-      </c>
+      <c r="L207" s="4" t="inlineStr"/>
+      <c r="M207" s="4" t="inlineStr"/>
       <c r="N207" s="4" t="inlineStr">
         <is>
-          <t>50 288</t>
+          <t>35 000</t>
         </is>
       </c>
       <c r="O207" s="4" t="inlineStr"/>
@@ -15011,7 +14771,7 @@
       </c>
       <c r="Q207" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -15053,19 +14813,11 @@
       </c>
       <c r="J208" s="18" t="inlineStr"/>
       <c r="K208" s="4" t="inlineStr"/>
-      <c r="L208" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M208" s="4" t="inlineStr">
-        <is>
-          <t>13 969</t>
-        </is>
-      </c>
+      <c r="L208" s="4" t="inlineStr"/>
+      <c r="M208" s="4" t="inlineStr"/>
       <c r="N208" s="4" t="inlineStr">
         <is>
-          <t>13 969</t>
+          <t>15 000</t>
         </is>
       </c>
       <c r="O208" s="4" t="inlineStr"/>
@@ -15076,7 +14828,7 @@
       </c>
       <c r="Q208" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -15118,19 +14870,11 @@
       </c>
       <c r="J209" s="18" t="inlineStr"/>
       <c r="K209" s="4" t="inlineStr"/>
-      <c r="L209" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M209" s="4" t="inlineStr">
-        <is>
-          <t>13 969</t>
-        </is>
-      </c>
+      <c r="L209" s="4" t="inlineStr"/>
+      <c r="M209" s="4" t="inlineStr"/>
       <c r="N209" s="4" t="inlineStr">
         <is>
-          <t>13 969</t>
+          <t>15 000</t>
         </is>
       </c>
       <c r="O209" s="4" t="inlineStr"/>
@@ -15141,7 +14885,7 @@
       </c>
       <c r="Q209" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -15169,7 +14913,7 @@
       <c r="Q210" s="23" t="n"/>
     </row>
     <row r="211">
-      <c r="A211" s="24" t="n">
+      <c r="A211" s="25" t="n">
         <v>188</v>
       </c>
       <c r="B211" s="13" t="inlineStr">
@@ -15182,25 +14926,25 @@
           <t>587-35.8490-04</t>
         </is>
       </c>
-      <c r="D211" s="24" t="n">
+      <c r="D211" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="E211" s="24" t="inlineStr"/>
-      <c r="F211" s="24" t="inlineStr">
+      <c r="E211" s="25" t="inlineStr"/>
+      <c r="F211" s="25" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G211" s="24" t="n">
+      <c r="G211" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H211" s="24" t="n">
+      <c r="H211" s="25" t="n">
         <v>11.6</v>
       </c>
-      <c r="I211" s="24" t="n">
+      <c r="I211" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="J211" s="24" t="inlineStr"/>
+      <c r="J211" s="25" t="inlineStr"/>
       <c r="K211" s="12" t="inlineStr"/>
       <c r="L211" s="12" t="inlineStr"/>
       <c r="M211" s="12" t="inlineStr"/>
@@ -15217,12 +14961,12 @@
       </c>
       <c r="Q211" s="12" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="24" t="n">
+      <c r="A212" s="25" t="n">
         <v>189</v>
       </c>
       <c r="B212" s="13" t="inlineStr">
@@ -15235,23 +14979,23 @@
           <t>587-182.126</t>
         </is>
       </c>
-      <c r="D212" s="24" t="inlineStr"/>
-      <c r="E212" s="24" t="inlineStr"/>
-      <c r="F212" s="24" t="inlineStr">
+      <c r="D212" s="25" t="inlineStr"/>
+      <c r="E212" s="25" t="inlineStr"/>
+      <c r="F212" s="25" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G212" s="24" t="n">
+      <c r="G212" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H212" s="24" t="n">
+      <c r="H212" s="25" t="n">
         <v>12.3</v>
       </c>
-      <c r="I212" s="24" t="n">
+      <c r="I212" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="J212" s="24" t="inlineStr"/>
+      <c r="J212" s="25" t="inlineStr"/>
       <c r="K212" s="12" t="inlineStr"/>
       <c r="L212" s="12" t="inlineStr"/>
       <c r="M212" s="12" t="inlineStr"/>
@@ -15268,7 +15012,7 @@
       </c>
       <c r="Q212" s="12" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -15310,19 +15054,11 @@
       </c>
       <c r="J213" s="18" t="inlineStr"/>
       <c r="K213" s="4" t="inlineStr"/>
-      <c r="L213" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M213" s="4" t="inlineStr">
-        <is>
-          <t>16 390</t>
-        </is>
-      </c>
+      <c r="L213" s="4" t="inlineStr"/>
+      <c r="M213" s="4" t="inlineStr"/>
       <c r="N213" s="4" t="inlineStr">
         <is>
-          <t>16 390</t>
+          <t>30 000</t>
         </is>
       </c>
       <c r="O213" s="4" t="inlineStr"/>
@@ -15333,7 +15069,7 @@
       </c>
       <c r="Q213" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -15375,19 +15111,11 @@
       </c>
       <c r="J214" s="18" t="inlineStr"/>
       <c r="K214" s="4" t="inlineStr"/>
-      <c r="L214" s="4" t="inlineStr">
-        <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M214" s="4" t="inlineStr">
-        <is>
-          <t>10 430</t>
-        </is>
-      </c>
+      <c r="L214" s="4" t="inlineStr"/>
+      <c r="M214" s="4" t="inlineStr"/>
       <c r="N214" s="4" t="inlineStr">
         <is>
-          <t>10 430</t>
+          <t>25 000</t>
         </is>
       </c>
       <c r="O214" s="4" t="inlineStr"/>
@@ -15398,12 +15126,12 @@
       </c>
       <c r="Q214" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="24" t="n">
+      <c r="A215" s="25" t="n">
         <v>192</v>
       </c>
       <c r="B215" s="13" t="inlineStr">
@@ -15416,29 +15144,29 @@
           <t>586-35.043</t>
         </is>
       </c>
-      <c r="D215" s="24" t="n">
+      <c r="D215" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="E215" s="24" t="inlineStr">
+      <c r="E215" s="25" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F215" s="24" t="inlineStr">
+      <c r="F215" s="25" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G215" s="24" t="n">
+      <c r="G215" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H215" s="24" t="n">
+      <c r="H215" s="25" t="n">
         <v>43</v>
       </c>
-      <c r="I215" s="24" t="n">
+      <c r="I215" s="25" t="n">
         <v>43</v>
       </c>
-      <c r="J215" s="24" t="inlineStr"/>
+      <c r="J215" s="25" t="inlineStr"/>
       <c r="K215" s="12" t="inlineStr"/>
       <c r="L215" s="12" t="inlineStr"/>
       <c r="M215" s="12" t="inlineStr"/>
@@ -15455,7 +15183,7 @@
       </c>
       <c r="Q215" s="12" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -15514,7 +15242,7 @@
       </c>
       <c r="Q216" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -15573,12 +15301,12 @@
       </c>
       <c r="Q217" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="24" t="n">
+      <c r="A218" s="25" t="n">
         <v>195</v>
       </c>
       <c r="B218" s="13" t="inlineStr">
@@ -15591,23 +15319,23 @@
           <t>587-35.8491-02</t>
         </is>
       </c>
-      <c r="D218" s="24" t="inlineStr"/>
-      <c r="E218" s="24" t="inlineStr"/>
-      <c r="F218" s="24" t="inlineStr">
+      <c r="D218" s="25" t="inlineStr"/>
+      <c r="E218" s="25" t="inlineStr"/>
+      <c r="F218" s="25" t="inlineStr">
         <is>
           <t>б/у</t>
         </is>
       </c>
-      <c r="G218" s="24" t="n">
+      <c r="G218" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="H218" s="24" t="n">
+      <c r="H218" s="25" t="n">
         <v>13.9</v>
       </c>
-      <c r="I218" s="24" t="n">
+      <c r="I218" s="25" t="n">
         <v>28</v>
       </c>
-      <c r="J218" s="24" t="inlineStr"/>
+      <c r="J218" s="25" t="inlineStr"/>
       <c r="K218" s="12" t="inlineStr"/>
       <c r="L218" s="12" t="inlineStr"/>
       <c r="M218" s="12" t="inlineStr"/>
@@ -15624,12 +15352,12 @@
       </c>
       <c r="Q218" s="12" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="24" t="n">
+      <c r="A219" s="25" t="n">
         <v>196</v>
       </c>
       <c r="B219" s="13" t="inlineStr">
@@ -15642,23 +15370,23 @@
           <t>587-35.8491-07</t>
         </is>
       </c>
-      <c r="D219" s="24" t="inlineStr"/>
-      <c r="E219" s="24" t="inlineStr"/>
-      <c r="F219" s="24" t="inlineStr">
+      <c r="D219" s="25" t="inlineStr"/>
+      <c r="E219" s="25" t="inlineStr"/>
+      <c r="F219" s="25" t="inlineStr">
         <is>
           <t>б/у</t>
         </is>
       </c>
-      <c r="G219" s="24" t="n">
+      <c r="G219" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="H219" s="24" t="n">
+      <c r="H219" s="25" t="n">
         <v>13.9</v>
       </c>
-      <c r="I219" s="24" t="n">
+      <c r="I219" s="25" t="n">
         <v>28</v>
       </c>
-      <c r="J219" s="24" t="inlineStr"/>
+      <c r="J219" s="25" t="inlineStr"/>
       <c r="K219" s="12" t="inlineStr"/>
       <c r="L219" s="12" t="inlineStr"/>
       <c r="M219" s="12" t="inlineStr"/>
@@ -15675,7 +15403,7 @@
       </c>
       <c r="Q219" s="12" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -15767,7 +15495,7 @@
       </c>
       <c r="Q221" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -15851,7 +15579,7 @@
       </c>
       <c r="Q223" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -15879,7 +15607,7 @@
       <c r="Q224" s="23" t="n"/>
     </row>
     <row r="225">
-      <c r="A225" s="25" t="n">
+      <c r="A225" s="24" t="n">
         <v>199</v>
       </c>
       <c r="B225" s="15" t="inlineStr">
@@ -15892,25 +15620,25 @@
           <t>(541-03.316-04)</t>
         </is>
       </c>
-      <c r="D225" s="25" t="n">
+      <c r="D225" s="24" t="n">
         <v>200</v>
       </c>
-      <c r="E225" s="25" t="inlineStr"/>
-      <c r="F225" s="25" t="inlineStr">
+      <c r="E225" s="24" t="inlineStr"/>
+      <c r="F225" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G225" s="25" t="n">
+      <c r="G225" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="H225" s="25" t="n">
+      <c r="H225" s="24" t="n">
         <v>4.7</v>
       </c>
-      <c r="I225" s="25" t="n">
+      <c r="I225" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="J225" s="25" t="inlineStr"/>
+      <c r="J225" s="24" t="inlineStr"/>
       <c r="K225" s="14" t="inlineStr"/>
       <c r="L225" s="14" t="inlineStr">
         <is>
@@ -15940,7 +15668,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="25" t="n">
+      <c r="A226" s="24" t="n">
         <v>200</v>
       </c>
       <c r="B226" s="15" t="inlineStr">
@@ -15953,25 +15681,25 @@
           <t>541-03.316-03</t>
         </is>
       </c>
-      <c r="D226" s="25" t="n">
+      <c r="D226" s="24" t="n">
         <v>175</v>
       </c>
-      <c r="E226" s="25" t="inlineStr"/>
-      <c r="F226" s="25" t="inlineStr">
+      <c r="E226" s="24" t="inlineStr"/>
+      <c r="F226" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G226" s="25" t="n">
+      <c r="G226" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="H226" s="25" t="n">
+      <c r="H226" s="24" t="n">
         <v>3.8</v>
       </c>
-      <c r="I226" s="25" t="n">
+      <c r="I226" s="24" t="n">
         <v>38</v>
       </c>
-      <c r="J226" s="25" t="inlineStr"/>
+      <c r="J226" s="24" t="inlineStr"/>
       <c r="K226" s="14" t="inlineStr"/>
       <c r="L226" s="14" t="inlineStr">
         <is>
@@ -16001,7 +15729,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="25" t="n">
+      <c r="A227" s="24" t="n">
         <v>201</v>
       </c>
       <c r="B227" s="15" t="inlineStr">
@@ -16014,25 +15742,25 @@
           <t>(541-03.315-02)</t>
         </is>
       </c>
-      <c r="D227" s="25" t="n">
+      <c r="D227" s="24" t="n">
         <v>150</v>
       </c>
-      <c r="E227" s="25" t="inlineStr"/>
-      <c r="F227" s="25" t="inlineStr">
+      <c r="E227" s="24" t="inlineStr"/>
+      <c r="F227" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G227" s="25" t="n">
+      <c r="G227" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="H227" s="25" t="n">
+      <c r="H227" s="24" t="n">
         <v>2.9</v>
       </c>
-      <c r="I227" s="25" t="n">
+      <c r="I227" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="J227" s="25" t="inlineStr"/>
+      <c r="J227" s="24" t="inlineStr"/>
       <c r="K227" s="14" t="inlineStr"/>
       <c r="L227" s="14" t="inlineStr">
         <is>
@@ -16062,7 +15790,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="25" t="n">
+      <c r="A228" s="24" t="n">
         <v>202</v>
       </c>
       <c r="B228" s="15" t="inlineStr">
@@ -16075,25 +15803,25 @@
           <t>(541-03.316-02)</t>
         </is>
       </c>
-      <c r="D228" s="25" t="n">
+      <c r="D228" s="24" t="n">
         <v>150</v>
       </c>
-      <c r="E228" s="25" t="inlineStr"/>
-      <c r="F228" s="25" t="inlineStr">
+      <c r="E228" s="24" t="inlineStr"/>
+      <c r="F228" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G228" s="25" t="n">
+      <c r="G228" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="H228" s="25" t="n">
+      <c r="H228" s="24" t="n">
         <v>2.7</v>
       </c>
-      <c r="I228" s="25" t="n">
+      <c r="I228" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="J228" s="25" t="inlineStr"/>
+      <c r="J228" s="24" t="inlineStr"/>
       <c r="K228" s="14" t="inlineStr"/>
       <c r="L228" s="14" t="inlineStr">
         <is>
@@ -16179,7 +15907,7 @@
       </c>
       <c r="Q229" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -16240,7 +15968,7 @@
       </c>
       <c r="Q230" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -16301,7 +16029,7 @@
       </c>
       <c r="Q231" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -16362,7 +16090,7 @@
       </c>
       <c r="Q232" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16174,7 @@
       </c>
       <c r="Q234" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -16507,7 +16235,7 @@
       </c>
       <c r="Q235" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -16566,7 +16294,7 @@
       </c>
       <c r="Q236" s="4" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
     </row>
@@ -16594,7 +16322,7 @@
       <c r="Q237" s="23" t="n"/>
     </row>
     <row r="238">
-      <c r="A238" s="25" t="n">
+      <c r="A238" s="24" t="n">
         <v>210</v>
       </c>
       <c r="B238" s="15" t="inlineStr">
@@ -16607,40 +16335,32 @@
           <t>521-35.3437</t>
         </is>
       </c>
-      <c r="D238" s="25" t="n">
+      <c r="D238" s="24" t="n">
         <v>80</v>
       </c>
-      <c r="E238" s="25" t="inlineStr">
+      <c r="E238" s="24" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="F238" s="25" t="inlineStr">
+      <c r="F238" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G238" s="25" t="n">
+      <c r="G238" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H238" s="25" t="n">
+      <c r="H238" s="24" t="n">
         <v>33</v>
       </c>
-      <c r="I238" s="25" t="n">
+      <c r="I238" s="24" t="n">
         <v>33</v>
       </c>
-      <c r="J238" s="25" t="inlineStr"/>
+      <c r="J238" s="24" t="inlineStr"/>
       <c r="K238" s="14" t="inlineStr"/>
-      <c r="L238" s="14" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="M238" s="14" t="inlineStr">
-        <is>
-          <t>1 568</t>
-        </is>
-      </c>
+      <c r="L238" s="14" t="inlineStr"/>
+      <c r="M238" s="14" t="inlineStr"/>
       <c r="N238" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
@@ -16659,7 +16379,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="25" t="n">
+      <c r="A239" s="24" t="n">
         <v>211</v>
       </c>
       <c r="B239" s="15" t="inlineStr">
@@ -16672,42 +16392,34 @@
           <t>522-01.101</t>
         </is>
       </c>
-      <c r="D239" s="25" t="n">
+      <c r="D239" s="24" t="n">
         <v>80</v>
       </c>
-      <c r="E239" s="25" t="inlineStr">
+      <c r="E239" s="24" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="F239" s="25" t="inlineStr">
+      <c r="F239" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G239" s="25" t="n">
+      <c r="G239" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H239" s="25" t="n">
+      <c r="H239" s="24" t="n">
         <v>19.6</v>
       </c>
-      <c r="I239" s="25" t="n">
+      <c r="I239" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="J239" s="25" t="n">
+      <c r="J239" s="24" t="n">
         <v>1</v>
       </c>
       <c r="K239" s="14" t="inlineStr"/>
-      <c r="L239" s="14" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="M239" s="14" t="inlineStr">
-        <is>
-          <t>931</t>
-        </is>
-      </c>
+      <c r="L239" s="14" t="inlineStr"/>
+      <c r="M239" s="14" t="inlineStr"/>
       <c r="N239" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
@@ -16726,7 +16438,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="25" t="n">
+      <c r="A240" s="24" t="n">
         <v>212</v>
       </c>
       <c r="B240" s="15" t="inlineStr">
@@ -16739,42 +16451,34 @@
           <t>522-01.322</t>
         </is>
       </c>
-      <c r="D240" s="25" t="n">
+      <c r="D240" s="24" t="n">
         <v>50</v>
       </c>
-      <c r="E240" s="25" t="inlineStr">
+      <c r="E240" s="24" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="F240" s="25" t="inlineStr">
+      <c r="F240" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G240" s="25" t="n">
+      <c r="G240" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="H240" s="25" t="n">
+      <c r="H240" s="24" t="n">
         <v>15.9</v>
       </c>
-      <c r="I240" s="25" t="n">
+      <c r="I240" s="24" t="n">
         <v>32</v>
       </c>
-      <c r="J240" s="25" t="n">
+      <c r="J240" s="24" t="n">
         <v>1</v>
       </c>
       <c r="K240" s="14" t="inlineStr"/>
-      <c r="L240" s="14" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="M240" s="14" t="inlineStr">
-        <is>
-          <t>755</t>
-        </is>
-      </c>
+      <c r="L240" s="14" t="inlineStr"/>
+      <c r="M240" s="14" t="inlineStr"/>
       <c r="N240" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
@@ -16816,7 +16520,7 @@
       <c r="Q241" s="23" t="n"/>
     </row>
     <row r="242">
-      <c r="A242" s="25" t="n">
+      <c r="A242" s="24" t="n">
         <v>213</v>
       </c>
       <c r="B242" s="15" t="inlineStr">
@@ -16829,36 +16533,28 @@
           <t>427-130.10727</t>
         </is>
       </c>
-      <c r="D242" s="25" t="n">
+      <c r="D242" s="24" t="n">
         <v>80</v>
       </c>
-      <c r="E242" s="25" t="inlineStr"/>
-      <c r="F242" s="25" t="inlineStr">
+      <c r="E242" s="24" t="inlineStr"/>
+      <c r="F242" s="24" t="inlineStr">
         <is>
           <t>б/у</t>
         </is>
       </c>
-      <c r="G242" s="25" t="n">
+      <c r="G242" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H242" s="25" t="n">
+      <c r="H242" s="24" t="n">
         <v>27</v>
       </c>
-      <c r="I242" s="25" t="n">
+      <c r="I242" s="24" t="n">
         <v>27</v>
       </c>
-      <c r="J242" s="25" t="inlineStr"/>
+      <c r="J242" s="24" t="inlineStr"/>
       <c r="K242" s="14" t="inlineStr"/>
-      <c r="L242" s="14" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="M242" s="14" t="inlineStr">
-        <is>
-          <t>1 282</t>
-        </is>
-      </c>
+      <c r="L242" s="14" t="inlineStr"/>
+      <c r="M242" s="14" t="inlineStr"/>
       <c r="N242" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
@@ -16900,7 +16596,7 @@
       <c r="Q243" s="23" t="n"/>
     </row>
     <row r="244">
-      <c r="A244" s="25" t="n">
+      <c r="A244" s="24" t="n">
         <v>214</v>
       </c>
       <c r="B244" s="15" t="inlineStr">
@@ -16913,36 +16609,28 @@
           <t>521-3м.530</t>
         </is>
       </c>
-      <c r="D244" s="25" t="n">
+      <c r="D244" s="24" t="n">
         <v>80</v>
       </c>
-      <c r="E244" s="25" t="inlineStr"/>
-      <c r="F244" s="25" t="inlineStr">
+      <c r="E244" s="24" t="inlineStr"/>
+      <c r="F244" s="24" t="inlineStr">
         <is>
           <t>б/у</t>
         </is>
       </c>
-      <c r="G244" s="25" t="n">
+      <c r="G244" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H244" s="25" t="n">
+      <c r="H244" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="I244" s="25" t="n">
+      <c r="I244" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="J244" s="25" t="inlineStr"/>
+      <c r="J244" s="24" t="inlineStr"/>
       <c r="K244" s="14" t="inlineStr"/>
-      <c r="L244" s="14" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="M244" s="14" t="inlineStr">
-        <is>
-          <t>950</t>
-        </is>
-      </c>
+      <c r="L244" s="14" t="inlineStr"/>
+      <c r="M244" s="14" t="inlineStr"/>
       <c r="N244" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
@@ -16965,7 +16653,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="25" t="n">
+      <c r="A245" s="24" t="n">
         <v>215</v>
       </c>
       <c r="B245" s="15" t="inlineStr">
@@ -16978,36 +16666,28 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D245" s="25" t="n">
+      <c r="D245" s="24" t="n">
         <v>25</v>
       </c>
-      <c r="E245" s="25" t="inlineStr"/>
-      <c r="F245" s="25" t="inlineStr">
+      <c r="E245" s="24" t="inlineStr"/>
+      <c r="F245" s="24" t="inlineStr">
         <is>
           <t>б/у</t>
         </is>
       </c>
-      <c r="G245" s="25" t="n">
+      <c r="G245" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H245" s="25" t="n">
+      <c r="H245" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="I245" s="25" t="n">
+      <c r="I245" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="J245" s="25" t="inlineStr"/>
+      <c r="J245" s="24" t="inlineStr"/>
       <c r="K245" s="14" t="inlineStr"/>
-      <c r="L245" s="14" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="M245" s="14" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
+      <c r="L245" s="14" t="inlineStr"/>
+      <c r="M245" s="14" t="inlineStr"/>
       <c r="N245" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
@@ -17094,16 +16774,8 @@
           <t>коробка №7</t>
         </is>
       </c>
-      <c r="L247" s="4" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="M247" s="4" t="inlineStr">
-        <is>
-          <t>3 152</t>
-        </is>
-      </c>
+      <c r="L247" s="4" t="inlineStr"/>
+      <c r="M247" s="4" t="inlineStr"/>
       <c r="N247" s="4" t="inlineStr">
         <is>
           <t>55 000</t>
@@ -17163,16 +16835,8 @@
           <t>коробка №6</t>
         </is>
       </c>
-      <c r="L248" s="4" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="M248" s="4" t="inlineStr">
-        <is>
-          <t>1 138</t>
-        </is>
-      </c>
+      <c r="L248" s="4" t="inlineStr"/>
+      <c r="M248" s="4" t="inlineStr"/>
       <c r="N248" s="4" t="inlineStr">
         <is>
           <t>35 000</t>
@@ -17232,7 +16896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -17257,7 +16921,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Договоренность с Антоном Бурыкиным от 25.10.2026. Цены приемки на 13.10.2026. По бронзе 745 * 2,5 = 1 862,50 руб за кг — это и есть ставка, по которой посчитана вся бронза в спецификации.</t>
+          <t>Договоренность с Антоном Бурыкиным от 25.10.2026. Цены приемки на 13.10.2026. По бронзе 745 * 2,5 = 1 862,50 руб за кг — это и есть ставка, по которой посчитана вся бронза в спецификации. Оранжевым — то, что от металла не считается.</t>
         </is>
       </c>
     </row>
@@ -17314,19 +16978,19 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>бронза/латунь</t>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>бронза</t>
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>200</v>
+        <v>163</v>
       </c>
       <c r="C5" s="18" t="n">
-        <v>1736</v>
+        <v>1519</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>18739</v>
+        <v>17847</v>
       </c>
       <c r="E5" s="19" t="n">
         <v>745</v>
@@ -17340,376 +17004,324 @@
         <v>1862.5</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>34901052</v>
+        <v>33236126</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>35051041</v>
+        <v>33386124</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>149989</v>
+        <v>149998</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>сталь</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="C6" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="D6" s="19" t="n">
-        <v>140</v>
-      </c>
-      <c r="E6" s="19" t="n">
-        <v>19</v>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>цена не от металла</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="C6" s="24" t="n">
+        <v>237</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>1183</v>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="26" t="n">
+        <v>1433500</v>
+      </c>
+      <c r="J6" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>алюминий</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>61</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>260</v>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>2,5</t>
         </is>
       </c>
-      <c r="G6" s="19" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>6622</v>
-      </c>
-      <c r="I6" s="19" t="inlineStr">
+      <c r="G7" s="19" t="n">
+        <v>650</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>39975</v>
+      </c>
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="19" t="inlineStr">
+      <c r="J7" s="19" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>цена не от металла</t>
-        </is>
-      </c>
-      <c r="B7" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" s="25" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" s="26" t="n">
-        <v>123</v>
-      </c>
-      <c r="E7" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I7" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>алюминий</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="18" t="n">
-        <v>17</v>
-      </c>
-      <c r="D8" s="19" t="n">
-        <v>61</v>
-      </c>
-      <c r="E8" s="19" t="n">
-        <v>260</v>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>2,5</t>
-        </is>
-      </c>
-      <c r="G8" s="19" t="n">
-        <v>650</v>
-      </c>
-      <c r="H8" s="19" t="n">
-        <v>39975</v>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>титан</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9" s="19" t="n">
-        <v>28</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>130</v>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>2,5</t>
-        </is>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>325</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>8840</v>
-      </c>
-      <c r="I9" s="19" t="n">
-        <v>230000</v>
-      </c>
-      <c r="J9" s="19" t="n">
-        <v>221160</v>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="n">
+        <v>217</v>
+      </c>
+      <c r="C8" s="20" t="n">
+        <v>1773</v>
+      </c>
+      <c r="D8" s="21" t="n">
+        <v>19091</v>
+      </c>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="21" t="n">
+        <v>33276101</v>
+      </c>
+      <c r="I8" s="21" t="n">
+        <v>34819624</v>
+      </c>
+      <c r="J8" s="21" t="n">
+        <v>1543523</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="n">
-        <v>217</v>
-      </c>
-      <c r="C10" s="20" t="n">
-        <v>1773</v>
-      </c>
-      <c r="D10" s="21" t="n">
-        <v>19091</v>
-      </c>
-      <c r="E10" s="6" t="inlineStr"/>
-      <c r="F10" s="6" t="inlineStr"/>
-      <c r="G10" s="6" t="inlineStr"/>
-      <c r="H10" s="21" t="n">
-        <v>34956489</v>
-      </c>
-      <c r="I10" s="21" t="n">
-        <v>35281041</v>
-      </c>
-      <c r="J10" s="21" t="n">
-        <v>324552</v>
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Прайс приемки на 13.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Металл</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Лом, руб за кг</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Закуп, руб за кг</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Прайс приемки на 13.10.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Лом, руб за кг</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Закуп, руб за кг</t>
-        </is>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>нихром</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="n">
+        <v>1342</v>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>3355</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>медь</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>945</v>
+      </c>
+      <c r="C13" s="19" t="n">
+        <v>2362.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>нихром</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="B14" s="19" t="n">
-        <v>1342</v>
+        <v>745</v>
       </c>
       <c r="C14" s="19" t="n">
-        <v>3355</v>
+        <v>1862.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>медь</t>
+          <t>латунь</t>
         </is>
       </c>
       <c r="B15" s="19" t="n">
-        <v>945</v>
+        <v>635</v>
       </c>
       <c r="C15" s="19" t="n">
-        <v>2362.5</v>
+        <v>1587.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>бронза</t>
+          <t>алюминий</t>
         </is>
       </c>
       <c r="B16" s="19" t="n">
-        <v>745</v>
+        <v>260</v>
       </c>
       <c r="C16" s="19" t="n">
-        <v>1862.5</v>
+        <v>650</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>латунь</t>
+          <t>титан</t>
         </is>
       </c>
       <c r="B17" s="19" t="n">
-        <v>635</v>
+        <v>130</v>
       </c>
       <c r="C17" s="19" t="n">
-        <v>1587.5</v>
+        <v>325</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>алюминий</t>
+          <t>цам</t>
         </is>
       </c>
       <c r="B18" s="19" t="n">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="C18" s="19" t="n">
-        <v>650</v>
+        <v>325</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>титан</t>
+          <t>свинец</t>
         </is>
       </c>
       <c r="B19" s="19" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="C19" s="19" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>цам</t>
+          <t>нержавейка</t>
         </is>
       </c>
       <c r="B20" s="19" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="C20" s="19" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>свинец</t>
+          <t>аккумуляторы</t>
         </is>
       </c>
       <c r="B21" s="19" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="C21" s="19" t="n">
-        <v>175</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>нержавейка</t>
+          <t>трансформаторы</t>
         </is>
       </c>
       <c r="B22" s="19" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C22" s="19" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>аккумуляторы</t>
+          <t>черный металл</t>
         </is>
       </c>
       <c r="B23" s="19" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>87.5</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>трансформаторы</t>
+          <t>чугун</t>
         </is>
       </c>
       <c r="B24" s="19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>50</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>черный металл</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="B25" s="19" t="n">
@@ -17722,76 +17334,58 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>чугун</t>
+          <t>электродвигатели</t>
         </is>
       </c>
       <c r="B26" s="19" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C26" s="19" t="n">
-        <v>47.5</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>сталь</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="n">
-        <v>19</v>
-      </c>
-      <c r="C27" s="19" t="n">
-        <v>47.5</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>электродвигатели</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="n">
-        <v>15</v>
-      </c>
-      <c r="C28" s="19" t="n">
         <v>37.5</v>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>— Лом — это нижняя граница цены. Любая позиция стоит хотя бы как металл, и ниже продавать незачем: сдать быстрее и без споров по состоянию.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>— Вся арматура бронзовая, 745 руб за кг: на море ставят бронзу, латунь идет на реки. Из этого и выходит ставка 1 862,50.</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>— Лом — это нижняя граница цены. Любая позиция стоит хотя бы как металл, и ниже продавать незачем: сдать быстрее и без споров по состоянию.</t>
+          <t>— Сталь и титан от лома не считаем вовсе: множитель дал бы по стали 47,50 руб за кг, а у конкурента стальная задвижка Ду200 стоит 40 000 руб. Цену по ним согласовываем отдельно.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="17" t="inlineStr">
         <is>
-          <t>— Класс «бронза/латунь» считаем ПО БРОНЗЕ, 745 руб за кг: так решил собственник, и из этого выходит ставка 1 862,50.</t>
+          <t>— Так же не считаются электромагнитные и редукционные клапаны и клапаны на высокое давление Ру от 100: корпус у них та же бронза, но платят не за нее.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>— По стали множитель дает 47,50 руб за кг. Для стальной арматуры это мало — у конкурента стальная задвижка Ду200 стоит 40 000 руб. По стали, титану и нержавейке цену согласовываем отдельно, а не от лома.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="17" t="inlineStr">
-        <is>
           <t>— Если приемка поменяет цены, пересчитывается и ставка: она считается из прайса, а не вписана руками.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A33:J33"/>
+  <mergeCells count="5">
     <mergeCell ref="A32:J32"/>
     <mergeCell ref="A31:J31"/>
     <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A28:J28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
@@ -18095,12 +17689,12 @@
       </c>
     </row>
     <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="25" t="n">
+      <c r="A5" s="24" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Согласовать письменно цену по 10 позициям «по согласованию» (201 кг)</t>
+          <t>Согласовать письменно цену по 28 позициям «по согласованию» (521 кг)</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
@@ -18111,7 +17705,7 @@
       <c r="D5" s="14" t="inlineStr"/>
     </row>
     <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="25" t="n">
+      <c r="A6" s="24" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="15" t="inlineStr">

--- a/outputs/marine_equipment/Контейнер_погрузка.xlsx
+++ b/outputs/marine_equipment/Контейнер_погрузка.xlsx
@@ -10,13 +10,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="По группам" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Перечень" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Закуп от лома" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Как считаем цены" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Укладка" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Перед погрузкой" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Снято с отгрузки" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Перечень'!$A$4:$Q$248</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Перечень'!$A$4:$P$248</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Перечень'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -728,68 +728,68 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Закуп от лома</t>
+          <t>1. ЗАКУП по Договору</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>33 276 101 руб</t>
+          <t>34 819 624 руб</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>цена приемки, умноженная на 2,5 — договоренность с Антоном от 25.10.2026</t>
+          <t>по этой цене мы продаем арматуру ПКФ «АРМА». Бронза — по ставке 1 862,50 руб за кг</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Сумма по Договору</t>
+          <t>2. Ремонт</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>34 819 624 руб</t>
+          <t>3 267 000 руб</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>по ставке 1 862,50 руб за кг на бронзу и латунь</t>
+          <t>компания приводит товар в порядок, прайс мастерской. В цену закупа не входит</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Ремонт</t>
+          <t>3. Реализация</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>3 267 000 руб</t>
+          <t>58 844 000 руб</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>прайс мастерской, в цену по Договору не входит</t>
+          <t>продаем вместе с компанией конечному покупателю. Ориентир: цену согласуют письменно по пункту 3.2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Ориентир реализации</t>
+          <t>Разница 3 минус 1 и 2</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>58 844 000 руб</t>
+          <t>20 757 376 руб</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>информационно, цену согласуют письменно по пункту 3.2</t>
+          <t>сколько цепочка дает сверх закупа и ремонта</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>50 позиций, 1 183 кг</t>
+          <t>54 позиций, 1 244 кг</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -940,7 +940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -949,11 +949,10 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -966,7 +965,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Порядок групп — как грузим. Нарастающий вес показывает, сколько тонн уже в контейнере к концу каждой группы.</t>
+          <t>Порядок групп — как грузим. Нарастающий вес показывает, сколько тонн уже в контейнере к концу каждой группы. Три колонки денег — это цепочка: закуп по Договору (мы продаем компании), ремонт по прайсу мастерской, реализация (продаем вместе конечному покупателю).</t>
         </is>
       </c>
     </row>
@@ -1003,27 +1002,22 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Закуп от лома, руб</t>
+          <t>1. ЗАКУП по Договору, руб</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>По Договору, руб</t>
+          <t>2. Ремонт, руб</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Ремонт, руб</t>
+          <t>3. Реализация, руб</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Реализация, руб</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Руб за кг</t>
+          <t>Закуп, руб за кг</t>
         </is>
       </c>
     </row>
@@ -1051,18 +1045,15 @@
         <v>7304</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>13606680</v>
+        <v>13606675</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>13606675</v>
+        <v>1622000</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>1622000</v>
+        <v>18250000</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>18250000</v>
-      </c>
-      <c r="K5" s="19" t="n">
         <v>1863</v>
       </c>
     </row>
@@ -1090,18 +1081,15 @@
         <v>10482</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>5919584</v>
+        <v>5919559</v>
       </c>
       <c r="H6" s="19" t="n">
-        <v>5919559</v>
+        <v>570000</v>
       </c>
       <c r="I6" s="19" t="n">
-        <v>570000</v>
+        <v>7365000</v>
       </c>
       <c r="J6" s="19" t="n">
-        <v>7365000</v>
-      </c>
-      <c r="K6" s="19" t="n">
         <v>1863</v>
       </c>
     </row>
@@ -1132,15 +1120,12 @@
         <v>3192511</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>3192511</v>
+        <v>0</v>
       </c>
       <c r="I7" s="19" t="n">
-        <v>0</v>
+        <v>3670000</v>
       </c>
       <c r="J7" s="19" t="n">
-        <v>3670000</v>
-      </c>
-      <c r="K7" s="19" t="n">
         <v>1863</v>
       </c>
     </row>
@@ -1168,18 +1153,15 @@
         <v>13390</v>
       </c>
       <c r="G8" s="19" t="n">
-        <v>2221031</v>
+        <v>2371037</v>
       </c>
       <c r="H8" s="19" t="n">
-        <v>2371037</v>
+        <v>351500</v>
       </c>
       <c r="I8" s="19" t="n">
-        <v>351500</v>
+        <v>3480000</v>
       </c>
       <c r="J8" s="19" t="n">
-        <v>3480000</v>
-      </c>
-      <c r="K8" s="19" t="n">
         <v>1986</v>
       </c>
     </row>
@@ -1207,18 +1189,15 @@
         <v>13428</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>70589</v>
+        <v>70590</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>70590</v>
+        <v>11000</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="19" t="n">
         <v>1858</v>
       </c>
     </row>
@@ -1246,18 +1225,15 @@
         <v>15169</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>3242612</v>
+        <v>3242617</v>
       </c>
       <c r="H10" s="19" t="n">
-        <v>3242617</v>
+        <v>0</v>
       </c>
       <c r="I10" s="19" t="n">
-        <v>0</v>
+        <v>4725000</v>
       </c>
       <c r="J10" s="19" t="n">
-        <v>4725000</v>
-      </c>
-      <c r="K10" s="19" t="n">
         <v>1863</v>
       </c>
     </row>
@@ -1288,15 +1264,12 @@
         <v>432286</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>432286</v>
+        <v>0</v>
       </c>
       <c r="I11" s="19" t="n">
-        <v>0</v>
+        <v>540000</v>
       </c>
       <c r="J11" s="19" t="n">
-        <v>540000</v>
-      </c>
-      <c r="K11" s="19" t="n">
         <v>1863</v>
       </c>
     </row>
@@ -1324,18 +1297,15 @@
         <v>15501</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>187368</v>
+        <v>187370</v>
       </c>
       <c r="H12" s="19" t="n">
-        <v>187370</v>
+        <v>0</v>
       </c>
       <c r="I12" s="19" t="n">
-        <v>0</v>
+        <v>450000</v>
       </c>
       <c r="J12" s="19" t="n">
-        <v>450000</v>
-      </c>
-      <c r="K12" s="19" t="n">
         <v>1874</v>
       </c>
     </row>
@@ -1363,18 +1333,15 @@
         <v>15675</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>323516</v>
+        <v>323518</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>323518</v>
+        <v>0</v>
       </c>
       <c r="I13" s="19" t="n">
-        <v>0</v>
+        <v>2055000</v>
       </c>
       <c r="J13" s="19" t="n">
-        <v>2055000</v>
-      </c>
-      <c r="K13" s="19" t="n">
         <v>1859</v>
       </c>
     </row>
@@ -1402,18 +1369,15 @@
         <v>15692</v>
       </c>
       <c r="G14" s="19" t="n">
-        <v>16762</v>
+        <v>36763</v>
       </c>
       <c r="H14" s="19" t="n">
-        <v>36763</v>
+        <v>5000</v>
       </c>
       <c r="I14" s="19" t="n">
-        <v>5000</v>
+        <v>85000</v>
       </c>
       <c r="J14" s="19" t="n">
-        <v>85000</v>
-      </c>
-      <c r="K14" s="19" t="n">
         <v>2163</v>
       </c>
     </row>
@@ -1452,9 +1416,6 @@
       <c r="J15" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="19" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1483,15 +1444,12 @@
         <v>60718</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>60718</v>
+        <v>0</v>
       </c>
       <c r="I16" s="19" t="n">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="J16" s="19" t="n">
-        <v>160000</v>
-      </c>
-      <c r="K16" s="19" t="n">
         <v>1840</v>
       </c>
     </row>
@@ -1519,18 +1477,15 @@
         <v>16190</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>178651</v>
+        <v>582150</v>
       </c>
       <c r="H17" s="19" t="n">
-        <v>582150</v>
+        <v>190500</v>
       </c>
       <c r="I17" s="19" t="n">
-        <v>190500</v>
+        <v>1738000</v>
       </c>
       <c r="J17" s="19" t="n">
-        <v>1738000</v>
-      </c>
-      <c r="K17" s="19" t="n">
         <v>1257</v>
       </c>
     </row>
@@ -1558,18 +1513,15 @@
         <v>17427</v>
       </c>
       <c r="G18" s="19" t="n">
-        <v>2026772</v>
+        <v>2046757</v>
       </c>
       <c r="H18" s="19" t="n">
-        <v>2046757</v>
+        <v>426500</v>
       </c>
       <c r="I18" s="19" t="n">
-        <v>426500</v>
+        <v>11224000</v>
       </c>
       <c r="J18" s="19" t="n">
-        <v>11224000</v>
-      </c>
-      <c r="K18" s="19" t="n">
         <v>1655</v>
       </c>
     </row>
@@ -1600,15 +1552,12 @@
         <v>173920</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>173920</v>
+        <v>76000</v>
       </c>
       <c r="I19" s="19" t="n">
-        <v>76000</v>
+        <v>332000</v>
       </c>
       <c r="J19" s="19" t="n">
-        <v>332000</v>
-      </c>
-      <c r="K19" s="19" t="n">
         <v>1870</v>
       </c>
     </row>
@@ -1636,18 +1585,15 @@
         <v>17867</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>645356</v>
+        <v>645372</v>
       </c>
       <c r="H20" s="19" t="n">
-        <v>645372</v>
+        <v>4000</v>
       </c>
       <c r="I20" s="19" t="n">
-        <v>4000</v>
+        <v>1890000</v>
       </c>
       <c r="J20" s="19" t="n">
-        <v>1890000</v>
-      </c>
-      <c r="K20" s="19" t="n">
         <v>1860</v>
       </c>
     </row>
@@ -1675,18 +1621,15 @@
         <v>17919</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>97036</v>
+        <v>97044</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>97044</v>
+        <v>0</v>
       </c>
       <c r="I21" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="19" t="n">
         <v>1866</v>
       </c>
     </row>
@@ -1714,18 +1657,15 @@
         <v>18178</v>
       </c>
       <c r="G22" s="19" t="n">
+        <v>345000</v>
+      </c>
+      <c r="H22" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="19" t="n">
-        <v>345000</v>
-      </c>
       <c r="I22" s="19" t="n">
-        <v>0</v>
+        <v>1170000</v>
       </c>
       <c r="J22" s="19" t="n">
-        <v>1170000</v>
-      </c>
-      <c r="K22" s="19" t="n">
         <v>1332</v>
       </c>
     </row>
@@ -1753,18 +1693,15 @@
         <v>18424</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>26075</v>
+        <v>441075</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>441075</v>
+        <v>0</v>
       </c>
       <c r="I23" s="19" t="n">
-        <v>0</v>
+        <v>1070000</v>
       </c>
       <c r="J23" s="19" t="n">
-        <v>1070000</v>
-      </c>
-      <c r="K23" s="19" t="n">
         <v>1793</v>
       </c>
     </row>
@@ -1792,18 +1729,15 @@
         <v>18433</v>
       </c>
       <c r="G24" s="19" t="n">
-        <v>16762</v>
+        <v>16764</v>
       </c>
       <c r="H24" s="19" t="n">
-        <v>16764</v>
+        <v>0</v>
       </c>
       <c r="I24" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="19" t="n">
         <v>1863</v>
       </c>
     </row>
@@ -1834,15 +1768,12 @@
         <v>7450</v>
       </c>
       <c r="H25" s="19" t="n">
-        <v>7450</v>
+        <v>0</v>
       </c>
       <c r="I25" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="19" t="n">
         <v>1862</v>
       </c>
     </row>
@@ -1870,18 +1801,15 @@
         <v>18837</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>671921</v>
+        <v>631950</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>631950</v>
+        <v>0</v>
       </c>
       <c r="I26" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="19" t="n">
         <v>1580</v>
       </c>
     </row>
@@ -1909,18 +1837,15 @@
         <v>18923</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>158499</v>
+        <v>158498</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>158498</v>
+        <v>0</v>
       </c>
       <c r="I27" s="19" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="19" t="n">
         <v>1843</v>
       </c>
     </row>
@@ -1959,9 +1884,6 @@
       <c r="J28" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K28" s="19" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -1998,9 +1920,6 @@
       <c r="J29" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K29" s="19" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -2029,17 +1948,14 @@
         <v>0</v>
       </c>
       <c r="H30" s="19" t="n">
+        <v>10500</v>
+      </c>
+      <c r="I30" s="19" t="n">
         <v>0</v>
-      </c>
-      <c r="I30" s="19" t="n">
-        <v>10500</v>
       </c>
       <c r="J30" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K30" s="19" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -2065,18 +1981,15 @@
         <v>19091</v>
       </c>
       <c r="G31" s="19" t="n">
+        <v>230000</v>
+      </c>
+      <c r="H31" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="19" t="n">
-        <v>230000</v>
-      </c>
       <c r="I31" s="19" t="n">
-        <v>0</v>
+        <v>640000</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>640000</v>
-      </c>
-      <c r="K31" s="19" t="n">
         <v>8214</v>
       </c>
     </row>
@@ -2104,18 +2017,15 @@
         <v>19091</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>33276101</v>
+        <v>34819624</v>
       </c>
       <c r="H32" s="21" t="n">
-        <v>34819624</v>
+        <v>3267000</v>
       </c>
       <c r="I32" s="21" t="n">
-        <v>3267000</v>
+        <v>58844000</v>
       </c>
       <c r="J32" s="21" t="n">
-        <v>58844000</v>
-      </c>
-      <c r="K32" s="21" t="n">
         <v>1824</v>
       </c>
     </row>
@@ -2131,7 +2041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q248"/>
+  <dimension ref="A1:P248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2146,11 +2056,10 @@
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2225,30 +2134,25 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Закуп за кг, руб</t>
+          <t>Ставка закупа, руб за кг</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>Закуп за ед., руб</t>
+          <t>1. ЗАКУП по Договору за ед., руб</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>По Договору за ед., руб</t>
+          <t>2. Ремонт за ед., руб</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Ремонт за ед., руб</t>
+          <t>3. Реализация за ед., руб</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>Реализация за ед., руб</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>Материал</t>
         </is>
@@ -2275,7 +2179,6 @@
       <c r="N5" s="23" t="n"/>
       <c r="O5" s="23" t="n"/>
       <c r="P5" s="23" t="n"/>
-      <c r="Q5" s="23" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="18" t="n">
@@ -2329,20 +2232,15 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>395 781</t>
+          <t>30 000</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>30 000</t>
+          <t>900 000</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr">
-        <is>
-          <t>900 000</t>
-        </is>
-      </c>
-      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -2400,20 +2298,15 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>357 600</t>
+          <t>28 000</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>28 000</t>
+          <t>550 000</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
-        <is>
-          <t>550 000</t>
-        </is>
-      </c>
-      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -2469,20 +2362,15 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>357 600</t>
+          <t>28 000</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>28 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -2540,20 +2428,15 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>232 812</t>
+          <t>25 000</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>25 000</t>
+          <t>400 000</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
-        <is>
-          <t>400 000</t>
-        </is>
-      </c>
-      <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -2609,20 +2492,15 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>186 250</t>
+          <t>25 000</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>25 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q10" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -2680,20 +2558,15 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>142 481</t>
+          <t>20 000</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>20 000</t>
+          <t>210 000</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
-        <is>
-          <t>210 000</t>
-        </is>
-      </c>
-      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -2751,20 +2624,15 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>69 285</t>
+          <t>15 000</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>15 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -2822,20 +2690,15 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>52 709</t>
+          <t>12 000</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>12 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -2893,20 +2756,15 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>40 789</t>
+          <t>10 000</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>10 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -2962,20 +2820,15 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>22 722</t>
+          <t>8 500</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>8 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q15" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3031,20 +2884,15 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>15 831</t>
+          <t>7 500</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>7 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q16" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3071,7 +2919,6 @@
       <c r="N17" s="23" t="n"/>
       <c r="O17" s="23" t="n"/>
       <c r="P17" s="23" t="n"/>
-      <c r="Q17" s="23" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="18" t="n">
@@ -3121,20 +2968,15 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>204 875</t>
+          <t>12 000</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>12 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3188,20 +3030,15 @@
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>204 875</t>
+          <t>12 000</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>12 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3257,20 +3094,15 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>85 675</t>
+          <t>7 000</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>7 000</t>
+          <t>140 000</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
-        <is>
-          <t>140 000</t>
-        </is>
-      </c>
-      <c r="Q20" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3326,20 +3158,15 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>84 744</t>
+          <t>7 000</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>7 000</t>
+          <t>140 000</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
-        <is>
-          <t>140 000</t>
-        </is>
-      </c>
-      <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3395,20 +3222,15 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>111 750</t>
+          <t>7 000</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>7 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q22" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3464,20 +3286,15 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>85 675</t>
+          <t>7 000</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>7 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q23" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3529,20 +3346,15 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>54 012</t>
+          <t>6 500</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>6 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3592,18 +3404,13 @@
           <t>53 640</t>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>53 640</t>
-        </is>
-      </c>
-      <c r="O25" s="4" t="inlineStr"/>
+      <c r="N25" s="4" t="inlineStr"/>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P25" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q25" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3653,18 +3460,13 @@
           <t>53 640</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
-        <is>
-          <t>53 640</t>
-        </is>
-      </c>
-      <c r="O26" s="4" t="inlineStr"/>
+      <c r="N26" s="4" t="inlineStr"/>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P26" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3714,18 +3516,13 @@
           <t>33 152</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
-        <is>
-          <t>33 152</t>
-        </is>
-      </c>
-      <c r="O27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="inlineStr"/>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>55 000</t>
+        </is>
+      </c>
       <c r="P27" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="Q27" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3781,20 +3578,15 @@
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>26 075</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="P28" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="Q28" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3850,20 +3642,15 @@
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>21 046</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="P29" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="Q29" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3919,20 +3706,15 @@
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>22 164</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="P30" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="Q30" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3988,20 +3770,15 @@
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>23 281</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="P31" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="Q31" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4053,20 +3830,15 @@
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>22 350</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="P32" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="Q32" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4122,20 +3894,15 @@
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>35 388</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4191,20 +3958,15 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>22 350</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="P34" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="Q34" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4256,20 +4018,15 @@
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>22 350</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="P35" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="Q35" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4325,20 +4082,15 @@
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>25 889</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="P36" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="Q36" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4394,20 +4146,15 @@
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>22 350</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="Q37" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4463,20 +4210,15 @@
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>23 095</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="Q38" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4528,20 +4270,15 @@
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>22 350</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="Q39" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4593,20 +4330,15 @@
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>22 350</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="Q40" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4658,20 +4390,15 @@
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>22 350</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="P41" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="Q41" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4723,20 +4450,15 @@
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>22 350</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="P42" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="Q42" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4790,20 +4512,15 @@
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>22 350</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="Q43" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4859,20 +4576,15 @@
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>21 419</t>
+          <t>5 000</t>
         </is>
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>5 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P44" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q44" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4924,20 +4636,15 @@
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>41 906</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q45" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4989,20 +4696,15 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>67 050</t>
+          <t>6 500</t>
         </is>
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>6 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P46" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q46" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5060,20 +4762,15 @@
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>9 871</t>
+          <t>4 500</t>
         </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>4 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q47" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5131,20 +4828,15 @@
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>10 244</t>
+          <t>4 500</t>
         </is>
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>4 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P48" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q48" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5171,7 +4863,6 @@
       <c r="N49" s="23" t="n"/>
       <c r="O49" s="23" t="n"/>
       <c r="P49" s="23" t="n"/>
-      <c r="Q49" s="23" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="18" t="n">
@@ -5217,18 +4908,13 @@
           <t>276 581</t>
         </is>
       </c>
-      <c r="N50" s="4" t="inlineStr">
-        <is>
-          <t>276 581</t>
-        </is>
-      </c>
-      <c r="O50" s="4" t="inlineStr"/>
+      <c r="N50" s="4" t="inlineStr"/>
+      <c r="O50" s="4" t="inlineStr">
+        <is>
+          <t>320 000</t>
+        </is>
+      </c>
       <c r="P50" s="4" t="inlineStr">
-        <is>
-          <t>320 000</t>
-        </is>
-      </c>
-      <c r="Q50" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5278,18 +4964,13 @@
           <t>119 200</t>
         </is>
       </c>
-      <c r="N51" s="4" t="inlineStr">
-        <is>
-          <t>119 200</t>
-        </is>
-      </c>
-      <c r="O51" s="4" t="inlineStr"/>
+      <c r="N51" s="4" t="inlineStr"/>
+      <c r="O51" s="4" t="inlineStr">
+        <is>
+          <t>190 000</t>
+        </is>
+      </c>
       <c r="P51" s="4" t="inlineStr">
-        <is>
-          <t>190 000</t>
-        </is>
-      </c>
-      <c r="Q51" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5339,18 +5020,13 @@
           <t>78 225</t>
         </is>
       </c>
-      <c r="N52" s="4" t="inlineStr">
-        <is>
-          <t>78 225</t>
-        </is>
-      </c>
-      <c r="O52" s="4" t="inlineStr"/>
+      <c r="N52" s="4" t="inlineStr"/>
+      <c r="O52" s="4" t="inlineStr">
+        <is>
+          <t>160 000</t>
+        </is>
+      </c>
       <c r="P52" s="4" t="inlineStr">
-        <is>
-          <t>160 000</t>
-        </is>
-      </c>
-      <c r="Q52" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5400,18 +5076,13 @@
           <t>50 288</t>
         </is>
       </c>
-      <c r="N53" s="4" t="inlineStr">
-        <is>
-          <t>50 288</t>
-        </is>
-      </c>
-      <c r="O53" s="4" t="inlineStr"/>
+      <c r="N53" s="4" t="inlineStr"/>
+      <c r="O53" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P53" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q53" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5461,18 +5132,13 @@
           <t>37 250</t>
         </is>
       </c>
-      <c r="N54" s="4" t="inlineStr">
-        <is>
-          <t>37 250</t>
-        </is>
-      </c>
-      <c r="O54" s="4" t="inlineStr"/>
+      <c r="N54" s="4" t="inlineStr"/>
+      <c r="O54" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P54" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q54" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5522,18 +5188,13 @@
           <t>17 135</t>
         </is>
       </c>
-      <c r="N55" s="4" t="inlineStr">
-        <is>
-          <t>17 135</t>
-        </is>
-      </c>
-      <c r="O55" s="4" t="inlineStr"/>
+      <c r="N55" s="4" t="inlineStr"/>
+      <c r="O55" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P55" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q55" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5583,18 +5244,13 @@
           <t>15 831</t>
         </is>
       </c>
-      <c r="N56" s="4" t="inlineStr">
-        <is>
-          <t>15 831</t>
-        </is>
-      </c>
-      <c r="O56" s="4" t="inlineStr"/>
+      <c r="N56" s="4" t="inlineStr"/>
+      <c r="O56" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P56" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q56" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5621,7 +5277,6 @@
       <c r="N57" s="23" t="n"/>
       <c r="O57" s="23" t="n"/>
       <c r="P57" s="23" t="n"/>
-      <c r="Q57" s="23" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="18" t="n">
@@ -5669,20 +5324,15 @@
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>52 150</t>
+          <t>6 500</t>
         </is>
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t>6 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P58" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q58" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5734,20 +5384,15 @@
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>52 150</t>
+          <t>6 500</t>
         </is>
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
-          <t>6 500</t>
+          <t>70 000</t>
         </is>
       </c>
       <c r="P59" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="Q59" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5799,20 +5444,15 @@
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>52 150</t>
+          <t>6 500</t>
         </is>
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t>6 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P60" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q60" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5868,20 +5508,15 @@
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>65 932</t>
+          <t>6 500</t>
         </is>
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>6 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P61" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q61" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5937,20 +5572,15 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>48 425</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>70 000</t>
         </is>
       </c>
       <c r="P62" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="Q62" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6006,20 +5636,15 @@
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>41 906</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>70 000</t>
         </is>
       </c>
       <c r="P63" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="Q63" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6071,20 +5696,15 @@
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>37 250</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>70 000</t>
         </is>
       </c>
       <c r="P64" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="Q64" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6140,20 +5760,15 @@
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>36 319</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>70 000</t>
         </is>
       </c>
       <c r="P65" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="Q65" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6202,23 +5817,22 @@
           <t>1 862</t>
         </is>
       </c>
-      <c r="M66" s="4" t="inlineStr"/>
+      <c r="M66" s="4" t="inlineStr">
+        <is>
+          <t>30 000</t>
+        </is>
+      </c>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>30 000</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="O66" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>70 000</t>
         </is>
       </c>
       <c r="P66" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="Q66" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6270,20 +5884,15 @@
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>37 250</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>70 000</t>
         </is>
       </c>
       <c r="P67" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="Q67" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6333,18 +5942,13 @@
           <t>37 250</t>
         </is>
       </c>
-      <c r="N68" s="4" t="inlineStr">
-        <is>
-          <t>37 250</t>
-        </is>
-      </c>
-      <c r="O68" s="4" t="inlineStr"/>
+      <c r="N68" s="4" t="inlineStr"/>
+      <c r="O68" s="4" t="inlineStr">
+        <is>
+          <t>70 000</t>
+        </is>
+      </c>
       <c r="P68" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="Q68" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6396,20 +6000,15 @@
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>37 250</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>70 000</t>
         </is>
       </c>
       <c r="P69" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="Q69" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6459,18 +6058,13 @@
           <t>37 250</t>
         </is>
       </c>
-      <c r="N70" s="4" t="inlineStr">
-        <is>
-          <t>37 250</t>
-        </is>
-      </c>
-      <c r="O70" s="4" t="inlineStr"/>
+      <c r="N70" s="4" t="inlineStr"/>
+      <c r="O70" s="4" t="inlineStr">
+        <is>
+          <t>70 000</t>
+        </is>
+      </c>
       <c r="P70" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="Q70" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6526,20 +6120,15 @@
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>45 631</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="O71" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>70 000</t>
         </is>
       </c>
       <c r="P71" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="Q71" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6593,18 +6182,13 @@
           <t>34 829</t>
         </is>
       </c>
-      <c r="N72" s="4" t="inlineStr">
-        <is>
-          <t>34 829</t>
-        </is>
-      </c>
-      <c r="O72" s="4" t="inlineStr"/>
+      <c r="N72" s="4" t="inlineStr"/>
+      <c r="O72" s="4" t="inlineStr">
+        <is>
+          <t>70 000</t>
+        </is>
+      </c>
       <c r="P72" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="Q72" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6658,18 +6242,13 @@
           <t>34 829</t>
         </is>
       </c>
-      <c r="N73" s="4" t="inlineStr">
-        <is>
-          <t>34 829</t>
-        </is>
-      </c>
-      <c r="O73" s="4" t="inlineStr"/>
+      <c r="N73" s="4" t="inlineStr"/>
+      <c r="O73" s="4" t="inlineStr">
+        <is>
+          <t>70 000</t>
+        </is>
+      </c>
       <c r="P73" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="Q73" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6725,20 +6304,15 @@
       </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>34 829</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="O74" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>70 000</t>
         </is>
       </c>
       <c r="P74" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="Q74" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6792,18 +6366,13 @@
           <t>47 494</t>
         </is>
       </c>
-      <c r="N75" s="4" t="inlineStr">
-        <is>
-          <t>47 494</t>
-        </is>
-      </c>
-      <c r="O75" s="4" t="inlineStr"/>
+      <c r="N75" s="4" t="inlineStr"/>
+      <c r="O75" s="4" t="inlineStr">
+        <is>
+          <t>70 000</t>
+        </is>
+      </c>
       <c r="P75" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="Q75" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6855,20 +6424,15 @@
       </c>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>28 869</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="O76" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P76" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q76" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6924,20 +6488,15 @@
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>29 800</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="O77" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>65 000</t>
         </is>
       </c>
       <c r="P77" s="4" t="inlineStr">
-        <is>
-          <t>65 000</t>
-        </is>
-      </c>
-      <c r="Q77" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6993,20 +6552,15 @@
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>31 662</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="O78" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>65 000</t>
         </is>
       </c>
       <c r="P78" s="4" t="inlineStr">
-        <is>
-          <t>65 000</t>
-        </is>
-      </c>
-      <c r="Q78" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7060,18 +6614,13 @@
           <t>37 250</t>
         </is>
       </c>
-      <c r="N79" s="4" t="inlineStr">
-        <is>
-          <t>37 250</t>
-        </is>
-      </c>
-      <c r="O79" s="4" t="inlineStr"/>
+      <c r="N79" s="4" t="inlineStr"/>
+      <c r="O79" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P79" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q79" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7123,20 +6672,15 @@
       </c>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>20 488</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="O80" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P80" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q80" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7192,20 +6736,15 @@
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>20 115</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P81" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q81" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7257,20 +6796,15 @@
       </c>
       <c r="N82" s="4" t="inlineStr">
         <is>
-          <t>20 488</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="O82" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P82" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q82" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7324,18 +6858,13 @@
           <t>24 399</t>
         </is>
       </c>
-      <c r="N83" s="4" t="inlineStr">
-        <is>
-          <t>24 399</t>
-        </is>
-      </c>
-      <c r="O83" s="4" t="inlineStr"/>
+      <c r="N83" s="4" t="inlineStr"/>
+      <c r="O83" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P83" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q83" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7391,20 +6920,15 @@
       </c>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t>10 430</t>
+          <t>5 000</t>
         </is>
       </c>
       <c r="O84" s="4" t="inlineStr">
         <is>
-          <t>5 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P84" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q84" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7456,20 +6980,15 @@
       </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t>10 244</t>
+          <t>4 500</t>
         </is>
       </c>
       <c r="O85" s="4" t="inlineStr">
         <is>
-          <t>4 500</t>
+          <t>40 000</t>
         </is>
       </c>
       <c r="P85" s="4" t="inlineStr">
-        <is>
-          <t>40 000</t>
-        </is>
-      </c>
-      <c r="Q85" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7521,20 +7040,15 @@
       </c>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>10 244</t>
+          <t>4 500</t>
         </is>
       </c>
       <c r="O86" s="4" t="inlineStr">
         <is>
-          <t>4 500</t>
+          <t>40 000</t>
         </is>
       </c>
       <c r="P86" s="4" t="inlineStr">
-        <is>
-          <t>40 000</t>
-        </is>
-      </c>
-      <c r="Q86" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7561,7 +7075,6 @@
       <c r="N87" s="23" t="n"/>
       <c r="O87" s="23" t="n"/>
       <c r="P87" s="23" t="n"/>
-      <c r="Q87" s="23" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="18" t="n">
@@ -7611,18 +7124,13 @@
           <t>10 802</t>
         </is>
       </c>
-      <c r="N88" s="4" t="inlineStr">
-        <is>
-          <t>10 802</t>
-        </is>
-      </c>
-      <c r="O88" s="4" t="inlineStr"/>
+      <c r="N88" s="4" t="inlineStr"/>
+      <c r="O88" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P88" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q88" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7676,18 +7184,13 @@
           <t>10 058</t>
         </is>
       </c>
-      <c r="N89" s="4" t="inlineStr">
-        <is>
-          <t>10 058</t>
-        </is>
-      </c>
-      <c r="O89" s="4" t="inlineStr"/>
+      <c r="N89" s="4" t="inlineStr"/>
+      <c r="O89" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P89" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q89" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7743,20 +7246,15 @@
       </c>
       <c r="N90" s="4" t="inlineStr">
         <is>
-          <t>19 184</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="O90" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P90" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q90" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7812,20 +7310,15 @@
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
-          <t>20 488</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="O91" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P91" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q91" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7852,7 +7345,6 @@
       <c r="N92" s="23" t="n"/>
       <c r="O92" s="23" t="n"/>
       <c r="P92" s="23" t="n"/>
-      <c r="Q92" s="23" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="18" t="n">
@@ -7898,18 +7390,13 @@
           <t>166 694</t>
         </is>
       </c>
-      <c r="N93" s="4" t="inlineStr">
-        <is>
-          <t>166 694</t>
-        </is>
-      </c>
-      <c r="O93" s="4" t="inlineStr"/>
+      <c r="N93" s="4" t="inlineStr"/>
+      <c r="O93" s="4" t="inlineStr">
+        <is>
+          <t>180 000</t>
+        </is>
+      </c>
       <c r="P93" s="4" t="inlineStr">
-        <is>
-          <t>180 000</t>
-        </is>
-      </c>
-      <c r="Q93" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7959,18 +7446,13 @@
           <t>78 225</t>
         </is>
       </c>
-      <c r="N94" s="4" t="inlineStr">
-        <is>
-          <t>78 225</t>
-        </is>
-      </c>
-      <c r="O94" s="4" t="inlineStr"/>
+      <c r="N94" s="4" t="inlineStr"/>
+      <c r="O94" s="4" t="inlineStr">
+        <is>
+          <t>140 000</t>
+        </is>
+      </c>
       <c r="P94" s="4" t="inlineStr">
-        <is>
-          <t>140 000</t>
-        </is>
-      </c>
-      <c r="Q94" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8020,18 +7502,13 @@
           <t>87 910</t>
         </is>
       </c>
-      <c r="N95" s="4" t="inlineStr">
-        <is>
-          <t>87 910</t>
-        </is>
-      </c>
-      <c r="O95" s="4" t="inlineStr"/>
+      <c r="N95" s="4" t="inlineStr"/>
+      <c r="O95" s="4" t="inlineStr">
+        <is>
+          <t>140 000</t>
+        </is>
+      </c>
       <c r="P95" s="4" t="inlineStr">
-        <is>
-          <t>140 000</t>
-        </is>
-      </c>
-      <c r="Q95" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8081,18 +7558,13 @@
           <t>115 475</t>
         </is>
       </c>
-      <c r="N96" s="4" t="inlineStr">
-        <is>
-          <t>115 475</t>
-        </is>
-      </c>
-      <c r="O96" s="4" t="inlineStr"/>
+      <c r="N96" s="4" t="inlineStr"/>
+      <c r="O96" s="4" t="inlineStr">
+        <is>
+          <t>160 000</t>
+        </is>
+      </c>
       <c r="P96" s="4" t="inlineStr">
-        <is>
-          <t>160 000</t>
-        </is>
-      </c>
-      <c r="Q96" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8142,18 +7614,13 @@
           <t>109 888</t>
         </is>
       </c>
-      <c r="N97" s="4" t="inlineStr">
-        <is>
-          <t>109 888</t>
-        </is>
-      </c>
-      <c r="O97" s="4" t="inlineStr"/>
+      <c r="N97" s="4" t="inlineStr"/>
+      <c r="O97" s="4" t="inlineStr">
+        <is>
+          <t>160 000</t>
+        </is>
+      </c>
       <c r="P97" s="4" t="inlineStr">
-        <is>
-          <t>160 000</t>
-        </is>
-      </c>
-      <c r="Q97" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8207,18 +7674,13 @@
           <t>125 533</t>
         </is>
       </c>
-      <c r="N98" s="4" t="inlineStr">
-        <is>
-          <t>125 533</t>
-        </is>
-      </c>
-      <c r="O98" s="4" t="inlineStr"/>
+      <c r="N98" s="4" t="inlineStr"/>
+      <c r="O98" s="4" t="inlineStr">
+        <is>
+          <t>160 000</t>
+        </is>
+      </c>
       <c r="P98" s="4" t="inlineStr">
-        <is>
-          <t>160 000</t>
-        </is>
-      </c>
-      <c r="Q98" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8268,18 +7730,13 @@
           <t>47 494</t>
         </is>
       </c>
-      <c r="N99" s="4" t="inlineStr">
-        <is>
-          <t>47 494</t>
-        </is>
-      </c>
-      <c r="O99" s="4" t="inlineStr"/>
+      <c r="N99" s="4" t="inlineStr"/>
+      <c r="O99" s="4" t="inlineStr">
+        <is>
+          <t>60 000</t>
+        </is>
+      </c>
       <c r="P99" s="4" t="inlineStr">
-        <is>
-          <t>60 000</t>
-        </is>
-      </c>
-      <c r="Q99" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8329,18 +7786,13 @@
           <t>53 268</t>
         </is>
       </c>
-      <c r="N100" s="4" t="inlineStr">
-        <is>
-          <t>53 268</t>
-        </is>
-      </c>
-      <c r="O100" s="4" t="inlineStr"/>
+      <c r="N100" s="4" t="inlineStr"/>
+      <c r="O100" s="4" t="inlineStr">
+        <is>
+          <t>60 000</t>
+        </is>
+      </c>
       <c r="P100" s="4" t="inlineStr">
-        <is>
-          <t>60 000</t>
-        </is>
-      </c>
-      <c r="Q100" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8390,18 +7842,13 @@
           <t>70 775</t>
         </is>
       </c>
-      <c r="N101" s="4" t="inlineStr">
-        <is>
-          <t>70 775</t>
-        </is>
-      </c>
-      <c r="O101" s="4" t="inlineStr"/>
+      <c r="N101" s="4" t="inlineStr"/>
+      <c r="O101" s="4" t="inlineStr">
+        <is>
+          <t>95 000</t>
+        </is>
+      </c>
       <c r="P101" s="4" t="inlineStr">
-        <is>
-          <t>95 000</t>
-        </is>
-      </c>
-      <c r="Q101" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8451,18 +7898,13 @@
           <t>63 884</t>
         </is>
       </c>
-      <c r="N102" s="4" t="inlineStr">
-        <is>
-          <t>63 884</t>
-        </is>
-      </c>
-      <c r="O102" s="4" t="inlineStr"/>
+      <c r="N102" s="4" t="inlineStr"/>
+      <c r="O102" s="4" t="inlineStr">
+        <is>
+          <t>95 000</t>
+        </is>
+      </c>
       <c r="P102" s="4" t="inlineStr">
-        <is>
-          <t>95 000</t>
-        </is>
-      </c>
-      <c r="Q102" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8489,7 +7931,6 @@
       <c r="N103" s="23" t="n"/>
       <c r="O103" s="23" t="n"/>
       <c r="P103" s="23" t="n"/>
-      <c r="Q103" s="23" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="18" t="n">
@@ -8539,18 +7980,13 @@
           <t>62 766</t>
         </is>
       </c>
-      <c r="N104" s="4" t="inlineStr">
-        <is>
-          <t>62 766</t>
-        </is>
-      </c>
-      <c r="O104" s="4" t="inlineStr"/>
+      <c r="N104" s="4" t="inlineStr"/>
+      <c r="O104" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P104" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q104" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8604,18 +8040,13 @@
           <t>40 975</t>
         </is>
       </c>
-      <c r="N105" s="4" t="inlineStr">
-        <is>
-          <t>40 975</t>
-        </is>
-      </c>
-      <c r="O105" s="4" t="inlineStr"/>
+      <c r="N105" s="4" t="inlineStr"/>
+      <c r="O105" s="4" t="inlineStr">
+        <is>
+          <t>95 000</t>
+        </is>
+      </c>
       <c r="P105" s="4" t="inlineStr">
-        <is>
-          <t>95 000</t>
-        </is>
-      </c>
-      <c r="Q105" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8669,18 +8100,13 @@
           <t>43 955</t>
         </is>
       </c>
-      <c r="N106" s="4" t="inlineStr">
-        <is>
-          <t>43 955</t>
-        </is>
-      </c>
-      <c r="O106" s="4" t="inlineStr"/>
+      <c r="N106" s="4" t="inlineStr"/>
+      <c r="O106" s="4" t="inlineStr">
+        <is>
+          <t>95 000</t>
+        </is>
+      </c>
       <c r="P106" s="4" t="inlineStr">
-        <is>
-          <t>95 000</t>
-        </is>
-      </c>
-      <c r="Q106" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8734,18 +8160,13 @@
           <t>48 425</t>
         </is>
       </c>
-      <c r="N107" s="4" t="inlineStr">
-        <is>
-          <t>48 425</t>
-        </is>
-      </c>
-      <c r="O107" s="4" t="inlineStr"/>
+      <c r="N107" s="4" t="inlineStr"/>
+      <c r="O107" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P107" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q107" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8799,18 +8220,13 @@
           <t>19 556</t>
         </is>
       </c>
-      <c r="N108" s="4" t="inlineStr">
-        <is>
-          <t>19 556</t>
-        </is>
-      </c>
-      <c r="O108" s="4" t="inlineStr"/>
+      <c r="N108" s="4" t="inlineStr"/>
+      <c r="O108" s="4" t="inlineStr">
+        <is>
+          <t>65 000</t>
+        </is>
+      </c>
       <c r="P108" s="4" t="inlineStr">
-        <is>
-          <t>65 000</t>
-        </is>
-      </c>
-      <c r="Q108" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8864,18 +8280,13 @@
           <t>20 860</t>
         </is>
       </c>
-      <c r="N109" s="4" t="inlineStr">
-        <is>
-          <t>20 860</t>
-        </is>
-      </c>
-      <c r="O109" s="4" t="inlineStr"/>
+      <c r="N109" s="4" t="inlineStr"/>
+      <c r="O109" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P109" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q109" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8929,18 +8340,13 @@
           <t>46 004</t>
         </is>
       </c>
-      <c r="N110" s="4" t="inlineStr">
-        <is>
-          <t>46 004</t>
-        </is>
-      </c>
-      <c r="O110" s="4" t="inlineStr"/>
+      <c r="N110" s="4" t="inlineStr"/>
+      <c r="O110" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P110" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q110" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8994,18 +8400,13 @@
           <t>26 820</t>
         </is>
       </c>
-      <c r="N111" s="4" t="inlineStr">
-        <is>
-          <t>26 820</t>
-        </is>
-      </c>
-      <c r="O111" s="4" t="inlineStr"/>
+      <c r="N111" s="4" t="inlineStr"/>
+      <c r="O111" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P111" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q111" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9032,7 +8433,6 @@
       <c r="N112" s="23" t="n"/>
       <c r="O112" s="23" t="n"/>
       <c r="P112" s="23" t="n"/>
-      <c r="Q112" s="23" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="18" t="n">
@@ -9082,18 +8482,13 @@
           <t>35 388</t>
         </is>
       </c>
-      <c r="N113" s="4" t="inlineStr">
-        <is>
-          <t>35 388</t>
-        </is>
-      </c>
-      <c r="O113" s="4" t="inlineStr"/>
+      <c r="N113" s="4" t="inlineStr"/>
+      <c r="O113" s="4" t="inlineStr">
+        <is>
+          <t>95 000</t>
+        </is>
+      </c>
       <c r="P113" s="4" t="inlineStr">
-        <is>
-          <t>95 000</t>
-        </is>
-      </c>
-      <c r="Q113" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9147,18 +8542,13 @@
           <t>37 250</t>
         </is>
       </c>
-      <c r="N114" s="4" t="inlineStr">
-        <is>
-          <t>37 250</t>
-        </is>
-      </c>
-      <c r="O114" s="4" t="inlineStr"/>
+      <c r="N114" s="4" t="inlineStr"/>
+      <c r="O114" s="4" t="inlineStr">
+        <is>
+          <t>95 000</t>
+        </is>
+      </c>
       <c r="P114" s="4" t="inlineStr">
-        <is>
-          <t>95 000</t>
-        </is>
-      </c>
-      <c r="Q114" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9212,18 +8602,13 @@
           <t>20 488</t>
         </is>
       </c>
-      <c r="N115" s="4" t="inlineStr">
-        <is>
-          <t>20 488</t>
-        </is>
-      </c>
-      <c r="O115" s="4" t="inlineStr"/>
+      <c r="N115" s="4" t="inlineStr"/>
+      <c r="O115" s="4" t="inlineStr">
+        <is>
+          <t>55 000</t>
+        </is>
+      </c>
       <c r="P115" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="Q115" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9277,18 +8662,13 @@
           <t>17 508</t>
         </is>
       </c>
-      <c r="N116" s="4" t="inlineStr">
-        <is>
-          <t>17 508</t>
-        </is>
-      </c>
-      <c r="O116" s="4" t="inlineStr"/>
+      <c r="N116" s="4" t="inlineStr"/>
+      <c r="O116" s="4" t="inlineStr">
+        <is>
+          <t>55 000</t>
+        </is>
+      </c>
       <c r="P116" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="Q116" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9342,18 +8722,13 @@
           <t>20 860</t>
         </is>
       </c>
-      <c r="N117" s="4" t="inlineStr">
-        <is>
-          <t>20 860</t>
-        </is>
-      </c>
-      <c r="O117" s="4" t="inlineStr"/>
+      <c r="N117" s="4" t="inlineStr"/>
+      <c r="O117" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P117" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q117" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9380,7 +8755,6 @@
       <c r="N118" s="23" t="n"/>
       <c r="O118" s="23" t="n"/>
       <c r="P118" s="23" t="n"/>
-      <c r="Q118" s="23" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="18" t="n">
@@ -9432,18 +8806,13 @@
           <t>10 616</t>
         </is>
       </c>
-      <c r="N119" s="4" t="inlineStr">
-        <is>
-          <t>10 616</t>
-        </is>
-      </c>
-      <c r="O119" s="4" t="inlineStr"/>
+      <c r="N119" s="4" t="inlineStr"/>
+      <c r="O119" s="4" t="inlineStr">
+        <is>
+          <t>75 000</t>
+        </is>
+      </c>
       <c r="P119" s="4" t="inlineStr">
-        <is>
-          <t>75 000</t>
-        </is>
-      </c>
-      <c r="Q119" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9499,18 +8868,13 @@
           <t>10 616</t>
         </is>
       </c>
-      <c r="N120" s="4" t="inlineStr">
-        <is>
-          <t>10 616</t>
-        </is>
-      </c>
-      <c r="O120" s="4" t="inlineStr"/>
+      <c r="N120" s="4" t="inlineStr"/>
+      <c r="O120" s="4" t="inlineStr">
+        <is>
+          <t>75 000</t>
+        </is>
+      </c>
       <c r="P120" s="4" t="inlineStr">
-        <is>
-          <t>75 000</t>
-        </is>
-      </c>
-      <c r="Q120" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9566,18 +8930,13 @@
           <t>10 244</t>
         </is>
       </c>
-      <c r="N121" s="4" t="inlineStr">
-        <is>
-          <t>10 244</t>
-        </is>
-      </c>
-      <c r="O121" s="4" t="inlineStr"/>
+      <c r="N121" s="4" t="inlineStr"/>
+      <c r="O121" s="4" t="inlineStr">
+        <is>
+          <t>55 000</t>
+        </is>
+      </c>
       <c r="P121" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="Q121" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9633,18 +8992,13 @@
           <t>10 244</t>
         </is>
       </c>
-      <c r="N122" s="4" t="inlineStr">
-        <is>
-          <t>10 244</t>
-        </is>
-      </c>
-      <c r="O122" s="4" t="inlineStr"/>
+      <c r="N122" s="4" t="inlineStr"/>
+      <c r="O122" s="4" t="inlineStr">
+        <is>
+          <t>55 000</t>
+        </is>
+      </c>
       <c r="P122" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="Q122" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9700,18 +9054,13 @@
           <t>10 244</t>
         </is>
       </c>
-      <c r="N123" s="4" t="inlineStr">
-        <is>
-          <t>10 244</t>
-        </is>
-      </c>
-      <c r="O123" s="4" t="inlineStr"/>
+      <c r="N123" s="4" t="inlineStr"/>
+      <c r="O123" s="4" t="inlineStr">
+        <is>
+          <t>55 000</t>
+        </is>
+      </c>
       <c r="P123" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="Q123" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9769,18 +9118,13 @@
           <t>2 794</t>
         </is>
       </c>
-      <c r="N124" s="4" t="inlineStr">
-        <is>
-          <t>2 794</t>
-        </is>
-      </c>
-      <c r="O124" s="4" t="inlineStr"/>
+      <c r="N124" s="4" t="inlineStr"/>
+      <c r="O124" s="4" t="inlineStr">
+        <is>
+          <t>45 000</t>
+        </is>
+      </c>
       <c r="P124" s="4" t="inlineStr">
-        <is>
-          <t>45 000</t>
-        </is>
-      </c>
-      <c r="Q124" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9838,18 +9182,13 @@
           <t>2 421</t>
         </is>
       </c>
-      <c r="N125" s="4" t="inlineStr">
-        <is>
-          <t>2 421</t>
-        </is>
-      </c>
-      <c r="O125" s="4" t="inlineStr"/>
+      <c r="N125" s="4" t="inlineStr"/>
+      <c r="O125" s="4" t="inlineStr">
+        <is>
+          <t>40 000</t>
+        </is>
+      </c>
       <c r="P125" s="4" t="inlineStr">
-        <is>
-          <t>40 000</t>
-        </is>
-      </c>
-      <c r="Q125" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9876,7 +9215,6 @@
       <c r="N126" s="23" t="n"/>
       <c r="O126" s="23" t="n"/>
       <c r="P126" s="23" t="n"/>
-      <c r="Q126" s="23" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="18" t="n">
@@ -9930,18 +9268,13 @@
           <t>1 490</t>
         </is>
       </c>
-      <c r="N127" s="4" t="inlineStr">
-        <is>
-          <t>1 490</t>
-        </is>
-      </c>
-      <c r="O127" s="4" t="inlineStr"/>
+      <c r="N127" s="4" t="inlineStr"/>
+      <c r="O127" s="4" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
       <c r="P127" s="4" t="inlineStr">
-        <is>
-          <t>15 000</t>
-        </is>
-      </c>
-      <c r="Q127" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9999,18 +9332,13 @@
           <t>2 235</t>
         </is>
       </c>
-      <c r="N128" s="4" t="inlineStr">
-        <is>
-          <t>2 235</t>
-        </is>
-      </c>
-      <c r="O128" s="4" t="inlineStr"/>
+      <c r="N128" s="4" t="inlineStr"/>
+      <c r="O128" s="4" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
       <c r="P128" s="4" t="inlineStr">
-        <is>
-          <t>15 000</t>
-        </is>
-      </c>
-      <c r="Q128" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10059,19 +9387,18 @@
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr"/>
-      <c r="M129" s="4" t="inlineStr"/>
-      <c r="N129" s="4" t="inlineStr">
+      <c r="M129" s="4" t="inlineStr">
         <is>
           <t>20 000</t>
         </is>
       </c>
-      <c r="O129" s="4" t="inlineStr"/>
+      <c r="N129" s="4" t="inlineStr"/>
+      <c r="O129" s="4" t="inlineStr">
+        <is>
+          <t>55 000</t>
+        </is>
+      </c>
       <c r="P129" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="Q129" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10120,19 +9447,18 @@
         </is>
       </c>
       <c r="L130" s="14" t="inlineStr"/>
-      <c r="M130" s="14" t="inlineStr"/>
-      <c r="N130" s="14" t="inlineStr">
+      <c r="M130" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O130" s="14" t="inlineStr"/>
+      <c r="N130" s="14" t="inlineStr"/>
+      <c r="O130" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P130" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q130" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10188,20 +9514,15 @@
       </c>
       <c r="N131" s="4" t="inlineStr">
         <is>
-          <t>13 038</t>
+          <t>5 000</t>
         </is>
       </c>
       <c r="O131" s="4" t="inlineStr">
         <is>
-          <t>5 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P131" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q131" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10228,7 +9549,6 @@
       <c r="N132" s="23" t="n"/>
       <c r="O132" s="23" t="n"/>
       <c r="P132" s="23" t="n"/>
-      <c r="Q132" s="23" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="24" t="n">
@@ -10273,19 +9593,18 @@
         </is>
       </c>
       <c r="L133" s="14" t="inlineStr"/>
-      <c r="M133" s="14" t="inlineStr"/>
-      <c r="N133" s="14" t="inlineStr">
+      <c r="M133" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O133" s="14" t="inlineStr"/>
+      <c r="N133" s="14" t="inlineStr"/>
+      <c r="O133" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P133" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q133" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10312,7 +9631,6 @@
       <c r="N134" s="23" t="n"/>
       <c r="O134" s="23" t="n"/>
       <c r="P134" s="23" t="n"/>
-      <c r="Q134" s="23" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="18" t="n">
@@ -10362,18 +9680,13 @@
           <t>60 718</t>
         </is>
       </c>
-      <c r="N135" s="4" t="inlineStr">
-        <is>
-          <t>60 718</t>
-        </is>
-      </c>
-      <c r="O135" s="4" t="inlineStr"/>
+      <c r="N135" s="4" t="inlineStr"/>
+      <c r="O135" s="4" t="inlineStr">
+        <is>
+          <t>160 000</t>
+        </is>
+      </c>
       <c r="P135" s="4" t="inlineStr">
-        <is>
-          <t>160 000</t>
-        </is>
-      </c>
-      <c r="Q135" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10400,7 +9713,6 @@
       <c r="N136" s="23" t="n"/>
       <c r="O136" s="23" t="n"/>
       <c r="P136" s="23" t="n"/>
-      <c r="Q136" s="23" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="24" t="n">
@@ -10441,19 +9753,18 @@
       <c r="J137" s="24" t="inlineStr"/>
       <c r="K137" s="14" t="inlineStr"/>
       <c r="L137" s="14" t="inlineStr"/>
-      <c r="M137" s="14" t="inlineStr"/>
-      <c r="N137" s="14" t="inlineStr">
+      <c r="M137" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O137" s="14" t="inlineStr"/>
+      <c r="N137" s="14" t="inlineStr"/>
+      <c r="O137" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P137" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q137" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10498,19 +9809,18 @@
       <c r="J138" s="24" t="inlineStr"/>
       <c r="K138" s="14" t="inlineStr"/>
       <c r="L138" s="14" t="inlineStr"/>
-      <c r="M138" s="14" t="inlineStr"/>
-      <c r="N138" s="14" t="inlineStr">
+      <c r="M138" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O138" s="14" t="inlineStr"/>
+      <c r="N138" s="14" t="inlineStr"/>
+      <c r="O138" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P138" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q138" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10561,19 +9871,18 @@
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr"/>
-      <c r="M139" s="4" t="inlineStr"/>
-      <c r="N139" s="4" t="inlineStr">
+      <c r="M139" s="4" t="inlineStr">
         <is>
           <t>6 500</t>
         </is>
       </c>
-      <c r="O139" s="4" t="inlineStr"/>
+      <c r="N139" s="4" t="inlineStr"/>
+      <c r="O139" s="4" t="inlineStr">
+        <is>
+          <t>22 000</t>
+        </is>
+      </c>
       <c r="P139" s="4" t="inlineStr">
-        <is>
-          <t>22 000</t>
-        </is>
-      </c>
-      <c r="Q139" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10624,19 +9933,18 @@
         </is>
       </c>
       <c r="L140" s="4" t="inlineStr"/>
-      <c r="M140" s="4" t="inlineStr"/>
-      <c r="N140" s="4" t="inlineStr">
+      <c r="M140" s="4" t="inlineStr">
         <is>
           <t>6 500</t>
         </is>
       </c>
-      <c r="O140" s="4" t="inlineStr"/>
+      <c r="N140" s="4" t="inlineStr"/>
+      <c r="O140" s="4" t="inlineStr">
+        <is>
+          <t>22 000</t>
+        </is>
+      </c>
       <c r="P140" s="4" t="inlineStr">
-        <is>
-          <t>22 000</t>
-        </is>
-      </c>
-      <c r="Q140" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10685,19 +9993,18 @@
         </is>
       </c>
       <c r="L141" s="4" t="inlineStr"/>
-      <c r="M141" s="4" t="inlineStr"/>
-      <c r="N141" s="4" t="inlineStr">
+      <c r="M141" s="4" t="inlineStr">
         <is>
           <t>6 500</t>
         </is>
       </c>
-      <c r="O141" s="4" t="inlineStr"/>
+      <c r="N141" s="4" t="inlineStr"/>
+      <c r="O141" s="4" t="inlineStr">
+        <is>
+          <t>22 000</t>
+        </is>
+      </c>
       <c r="P141" s="4" t="inlineStr">
-        <is>
-          <t>22 000</t>
-        </is>
-      </c>
-      <c r="Q141" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10746,19 +10053,18 @@
         </is>
       </c>
       <c r="L142" s="4" t="inlineStr"/>
-      <c r="M142" s="4" t="inlineStr"/>
-      <c r="N142" s="4" t="inlineStr">
+      <c r="M142" s="4" t="inlineStr">
         <is>
           <t>6 500</t>
         </is>
       </c>
-      <c r="O142" s="4" t="inlineStr"/>
+      <c r="N142" s="4" t="inlineStr"/>
+      <c r="O142" s="4" t="inlineStr">
+        <is>
+          <t>22 000</t>
+        </is>
+      </c>
       <c r="P142" s="4" t="inlineStr">
-        <is>
-          <t>22 000</t>
-        </is>
-      </c>
-      <c r="Q142" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10810,20 +10116,15 @@
       </c>
       <c r="N143" s="4" t="inlineStr">
         <is>
-          <t>6 891</t>
+          <t>4 500</t>
         </is>
       </c>
       <c r="O143" s="4" t="inlineStr">
         <is>
-          <t>4 500</t>
+          <t>22 000</t>
         </is>
       </c>
       <c r="P143" s="4" t="inlineStr">
-        <is>
-          <t>22 000</t>
-        </is>
-      </c>
-      <c r="Q143" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10875,20 +10176,15 @@
       </c>
       <c r="N144" s="4" t="inlineStr">
         <is>
-          <t>6 891</t>
+          <t>4 500</t>
         </is>
       </c>
       <c r="O144" s="4" t="inlineStr">
         <is>
-          <t>4 500</t>
+          <t>22 000</t>
         </is>
       </c>
       <c r="P144" s="4" t="inlineStr">
-        <is>
-          <t>22 000</t>
-        </is>
-      </c>
-      <c r="Q144" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10937,19 +10233,18 @@
         </is>
       </c>
       <c r="L145" s="4" t="inlineStr"/>
-      <c r="M145" s="4" t="inlineStr"/>
-      <c r="N145" s="4" t="inlineStr">
+      <c r="M145" s="4" t="inlineStr">
         <is>
           <t>5 000</t>
         </is>
       </c>
-      <c r="O145" s="4" t="inlineStr"/>
+      <c r="N145" s="4" t="inlineStr"/>
+      <c r="O145" s="4" t="inlineStr">
+        <is>
+          <t>20 000</t>
+        </is>
+      </c>
       <c r="P145" s="4" t="inlineStr">
-        <is>
-          <t>20 000</t>
-        </is>
-      </c>
-      <c r="Q145" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10994,23 +10289,22 @@
       <c r="J146" s="18" t="inlineStr"/>
       <c r="K146" s="4" t="inlineStr"/>
       <c r="L146" s="4" t="inlineStr"/>
-      <c r="M146" s="4" t="inlineStr"/>
+      <c r="M146" s="4" t="inlineStr">
+        <is>
+          <t>5 000</t>
+        </is>
+      </c>
       <c r="N146" s="4" t="inlineStr">
         <is>
-          <t>5 000</t>
+          <t>4 000</t>
         </is>
       </c>
       <c r="O146" s="4" t="inlineStr">
         <is>
-          <t>4 000</t>
+          <t>20 000</t>
         </is>
       </c>
       <c r="P146" s="4" t="inlineStr">
-        <is>
-          <t>20 000</t>
-        </is>
-      </c>
-      <c r="Q146" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11055,23 +10349,22 @@
       <c r="J147" s="24" t="inlineStr"/>
       <c r="K147" s="14" t="inlineStr"/>
       <c r="L147" s="14" t="inlineStr"/>
-      <c r="M147" s="14" t="inlineStr"/>
+      <c r="M147" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="N147" s="14" t="inlineStr">
         <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="O147" s="14" t="inlineStr">
+        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O147" s="14" t="inlineStr">
-        <is>
-          <t>4 000</t>
-        </is>
-      </c>
       <c r="P147" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q147" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11116,23 +10409,22 @@
       <c r="J148" s="18" t="inlineStr"/>
       <c r="K148" s="4" t="inlineStr"/>
       <c r="L148" s="4" t="inlineStr"/>
-      <c r="M148" s="4" t="inlineStr"/>
+      <c r="M148" s="4" t="inlineStr">
+        <is>
+          <t>5 000</t>
+        </is>
+      </c>
       <c r="N148" s="4" t="inlineStr">
         <is>
-          <t>5 000</t>
+          <t>4 000</t>
         </is>
       </c>
       <c r="O148" s="4" t="inlineStr">
         <is>
-          <t>4 000</t>
+          <t>20 000</t>
         </is>
       </c>
       <c r="P148" s="4" t="inlineStr">
-        <is>
-          <t>20 000</t>
-        </is>
-      </c>
-      <c r="Q148" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11177,23 +10469,22 @@
       <c r="J149" s="24" t="inlineStr"/>
       <c r="K149" s="14" t="inlineStr"/>
       <c r="L149" s="14" t="inlineStr"/>
-      <c r="M149" s="14" t="inlineStr"/>
+      <c r="M149" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="N149" s="14" t="inlineStr">
         <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="O149" s="14" t="inlineStr">
+        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O149" s="14" t="inlineStr">
-        <is>
-          <t>4 000</t>
-        </is>
-      </c>
       <c r="P149" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q149" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11249,20 +10540,15 @@
       </c>
       <c r="N150" s="4" t="inlineStr">
         <is>
-          <t>5 774</t>
+          <t>4 000</t>
         </is>
       </c>
       <c r="O150" s="4" t="inlineStr">
         <is>
-          <t>4 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P150" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q150" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11318,20 +10604,15 @@
       </c>
       <c r="N151" s="4" t="inlineStr">
         <is>
-          <t>5 774</t>
+          <t>4 000</t>
         </is>
       </c>
       <c r="O151" s="4" t="inlineStr">
         <is>
-          <t>4 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P151" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q151" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11387,20 +10668,15 @@
       </c>
       <c r="N152" s="4" t="inlineStr">
         <is>
-          <t>5 774</t>
+          <t>4 000</t>
         </is>
       </c>
       <c r="O152" s="4" t="inlineStr">
         <is>
-          <t>4 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P152" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q152" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11458,18 +10734,13 @@
           <t>3 352</t>
         </is>
       </c>
-      <c r="N153" s="4" t="inlineStr">
-        <is>
-          <t>3 352</t>
-        </is>
-      </c>
-      <c r="O153" s="4" t="inlineStr"/>
+      <c r="N153" s="4" t="inlineStr"/>
+      <c r="O153" s="4" t="inlineStr">
+        <is>
+          <t>25 000</t>
+        </is>
+      </c>
       <c r="P153" s="4" t="inlineStr">
-        <is>
-          <t>25 000</t>
-        </is>
-      </c>
-      <c r="Q153" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11518,19 +10789,18 @@
         </is>
       </c>
       <c r="L154" s="4" t="inlineStr"/>
-      <c r="M154" s="4" t="inlineStr"/>
-      <c r="N154" s="4" t="inlineStr">
+      <c r="M154" s="4" t="inlineStr">
         <is>
           <t>4 500</t>
         </is>
       </c>
-      <c r="O154" s="4" t="inlineStr"/>
+      <c r="N154" s="4" t="inlineStr"/>
+      <c r="O154" s="4" t="inlineStr">
+        <is>
+          <t>22 000</t>
+        </is>
+      </c>
       <c r="P154" s="4" t="inlineStr">
-        <is>
-          <t>22 000</t>
-        </is>
-      </c>
-      <c r="Q154" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11579,23 +10849,22 @@
         </is>
       </c>
       <c r="L155" s="4" t="inlineStr"/>
-      <c r="M155" s="4" t="inlineStr"/>
+      <c r="M155" s="4" t="inlineStr">
+        <is>
+          <t>6 500</t>
+        </is>
+      </c>
       <c r="N155" s="4" t="inlineStr">
         <is>
-          <t>6 500</t>
+          <t>3 000</t>
         </is>
       </c>
       <c r="O155" s="4" t="inlineStr">
         <is>
-          <t>3 000</t>
+          <t>24 000</t>
         </is>
       </c>
       <c r="P155" s="4" t="inlineStr">
-        <is>
-          <t>24 000</t>
-        </is>
-      </c>
-      <c r="Q155" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11647,20 +10916,15 @@
       </c>
       <c r="N156" s="4" t="inlineStr">
         <is>
-          <t>3 725</t>
+          <t>3 000</t>
         </is>
       </c>
       <c r="O156" s="4" t="inlineStr">
         <is>
-          <t>3 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P156" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q156" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11712,20 +10976,15 @@
       </c>
       <c r="N157" s="4" t="inlineStr">
         <is>
-          <t>3 725</t>
+          <t>3 000</t>
         </is>
       </c>
       <c r="O157" s="4" t="inlineStr">
         <is>
-          <t>3 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P157" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q157" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11779,18 +11038,13 @@
           <t>3 725</t>
         </is>
       </c>
-      <c r="N158" s="4" t="inlineStr">
-        <is>
-          <t>3 725</t>
-        </is>
-      </c>
-      <c r="O158" s="4" t="inlineStr"/>
+      <c r="N158" s="4" t="inlineStr"/>
+      <c r="O158" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P158" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q158" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11842,20 +11096,15 @@
       </c>
       <c r="N159" s="4" t="inlineStr">
         <is>
-          <t>3 725</t>
+          <t>3 000</t>
         </is>
       </c>
       <c r="O159" s="4" t="inlineStr">
         <is>
-          <t>3 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P159" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q159" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11907,20 +11156,15 @@
       </c>
       <c r="N160" s="4" t="inlineStr">
         <is>
-          <t>3 725</t>
+          <t>3 000</t>
         </is>
       </c>
       <c r="O160" s="4" t="inlineStr">
         <is>
-          <t>3 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P160" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q160" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11967,19 +11211,18 @@
       </c>
       <c r="K161" s="14" t="inlineStr"/>
       <c r="L161" s="14" t="inlineStr"/>
-      <c r="M161" s="14" t="inlineStr"/>
-      <c r="N161" s="14" t="inlineStr">
+      <c r="M161" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O161" s="14" t="inlineStr"/>
+      <c r="N161" s="14" t="inlineStr"/>
+      <c r="O161" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P161" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q161" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12024,19 +11267,18 @@
       <c r="J162" s="24" t="inlineStr"/>
       <c r="K162" s="14" t="inlineStr"/>
       <c r="L162" s="14" t="inlineStr"/>
-      <c r="M162" s="14" t="inlineStr"/>
-      <c r="N162" s="14" t="inlineStr">
+      <c r="M162" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O162" s="14" t="inlineStr"/>
+      <c r="N162" s="14" t="inlineStr"/>
+      <c r="O162" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P162" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q162" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12081,23 +11323,22 @@
       <c r="J163" s="24" t="inlineStr"/>
       <c r="K163" s="14" t="inlineStr"/>
       <c r="L163" s="14" t="inlineStr"/>
-      <c r="M163" s="14" t="inlineStr"/>
+      <c r="M163" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="N163" s="14" t="inlineStr">
         <is>
+          <t>3 000</t>
+        </is>
+      </c>
+      <c r="O163" s="14" t="inlineStr">
+        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O163" s="14" t="inlineStr">
-        <is>
-          <t>3 000</t>
-        </is>
-      </c>
       <c r="P163" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q163" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12153,20 +11394,15 @@
       </c>
       <c r="N164" s="4" t="inlineStr">
         <is>
-          <t>3 725</t>
+          <t>3 000</t>
         </is>
       </c>
       <c r="O164" s="4" t="inlineStr">
         <is>
-          <t>3 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P164" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q164" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12215,19 +11451,18 @@
         </is>
       </c>
       <c r="L165" s="4" t="inlineStr"/>
-      <c r="M165" s="4" t="inlineStr"/>
-      <c r="N165" s="4" t="inlineStr">
+      <c r="M165" s="4" t="inlineStr">
         <is>
           <t>3 000</t>
         </is>
       </c>
-      <c r="O165" s="4" t="inlineStr"/>
+      <c r="N165" s="4" t="inlineStr"/>
+      <c r="O165" s="4" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
       <c r="P165" s="4" t="inlineStr">
-        <is>
-          <t>15 000</t>
-        </is>
-      </c>
-      <c r="Q165" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12285,18 +11520,13 @@
           <t>2 831</t>
         </is>
       </c>
-      <c r="N166" s="4" t="inlineStr">
-        <is>
-          <t>2 831</t>
-        </is>
-      </c>
-      <c r="O166" s="4" t="inlineStr"/>
+      <c r="N166" s="4" t="inlineStr"/>
+      <c r="O166" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P166" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q166" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12345,19 +11575,18 @@
         </is>
       </c>
       <c r="L167" s="4" t="inlineStr"/>
-      <c r="M167" s="4" t="inlineStr"/>
-      <c r="N167" s="4" t="inlineStr">
+      <c r="M167" s="4" t="inlineStr">
         <is>
           <t>3 000</t>
         </is>
       </c>
-      <c r="O167" s="4" t="inlineStr"/>
+      <c r="N167" s="4" t="inlineStr"/>
+      <c r="O167" s="4" t="inlineStr">
+        <is>
+          <t>12 000</t>
+        </is>
+      </c>
       <c r="P167" s="4" t="inlineStr">
-        <is>
-          <t>12 000</t>
-        </is>
-      </c>
-      <c r="Q167" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12384,7 +11613,6 @@
       <c r="N168" s="23" t="n"/>
       <c r="O168" s="23" t="n"/>
       <c r="P168" s="23" t="n"/>
-      <c r="Q168" s="23" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="24" t="n">
@@ -12429,19 +11657,18 @@
         </is>
       </c>
       <c r="L169" s="14" t="inlineStr"/>
-      <c r="M169" s="14" t="inlineStr"/>
-      <c r="N169" s="14" t="inlineStr">
+      <c r="M169" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O169" s="14" t="inlineStr"/>
+      <c r="N169" s="14" t="inlineStr"/>
+      <c r="O169" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P169" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q169" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12499,18 +11726,13 @@
           <t>3 539</t>
         </is>
       </c>
-      <c r="N170" s="4" t="inlineStr">
-        <is>
-          <t>3 539</t>
-        </is>
-      </c>
-      <c r="O170" s="4" t="inlineStr"/>
+      <c r="N170" s="4" t="inlineStr"/>
+      <c r="O170" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P170" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q170" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12559,19 +11781,18 @@
         </is>
       </c>
       <c r="L171" s="14" t="inlineStr"/>
-      <c r="M171" s="14" t="inlineStr"/>
-      <c r="N171" s="14" t="inlineStr">
+      <c r="M171" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O171" s="14" t="inlineStr"/>
+      <c r="N171" s="14" t="inlineStr"/>
+      <c r="O171" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P171" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q171" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12616,23 +11837,22 @@
       <c r="J172" s="24" t="inlineStr"/>
       <c r="K172" s="14" t="inlineStr"/>
       <c r="L172" s="14" t="inlineStr"/>
-      <c r="M172" s="14" t="inlineStr"/>
+      <c r="M172" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="N172" s="14" t="inlineStr">
         <is>
+          <t>3 500</t>
+        </is>
+      </c>
+      <c r="O172" s="14" t="inlineStr">
+        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O172" s="14" t="inlineStr">
-        <is>
-          <t>3 500</t>
-        </is>
-      </c>
       <c r="P172" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q172" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12677,23 +11897,22 @@
       <c r="J173" s="24" t="inlineStr"/>
       <c r="K173" s="14" t="inlineStr"/>
       <c r="L173" s="14" t="inlineStr"/>
-      <c r="M173" s="14" t="inlineStr"/>
+      <c r="M173" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="N173" s="14" t="inlineStr">
         <is>
+          <t>3 500</t>
+        </is>
+      </c>
+      <c r="O173" s="14" t="inlineStr">
+        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O173" s="14" t="inlineStr">
-        <is>
-          <t>3 500</t>
-        </is>
-      </c>
       <c r="P173" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q173" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12738,23 +11957,22 @@
       <c r="J174" s="24" t="inlineStr"/>
       <c r="K174" s="14" t="inlineStr"/>
       <c r="L174" s="14" t="inlineStr"/>
-      <c r="M174" s="14" t="inlineStr"/>
+      <c r="M174" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="N174" s="14" t="inlineStr">
         <is>
+          <t>3 500</t>
+        </is>
+      </c>
+      <c r="O174" s="14" t="inlineStr">
+        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O174" s="14" t="inlineStr">
-        <is>
-          <t>3 500</t>
-        </is>
-      </c>
       <c r="P174" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q174" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12799,23 +12017,22 @@
       <c r="J175" s="24" t="inlineStr"/>
       <c r="K175" s="14" t="inlineStr"/>
       <c r="L175" s="14" t="inlineStr"/>
-      <c r="M175" s="14" t="inlineStr"/>
+      <c r="M175" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="N175" s="14" t="inlineStr">
         <is>
+          <t>3 500</t>
+        </is>
+      </c>
+      <c r="O175" s="14" t="inlineStr">
+        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O175" s="14" t="inlineStr">
-        <is>
-          <t>3 500</t>
-        </is>
-      </c>
       <c r="P175" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q175" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12860,23 +12077,22 @@
       <c r="J176" s="24" t="inlineStr"/>
       <c r="K176" s="14" t="inlineStr"/>
       <c r="L176" s="14" t="inlineStr"/>
-      <c r="M176" s="14" t="inlineStr"/>
+      <c r="M176" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="N176" s="14" t="inlineStr">
         <is>
+          <t>3 500</t>
+        </is>
+      </c>
+      <c r="O176" s="14" t="inlineStr">
+        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O176" s="14" t="inlineStr">
-        <is>
-          <t>3 500</t>
-        </is>
-      </c>
       <c r="P176" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q176" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12923,23 +12139,22 @@
       </c>
       <c r="K177" s="14" t="inlineStr"/>
       <c r="L177" s="14" t="inlineStr"/>
-      <c r="M177" s="14" t="inlineStr"/>
+      <c r="M177" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="N177" s="14" t="inlineStr">
         <is>
+          <t>3 500</t>
+        </is>
+      </c>
+      <c r="O177" s="14" t="inlineStr">
+        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O177" s="14" t="inlineStr">
-        <is>
-          <t>3 500</t>
-        </is>
-      </c>
       <c r="P177" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q177" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12984,23 +12199,22 @@
       <c r="J178" s="24" t="inlineStr"/>
       <c r="K178" s="14" t="inlineStr"/>
       <c r="L178" s="14" t="inlineStr"/>
-      <c r="M178" s="14" t="inlineStr"/>
+      <c r="M178" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="N178" s="14" t="inlineStr">
         <is>
+          <t>3 500</t>
+        </is>
+      </c>
+      <c r="O178" s="14" t="inlineStr">
+        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O178" s="14" t="inlineStr">
-        <is>
-          <t>3 500</t>
-        </is>
-      </c>
       <c r="P178" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q178" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13056,20 +12270,15 @@
       </c>
       <c r="N179" s="4" t="inlineStr">
         <is>
-          <t>3 911</t>
+          <t>3 500</t>
         </is>
       </c>
       <c r="O179" s="4" t="inlineStr">
         <is>
-          <t>3 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P179" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q179" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13125,20 +12334,15 @@
       </c>
       <c r="N180" s="4" t="inlineStr">
         <is>
-          <t>3 911</t>
+          <t>3 500</t>
         </is>
       </c>
       <c r="O180" s="4" t="inlineStr">
         <is>
-          <t>3 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P180" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q180" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13196,18 +12400,13 @@
           <t>1 490</t>
         </is>
       </c>
-      <c r="N181" s="4" t="inlineStr">
-        <is>
-          <t>1 490</t>
-        </is>
-      </c>
-      <c r="O181" s="4" t="inlineStr"/>
+      <c r="N181" s="4" t="inlineStr"/>
+      <c r="O181" s="4" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
       <c r="P181" s="4" t="inlineStr">
-        <is>
-          <t>15 000</t>
-        </is>
-      </c>
-      <c r="Q181" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13261,18 +12460,13 @@
           <t>10 616</t>
         </is>
       </c>
-      <c r="N182" s="4" t="inlineStr">
-        <is>
-          <t>10 616</t>
-        </is>
-      </c>
-      <c r="O182" s="4" t="inlineStr"/>
+      <c r="N182" s="4" t="inlineStr"/>
+      <c r="O182" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P182" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q182" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13326,18 +12520,13 @@
           <t>2 235</t>
         </is>
       </c>
-      <c r="N183" s="4" t="inlineStr">
-        <is>
-          <t>2 235</t>
-        </is>
-      </c>
-      <c r="O183" s="4" t="inlineStr"/>
+      <c r="N183" s="4" t="inlineStr"/>
+      <c r="O183" s="4" t="inlineStr">
+        <is>
+          <t>14 000</t>
+        </is>
+      </c>
       <c r="P183" s="4" t="inlineStr">
-        <is>
-          <t>14 000</t>
-        </is>
-      </c>
-      <c r="Q183" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13386,19 +12575,18 @@
         </is>
       </c>
       <c r="L184" s="4" t="inlineStr"/>
-      <c r="M184" s="4" t="inlineStr"/>
-      <c r="N184" s="4" t="inlineStr">
+      <c r="M184" s="4" t="inlineStr">
         <is>
           <t>20 000</t>
         </is>
       </c>
-      <c r="O184" s="4" t="inlineStr"/>
+      <c r="N184" s="4" t="inlineStr"/>
+      <c r="O184" s="4" t="inlineStr">
+        <is>
+          <t>65 000</t>
+        </is>
+      </c>
       <c r="P184" s="4" t="inlineStr">
-        <is>
-          <t>65 000</t>
-        </is>
-      </c>
-      <c r="Q184" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13454,20 +12642,15 @@
       </c>
       <c r="N185" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>2 500</t>
         </is>
       </c>
       <c r="O185" s="4" t="inlineStr">
         <is>
-          <t>2 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P185" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q185" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13494,7 +12677,6 @@
       <c r="N186" s="23" t="n"/>
       <c r="O186" s="23" t="n"/>
       <c r="P186" s="23" t="n"/>
-      <c r="Q186" s="23" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="18" t="n">
@@ -13544,18 +12726,13 @@
           <t>9 312</t>
         </is>
       </c>
-      <c r="N187" s="4" t="inlineStr">
-        <is>
-          <t>9 312</t>
-        </is>
-      </c>
-      <c r="O187" s="4" t="inlineStr"/>
+      <c r="N187" s="4" t="inlineStr"/>
+      <c r="O187" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P187" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q187" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13609,18 +12786,13 @@
           <t>16 390</t>
         </is>
       </c>
-      <c r="N188" s="4" t="inlineStr">
-        <is>
-          <t>16 390</t>
-        </is>
-      </c>
-      <c r="O188" s="4" t="inlineStr"/>
+      <c r="N188" s="4" t="inlineStr"/>
+      <c r="O188" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P188" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q188" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13676,20 +12848,15 @@
       </c>
       <c r="N189" s="4" t="inlineStr">
         <is>
-          <t>27 938</t>
+          <t>4 500</t>
         </is>
       </c>
       <c r="O189" s="4" t="inlineStr">
         <is>
-          <t>4 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P189" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q189" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13741,20 +12908,15 @@
       </c>
       <c r="N190" s="4" t="inlineStr">
         <is>
-          <t>32 035</t>
+          <t>4 500</t>
         </is>
       </c>
       <c r="O190" s="4" t="inlineStr">
         <is>
-          <t>4 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P190" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q190" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13812,18 +12974,13 @@
           <t>7 636</t>
         </is>
       </c>
-      <c r="N191" s="4" t="inlineStr">
-        <is>
-          <t>7 636</t>
-        </is>
-      </c>
-      <c r="O191" s="4" t="inlineStr"/>
+      <c r="N191" s="4" t="inlineStr"/>
+      <c r="O191" s="4" t="inlineStr">
+        <is>
+          <t>24 000</t>
+        </is>
+      </c>
       <c r="P191" s="4" t="inlineStr">
-        <is>
-          <t>24 000</t>
-        </is>
-      </c>
-      <c r="Q191" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13883,20 +13040,15 @@
       </c>
       <c r="N192" s="4" t="inlineStr">
         <is>
-          <t>7 636</t>
+          <t>4 500</t>
         </is>
       </c>
       <c r="O192" s="4" t="inlineStr">
         <is>
-          <t>4 500</t>
+          <t>24 000</t>
         </is>
       </c>
       <c r="P192" s="4" t="inlineStr">
-        <is>
-          <t>24 000</t>
-        </is>
-      </c>
-      <c r="Q192" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13956,20 +13108,15 @@
       </c>
       <c r="N193" s="4" t="inlineStr">
         <is>
-          <t>2 235</t>
+          <t>3 500</t>
         </is>
       </c>
       <c r="O193" s="4" t="inlineStr">
         <is>
-          <t>3 500</t>
+          <t>20 000</t>
         </is>
       </c>
       <c r="P193" s="4" t="inlineStr">
-        <is>
-          <t>20 000</t>
-        </is>
-      </c>
-      <c r="Q193" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14029,20 +13176,15 @@
       </c>
       <c r="N194" s="4" t="inlineStr">
         <is>
-          <t>5 215</t>
+          <t>3 500</t>
         </is>
       </c>
       <c r="O194" s="4" t="inlineStr">
         <is>
-          <t>3 500</t>
+          <t>20 000</t>
         </is>
       </c>
       <c r="P194" s="4" t="inlineStr">
-        <is>
-          <t>20 000</t>
-        </is>
-      </c>
-      <c r="Q194" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14102,20 +13244,15 @@
       </c>
       <c r="N195" s="4" t="inlineStr">
         <is>
-          <t>3 390</t>
+          <t>3 000</t>
         </is>
       </c>
       <c r="O195" s="4" t="inlineStr">
         <is>
-          <t>3 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P195" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q195" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14171,20 +13308,15 @@
       </c>
       <c r="N196" s="4" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>2 500</t>
         </is>
       </c>
       <c r="O196" s="4" t="inlineStr">
         <is>
-          <t>2 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="P196" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q196" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14211,7 +13343,6 @@
       <c r="N197" s="23" t="n"/>
       <c r="O197" s="23" t="n"/>
       <c r="P197" s="23" t="n"/>
-      <c r="Q197" s="23" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="18" t="n">
@@ -14259,20 +13390,15 @@
       </c>
       <c r="N198" s="4" t="inlineStr">
         <is>
-          <t>10 244</t>
+          <t>4 000</t>
         </is>
       </c>
       <c r="O198" s="4" t="inlineStr">
         <is>
-          <t>4 000</t>
+          <t>30 000</t>
         </is>
       </c>
       <c r="P198" s="4" t="inlineStr">
-        <is>
-          <t>30 000</t>
-        </is>
-      </c>
-      <c r="Q198" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14322,18 +13448,13 @@
           <t>10 244</t>
         </is>
       </c>
-      <c r="N199" s="4" t="inlineStr">
-        <is>
-          <t>10 244</t>
-        </is>
-      </c>
-      <c r="O199" s="4" t="inlineStr"/>
+      <c r="N199" s="4" t="inlineStr"/>
+      <c r="O199" s="4" t="inlineStr">
+        <is>
+          <t>30 000</t>
+        </is>
+      </c>
       <c r="P199" s="4" t="inlineStr">
-        <is>
-          <t>30 000</t>
-        </is>
-      </c>
-      <c r="Q199" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14360,7 +13481,6 @@
       <c r="N200" s="23" t="n"/>
       <c r="O200" s="23" t="n"/>
       <c r="P200" s="23" t="n"/>
-      <c r="Q200" s="23" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="18" t="n">
@@ -14414,18 +13534,13 @@
           <t>4 656</t>
         </is>
       </c>
-      <c r="N201" s="4" t="inlineStr">
-        <is>
-          <t>4 656</t>
-        </is>
-      </c>
-      <c r="O201" s="4" t="inlineStr"/>
+      <c r="N201" s="4" t="inlineStr"/>
+      <c r="O201" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P201" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q201" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14483,18 +13598,13 @@
           <t>3 166</t>
         </is>
       </c>
-      <c r="N202" s="4" t="inlineStr">
-        <is>
-          <t>3 166</t>
-        </is>
-      </c>
-      <c r="O202" s="4" t="inlineStr"/>
+      <c r="N202" s="4" t="inlineStr"/>
+      <c r="O202" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P202" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q202" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14552,18 +13662,13 @@
           <t>2 794</t>
         </is>
       </c>
-      <c r="N203" s="4" t="inlineStr">
-        <is>
-          <t>2 794</t>
-        </is>
-      </c>
-      <c r="O203" s="4" t="inlineStr"/>
+      <c r="N203" s="4" t="inlineStr"/>
+      <c r="O203" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P203" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q203" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14621,18 +13726,13 @@
           <t>1 118</t>
         </is>
       </c>
-      <c r="N204" s="4" t="inlineStr">
-        <is>
-          <t>1 118</t>
-        </is>
-      </c>
-      <c r="O204" s="4" t="inlineStr"/>
+      <c r="N204" s="4" t="inlineStr"/>
+      <c r="O204" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P204" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q204" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14659,7 +13759,6 @@
       <c r="N205" s="23" t="n"/>
       <c r="O205" s="23" t="n"/>
       <c r="P205" s="23" t="n"/>
-      <c r="Q205" s="23" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="18" t="n">
@@ -14700,19 +13799,18 @@
       <c r="J206" s="18" t="inlineStr"/>
       <c r="K206" s="4" t="inlineStr"/>
       <c r="L206" s="4" t="inlineStr"/>
-      <c r="M206" s="4" t="inlineStr"/>
-      <c r="N206" s="4" t="inlineStr">
+      <c r="M206" s="4" t="inlineStr">
         <is>
           <t>35 000</t>
         </is>
       </c>
-      <c r="O206" s="4" t="inlineStr"/>
+      <c r="N206" s="4" t="inlineStr"/>
+      <c r="O206" s="4" t="inlineStr">
+        <is>
+          <t>120 000</t>
+        </is>
+      </c>
       <c r="P206" s="4" t="inlineStr">
-        <is>
-          <t>120 000</t>
-        </is>
-      </c>
-      <c r="Q206" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14757,19 +13855,18 @@
       <c r="J207" s="18" t="inlineStr"/>
       <c r="K207" s="4" t="inlineStr"/>
       <c r="L207" s="4" t="inlineStr"/>
-      <c r="M207" s="4" t="inlineStr"/>
-      <c r="N207" s="4" t="inlineStr">
+      <c r="M207" s="4" t="inlineStr">
         <is>
           <t>35 000</t>
         </is>
       </c>
-      <c r="O207" s="4" t="inlineStr"/>
+      <c r="N207" s="4" t="inlineStr"/>
+      <c r="O207" s="4" t="inlineStr">
+        <is>
+          <t>120 000</t>
+        </is>
+      </c>
       <c r="P207" s="4" t="inlineStr">
-        <is>
-          <t>120 000</t>
-        </is>
-      </c>
-      <c r="Q207" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14814,19 +13911,18 @@
       <c r="J208" s="18" t="inlineStr"/>
       <c r="K208" s="4" t="inlineStr"/>
       <c r="L208" s="4" t="inlineStr"/>
-      <c r="M208" s="4" t="inlineStr"/>
-      <c r="N208" s="4" t="inlineStr">
+      <c r="M208" s="4" t="inlineStr">
         <is>
           <t>15 000</t>
         </is>
       </c>
-      <c r="O208" s="4" t="inlineStr"/>
+      <c r="N208" s="4" t="inlineStr"/>
+      <c r="O208" s="4" t="inlineStr">
+        <is>
+          <t>45 000</t>
+        </is>
+      </c>
       <c r="P208" s="4" t="inlineStr">
-        <is>
-          <t>45 000</t>
-        </is>
-      </c>
-      <c r="Q208" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14871,19 +13967,18 @@
       <c r="J209" s="18" t="inlineStr"/>
       <c r="K209" s="4" t="inlineStr"/>
       <c r="L209" s="4" t="inlineStr"/>
-      <c r="M209" s="4" t="inlineStr"/>
-      <c r="N209" s="4" t="inlineStr">
+      <c r="M209" s="4" t="inlineStr">
         <is>
           <t>15 000</t>
         </is>
       </c>
-      <c r="O209" s="4" t="inlineStr"/>
+      <c r="N209" s="4" t="inlineStr"/>
+      <c r="O209" s="4" t="inlineStr">
+        <is>
+          <t>45 000</t>
+        </is>
+      </c>
       <c r="P209" s="4" t="inlineStr">
-        <is>
-          <t>45 000</t>
-        </is>
-      </c>
-      <c r="Q209" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14910,7 +14005,6 @@
       <c r="N210" s="23" t="n"/>
       <c r="O210" s="23" t="n"/>
       <c r="P210" s="23" t="n"/>
-      <c r="Q210" s="23" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="25" t="n">
@@ -14947,19 +14041,18 @@
       <c r="J211" s="25" t="inlineStr"/>
       <c r="K211" s="12" t="inlineStr"/>
       <c r="L211" s="12" t="inlineStr"/>
-      <c r="M211" s="12" t="inlineStr"/>
-      <c r="N211" s="12" t="inlineStr">
+      <c r="M211" s="12" t="inlineStr">
         <is>
           <t>цена отдельно</t>
         </is>
       </c>
-      <c r="O211" s="12" t="inlineStr"/>
+      <c r="N211" s="12" t="inlineStr"/>
+      <c r="O211" s="12" t="inlineStr">
+        <is>
+          <t>55 000</t>
+        </is>
+      </c>
       <c r="P211" s="12" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="Q211" s="12" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14998,19 +14091,18 @@
       <c r="J212" s="25" t="inlineStr"/>
       <c r="K212" s="12" t="inlineStr"/>
       <c r="L212" s="12" t="inlineStr"/>
-      <c r="M212" s="12" t="inlineStr"/>
-      <c r="N212" s="12" t="inlineStr">
+      <c r="M212" s="12" t="inlineStr">
         <is>
           <t>цена отдельно</t>
         </is>
       </c>
-      <c r="O212" s="12" t="inlineStr"/>
+      <c r="N212" s="12" t="inlineStr"/>
+      <c r="O212" s="12" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P212" s="12" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q212" s="12" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -15055,19 +14147,18 @@
       <c r="J213" s="18" t="inlineStr"/>
       <c r="K213" s="4" t="inlineStr"/>
       <c r="L213" s="4" t="inlineStr"/>
-      <c r="M213" s="4" t="inlineStr"/>
-      <c r="N213" s="4" t="inlineStr">
+      <c r="M213" s="4" t="inlineStr">
         <is>
           <t>30 000</t>
         </is>
       </c>
-      <c r="O213" s="4" t="inlineStr"/>
+      <c r="N213" s="4" t="inlineStr"/>
+      <c r="O213" s="4" t="inlineStr">
+        <is>
+          <t>70 000</t>
+        </is>
+      </c>
       <c r="P213" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="Q213" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -15112,19 +14203,18 @@
       <c r="J214" s="18" t="inlineStr"/>
       <c r="K214" s="4" t="inlineStr"/>
       <c r="L214" s="4" t="inlineStr"/>
-      <c r="M214" s="4" t="inlineStr"/>
-      <c r="N214" s="4" t="inlineStr">
+      <c r="M214" s="4" t="inlineStr">
         <is>
           <t>25 000</t>
         </is>
       </c>
-      <c r="O214" s="4" t="inlineStr"/>
+      <c r="N214" s="4" t="inlineStr"/>
+      <c r="O214" s="4" t="inlineStr">
+        <is>
+          <t>65 000</t>
+        </is>
+      </c>
       <c r="P214" s="4" t="inlineStr">
-        <is>
-          <t>65 000</t>
-        </is>
-      </c>
-      <c r="Q214" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -15169,19 +14259,18 @@
       <c r="J215" s="25" t="inlineStr"/>
       <c r="K215" s="12" t="inlineStr"/>
       <c r="L215" s="12" t="inlineStr"/>
-      <c r="M215" s="12" t="inlineStr"/>
-      <c r="N215" s="12" t="inlineStr">
+      <c r="M215" s="12" t="inlineStr">
         <is>
           <t>цена отдельно</t>
         </is>
       </c>
-      <c r="O215" s="12" t="inlineStr"/>
+      <c r="N215" s="12" t="inlineStr"/>
+      <c r="O215" s="12" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P215" s="12" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q215" s="12" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -15229,18 +14318,13 @@
           <t>12 665</t>
         </is>
       </c>
-      <c r="N216" s="4" t="inlineStr">
-        <is>
-          <t>12 665</t>
-        </is>
-      </c>
-      <c r="O216" s="4" t="inlineStr"/>
+      <c r="N216" s="4" t="inlineStr"/>
+      <c r="O216" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P216" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q216" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -15288,18 +14372,13 @@
           <t>4 470</t>
         </is>
       </c>
-      <c r="N217" s="4" t="inlineStr">
-        <is>
-          <t>4 470</t>
-        </is>
-      </c>
-      <c r="O217" s="4" t="inlineStr"/>
+      <c r="N217" s="4" t="inlineStr"/>
+      <c r="O217" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P217" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q217" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -15338,19 +14417,18 @@
       <c r="J218" s="25" t="inlineStr"/>
       <c r="K218" s="12" t="inlineStr"/>
       <c r="L218" s="12" t="inlineStr"/>
-      <c r="M218" s="12" t="inlineStr"/>
-      <c r="N218" s="12" t="inlineStr">
+      <c r="M218" s="12" t="inlineStr">
         <is>
           <t>цена отдельно</t>
         </is>
       </c>
-      <c r="O218" s="12" t="inlineStr"/>
+      <c r="N218" s="12" t="inlineStr"/>
+      <c r="O218" s="12" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P218" s="12" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q218" s="12" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -15389,19 +14467,18 @@
       <c r="J219" s="25" t="inlineStr"/>
       <c r="K219" s="12" t="inlineStr"/>
       <c r="L219" s="12" t="inlineStr"/>
-      <c r="M219" s="12" t="inlineStr"/>
-      <c r="N219" s="12" t="inlineStr">
+      <c r="M219" s="12" t="inlineStr">
         <is>
           <t>цена отдельно</t>
         </is>
       </c>
-      <c r="O219" s="12" t="inlineStr"/>
+      <c r="N219" s="12" t="inlineStr"/>
+      <c r="O219" s="12" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P219" s="12" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q219" s="12" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -15428,7 +14505,6 @@
       <c r="N220" s="23" t="n"/>
       <c r="O220" s="23" t="n"/>
       <c r="P220" s="23" t="n"/>
-      <c r="Q220" s="23" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="18" t="n">
@@ -15482,18 +14558,13 @@
           <t>2 794</t>
         </is>
       </c>
-      <c r="N221" s="4" t="inlineStr">
-        <is>
-          <t>2 794</t>
-        </is>
-      </c>
-      <c r="O221" s="4" t="inlineStr"/>
+      <c r="N221" s="4" t="inlineStr"/>
+      <c r="O221" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P221" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q221" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -15520,7 +14591,6 @@
       <c r="N222" s="23" t="n"/>
       <c r="O222" s="23" t="n"/>
       <c r="P222" s="23" t="n"/>
-      <c r="Q222" s="23" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="18" t="n">
@@ -15566,18 +14636,13 @@
           <t>7 450</t>
         </is>
       </c>
-      <c r="N223" s="4" t="inlineStr">
-        <is>
-          <t>7 450</t>
-        </is>
-      </c>
-      <c r="O223" s="4" t="inlineStr"/>
+      <c r="N223" s="4" t="inlineStr"/>
+      <c r="O223" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P223" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q223" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -15604,7 +14669,6 @@
       <c r="N224" s="23" t="n"/>
       <c r="O224" s="23" t="n"/>
       <c r="P224" s="23" t="n"/>
-      <c r="Q224" s="23" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="24" t="n">
@@ -15640,28 +14704,19 @@
       </c>
       <c r="J225" s="24" t="inlineStr"/>
       <c r="K225" s="14" t="inlineStr"/>
-      <c r="L225" s="14" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
+      <c r="L225" s="14" t="inlineStr"/>
       <c r="M225" s="14" t="inlineStr">
         <is>
-          <t>3 055</t>
-        </is>
-      </c>
-      <c r="N225" s="14" t="inlineStr">
-        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O225" s="14" t="inlineStr"/>
+      <c r="N225" s="14" t="inlineStr"/>
+      <c r="O225" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P225" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q225" s="14" t="inlineStr">
         <is>
           <t>алюминий</t>
         </is>
@@ -15701,28 +14756,19 @@
       </c>
       <c r="J226" s="24" t="inlineStr"/>
       <c r="K226" s="14" t="inlineStr"/>
-      <c r="L226" s="14" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
+      <c r="L226" s="14" t="inlineStr"/>
       <c r="M226" s="14" t="inlineStr">
         <is>
-          <t>2 470</t>
-        </is>
-      </c>
-      <c r="N226" s="14" t="inlineStr">
-        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O226" s="14" t="inlineStr"/>
+      <c r="N226" s="14" t="inlineStr"/>
+      <c r="O226" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P226" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q226" s="14" t="inlineStr">
         <is>
           <t>алюминий</t>
         </is>
@@ -15762,28 +14808,19 @@
       </c>
       <c r="J227" s="24" t="inlineStr"/>
       <c r="K227" s="14" t="inlineStr"/>
-      <c r="L227" s="14" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
+      <c r="L227" s="14" t="inlineStr"/>
       <c r="M227" s="14" t="inlineStr">
         <is>
-          <t>1 885</t>
-        </is>
-      </c>
-      <c r="N227" s="14" t="inlineStr">
-        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O227" s="14" t="inlineStr"/>
+      <c r="N227" s="14" t="inlineStr"/>
+      <c r="O227" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P227" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q227" s="14" t="inlineStr">
         <is>
           <t>алюминий</t>
         </is>
@@ -15823,28 +14860,19 @@
       </c>
       <c r="J228" s="24" t="inlineStr"/>
       <c r="K228" s="14" t="inlineStr"/>
-      <c r="L228" s="14" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
+      <c r="L228" s="14" t="inlineStr"/>
       <c r="M228" s="14" t="inlineStr">
         <is>
-          <t>1 755</t>
-        </is>
-      </c>
-      <c r="N228" s="14" t="inlineStr">
-        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O228" s="14" t="inlineStr"/>
+      <c r="N228" s="14" t="inlineStr"/>
+      <c r="O228" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P228" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q228" s="14" t="inlineStr">
         <is>
           <t>алюминий</t>
         </is>
@@ -15894,18 +14922,13 @@
           <t>33 898</t>
         </is>
       </c>
-      <c r="N229" s="4" t="inlineStr">
-        <is>
-          <t>33 898</t>
-        </is>
-      </c>
-      <c r="O229" s="4" t="inlineStr"/>
+      <c r="N229" s="4" t="inlineStr"/>
+      <c r="O229" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P229" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q229" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -15955,18 +14978,13 @@
           <t>20 860</t>
         </is>
       </c>
-      <c r="N230" s="4" t="inlineStr">
-        <is>
-          <t>20 860</t>
-        </is>
-      </c>
-      <c r="O230" s="4" t="inlineStr"/>
+      <c r="N230" s="4" t="inlineStr"/>
+      <c r="O230" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P230" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q230" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -16016,18 +15034,13 @@
           <t>2 794</t>
         </is>
       </c>
-      <c r="N231" s="4" t="inlineStr">
-        <is>
-          <t>2 794</t>
-        </is>
-      </c>
-      <c r="O231" s="4" t="inlineStr"/>
+      <c r="N231" s="4" t="inlineStr"/>
+      <c r="O231" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P231" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q231" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -16077,18 +15090,13 @@
           <t>2 980</t>
         </is>
       </c>
-      <c r="N232" s="4" t="inlineStr">
-        <is>
-          <t>2 980</t>
-        </is>
-      </c>
-      <c r="O232" s="4" t="inlineStr"/>
+      <c r="N232" s="4" t="inlineStr"/>
+      <c r="O232" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P232" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q232" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -16115,7 +15123,6 @@
       <c r="N233" s="23" t="n"/>
       <c r="O233" s="23" t="n"/>
       <c r="P233" s="23" t="n"/>
-      <c r="Q233" s="23" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="18" t="n">
@@ -16161,18 +15168,13 @@
           <t>20 115</t>
         </is>
       </c>
-      <c r="N234" s="4" t="inlineStr">
-        <is>
-          <t>20 115</t>
-        </is>
-      </c>
-      <c r="O234" s="4" t="inlineStr"/>
+      <c r="N234" s="4" t="inlineStr"/>
+      <c r="O234" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P234" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q234" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -16222,18 +15224,13 @@
           <t>25 144</t>
         </is>
       </c>
-      <c r="N235" s="4" t="inlineStr">
-        <is>
-          <t>25 144</t>
-        </is>
-      </c>
-      <c r="O235" s="4" t="inlineStr"/>
+      <c r="N235" s="4" t="inlineStr"/>
+      <c r="O235" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P235" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q235" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -16281,18 +15278,13 @@
           <t>6 332</t>
         </is>
       </c>
-      <c r="N236" s="4" t="inlineStr">
-        <is>
-          <t>6 332</t>
-        </is>
-      </c>
-      <c r="O236" s="4" t="inlineStr"/>
+      <c r="N236" s="4" t="inlineStr"/>
+      <c r="O236" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P236" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q236" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -16319,7 +15311,6 @@
       <c r="N237" s="23" t="n"/>
       <c r="O237" s="23" t="n"/>
       <c r="P237" s="23" t="n"/>
-      <c r="Q237" s="23" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="24" t="n">
@@ -16360,19 +15351,18 @@
       <c r="J238" s="24" t="inlineStr"/>
       <c r="K238" s="14" t="inlineStr"/>
       <c r="L238" s="14" t="inlineStr"/>
-      <c r="M238" s="14" t="inlineStr"/>
-      <c r="N238" s="14" t="inlineStr">
+      <c r="M238" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O238" s="14" t="inlineStr"/>
+      <c r="N238" s="14" t="inlineStr"/>
+      <c r="O238" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P238" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q238" s="14" t="inlineStr">
         <is>
           <t>сталь</t>
         </is>
@@ -16419,19 +15409,18 @@
       </c>
       <c r="K239" s="14" t="inlineStr"/>
       <c r="L239" s="14" t="inlineStr"/>
-      <c r="M239" s="14" t="inlineStr"/>
-      <c r="N239" s="14" t="inlineStr">
+      <c r="M239" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O239" s="14" t="inlineStr"/>
+      <c r="N239" s="14" t="inlineStr"/>
+      <c r="O239" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P239" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q239" s="14" t="inlineStr">
         <is>
           <t>сталь</t>
         </is>
@@ -16478,19 +15467,18 @@
       </c>
       <c r="K240" s="14" t="inlineStr"/>
       <c r="L240" s="14" t="inlineStr"/>
-      <c r="M240" s="14" t="inlineStr"/>
-      <c r="N240" s="14" t="inlineStr">
+      <c r="M240" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O240" s="14" t="inlineStr"/>
+      <c r="N240" s="14" t="inlineStr"/>
+      <c r="O240" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P240" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q240" s="14" t="inlineStr">
         <is>
           <t>сталь</t>
         </is>
@@ -16517,7 +15505,6 @@
       <c r="N241" s="23" t="n"/>
       <c r="O241" s="23" t="n"/>
       <c r="P241" s="23" t="n"/>
-      <c r="Q241" s="23" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="24" t="n">
@@ -16554,19 +15541,18 @@
       <c r="J242" s="24" t="inlineStr"/>
       <c r="K242" s="14" t="inlineStr"/>
       <c r="L242" s="14" t="inlineStr"/>
-      <c r="M242" s="14" t="inlineStr"/>
-      <c r="N242" s="14" t="inlineStr">
+      <c r="M242" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O242" s="14" t="inlineStr"/>
+      <c r="N242" s="14" t="inlineStr"/>
+      <c r="O242" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="P242" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q242" s="14" t="inlineStr">
         <is>
           <t>сталь</t>
         </is>
@@ -16593,7 +15579,6 @@
       <c r="N243" s="23" t="n"/>
       <c r="O243" s="23" t="n"/>
       <c r="P243" s="23" t="n"/>
-      <c r="Q243" s="23" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="24" t="n">
@@ -16630,23 +15615,22 @@
       <c r="J244" s="24" t="inlineStr"/>
       <c r="K244" s="14" t="inlineStr"/>
       <c r="L244" s="14" t="inlineStr"/>
-      <c r="M244" s="14" t="inlineStr"/>
+      <c r="M244" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="N244" s="14" t="inlineStr">
         <is>
+          <t>6 000</t>
+        </is>
+      </c>
+      <c r="O244" s="14" t="inlineStr">
+        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O244" s="14" t="inlineStr">
-        <is>
-          <t>6 000</t>
-        </is>
-      </c>
       <c r="P244" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q244" s="14" t="inlineStr">
         <is>
           <t>сталь</t>
         </is>
@@ -16687,23 +15671,22 @@
       <c r="J245" s="24" t="inlineStr"/>
       <c r="K245" s="14" t="inlineStr"/>
       <c r="L245" s="14" t="inlineStr"/>
-      <c r="M245" s="14" t="inlineStr"/>
+      <c r="M245" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="N245" s="14" t="inlineStr">
         <is>
+          <t>4 500</t>
+        </is>
+      </c>
+      <c r="O245" s="14" t="inlineStr">
+        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="O245" s="14" t="inlineStr">
-        <is>
-          <t>4 500</t>
-        </is>
-      </c>
       <c r="P245" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="Q245" s="14" t="inlineStr">
         <is>
           <t>сталь</t>
         </is>
@@ -16730,7 +15713,6 @@
       <c r="N246" s="23" t="n"/>
       <c r="O246" s="23" t="n"/>
       <c r="P246" s="23" t="n"/>
-      <c r="Q246" s="23" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="18" t="n">
@@ -16775,19 +15757,18 @@
         </is>
       </c>
       <c r="L247" s="4" t="inlineStr"/>
-      <c r="M247" s="4" t="inlineStr"/>
-      <c r="N247" s="4" t="inlineStr">
+      <c r="M247" s="4" t="inlineStr">
         <is>
           <t>55 000</t>
         </is>
       </c>
-      <c r="O247" s="4" t="inlineStr"/>
+      <c r="N247" s="4" t="inlineStr"/>
+      <c r="O247" s="4" t="inlineStr">
+        <is>
+          <t>140 000</t>
+        </is>
+      </c>
       <c r="P247" s="4" t="inlineStr">
-        <is>
-          <t>140 000</t>
-        </is>
-      </c>
-      <c r="Q247" s="4" t="inlineStr">
         <is>
           <t>титан</t>
         </is>
@@ -16836,54 +15817,53 @@
         </is>
       </c>
       <c r="L248" s="4" t="inlineStr"/>
-      <c r="M248" s="4" t="inlineStr"/>
-      <c r="N248" s="4" t="inlineStr">
+      <c r="M248" s="4" t="inlineStr">
         <is>
           <t>35 000</t>
         </is>
       </c>
-      <c r="O248" s="4" t="inlineStr"/>
+      <c r="N248" s="4" t="inlineStr"/>
+      <c r="O248" s="4" t="inlineStr">
+        <is>
+          <t>100 000</t>
+        </is>
+      </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>100 000</t>
-        </is>
-      </c>
-      <c r="Q248" s="4" t="inlineStr">
-        <is>
           <t>титан</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Q248"/>
+  <autoFilter ref="A4:P248"/>
   <mergeCells count="27">
-    <mergeCell ref="A220:Q220"/>
-    <mergeCell ref="A92:Q92"/>
-    <mergeCell ref="A186:Q186"/>
-    <mergeCell ref="A222:Q222"/>
-    <mergeCell ref="A49:Q49"/>
-    <mergeCell ref="A103:Q103"/>
-    <mergeCell ref="A132:Q132"/>
-    <mergeCell ref="A241:Q241"/>
-    <mergeCell ref="A168:Q168"/>
-    <mergeCell ref="A197:Q197"/>
-    <mergeCell ref="A237:Q237"/>
-    <mergeCell ref="A87:Q87"/>
-    <mergeCell ref="A205:Q205"/>
-    <mergeCell ref="A243:Q243"/>
-    <mergeCell ref="A118:Q118"/>
-    <mergeCell ref="A246:Q246"/>
-    <mergeCell ref="A233:Q233"/>
-    <mergeCell ref="A136:Q136"/>
-    <mergeCell ref="A57:Q57"/>
-    <mergeCell ref="A210:Q210"/>
-    <mergeCell ref="A5:Q5"/>
-    <mergeCell ref="A17:Q17"/>
-    <mergeCell ref="A126:Q126"/>
-    <mergeCell ref="A200:Q200"/>
-    <mergeCell ref="A224:Q224"/>
-    <mergeCell ref="A134:Q134"/>
-    <mergeCell ref="A112:Q112"/>
+    <mergeCell ref="A5:P5"/>
+    <mergeCell ref="A17:P17"/>
+    <mergeCell ref="A126:P126"/>
+    <mergeCell ref="A200:P200"/>
+    <mergeCell ref="A224:P224"/>
+    <mergeCell ref="A134:P134"/>
+    <mergeCell ref="A112:P112"/>
+    <mergeCell ref="A220:P220"/>
+    <mergeCell ref="A92:P92"/>
+    <mergeCell ref="A186:P186"/>
+    <mergeCell ref="A49:P49"/>
+    <mergeCell ref="A103:P103"/>
+    <mergeCell ref="A222:P222"/>
+    <mergeCell ref="A132:P132"/>
+    <mergeCell ref="A197:P197"/>
+    <mergeCell ref="A241:P241"/>
+    <mergeCell ref="A168:P168"/>
+    <mergeCell ref="A237:P237"/>
+    <mergeCell ref="A205:P205"/>
+    <mergeCell ref="A87:P87"/>
+    <mergeCell ref="A243:P243"/>
+    <mergeCell ref="A246:P246"/>
+    <mergeCell ref="A118:P118"/>
+    <mergeCell ref="A233:P233"/>
+    <mergeCell ref="A136:P136"/>
+    <mergeCell ref="A210:P210"/>
+    <mergeCell ref="A57:P57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
@@ -16896,32 +15876,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Закупочная цена: лом, умноженный на 2,5</t>
+          <t>Три цены: закуп, ремонт, реализация</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Договоренность с Антоном Бурыкиным от 25.10.2026. Цены приемки на 13.10.2026. По бронзе 745 * 2,5 = 1 862,50 руб за кг — это и есть ставка, по которой посчитана вся бронза в спецификации. Оранжевым — то, что от металла не считается.</t>
+          <t>Закуп по Договору — по этой цене мы продаем арматуру ПКФ «АРМА». Дальше компания приводит товар в порядок и при необходимости ремонтирует, ремонт считается по прайсу мастерской. Потом мы вместе с ней продаем арматуру конечному покупателю — это цена реализации. Оранжевым — то, у чего закуп от металла не считается.</t>
         </is>
       </c>
     </row>
@@ -16958,22 +15938,22 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Закуп, руб за кг</t>
+          <t>Ставка закупа, руб за кг</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Закуп, руб</t>
+          <t>1. ЗАКУП по Договору, руб</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>По Договору, руб</t>
+          <t>2. Ремонт, руб</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Разница, руб</t>
+          <t>3. Реализация, руб</t>
         </is>
       </c>
     </row>
@@ -17000,33 +15980,33 @@
           <t>2,5</t>
         </is>
       </c>
-      <c r="G5" s="19" t="n">
+      <c r="G5" s="5" t="n">
         <v>1862.5</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>33236126</v>
+        <v>33386124</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>33386124</v>
+        <v>2946000</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>149998</v>
+        <v>54398000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>цена не от металла</t>
+          <t>высокое давление, Ру от 100</t>
         </is>
       </c>
       <c r="B6" s="24" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>237</v>
+        <v>206</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>1183</v>
+        <v>633</v>
       </c>
       <c r="E6" s="26" t="inlineStr">
         <is>
@@ -17038,354 +16018,575 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>цену согласовываем</t>
+        </is>
+      </c>
+      <c r="H6" s="26" t="n">
+        <v>858500</v>
+      </c>
+      <c r="I6" s="26" t="n">
+        <v>310500</v>
+      </c>
+      <c r="J6" s="26" t="n">
+        <v>2581000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>редукционный, цена в редукторе</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>259</v>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H6" s="26" t="inlineStr">
+      <c r="F7" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I6" s="26" t="n">
-        <v>1433500</v>
-      </c>
-      <c r="J6" s="26" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>цену согласовываем</t>
+        </is>
+      </c>
+      <c r="H7" s="26" t="n">
+        <v>345000</v>
+      </c>
+      <c r="I7" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>алюминий</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="n">
+      <c r="J7" s="26" t="n">
+        <v>1170000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>сталь, цена не от массы металла</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>140</v>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>цену согласовываем</t>
+        </is>
+      </c>
+      <c r="H8" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="26" t="n">
+        <v>10500</v>
+      </c>
+      <c r="J8" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>электромагнитный, цена в приводе и катушке</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>123</v>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>цену согласовываем</t>
+        </is>
+      </c>
+      <c r="H9" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="26" t="n">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>алюминий, цена не от массы металла</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C10" s="24" t="n">
         <v>17</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D10" s="26" t="n">
         <v>61</v>
       </c>
-      <c r="E7" s="19" t="n">
-        <v>260</v>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>2,5</t>
-        </is>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>650</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>39975</v>
-      </c>
-      <c r="I7" s="19" t="inlineStr">
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="19" t="inlineStr">
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>цену согласовываем</t>
+        </is>
+      </c>
+      <c r="H10" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>титан, цена не от массы металла</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>28</v>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>цену согласовываем</t>
+        </is>
+      </c>
+      <c r="H11" s="26" t="n">
+        <v>230000</v>
+      </c>
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" s="26" t="n">
+        <v>640000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B12" s="20" t="n">
         <v>217</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C12" s="20" t="n">
         <v>1773</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D12" s="21" t="n">
         <v>19091</v>
       </c>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="21" t="n">
-        <v>33276101</v>
-      </c>
-      <c r="I8" s="21" t="n">
+      <c r="E12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="21" t="n">
         <v>34819624</v>
       </c>
-      <c r="J8" s="21" t="n">
-        <v>1543523</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="I12" s="21" t="n">
+        <v>3267000</v>
+      </c>
+      <c r="J12" s="21" t="n">
+        <v>58844000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Откуда берется ставка закупа</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>— Закупочная цена = цена металлолома * 2,5. Договоренность с Антоном Бурыкиным от 25.10.2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>— Бронза: 745 * 2,5 = 1 862,50 руб за килограмм. Это и есть ставка, по которой посчитана вся бронза в спецификации.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>— Уточнится вес при замере — цена пересчитается сама. Поменяет приемка цены — пересчитается и ставка.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Прайс приемки на 13.10.2026</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Металл</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Лом, руб за кг</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Закуп, руб за кг</t>
         </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>нихром</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="n">
-        <v>1342</v>
-      </c>
-      <c r="C12" s="19" t="n">
-        <v>3355</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>медь</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="n">
-        <v>945</v>
-      </c>
-      <c r="C13" s="19" t="n">
-        <v>2362.5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>бронза</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="n">
-        <v>745</v>
-      </c>
-      <c r="C14" s="19" t="n">
-        <v>1862.5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>латунь</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="n">
-        <v>635</v>
-      </c>
-      <c r="C15" s="19" t="n">
-        <v>1587.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>алюминий</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="n">
-        <v>260</v>
-      </c>
-      <c r="C16" s="19" t="n">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>титан</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="n">
-        <v>130</v>
-      </c>
-      <c r="C17" s="19" t="n">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>цам</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="n">
-        <v>130</v>
-      </c>
-      <c r="C18" s="19" t="n">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>свинец</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="n">
-        <v>70</v>
-      </c>
-      <c r="C19" s="19" t="n">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>нержавейка</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="n">
-        <v>60</v>
-      </c>
-      <c r="C20" s="19" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>аккумуляторы</t>
+          <t>нихром</t>
         </is>
       </c>
       <c r="B21" s="19" t="n">
-        <v>35</v>
+        <v>1342</v>
       </c>
       <c r="C21" s="19" t="n">
-        <v>87.5</v>
+        <v>3355</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>трансформаторы</t>
+          <t>медь</t>
         </is>
       </c>
       <c r="B22" s="19" t="n">
-        <v>20</v>
+        <v>945</v>
       </c>
       <c r="C22" s="19" t="n">
-        <v>50</v>
+        <v>2362.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>черный металл</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="B23" s="19" t="n">
-        <v>19</v>
+        <v>745</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>47.5</v>
+        <v>1862.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>чугун</t>
+          <t>латунь</t>
         </is>
       </c>
       <c r="B24" s="19" t="n">
-        <v>19</v>
+        <v>635</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>47.5</v>
+        <v>1587.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>сталь</t>
+          <t>алюминий</t>
         </is>
       </c>
       <c r="B25" s="19" t="n">
-        <v>19</v>
+        <v>260</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>47.5</v>
+        <v>650</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
+          <t>титан</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>130</v>
+      </c>
+      <c r="C26" s="19" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>цам</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="n">
+        <v>130</v>
+      </c>
+      <c r="C27" s="19" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>свинец</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="n">
+        <v>70</v>
+      </c>
+      <c r="C28" s="19" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>нержавейка</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="C29" s="19" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>аккумуляторы</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="n">
+        <v>35</v>
+      </c>
+      <c r="C30" s="19" t="n">
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>трансформаторы</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="C31" s="19" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>черный металл</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="n">
+        <v>19</v>
+      </c>
+      <c r="C32" s="19" t="n">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>чугун</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="n">
+        <v>19</v>
+      </c>
+      <c r="C33" s="19" t="n">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>сталь</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="n">
+        <v>19</v>
+      </c>
+      <c r="C34" s="19" t="n">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
           <t>электродвигатели</t>
         </is>
       </c>
-      <c r="B26" s="19" t="n">
+      <c r="B35" s="19" t="n">
         <v>15</v>
       </c>
-      <c r="C26" s="19" t="n">
+      <c r="C35" s="19" t="n">
         <v>37.5</v>
       </c>
     </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="17" t="inlineStr">
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>— Лом — это нижняя граница цены. Любая позиция стоит хотя бы как металл, и ниже продавать незачем: сдать быстрее и без споров по состоянию.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="17" t="inlineStr">
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>— Вся арматура бронзовая, 745 руб за кг: на море ставят бронзу, латунь идет на реки. Из этого и выходит ставка 1 862,50.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>— Сталь и титан от лома не считаем вовсе: множитель дал бы по стали 47,50 руб за кг, а у конкурента стальная задвижка Ду200 стоит 40 000 руб. Цену по ним согласовываем отдельно.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="17" t="inlineStr">
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>— Сталь, титан, алюминий и нержавейка от лома не считаются вовсе: множитель дал бы по стали 47,50 руб за кг, а у конкурента стальная задвижка Ду200 стоит 40 000 руб. Цену по ним согласовываем отдельно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>— Так же не считаются электромагнитные и редукционные клапаны и клапаны на высокое давление Ру от 100: корпус у них та же бронза, но платят не за нее.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="17" t="inlineStr">
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>— Ремонт в цену закупа не входит — это следующий шаг цепочки, его делает компания после покупки. Новое не ремонтируем.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>— Реализация — ориентир, а не согласованная цена: по пункту 3.2 Договора конкретную цену согласуют письменно до передачи товара конечному покупателю.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>— Если приемка поменяет цены, пересчитывается и ставка: она считается из прайса, а не вписана руками.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A32:J32"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="A28:J28"/>
+  <mergeCells count="10">
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A43:J43"/>
+    <mergeCell ref="A38:J38"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A42:J42"/>
+    <mergeCell ref="A41:J41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>

--- a/outputs/marine_equipment/Контейнер_погрузка.xlsx
+++ b/outputs/marine_equipment/Контейнер_погрузка.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Снято с отгрузки" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Перечень'!$A$4:$P$248</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Перечень'!$A$4:$O$248</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Перечень'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -940,7 +940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -952,7 +952,6 @@
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1015,11 +1014,6 @@
           <t>3. Реализация, руб</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Закуп, руб за кг</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -1053,9 +1047,6 @@
       <c r="I5" s="19" t="n">
         <v>18250000</v>
       </c>
-      <c r="J5" s="19" t="n">
-        <v>1863</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1089,9 +1080,6 @@
       <c r="I6" s="19" t="n">
         <v>7365000</v>
       </c>
-      <c r="J6" s="19" t="n">
-        <v>1863</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1125,9 +1113,6 @@
       <c r="I7" s="19" t="n">
         <v>3670000</v>
       </c>
-      <c r="J7" s="19" t="n">
-        <v>1863</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1161,9 +1146,6 @@
       <c r="I8" s="19" t="n">
         <v>3480000</v>
       </c>
-      <c r="J8" s="19" t="n">
-        <v>1986</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1197,9 +1179,6 @@
       <c r="I9" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="19" t="n">
-        <v>1858</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1233,9 +1212,6 @@
       <c r="I10" s="19" t="n">
         <v>4725000</v>
       </c>
-      <c r="J10" s="19" t="n">
-        <v>1863</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1269,9 +1245,6 @@
       <c r="I11" s="19" t="n">
         <v>540000</v>
       </c>
-      <c r="J11" s="19" t="n">
-        <v>1863</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1305,9 +1278,6 @@
       <c r="I12" s="19" t="n">
         <v>450000</v>
       </c>
-      <c r="J12" s="19" t="n">
-        <v>1874</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1341,9 +1311,6 @@
       <c r="I13" s="19" t="n">
         <v>2055000</v>
       </c>
-      <c r="J13" s="19" t="n">
-        <v>1859</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1377,9 +1344,6 @@
       <c r="I14" s="19" t="n">
         <v>85000</v>
       </c>
-      <c r="J14" s="19" t="n">
-        <v>2163</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1413,9 +1377,6 @@
       <c r="I15" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="19" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1449,9 +1410,6 @@
       <c r="I16" s="19" t="n">
         <v>160000</v>
       </c>
-      <c r="J16" s="19" t="n">
-        <v>1840</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1485,9 +1443,6 @@
       <c r="I17" s="19" t="n">
         <v>1738000</v>
       </c>
-      <c r="J17" s="19" t="n">
-        <v>1257</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1521,9 +1476,6 @@
       <c r="I18" s="19" t="n">
         <v>11224000</v>
       </c>
-      <c r="J18" s="19" t="n">
-        <v>1655</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1557,9 +1509,6 @@
       <c r="I19" s="19" t="n">
         <v>332000</v>
       </c>
-      <c r="J19" s="19" t="n">
-        <v>1870</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1593,9 +1542,6 @@
       <c r="I20" s="19" t="n">
         <v>1890000</v>
       </c>
-      <c r="J20" s="19" t="n">
-        <v>1860</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -1629,9 +1575,6 @@
       <c r="I21" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="19" t="n">
-        <v>1866</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -1665,9 +1608,6 @@
       <c r="I22" s="19" t="n">
         <v>1170000</v>
       </c>
-      <c r="J22" s="19" t="n">
-        <v>1332</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -1701,9 +1641,6 @@
       <c r="I23" s="19" t="n">
         <v>1070000</v>
       </c>
-      <c r="J23" s="19" t="n">
-        <v>1793</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -1737,9 +1674,6 @@
       <c r="I24" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="19" t="n">
-        <v>1863</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -1773,9 +1707,6 @@
       <c r="I25" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="19" t="n">
-        <v>1862</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -1809,9 +1740,6 @@
       <c r="I26" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="19" t="n">
-        <v>1580</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -1845,9 +1773,6 @@
       <c r="I27" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="19" t="n">
-        <v>1843</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -1881,9 +1806,6 @@
       <c r="I28" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="19" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -1917,9 +1839,6 @@
       <c r="I29" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="19" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -1953,9 +1872,6 @@
       <c r="I30" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="19" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -1989,9 +1905,6 @@
       <c r="I31" s="19" t="n">
         <v>640000</v>
       </c>
-      <c r="J31" s="19" t="n">
-        <v>8214</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -2024,9 +1937,6 @@
       </c>
       <c r="I32" s="21" t="n">
         <v>58844000</v>
-      </c>
-      <c r="J32" s="21" t="n">
-        <v>1824</v>
       </c>
     </row>
   </sheetData>
@@ -2041,7 +1951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P248"/>
+  <dimension ref="A1:O248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2055,11 +1965,10 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2134,25 +2043,20 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Ставка закупа, руб за кг</t>
+          <t>1. ЗАКУП по Договору за ед., руб</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1. ЗАКУП по Договору за ед., руб</t>
+          <t>2. Ремонт за ед., руб</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>2. Ремонт за ед., руб</t>
+          <t>3. Реализация за ед., руб</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>3. Реализация за ед., руб</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>Материал</t>
         </is>
@@ -2178,7 +2082,6 @@
       <c r="M5" s="23" t="n"/>
       <c r="N5" s="23" t="n"/>
       <c r="O5" s="23" t="n"/>
-      <c r="P5" s="23" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="18" t="n">
@@ -2222,25 +2125,20 @@
       <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>395 781</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>395 781</t>
+          <t>30 000</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>30 000</t>
+          <t>900 000</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>900 000</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -2288,25 +2186,20 @@
       <c r="K7" s="4" t="inlineStr"/>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>357 600</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>357 600</t>
+          <t>28 000</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>28 000</t>
+          <t>550 000</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>550 000</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -2352,25 +2245,20 @@
       <c r="K8" s="4" t="inlineStr"/>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>357 600</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>357 600</t>
+          <t>28 000</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>28 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -2418,25 +2306,20 @@
       <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>232 812</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>232 812</t>
+          <t>25 000</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>25 000</t>
+          <t>400 000</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t>400 000</t>
-        </is>
-      </c>
-      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -2482,25 +2365,20 @@
       <c r="K10" s="4" t="inlineStr"/>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>186 250</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>186 250</t>
+          <t>25 000</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>25 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -2548,25 +2426,20 @@
       <c r="K11" s="4" t="inlineStr"/>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>142 481</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>142 481</t>
+          <t>20 000</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>20 000</t>
+          <t>210 000</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t>210 000</t>
-        </is>
-      </c>
-      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -2614,25 +2487,20 @@
       <c r="K12" s="4" t="inlineStr"/>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>69 285</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>69 285</t>
+          <t>15 000</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>15 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P12" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -2680,25 +2548,20 @@
       <c r="K13" s="4" t="inlineStr"/>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>52 709</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>52 709</t>
+          <t>12 000</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>12 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P13" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -2746,25 +2609,20 @@
       <c r="K14" s="4" t="inlineStr"/>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>40 789</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>40 789</t>
+          <t>10 000</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>10 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P14" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -2810,25 +2668,20 @@
       <c r="K15" s="4" t="inlineStr"/>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>22 722</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>22 722</t>
+          <t>8 500</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>8 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P15" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -2874,25 +2727,20 @@
       <c r="K16" s="4" t="inlineStr"/>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>15 831</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>15 831</t>
+          <t>7 500</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>7 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P16" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -2918,7 +2766,6 @@
       <c r="M17" s="23" t="n"/>
       <c r="N17" s="23" t="n"/>
       <c r="O17" s="23" t="n"/>
-      <c r="P17" s="23" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="18" t="n">
@@ -2958,25 +2805,20 @@
       <c r="K18" s="4" t="inlineStr"/>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>204 875</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>204 875</t>
+          <t>12 000</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>12 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P18" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3020,25 +2862,20 @@
       <c r="K19" s="4" t="inlineStr"/>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>204 875</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>204 875</t>
+          <t>12 000</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>12 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3084,25 +2921,20 @@
       <c r="K20" s="4" t="inlineStr"/>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>85 675</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>85 675</t>
+          <t>7 000</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>7 000</t>
+          <t>140 000</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
-        <is>
-          <t>140 000</t>
-        </is>
-      </c>
-      <c r="P20" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3148,25 +2980,20 @@
       <c r="K21" s="4" t="inlineStr"/>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>84 744</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>84 744</t>
+          <t>7 000</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>7 000</t>
+          <t>140 000</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
-        <is>
-          <t>140 000</t>
-        </is>
-      </c>
-      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3212,25 +3039,20 @@
       <c r="K22" s="4" t="inlineStr"/>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>111 750</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>111 750</t>
+          <t>7 000</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>7 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P22" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3276,25 +3098,20 @@
       <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>85 675</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>85 675</t>
+          <t>7 000</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>7 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P23" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3336,25 +3153,20 @@
       <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>54 012</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>54 012</t>
+          <t>6 500</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>6 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P24" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3396,21 +3208,16 @@
       <c r="K25" s="4" t="inlineStr"/>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
           <t>53 640</t>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr"/>
+      <c r="M25" s="4" t="inlineStr"/>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O25" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P25" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3452,21 +3259,16 @@
       <c r="K26" s="4" t="inlineStr"/>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
-        <is>
           <t>53 640</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr"/>
+      <c r="M26" s="4" t="inlineStr"/>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O26" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P26" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3508,21 +3310,16 @@
       <c r="K27" s="4" t="inlineStr"/>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
-        <is>
           <t>33 152</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr"/>
+      <c r="M27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>55 000</t>
+        </is>
+      </c>
       <c r="O27" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="P27" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3568,25 +3365,20 @@
       <c r="K28" s="4" t="inlineStr"/>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>26 075</t>
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>26 075</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="P28" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3632,25 +3424,20 @@
       <c r="K29" s="4" t="inlineStr"/>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>21 046</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>21 046</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="P29" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3696,25 +3483,20 @@
       <c r="K30" s="4" t="inlineStr"/>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>22 164</t>
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>22 164</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="P30" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3760,25 +3542,20 @@
       <c r="K31" s="4" t="inlineStr"/>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>23 281</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>23 281</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="P31" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3820,25 +3597,20 @@
       <c r="K32" s="4" t="inlineStr"/>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>22 350</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>22 350</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="P32" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3884,25 +3656,20 @@
       <c r="K33" s="4" t="inlineStr"/>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>35 388</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>35 388</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="P33" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -3948,25 +3715,20 @@
       <c r="K34" s="4" t="inlineStr"/>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>22 350</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>22 350</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="P34" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4008,25 +3770,20 @@
       <c r="K35" s="4" t="inlineStr"/>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>22 350</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>22 350</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="P35" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4072,25 +3829,20 @@
       <c r="K36" s="4" t="inlineStr"/>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>25 889</t>
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>25 889</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="P36" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4136,25 +3888,20 @@
       <c r="K37" s="4" t="inlineStr"/>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>22 350</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>22 350</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="P37" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4200,25 +3947,20 @@
       <c r="K38" s="4" t="inlineStr"/>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>23 095</t>
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>23 095</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="P38" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4260,25 +4002,20 @@
       <c r="K39" s="4" t="inlineStr"/>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>22 350</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>22 350</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="P39" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4320,25 +4057,20 @@
       <c r="K40" s="4" t="inlineStr"/>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>22 350</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>22 350</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="O40" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="P40" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4380,25 +4112,20 @@
       <c r="K41" s="4" t="inlineStr"/>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>22 350</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>22 350</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="P41" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4440,25 +4167,20 @@
       <c r="K42" s="4" t="inlineStr"/>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>22 350</t>
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>22 350</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="O42" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="P42" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4502,25 +4224,20 @@
       <c r="K43" s="4" t="inlineStr"/>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>22 350</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>22 350</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>55 000</t>
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="P43" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4566,25 +4283,20 @@
       <c r="K44" s="4" t="inlineStr"/>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>21 419</t>
         </is>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>21 419</t>
+          <t>5 000</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>5 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O44" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P44" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4626,25 +4338,20 @@
       <c r="K45" s="4" t="inlineStr"/>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>41 906</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>41 906</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P45" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4686,25 +4393,20 @@
       <c r="K46" s="4" t="inlineStr"/>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>67 050</t>
         </is>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>67 050</t>
+          <t>6 500</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>6 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O46" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P46" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4752,25 +4454,20 @@
       <c r="K47" s="4" t="inlineStr"/>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>9 871</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>9 871</t>
+          <t>4 500</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>4 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P47" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4818,25 +4515,20 @@
       <c r="K48" s="4" t="inlineStr"/>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>10 244</t>
         </is>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>10 244</t>
+          <t>4 500</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>4 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O48" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P48" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4862,7 +4554,6 @@
       <c r="M49" s="23" t="n"/>
       <c r="N49" s="23" t="n"/>
       <c r="O49" s="23" t="n"/>
-      <c r="P49" s="23" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="18" t="n">
@@ -4900,21 +4591,16 @@
       <c r="K50" s="4" t="inlineStr"/>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M50" s="4" t="inlineStr">
-        <is>
           <t>276 581</t>
         </is>
       </c>
-      <c r="N50" s="4" t="inlineStr"/>
+      <c r="M50" s="4" t="inlineStr"/>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>320 000</t>
+        </is>
+      </c>
       <c r="O50" s="4" t="inlineStr">
-        <is>
-          <t>320 000</t>
-        </is>
-      </c>
-      <c r="P50" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -4956,21 +4642,16 @@
       <c r="K51" s="4" t="inlineStr"/>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M51" s="4" t="inlineStr">
-        <is>
           <t>119 200</t>
         </is>
       </c>
-      <c r="N51" s="4" t="inlineStr"/>
+      <c r="M51" s="4" t="inlineStr"/>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>190 000</t>
+        </is>
+      </c>
       <c r="O51" s="4" t="inlineStr">
-        <is>
-          <t>190 000</t>
-        </is>
-      </c>
-      <c r="P51" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5012,21 +4693,16 @@
       <c r="K52" s="4" t="inlineStr"/>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M52" s="4" t="inlineStr">
-        <is>
           <t>78 225</t>
         </is>
       </c>
-      <c r="N52" s="4" t="inlineStr"/>
+      <c r="M52" s="4" t="inlineStr"/>
+      <c r="N52" s="4" t="inlineStr">
+        <is>
+          <t>160 000</t>
+        </is>
+      </c>
       <c r="O52" s="4" t="inlineStr">
-        <is>
-          <t>160 000</t>
-        </is>
-      </c>
-      <c r="P52" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5068,21 +4744,16 @@
       <c r="K53" s="4" t="inlineStr"/>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M53" s="4" t="inlineStr">
-        <is>
           <t>50 288</t>
         </is>
       </c>
-      <c r="N53" s="4" t="inlineStr"/>
+      <c r="M53" s="4" t="inlineStr"/>
+      <c r="N53" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O53" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P53" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5124,21 +4795,16 @@
       <c r="K54" s="4" t="inlineStr"/>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M54" s="4" t="inlineStr">
-        <is>
           <t>37 250</t>
         </is>
       </c>
-      <c r="N54" s="4" t="inlineStr"/>
+      <c r="M54" s="4" t="inlineStr"/>
+      <c r="N54" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O54" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P54" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5180,21 +4846,16 @@
       <c r="K55" s="4" t="inlineStr"/>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M55" s="4" t="inlineStr">
-        <is>
           <t>17 135</t>
         </is>
       </c>
-      <c r="N55" s="4" t="inlineStr"/>
+      <c r="M55" s="4" t="inlineStr"/>
+      <c r="N55" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O55" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P55" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5236,21 +4897,16 @@
       <c r="K56" s="4" t="inlineStr"/>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M56" s="4" t="inlineStr">
-        <is>
           <t>15 831</t>
         </is>
       </c>
-      <c r="N56" s="4" t="inlineStr"/>
+      <c r="M56" s="4" t="inlineStr"/>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O56" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P56" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5276,7 +4932,6 @@
       <c r="M57" s="23" t="n"/>
       <c r="N57" s="23" t="n"/>
       <c r="O57" s="23" t="n"/>
-      <c r="P57" s="23" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="18" t="n">
@@ -5314,25 +4969,20 @@
       <c r="K58" s="4" t="inlineStr"/>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>52 150</t>
         </is>
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>52 150</t>
+          <t>6 500</t>
         </is>
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>6 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O58" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P58" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5374,25 +5024,20 @@
       <c r="K59" s="4" t="inlineStr"/>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>52 150</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>52 150</t>
+          <t>6 500</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>6 500</t>
+          <t>70 000</t>
         </is>
       </c>
       <c r="O59" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="P59" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5434,25 +5079,20 @@
       <c r="K60" s="4" t="inlineStr"/>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>52 150</t>
         </is>
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>52 150</t>
+          <t>6 500</t>
         </is>
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>6 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O60" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P60" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5498,25 +5138,20 @@
       <c r="K61" s="4" t="inlineStr"/>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>65 932</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>65 932</t>
+          <t>6 500</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>6 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O61" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P61" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5562,25 +5197,20 @@
       <c r="K62" s="4" t="inlineStr"/>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>48 425</t>
         </is>
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>48 425</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>70 000</t>
         </is>
       </c>
       <c r="O62" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="P62" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5626,25 +5256,20 @@
       <c r="K63" s="4" t="inlineStr"/>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>41 906</t>
         </is>
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>41 906</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>70 000</t>
         </is>
       </c>
       <c r="O63" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="P63" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5686,25 +5311,20 @@
       <c r="K64" s="4" t="inlineStr"/>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>37 250</t>
         </is>
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
-          <t>37 250</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>70 000</t>
         </is>
       </c>
       <c r="O64" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="P64" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5750,25 +5370,20 @@
       <c r="K65" s="4" t="inlineStr"/>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>36 319</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>36 319</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>70 000</t>
         </is>
       </c>
       <c r="O65" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="P65" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5814,25 +5429,20 @@
       <c r="K66" s="4" t="inlineStr"/>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>30 000</t>
         </is>
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>30 000</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>70 000</t>
         </is>
       </c>
       <c r="O66" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="P66" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5874,25 +5484,20 @@
       <c r="K67" s="4" t="inlineStr"/>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>37 250</t>
         </is>
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>37 250</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>70 000</t>
         </is>
       </c>
       <c r="O67" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="P67" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5934,21 +5539,16 @@
       <c r="K68" s="4" t="inlineStr"/>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M68" s="4" t="inlineStr">
-        <is>
           <t>37 250</t>
         </is>
       </c>
-      <c r="N68" s="4" t="inlineStr"/>
+      <c r="M68" s="4" t="inlineStr"/>
+      <c r="N68" s="4" t="inlineStr">
+        <is>
+          <t>70 000</t>
+        </is>
+      </c>
       <c r="O68" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="P68" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5990,25 +5590,20 @@
       <c r="K69" s="4" t="inlineStr"/>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>37 250</t>
         </is>
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>37 250</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>70 000</t>
         </is>
       </c>
       <c r="O69" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="P69" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6050,21 +5645,16 @@
       <c r="K70" s="4" t="inlineStr"/>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M70" s="4" t="inlineStr">
-        <is>
           <t>37 250</t>
         </is>
       </c>
-      <c r="N70" s="4" t="inlineStr"/>
+      <c r="M70" s="4" t="inlineStr"/>
+      <c r="N70" s="4" t="inlineStr">
+        <is>
+          <t>70 000</t>
+        </is>
+      </c>
       <c r="O70" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="P70" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6110,25 +5700,20 @@
       <c r="K71" s="4" t="inlineStr"/>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>45 631</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr">
         <is>
-          <t>45 631</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>70 000</t>
         </is>
       </c>
       <c r="O71" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="P71" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6174,21 +5759,16 @@
       <c r="K72" s="4" t="inlineStr"/>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M72" s="4" t="inlineStr">
-        <is>
           <t>34 829</t>
         </is>
       </c>
-      <c r="N72" s="4" t="inlineStr"/>
+      <c r="M72" s="4" t="inlineStr"/>
+      <c r="N72" s="4" t="inlineStr">
+        <is>
+          <t>70 000</t>
+        </is>
+      </c>
       <c r="O72" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="P72" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6234,21 +5814,16 @@
       <c r="K73" s="4" t="inlineStr"/>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M73" s="4" t="inlineStr">
-        <is>
           <t>34 829</t>
         </is>
       </c>
-      <c r="N73" s="4" t="inlineStr"/>
+      <c r="M73" s="4" t="inlineStr"/>
+      <c r="N73" s="4" t="inlineStr">
+        <is>
+          <t>70 000</t>
+        </is>
+      </c>
       <c r="O73" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="P73" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6294,25 +5869,20 @@
       <c r="K74" s="4" t="inlineStr"/>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>34 829</t>
         </is>
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>34 829</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>70 000</t>
         </is>
       </c>
       <c r="O74" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="P74" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6358,21 +5928,16 @@
       <c r="K75" s="4" t="inlineStr"/>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M75" s="4" t="inlineStr">
-        <is>
           <t>47 494</t>
         </is>
       </c>
-      <c r="N75" s="4" t="inlineStr"/>
+      <c r="M75" s="4" t="inlineStr"/>
+      <c r="N75" s="4" t="inlineStr">
+        <is>
+          <t>70 000</t>
+        </is>
+      </c>
       <c r="O75" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="P75" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6414,25 +5979,20 @@
       <c r="K76" s="4" t="inlineStr"/>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>28 869</t>
         </is>
       </c>
       <c r="M76" s="4" t="inlineStr">
         <is>
-          <t>28 869</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O76" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P76" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6478,25 +6038,20 @@
       <c r="K77" s="4" t="inlineStr"/>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>29 800</t>
         </is>
       </c>
       <c r="M77" s="4" t="inlineStr">
         <is>
-          <t>29 800</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>65 000</t>
         </is>
       </c>
       <c r="O77" s="4" t="inlineStr">
-        <is>
-          <t>65 000</t>
-        </is>
-      </c>
-      <c r="P77" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6542,25 +6097,20 @@
       <c r="K78" s="4" t="inlineStr"/>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>31 662</t>
         </is>
       </c>
       <c r="M78" s="4" t="inlineStr">
         <is>
-          <t>31 662</t>
+          <t>6 000</t>
         </is>
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>6 000</t>
+          <t>65 000</t>
         </is>
       </c>
       <c r="O78" s="4" t="inlineStr">
-        <is>
-          <t>65 000</t>
-        </is>
-      </c>
-      <c r="P78" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6606,21 +6156,16 @@
       <c r="K79" s="4" t="inlineStr"/>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M79" s="4" t="inlineStr">
-        <is>
           <t>37 250</t>
         </is>
       </c>
-      <c r="N79" s="4" t="inlineStr"/>
+      <c r="M79" s="4" t="inlineStr"/>
+      <c r="N79" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O79" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P79" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6662,25 +6207,20 @@
       <c r="K80" s="4" t="inlineStr"/>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>20 488</t>
         </is>
       </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>20 488</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O80" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P80" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6726,25 +6266,20 @@
       <c r="K81" s="4" t="inlineStr"/>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>20 115</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>20 115</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O81" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P81" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6786,25 +6321,20 @@
       <c r="K82" s="4" t="inlineStr"/>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>20 488</t>
         </is>
       </c>
       <c r="M82" s="4" t="inlineStr">
         <is>
-          <t>20 488</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="N82" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O82" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P82" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6850,21 +6380,16 @@
       <c r="K83" s="4" t="inlineStr"/>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M83" s="4" t="inlineStr">
-        <is>
           <t>24 399</t>
         </is>
       </c>
-      <c r="N83" s="4" t="inlineStr"/>
+      <c r="M83" s="4" t="inlineStr"/>
+      <c r="N83" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O83" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P83" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6910,25 +6435,20 @@
       <c r="K84" s="4" t="inlineStr"/>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>10 430</t>
         </is>
       </c>
       <c r="M84" s="4" t="inlineStr">
         <is>
-          <t>10 430</t>
+          <t>5 000</t>
         </is>
       </c>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t>5 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O84" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P84" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6970,25 +6490,20 @@
       <c r="K85" s="4" t="inlineStr"/>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>10 244</t>
         </is>
       </c>
       <c r="M85" s="4" t="inlineStr">
         <is>
-          <t>10 244</t>
+          <t>4 500</t>
         </is>
       </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t>4 500</t>
+          <t>40 000</t>
         </is>
       </c>
       <c r="O85" s="4" t="inlineStr">
-        <is>
-          <t>40 000</t>
-        </is>
-      </c>
-      <c r="P85" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7030,25 +6545,20 @@
       <c r="K86" s="4" t="inlineStr"/>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>10 244</t>
         </is>
       </c>
       <c r="M86" s="4" t="inlineStr">
         <is>
-          <t>10 244</t>
+          <t>4 500</t>
         </is>
       </c>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>4 500</t>
+          <t>40 000</t>
         </is>
       </c>
       <c r="O86" s="4" t="inlineStr">
-        <is>
-          <t>40 000</t>
-        </is>
-      </c>
-      <c r="P86" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7074,7 +6584,6 @@
       <c r="M87" s="23" t="n"/>
       <c r="N87" s="23" t="n"/>
       <c r="O87" s="23" t="n"/>
-      <c r="P87" s="23" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="18" t="n">
@@ -7116,21 +6625,16 @@
       <c r="K88" s="4" t="inlineStr"/>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M88" s="4" t="inlineStr">
-        <is>
           <t>10 802</t>
         </is>
       </c>
-      <c r="N88" s="4" t="inlineStr"/>
+      <c r="M88" s="4" t="inlineStr"/>
+      <c r="N88" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O88" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P88" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7176,21 +6680,16 @@
       <c r="K89" s="4" t="inlineStr"/>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M89" s="4" t="inlineStr">
-        <is>
           <t>10 058</t>
         </is>
       </c>
-      <c r="N89" s="4" t="inlineStr"/>
+      <c r="M89" s="4" t="inlineStr"/>
+      <c r="N89" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O89" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P89" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7236,25 +6735,20 @@
       <c r="K90" s="4" t="inlineStr"/>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>19 184</t>
         </is>
       </c>
       <c r="M90" s="4" t="inlineStr">
         <is>
-          <t>19 184</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="N90" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O90" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P90" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7300,25 +6794,20 @@
       <c r="K91" s="4" t="inlineStr"/>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>20 488</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>20 488</t>
+          <t>5 500</t>
         </is>
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
-          <t>5 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O91" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P91" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7344,7 +6833,6 @@
       <c r="M92" s="23" t="n"/>
       <c r="N92" s="23" t="n"/>
       <c r="O92" s="23" t="n"/>
-      <c r="P92" s="23" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="18" t="n">
@@ -7382,21 +6870,16 @@
       <c r="K93" s="4" t="inlineStr"/>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M93" s="4" t="inlineStr">
-        <is>
           <t>166 694</t>
         </is>
       </c>
-      <c r="N93" s="4" t="inlineStr"/>
+      <c r="M93" s="4" t="inlineStr"/>
+      <c r="N93" s="4" t="inlineStr">
+        <is>
+          <t>180 000</t>
+        </is>
+      </c>
       <c r="O93" s="4" t="inlineStr">
-        <is>
-          <t>180 000</t>
-        </is>
-      </c>
-      <c r="P93" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7438,21 +6921,16 @@
       <c r="K94" s="4" t="inlineStr"/>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M94" s="4" t="inlineStr">
-        <is>
           <t>78 225</t>
         </is>
       </c>
-      <c r="N94" s="4" t="inlineStr"/>
+      <c r="M94" s="4" t="inlineStr"/>
+      <c r="N94" s="4" t="inlineStr">
+        <is>
+          <t>140 000</t>
+        </is>
+      </c>
       <c r="O94" s="4" t="inlineStr">
-        <is>
-          <t>140 000</t>
-        </is>
-      </c>
-      <c r="P94" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7494,21 +6972,16 @@
       <c r="K95" s="4" t="inlineStr"/>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M95" s="4" t="inlineStr">
-        <is>
           <t>87 910</t>
         </is>
       </c>
-      <c r="N95" s="4" t="inlineStr"/>
+      <c r="M95" s="4" t="inlineStr"/>
+      <c r="N95" s="4" t="inlineStr">
+        <is>
+          <t>140 000</t>
+        </is>
+      </c>
       <c r="O95" s="4" t="inlineStr">
-        <is>
-          <t>140 000</t>
-        </is>
-      </c>
-      <c r="P95" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7550,21 +7023,16 @@
       <c r="K96" s="4" t="inlineStr"/>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M96" s="4" t="inlineStr">
-        <is>
           <t>115 475</t>
         </is>
       </c>
-      <c r="N96" s="4" t="inlineStr"/>
+      <c r="M96" s="4" t="inlineStr"/>
+      <c r="N96" s="4" t="inlineStr">
+        <is>
+          <t>160 000</t>
+        </is>
+      </c>
       <c r="O96" s="4" t="inlineStr">
-        <is>
-          <t>160 000</t>
-        </is>
-      </c>
-      <c r="P96" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7606,21 +7074,16 @@
       <c r="K97" s="4" t="inlineStr"/>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M97" s="4" t="inlineStr">
-        <is>
           <t>109 888</t>
         </is>
       </c>
-      <c r="N97" s="4" t="inlineStr"/>
+      <c r="M97" s="4" t="inlineStr"/>
+      <c r="N97" s="4" t="inlineStr">
+        <is>
+          <t>160 000</t>
+        </is>
+      </c>
       <c r="O97" s="4" t="inlineStr">
-        <is>
-          <t>160 000</t>
-        </is>
-      </c>
-      <c r="P97" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7666,21 +7129,16 @@
       <c r="K98" s="4" t="inlineStr"/>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M98" s="4" t="inlineStr">
-        <is>
           <t>125 533</t>
         </is>
       </c>
-      <c r="N98" s="4" t="inlineStr"/>
+      <c r="M98" s="4" t="inlineStr"/>
+      <c r="N98" s="4" t="inlineStr">
+        <is>
+          <t>160 000</t>
+        </is>
+      </c>
       <c r="O98" s="4" t="inlineStr">
-        <is>
-          <t>160 000</t>
-        </is>
-      </c>
-      <c r="P98" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7722,21 +7180,16 @@
       <c r="K99" s="4" t="inlineStr"/>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M99" s="4" t="inlineStr">
-        <is>
           <t>47 494</t>
         </is>
       </c>
-      <c r="N99" s="4" t="inlineStr"/>
+      <c r="M99" s="4" t="inlineStr"/>
+      <c r="N99" s="4" t="inlineStr">
+        <is>
+          <t>60 000</t>
+        </is>
+      </c>
       <c r="O99" s="4" t="inlineStr">
-        <is>
-          <t>60 000</t>
-        </is>
-      </c>
-      <c r="P99" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7778,21 +7231,16 @@
       <c r="K100" s="4" t="inlineStr"/>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M100" s="4" t="inlineStr">
-        <is>
           <t>53 268</t>
         </is>
       </c>
-      <c r="N100" s="4" t="inlineStr"/>
+      <c r="M100" s="4" t="inlineStr"/>
+      <c r="N100" s="4" t="inlineStr">
+        <is>
+          <t>60 000</t>
+        </is>
+      </c>
       <c r="O100" s="4" t="inlineStr">
-        <is>
-          <t>60 000</t>
-        </is>
-      </c>
-      <c r="P100" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7834,21 +7282,16 @@
       <c r="K101" s="4" t="inlineStr"/>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M101" s="4" t="inlineStr">
-        <is>
           <t>70 775</t>
         </is>
       </c>
-      <c r="N101" s="4" t="inlineStr"/>
+      <c r="M101" s="4" t="inlineStr"/>
+      <c r="N101" s="4" t="inlineStr">
+        <is>
+          <t>95 000</t>
+        </is>
+      </c>
       <c r="O101" s="4" t="inlineStr">
-        <is>
-          <t>95 000</t>
-        </is>
-      </c>
-      <c r="P101" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7890,21 +7333,16 @@
       <c r="K102" s="4" t="inlineStr"/>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M102" s="4" t="inlineStr">
-        <is>
           <t>63 884</t>
         </is>
       </c>
-      <c r="N102" s="4" t="inlineStr"/>
+      <c r="M102" s="4" t="inlineStr"/>
+      <c r="N102" s="4" t="inlineStr">
+        <is>
+          <t>95 000</t>
+        </is>
+      </c>
       <c r="O102" s="4" t="inlineStr">
-        <is>
-          <t>95 000</t>
-        </is>
-      </c>
-      <c r="P102" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7930,7 +7368,6 @@
       <c r="M103" s="23" t="n"/>
       <c r="N103" s="23" t="n"/>
       <c r="O103" s="23" t="n"/>
-      <c r="P103" s="23" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="18" t="n">
@@ -7972,21 +7409,16 @@
       <c r="K104" s="4" t="inlineStr"/>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M104" s="4" t="inlineStr">
-        <is>
           <t>62 766</t>
         </is>
       </c>
-      <c r="N104" s="4" t="inlineStr"/>
+      <c r="M104" s="4" t="inlineStr"/>
+      <c r="N104" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O104" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P104" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8032,21 +7464,16 @@
       <c r="K105" s="4" t="inlineStr"/>
       <c r="L105" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M105" s="4" t="inlineStr">
-        <is>
           <t>40 975</t>
         </is>
       </c>
-      <c r="N105" s="4" t="inlineStr"/>
+      <c r="M105" s="4" t="inlineStr"/>
+      <c r="N105" s="4" t="inlineStr">
+        <is>
+          <t>95 000</t>
+        </is>
+      </c>
       <c r="O105" s="4" t="inlineStr">
-        <is>
-          <t>95 000</t>
-        </is>
-      </c>
-      <c r="P105" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8092,21 +7519,16 @@
       <c r="K106" s="4" t="inlineStr"/>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M106" s="4" t="inlineStr">
-        <is>
           <t>43 955</t>
         </is>
       </c>
-      <c r="N106" s="4" t="inlineStr"/>
+      <c r="M106" s="4" t="inlineStr"/>
+      <c r="N106" s="4" t="inlineStr">
+        <is>
+          <t>95 000</t>
+        </is>
+      </c>
       <c r="O106" s="4" t="inlineStr">
-        <is>
-          <t>95 000</t>
-        </is>
-      </c>
-      <c r="P106" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8152,21 +7574,16 @@
       <c r="K107" s="4" t="inlineStr"/>
       <c r="L107" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M107" s="4" t="inlineStr">
-        <is>
           <t>48 425</t>
         </is>
       </c>
-      <c r="N107" s="4" t="inlineStr"/>
+      <c r="M107" s="4" t="inlineStr"/>
+      <c r="N107" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O107" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P107" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8212,21 +7629,16 @@
       <c r="K108" s="4" t="inlineStr"/>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M108" s="4" t="inlineStr">
-        <is>
           <t>19 556</t>
         </is>
       </c>
-      <c r="N108" s="4" t="inlineStr"/>
+      <c r="M108" s="4" t="inlineStr"/>
+      <c r="N108" s="4" t="inlineStr">
+        <is>
+          <t>65 000</t>
+        </is>
+      </c>
       <c r="O108" s="4" t="inlineStr">
-        <is>
-          <t>65 000</t>
-        </is>
-      </c>
-      <c r="P108" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8272,21 +7684,16 @@
       <c r="K109" s="4" t="inlineStr"/>
       <c r="L109" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M109" s="4" t="inlineStr">
-        <is>
           <t>20 860</t>
         </is>
       </c>
-      <c r="N109" s="4" t="inlineStr"/>
+      <c r="M109" s="4" t="inlineStr"/>
+      <c r="N109" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O109" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P109" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8332,21 +7739,16 @@
       <c r="K110" s="4" t="inlineStr"/>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M110" s="4" t="inlineStr">
-        <is>
           <t>46 004</t>
         </is>
       </c>
-      <c r="N110" s="4" t="inlineStr"/>
+      <c r="M110" s="4" t="inlineStr"/>
+      <c r="N110" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O110" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P110" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8392,21 +7794,16 @@
       <c r="K111" s="4" t="inlineStr"/>
       <c r="L111" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M111" s="4" t="inlineStr">
-        <is>
           <t>26 820</t>
         </is>
       </c>
-      <c r="N111" s="4" t="inlineStr"/>
+      <c r="M111" s="4" t="inlineStr"/>
+      <c r="N111" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O111" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P111" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8432,7 +7829,6 @@
       <c r="M112" s="23" t="n"/>
       <c r="N112" s="23" t="n"/>
       <c r="O112" s="23" t="n"/>
-      <c r="P112" s="23" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="18" t="n">
@@ -8474,21 +7870,16 @@
       <c r="K113" s="4" t="inlineStr"/>
       <c r="L113" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M113" s="4" t="inlineStr">
-        <is>
           <t>35 388</t>
         </is>
       </c>
-      <c r="N113" s="4" t="inlineStr"/>
+      <c r="M113" s="4" t="inlineStr"/>
+      <c r="N113" s="4" t="inlineStr">
+        <is>
+          <t>95 000</t>
+        </is>
+      </c>
       <c r="O113" s="4" t="inlineStr">
-        <is>
-          <t>95 000</t>
-        </is>
-      </c>
-      <c r="P113" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8534,21 +7925,16 @@
       <c r="K114" s="4" t="inlineStr"/>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M114" s="4" t="inlineStr">
-        <is>
           <t>37 250</t>
         </is>
       </c>
-      <c r="N114" s="4" t="inlineStr"/>
+      <c r="M114" s="4" t="inlineStr"/>
+      <c r="N114" s="4" t="inlineStr">
+        <is>
+          <t>95 000</t>
+        </is>
+      </c>
       <c r="O114" s="4" t="inlineStr">
-        <is>
-          <t>95 000</t>
-        </is>
-      </c>
-      <c r="P114" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8594,21 +7980,16 @@
       <c r="K115" s="4" t="inlineStr"/>
       <c r="L115" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M115" s="4" t="inlineStr">
-        <is>
           <t>20 488</t>
         </is>
       </c>
-      <c r="N115" s="4" t="inlineStr"/>
+      <c r="M115" s="4" t="inlineStr"/>
+      <c r="N115" s="4" t="inlineStr">
+        <is>
+          <t>55 000</t>
+        </is>
+      </c>
       <c r="O115" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="P115" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8654,21 +8035,16 @@
       <c r="K116" s="4" t="inlineStr"/>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M116" s="4" t="inlineStr">
-        <is>
           <t>17 508</t>
         </is>
       </c>
-      <c r="N116" s="4" t="inlineStr"/>
+      <c r="M116" s="4" t="inlineStr"/>
+      <c r="N116" s="4" t="inlineStr">
+        <is>
+          <t>55 000</t>
+        </is>
+      </c>
       <c r="O116" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="P116" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8714,21 +8090,16 @@
       <c r="K117" s="4" t="inlineStr"/>
       <c r="L117" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M117" s="4" t="inlineStr">
-        <is>
           <t>20 860</t>
         </is>
       </c>
-      <c r="N117" s="4" t="inlineStr"/>
+      <c r="M117" s="4" t="inlineStr"/>
+      <c r="N117" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O117" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P117" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8754,7 +8125,6 @@
       <c r="M118" s="23" t="n"/>
       <c r="N118" s="23" t="n"/>
       <c r="O118" s="23" t="n"/>
-      <c r="P118" s="23" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="18" t="n">
@@ -8798,21 +8168,16 @@
       <c r="K119" s="4" t="inlineStr"/>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M119" s="4" t="inlineStr">
-        <is>
           <t>10 616</t>
         </is>
       </c>
-      <c r="N119" s="4" t="inlineStr"/>
+      <c r="M119" s="4" t="inlineStr"/>
+      <c r="N119" s="4" t="inlineStr">
+        <is>
+          <t>75 000</t>
+        </is>
+      </c>
       <c r="O119" s="4" t="inlineStr">
-        <is>
-          <t>75 000</t>
-        </is>
-      </c>
-      <c r="P119" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8860,21 +8225,16 @@
       <c r="K120" s="4" t="inlineStr"/>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M120" s="4" t="inlineStr">
-        <is>
           <t>10 616</t>
         </is>
       </c>
-      <c r="N120" s="4" t="inlineStr"/>
+      <c r="M120" s="4" t="inlineStr"/>
+      <c r="N120" s="4" t="inlineStr">
+        <is>
+          <t>75 000</t>
+        </is>
+      </c>
       <c r="O120" s="4" t="inlineStr">
-        <is>
-          <t>75 000</t>
-        </is>
-      </c>
-      <c r="P120" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8922,21 +8282,16 @@
       <c r="K121" s="4" t="inlineStr"/>
       <c r="L121" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M121" s="4" t="inlineStr">
-        <is>
           <t>10 244</t>
         </is>
       </c>
-      <c r="N121" s="4" t="inlineStr"/>
+      <c r="M121" s="4" t="inlineStr"/>
+      <c r="N121" s="4" t="inlineStr">
+        <is>
+          <t>55 000</t>
+        </is>
+      </c>
       <c r="O121" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="P121" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8984,21 +8339,16 @@
       <c r="K122" s="4" t="inlineStr"/>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M122" s="4" t="inlineStr">
-        <is>
           <t>10 244</t>
         </is>
       </c>
-      <c r="N122" s="4" t="inlineStr"/>
+      <c r="M122" s="4" t="inlineStr"/>
+      <c r="N122" s="4" t="inlineStr">
+        <is>
+          <t>55 000</t>
+        </is>
+      </c>
       <c r="O122" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="P122" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9046,21 +8396,16 @@
       <c r="K123" s="4" t="inlineStr"/>
       <c r="L123" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M123" s="4" t="inlineStr">
-        <is>
           <t>10 244</t>
         </is>
       </c>
-      <c r="N123" s="4" t="inlineStr"/>
+      <c r="M123" s="4" t="inlineStr"/>
+      <c r="N123" s="4" t="inlineStr">
+        <is>
+          <t>55 000</t>
+        </is>
+      </c>
       <c r="O123" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="P123" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9110,21 +8455,16 @@
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M124" s="4" t="inlineStr">
-        <is>
           <t>2 794</t>
         </is>
       </c>
-      <c r="N124" s="4" t="inlineStr"/>
+      <c r="M124" s="4" t="inlineStr"/>
+      <c r="N124" s="4" t="inlineStr">
+        <is>
+          <t>45 000</t>
+        </is>
+      </c>
       <c r="O124" s="4" t="inlineStr">
-        <is>
-          <t>45 000</t>
-        </is>
-      </c>
-      <c r="P124" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9174,21 +8514,16 @@
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M125" s="4" t="inlineStr">
-        <is>
           <t>2 421</t>
         </is>
       </c>
-      <c r="N125" s="4" t="inlineStr"/>
+      <c r="M125" s="4" t="inlineStr"/>
+      <c r="N125" s="4" t="inlineStr">
+        <is>
+          <t>40 000</t>
+        </is>
+      </c>
       <c r="O125" s="4" t="inlineStr">
-        <is>
-          <t>40 000</t>
-        </is>
-      </c>
-      <c r="P125" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9214,7 +8549,6 @@
       <c r="M126" s="23" t="n"/>
       <c r="N126" s="23" t="n"/>
       <c r="O126" s="23" t="n"/>
-      <c r="P126" s="23" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="18" t="n">
@@ -9260,21 +8594,16 @@
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M127" s="4" t="inlineStr">
-        <is>
           <t>1 490</t>
         </is>
       </c>
-      <c r="N127" s="4" t="inlineStr"/>
+      <c r="M127" s="4" t="inlineStr"/>
+      <c r="N127" s="4" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
       <c r="O127" s="4" t="inlineStr">
-        <is>
-          <t>15 000</t>
-        </is>
-      </c>
-      <c r="P127" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9324,21 +8653,16 @@
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M128" s="4" t="inlineStr">
-        <is>
           <t>2 235</t>
         </is>
       </c>
-      <c r="N128" s="4" t="inlineStr"/>
+      <c r="M128" s="4" t="inlineStr"/>
+      <c r="N128" s="4" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
       <c r="O128" s="4" t="inlineStr">
-        <is>
-          <t>15 000</t>
-        </is>
-      </c>
-      <c r="P128" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9386,19 +8710,18 @@
           <t>коробка №5</t>
         </is>
       </c>
-      <c r="L129" s="4" t="inlineStr"/>
-      <c r="M129" s="4" t="inlineStr">
+      <c r="L129" s="4" t="inlineStr">
         <is>
           <t>20 000</t>
         </is>
       </c>
-      <c r="N129" s="4" t="inlineStr"/>
+      <c r="M129" s="4" t="inlineStr"/>
+      <c r="N129" s="4" t="inlineStr">
+        <is>
+          <t>55 000</t>
+        </is>
+      </c>
       <c r="O129" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="P129" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9446,19 +8769,18 @@
           <t>коробка №5</t>
         </is>
       </c>
-      <c r="L130" s="14" t="inlineStr"/>
-      <c r="M130" s="14" t="inlineStr">
+      <c r="L130" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N130" s="14" t="inlineStr"/>
+      <c r="M130" s="14" t="inlineStr"/>
+      <c r="N130" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O130" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P130" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9504,25 +8826,20 @@
       <c r="K131" s="4" t="inlineStr"/>
       <c r="L131" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>13 038</t>
         </is>
       </c>
       <c r="M131" s="4" t="inlineStr">
         <is>
-          <t>13 038</t>
+          <t>5 000</t>
         </is>
       </c>
       <c r="N131" s="4" t="inlineStr">
         <is>
-          <t>5 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O131" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P131" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9548,7 +8865,6 @@
       <c r="M132" s="23" t="n"/>
       <c r="N132" s="23" t="n"/>
       <c r="O132" s="23" t="n"/>
-      <c r="P132" s="23" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="24" t="n">
@@ -9592,19 +8908,18 @@
           <t>коробка №5</t>
         </is>
       </c>
-      <c r="L133" s="14" t="inlineStr"/>
-      <c r="M133" s="14" t="inlineStr">
+      <c r="L133" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N133" s="14" t="inlineStr"/>
+      <c r="M133" s="14" t="inlineStr"/>
+      <c r="N133" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O133" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P133" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9630,7 +8945,6 @@
       <c r="M134" s="23" t="n"/>
       <c r="N134" s="23" t="n"/>
       <c r="O134" s="23" t="n"/>
-      <c r="P134" s="23" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="18" t="n">
@@ -9672,21 +8986,16 @@
       <c r="K135" s="4" t="inlineStr"/>
       <c r="L135" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M135" s="4" t="inlineStr">
-        <is>
           <t>60 718</t>
         </is>
       </c>
-      <c r="N135" s="4" t="inlineStr"/>
+      <c r="M135" s="4" t="inlineStr"/>
+      <c r="N135" s="4" t="inlineStr">
+        <is>
+          <t>160 000</t>
+        </is>
+      </c>
       <c r="O135" s="4" t="inlineStr">
-        <is>
-          <t>160 000</t>
-        </is>
-      </c>
-      <c r="P135" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9712,7 +9021,6 @@
       <c r="M136" s="23" t="n"/>
       <c r="N136" s="23" t="n"/>
       <c r="O136" s="23" t="n"/>
-      <c r="P136" s="23" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="24" t="n">
@@ -9752,19 +9060,18 @@
       </c>
       <c r="J137" s="24" t="inlineStr"/>
       <c r="K137" s="14" t="inlineStr"/>
-      <c r="L137" s="14" t="inlineStr"/>
-      <c r="M137" s="14" t="inlineStr">
+      <c r="L137" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N137" s="14" t="inlineStr"/>
+      <c r="M137" s="14" t="inlineStr"/>
+      <c r="N137" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O137" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P137" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9808,19 +9115,18 @@
       </c>
       <c r="J138" s="24" t="inlineStr"/>
       <c r="K138" s="14" t="inlineStr"/>
-      <c r="L138" s="14" t="inlineStr"/>
-      <c r="M138" s="14" t="inlineStr">
+      <c r="L138" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N138" s="14" t="inlineStr"/>
+      <c r="M138" s="14" t="inlineStr"/>
+      <c r="N138" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O138" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P138" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9870,19 +9176,18 @@
           <t>ящик №1</t>
         </is>
       </c>
-      <c r="L139" s="4" t="inlineStr"/>
-      <c r="M139" s="4" t="inlineStr">
+      <c r="L139" s="4" t="inlineStr">
         <is>
           <t>6 500</t>
         </is>
       </c>
-      <c r="N139" s="4" t="inlineStr"/>
+      <c r="M139" s="4" t="inlineStr"/>
+      <c r="N139" s="4" t="inlineStr">
+        <is>
+          <t>22 000</t>
+        </is>
+      </c>
       <c r="O139" s="4" t="inlineStr">
-        <is>
-          <t>22 000</t>
-        </is>
-      </c>
-      <c r="P139" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9932,19 +9237,18 @@
           <t>ящик №1</t>
         </is>
       </c>
-      <c r="L140" s="4" t="inlineStr"/>
-      <c r="M140" s="4" t="inlineStr">
+      <c r="L140" s="4" t="inlineStr">
         <is>
           <t>6 500</t>
         </is>
       </c>
-      <c r="N140" s="4" t="inlineStr"/>
+      <c r="M140" s="4" t="inlineStr"/>
+      <c r="N140" s="4" t="inlineStr">
+        <is>
+          <t>22 000</t>
+        </is>
+      </c>
       <c r="O140" s="4" t="inlineStr">
-        <is>
-          <t>22 000</t>
-        </is>
-      </c>
-      <c r="P140" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9992,19 +9296,18 @@
           <t>ящик №1</t>
         </is>
       </c>
-      <c r="L141" s="4" t="inlineStr"/>
-      <c r="M141" s="4" t="inlineStr">
+      <c r="L141" s="4" t="inlineStr">
         <is>
           <t>6 500</t>
         </is>
       </c>
-      <c r="N141" s="4" t="inlineStr"/>
+      <c r="M141" s="4" t="inlineStr"/>
+      <c r="N141" s="4" t="inlineStr">
+        <is>
+          <t>22 000</t>
+        </is>
+      </c>
       <c r="O141" s="4" t="inlineStr">
-        <is>
-          <t>22 000</t>
-        </is>
-      </c>
-      <c r="P141" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10052,19 +9355,18 @@
           <t>ящик №1</t>
         </is>
       </c>
-      <c r="L142" s="4" t="inlineStr"/>
-      <c r="M142" s="4" t="inlineStr">
+      <c r="L142" s="4" t="inlineStr">
         <is>
           <t>6 500</t>
         </is>
       </c>
-      <c r="N142" s="4" t="inlineStr"/>
+      <c r="M142" s="4" t="inlineStr"/>
+      <c r="N142" s="4" t="inlineStr">
+        <is>
+          <t>22 000</t>
+        </is>
+      </c>
       <c r="O142" s="4" t="inlineStr">
-        <is>
-          <t>22 000</t>
-        </is>
-      </c>
-      <c r="P142" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10106,25 +9408,20 @@
       <c r="K143" s="4" t="inlineStr"/>
       <c r="L143" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>6 891</t>
         </is>
       </c>
       <c r="M143" s="4" t="inlineStr">
         <is>
-          <t>6 891</t>
+          <t>4 500</t>
         </is>
       </c>
       <c r="N143" s="4" t="inlineStr">
         <is>
-          <t>4 500</t>
+          <t>22 000</t>
         </is>
       </c>
       <c r="O143" s="4" t="inlineStr">
-        <is>
-          <t>22 000</t>
-        </is>
-      </c>
-      <c r="P143" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10166,25 +9463,20 @@
       <c r="K144" s="4" t="inlineStr"/>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>6 891</t>
         </is>
       </c>
       <c r="M144" s="4" t="inlineStr">
         <is>
-          <t>6 891</t>
+          <t>4 500</t>
         </is>
       </c>
       <c r="N144" s="4" t="inlineStr">
         <is>
-          <t>4 500</t>
+          <t>22 000</t>
         </is>
       </c>
       <c r="O144" s="4" t="inlineStr">
-        <is>
-          <t>22 000</t>
-        </is>
-      </c>
-      <c r="P144" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10232,19 +9524,18 @@
           <t>коробка №8</t>
         </is>
       </c>
-      <c r="L145" s="4" t="inlineStr"/>
-      <c r="M145" s="4" t="inlineStr">
+      <c r="L145" s="4" t="inlineStr">
         <is>
           <t>5 000</t>
         </is>
       </c>
-      <c r="N145" s="4" t="inlineStr"/>
+      <c r="M145" s="4" t="inlineStr"/>
+      <c r="N145" s="4" t="inlineStr">
+        <is>
+          <t>20 000</t>
+        </is>
+      </c>
       <c r="O145" s="4" t="inlineStr">
-        <is>
-          <t>20 000</t>
-        </is>
-      </c>
-      <c r="P145" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10288,23 +9579,22 @@
       </c>
       <c r="J146" s="18" t="inlineStr"/>
       <c r="K146" s="4" t="inlineStr"/>
-      <c r="L146" s="4" t="inlineStr"/>
+      <c r="L146" s="4" t="inlineStr">
+        <is>
+          <t>5 000</t>
+        </is>
+      </c>
       <c r="M146" s="4" t="inlineStr">
         <is>
-          <t>5 000</t>
+          <t>4 000</t>
         </is>
       </c>
       <c r="N146" s="4" t="inlineStr">
         <is>
-          <t>4 000</t>
+          <t>20 000</t>
         </is>
       </c>
       <c r="O146" s="4" t="inlineStr">
-        <is>
-          <t>20 000</t>
-        </is>
-      </c>
-      <c r="P146" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10348,23 +9638,22 @@
       </c>
       <c r="J147" s="24" t="inlineStr"/>
       <c r="K147" s="14" t="inlineStr"/>
-      <c r="L147" s="14" t="inlineStr"/>
+      <c r="L147" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="M147" s="14" t="inlineStr">
         <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="N147" s="14" t="inlineStr">
+        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N147" s="14" t="inlineStr">
-        <is>
-          <t>4 000</t>
-        </is>
-      </c>
       <c r="O147" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P147" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10408,23 +9697,22 @@
       </c>
       <c r="J148" s="18" t="inlineStr"/>
       <c r="K148" s="4" t="inlineStr"/>
-      <c r="L148" s="4" t="inlineStr"/>
+      <c r="L148" s="4" t="inlineStr">
+        <is>
+          <t>5 000</t>
+        </is>
+      </c>
       <c r="M148" s="4" t="inlineStr">
         <is>
-          <t>5 000</t>
+          <t>4 000</t>
         </is>
       </c>
       <c r="N148" s="4" t="inlineStr">
         <is>
-          <t>4 000</t>
+          <t>20 000</t>
         </is>
       </c>
       <c r="O148" s="4" t="inlineStr">
-        <is>
-          <t>20 000</t>
-        </is>
-      </c>
-      <c r="P148" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10468,23 +9756,22 @@
       </c>
       <c r="J149" s="24" t="inlineStr"/>
       <c r="K149" s="14" t="inlineStr"/>
-      <c r="L149" s="14" t="inlineStr"/>
+      <c r="L149" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="M149" s="14" t="inlineStr">
         <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="N149" s="14" t="inlineStr">
+        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N149" s="14" t="inlineStr">
-        <is>
-          <t>4 000</t>
-        </is>
-      </c>
       <c r="O149" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P149" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10530,25 +9817,20 @@
       <c r="K150" s="4" t="inlineStr"/>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>5 774</t>
         </is>
       </c>
       <c r="M150" s="4" t="inlineStr">
         <is>
-          <t>5 774</t>
+          <t>4 000</t>
         </is>
       </c>
       <c r="N150" s="4" t="inlineStr">
         <is>
-          <t>4 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O150" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P150" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10594,25 +9876,20 @@
       <c r="K151" s="4" t="inlineStr"/>
       <c r="L151" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>5 774</t>
         </is>
       </c>
       <c r="M151" s="4" t="inlineStr">
         <is>
-          <t>5 774</t>
+          <t>4 000</t>
         </is>
       </c>
       <c r="N151" s="4" t="inlineStr">
         <is>
-          <t>4 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O151" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P151" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10658,25 +9935,20 @@
       <c r="K152" s="4" t="inlineStr"/>
       <c r="L152" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>5 774</t>
         </is>
       </c>
       <c r="M152" s="4" t="inlineStr">
         <is>
-          <t>5 774</t>
+          <t>4 000</t>
         </is>
       </c>
       <c r="N152" s="4" t="inlineStr">
         <is>
-          <t>4 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O152" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P152" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10726,21 +9998,16 @@
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M153" s="4" t="inlineStr">
-        <is>
           <t>3 352</t>
         </is>
       </c>
-      <c r="N153" s="4" t="inlineStr"/>
+      <c r="M153" s="4" t="inlineStr"/>
+      <c r="N153" s="4" t="inlineStr">
+        <is>
+          <t>25 000</t>
+        </is>
+      </c>
       <c r="O153" s="4" t="inlineStr">
-        <is>
-          <t>25 000</t>
-        </is>
-      </c>
-      <c r="P153" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10788,19 +10055,18 @@
           <t>коробка  № 5</t>
         </is>
       </c>
-      <c r="L154" s="4" t="inlineStr"/>
-      <c r="M154" s="4" t="inlineStr">
+      <c r="L154" s="4" t="inlineStr">
         <is>
           <t>4 500</t>
         </is>
       </c>
-      <c r="N154" s="4" t="inlineStr"/>
+      <c r="M154" s="4" t="inlineStr"/>
+      <c r="N154" s="4" t="inlineStr">
+        <is>
+          <t>22 000</t>
+        </is>
+      </c>
       <c r="O154" s="4" t="inlineStr">
-        <is>
-          <t>22 000</t>
-        </is>
-      </c>
-      <c r="P154" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10848,23 +10114,22 @@
           <t>коробка №5</t>
         </is>
       </c>
-      <c r="L155" s="4" t="inlineStr"/>
+      <c r="L155" s="4" t="inlineStr">
+        <is>
+          <t>6 500</t>
+        </is>
+      </c>
       <c r="M155" s="4" t="inlineStr">
         <is>
-          <t>6 500</t>
+          <t>3 000</t>
         </is>
       </c>
       <c r="N155" s="4" t="inlineStr">
         <is>
-          <t>3 000</t>
+          <t>24 000</t>
         </is>
       </c>
       <c r="O155" s="4" t="inlineStr">
-        <is>
-          <t>24 000</t>
-        </is>
-      </c>
-      <c r="P155" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10906,25 +10171,20 @@
       <c r="K156" s="4" t="inlineStr"/>
       <c r="L156" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>3 725</t>
         </is>
       </c>
       <c r="M156" s="4" t="inlineStr">
         <is>
-          <t>3 725</t>
+          <t>3 000</t>
         </is>
       </c>
       <c r="N156" s="4" t="inlineStr">
         <is>
-          <t>3 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O156" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P156" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10966,25 +10226,20 @@
       <c r="K157" s="4" t="inlineStr"/>
       <c r="L157" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>3 725</t>
         </is>
       </c>
       <c r="M157" s="4" t="inlineStr">
         <is>
-          <t>3 725</t>
+          <t>3 000</t>
         </is>
       </c>
       <c r="N157" s="4" t="inlineStr">
         <is>
-          <t>3 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O157" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P157" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11030,21 +10285,16 @@
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M158" s="4" t="inlineStr">
-        <is>
           <t>3 725</t>
         </is>
       </c>
-      <c r="N158" s="4" t="inlineStr"/>
+      <c r="M158" s="4" t="inlineStr"/>
+      <c r="N158" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O158" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P158" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11086,25 +10336,20 @@
       <c r="K159" s="4" t="inlineStr"/>
       <c r="L159" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>3 725</t>
         </is>
       </c>
       <c r="M159" s="4" t="inlineStr">
         <is>
-          <t>3 725</t>
+          <t>3 000</t>
         </is>
       </c>
       <c r="N159" s="4" t="inlineStr">
         <is>
-          <t>3 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O159" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P159" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11146,25 +10391,20 @@
       <c r="K160" s="4" t="inlineStr"/>
       <c r="L160" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>3 725</t>
         </is>
       </c>
       <c r="M160" s="4" t="inlineStr">
         <is>
-          <t>3 725</t>
+          <t>3 000</t>
         </is>
       </c>
       <c r="N160" s="4" t="inlineStr">
         <is>
-          <t>3 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O160" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P160" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11210,19 +10450,18 @@
         <v>3</v>
       </c>
       <c r="K161" s="14" t="inlineStr"/>
-      <c r="L161" s="14" t="inlineStr"/>
-      <c r="M161" s="14" t="inlineStr">
+      <c r="L161" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N161" s="14" t="inlineStr"/>
+      <c r="M161" s="14" t="inlineStr"/>
+      <c r="N161" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O161" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P161" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11266,19 +10505,18 @@
       </c>
       <c r="J162" s="24" t="inlineStr"/>
       <c r="K162" s="14" t="inlineStr"/>
-      <c r="L162" s="14" t="inlineStr"/>
-      <c r="M162" s="14" t="inlineStr">
+      <c r="L162" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N162" s="14" t="inlineStr"/>
+      <c r="M162" s="14" t="inlineStr"/>
+      <c r="N162" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O162" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P162" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11322,23 +10560,22 @@
       </c>
       <c r="J163" s="24" t="inlineStr"/>
       <c r="K163" s="14" t="inlineStr"/>
-      <c r="L163" s="14" t="inlineStr"/>
+      <c r="L163" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="M163" s="14" t="inlineStr">
         <is>
+          <t>3 000</t>
+        </is>
+      </c>
+      <c r="N163" s="14" t="inlineStr">
+        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N163" s="14" t="inlineStr">
-        <is>
-          <t>3 000</t>
-        </is>
-      </c>
       <c r="O163" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P163" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11384,25 +10621,20 @@
       <c r="K164" s="4" t="inlineStr"/>
       <c r="L164" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>3 725</t>
         </is>
       </c>
       <c r="M164" s="4" t="inlineStr">
         <is>
-          <t>3 725</t>
+          <t>3 000</t>
         </is>
       </c>
       <c r="N164" s="4" t="inlineStr">
         <is>
-          <t>3 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O164" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P164" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11450,19 +10682,18 @@
           <t>коробка №5</t>
         </is>
       </c>
-      <c r="L165" s="4" t="inlineStr"/>
-      <c r="M165" s="4" t="inlineStr">
+      <c r="L165" s="4" t="inlineStr">
         <is>
           <t>3 000</t>
         </is>
       </c>
-      <c r="N165" s="4" t="inlineStr"/>
+      <c r="M165" s="4" t="inlineStr"/>
+      <c r="N165" s="4" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
       <c r="O165" s="4" t="inlineStr">
-        <is>
-          <t>15 000</t>
-        </is>
-      </c>
-      <c r="P165" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11512,21 +10743,16 @@
       </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M166" s="4" t="inlineStr">
-        <is>
           <t>2 831</t>
         </is>
       </c>
-      <c r="N166" s="4" t="inlineStr"/>
+      <c r="M166" s="4" t="inlineStr"/>
+      <c r="N166" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O166" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P166" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11574,19 +10800,18 @@
           <t>коробка №8</t>
         </is>
       </c>
-      <c r="L167" s="4" t="inlineStr"/>
-      <c r="M167" s="4" t="inlineStr">
+      <c r="L167" s="4" t="inlineStr">
         <is>
           <t>3 000</t>
         </is>
       </c>
-      <c r="N167" s="4" t="inlineStr"/>
+      <c r="M167" s="4" t="inlineStr"/>
+      <c r="N167" s="4" t="inlineStr">
+        <is>
+          <t>12 000</t>
+        </is>
+      </c>
       <c r="O167" s="4" t="inlineStr">
-        <is>
-          <t>12 000</t>
-        </is>
-      </c>
-      <c r="P167" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11612,7 +10837,6 @@
       <c r="M168" s="23" t="n"/>
       <c r="N168" s="23" t="n"/>
       <c r="O168" s="23" t="n"/>
-      <c r="P168" s="23" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="24" t="n">
@@ -11656,19 +10880,18 @@
           <t>коробка №9</t>
         </is>
       </c>
-      <c r="L169" s="14" t="inlineStr"/>
-      <c r="M169" s="14" t="inlineStr">
+      <c r="L169" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N169" s="14" t="inlineStr"/>
+      <c r="M169" s="14" t="inlineStr"/>
+      <c r="N169" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O169" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P169" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11718,21 +10941,16 @@
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M170" s="4" t="inlineStr">
-        <is>
           <t>3 539</t>
         </is>
       </c>
-      <c r="N170" s="4" t="inlineStr"/>
+      <c r="M170" s="4" t="inlineStr"/>
+      <c r="N170" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O170" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P170" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11780,19 +10998,18 @@
           <t>коробка №9</t>
         </is>
       </c>
-      <c r="L171" s="14" t="inlineStr"/>
-      <c r="M171" s="14" t="inlineStr">
+      <c r="L171" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N171" s="14" t="inlineStr"/>
+      <c r="M171" s="14" t="inlineStr"/>
+      <c r="N171" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O171" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P171" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11836,23 +11053,22 @@
       </c>
       <c r="J172" s="24" t="inlineStr"/>
       <c r="K172" s="14" t="inlineStr"/>
-      <c r="L172" s="14" t="inlineStr"/>
+      <c r="L172" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="M172" s="14" t="inlineStr">
         <is>
+          <t>3 500</t>
+        </is>
+      </c>
+      <c r="N172" s="14" t="inlineStr">
+        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N172" s="14" t="inlineStr">
-        <is>
-          <t>3 500</t>
-        </is>
-      </c>
       <c r="O172" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P172" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11896,23 +11112,22 @@
       </c>
       <c r="J173" s="24" t="inlineStr"/>
       <c r="K173" s="14" t="inlineStr"/>
-      <c r="L173" s="14" t="inlineStr"/>
+      <c r="L173" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="M173" s="14" t="inlineStr">
         <is>
+          <t>3 500</t>
+        </is>
+      </c>
+      <c r="N173" s="14" t="inlineStr">
+        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N173" s="14" t="inlineStr">
-        <is>
-          <t>3 500</t>
-        </is>
-      </c>
       <c r="O173" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P173" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11956,23 +11171,22 @@
       </c>
       <c r="J174" s="24" t="inlineStr"/>
       <c r="K174" s="14" t="inlineStr"/>
-      <c r="L174" s="14" t="inlineStr"/>
+      <c r="L174" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="M174" s="14" t="inlineStr">
         <is>
+          <t>3 500</t>
+        </is>
+      </c>
+      <c r="N174" s="14" t="inlineStr">
+        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N174" s="14" t="inlineStr">
-        <is>
-          <t>3 500</t>
-        </is>
-      </c>
       <c r="O174" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P174" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12016,23 +11230,22 @@
       </c>
       <c r="J175" s="24" t="inlineStr"/>
       <c r="K175" s="14" t="inlineStr"/>
-      <c r="L175" s="14" t="inlineStr"/>
+      <c r="L175" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="M175" s="14" t="inlineStr">
         <is>
+          <t>3 500</t>
+        </is>
+      </c>
+      <c r="N175" s="14" t="inlineStr">
+        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N175" s="14" t="inlineStr">
-        <is>
-          <t>3 500</t>
-        </is>
-      </c>
       <c r="O175" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P175" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12076,23 +11289,22 @@
       </c>
       <c r="J176" s="24" t="inlineStr"/>
       <c r="K176" s="14" t="inlineStr"/>
-      <c r="L176" s="14" t="inlineStr"/>
+      <c r="L176" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="M176" s="14" t="inlineStr">
         <is>
+          <t>3 500</t>
+        </is>
+      </c>
+      <c r="N176" s="14" t="inlineStr">
+        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N176" s="14" t="inlineStr">
-        <is>
-          <t>3 500</t>
-        </is>
-      </c>
       <c r="O176" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P176" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12138,23 +11350,22 @@
         <v>6</v>
       </c>
       <c r="K177" s="14" t="inlineStr"/>
-      <c r="L177" s="14" t="inlineStr"/>
+      <c r="L177" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="M177" s="14" t="inlineStr">
         <is>
+          <t>3 500</t>
+        </is>
+      </c>
+      <c r="N177" s="14" t="inlineStr">
+        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N177" s="14" t="inlineStr">
-        <is>
-          <t>3 500</t>
-        </is>
-      </c>
       <c r="O177" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P177" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12198,23 +11409,22 @@
       </c>
       <c r="J178" s="24" t="inlineStr"/>
       <c r="K178" s="14" t="inlineStr"/>
-      <c r="L178" s="14" t="inlineStr"/>
+      <c r="L178" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="M178" s="14" t="inlineStr">
         <is>
+          <t>3 500</t>
+        </is>
+      </c>
+      <c r="N178" s="14" t="inlineStr">
+        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N178" s="14" t="inlineStr">
-        <is>
-          <t>3 500</t>
-        </is>
-      </c>
       <c r="O178" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P178" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12260,25 +11470,20 @@
       <c r="K179" s="4" t="inlineStr"/>
       <c r="L179" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>3 911</t>
         </is>
       </c>
       <c r="M179" s="4" t="inlineStr">
         <is>
-          <t>3 911</t>
+          <t>3 500</t>
         </is>
       </c>
       <c r="N179" s="4" t="inlineStr">
         <is>
-          <t>3 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O179" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P179" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12324,25 +11529,20 @@
       <c r="K180" s="4" t="inlineStr"/>
       <c r="L180" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>3 911</t>
         </is>
       </c>
       <c r="M180" s="4" t="inlineStr">
         <is>
-          <t>3 911</t>
+          <t>3 500</t>
         </is>
       </c>
       <c r="N180" s="4" t="inlineStr">
         <is>
-          <t>3 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O180" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P180" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12392,21 +11592,16 @@
       </c>
       <c r="L181" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M181" s="4" t="inlineStr">
-        <is>
           <t>1 490</t>
         </is>
       </c>
-      <c r="N181" s="4" t="inlineStr"/>
+      <c r="M181" s="4" t="inlineStr"/>
+      <c r="N181" s="4" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
       <c r="O181" s="4" t="inlineStr">
-        <is>
-          <t>15 000</t>
-        </is>
-      </c>
-      <c r="P181" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12452,21 +11647,16 @@
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M182" s="4" t="inlineStr">
-        <is>
           <t>10 616</t>
         </is>
       </c>
-      <c r="N182" s="4" t="inlineStr"/>
+      <c r="M182" s="4" t="inlineStr"/>
+      <c r="N182" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O182" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P182" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12512,21 +11702,16 @@
       <c r="K183" s="4" t="inlineStr"/>
       <c r="L183" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M183" s="4" t="inlineStr">
-        <is>
           <t>2 235</t>
         </is>
       </c>
-      <c r="N183" s="4" t="inlineStr"/>
+      <c r="M183" s="4" t="inlineStr"/>
+      <c r="N183" s="4" t="inlineStr">
+        <is>
+          <t>14 000</t>
+        </is>
+      </c>
       <c r="O183" s="4" t="inlineStr">
-        <is>
-          <t>14 000</t>
-        </is>
-      </c>
-      <c r="P183" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12574,19 +11759,18 @@
           <t>коробка  № 5</t>
         </is>
       </c>
-      <c r="L184" s="4" t="inlineStr"/>
-      <c r="M184" s="4" t="inlineStr">
+      <c r="L184" s="4" t="inlineStr">
         <is>
           <t>20 000</t>
         </is>
       </c>
-      <c r="N184" s="4" t="inlineStr"/>
+      <c r="M184" s="4" t="inlineStr"/>
+      <c r="N184" s="4" t="inlineStr">
+        <is>
+          <t>65 000</t>
+        </is>
+      </c>
       <c r="O184" s="4" t="inlineStr">
-        <is>
-          <t>65 000</t>
-        </is>
-      </c>
-      <c r="P184" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12637,20 +11821,15 @@
       </c>
       <c r="M185" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>2 500</t>
         </is>
       </c>
       <c r="N185" s="4" t="inlineStr">
         <is>
-          <t>2 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O185" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P185" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12676,7 +11855,6 @@
       <c r="M186" s="23" t="n"/>
       <c r="N186" s="23" t="n"/>
       <c r="O186" s="23" t="n"/>
-      <c r="P186" s="23" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="18" t="n">
@@ -12718,21 +11896,16 @@
       <c r="K187" s="4" t="inlineStr"/>
       <c r="L187" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M187" s="4" t="inlineStr">
-        <is>
           <t>9 312</t>
         </is>
       </c>
-      <c r="N187" s="4" t="inlineStr"/>
+      <c r="M187" s="4" t="inlineStr"/>
+      <c r="N187" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O187" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P187" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12778,21 +11951,16 @@
       <c r="K188" s="4" t="inlineStr"/>
       <c r="L188" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M188" s="4" t="inlineStr">
-        <is>
           <t>16 390</t>
         </is>
       </c>
-      <c r="N188" s="4" t="inlineStr"/>
+      <c r="M188" s="4" t="inlineStr"/>
+      <c r="N188" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O188" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P188" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12838,25 +12006,20 @@
       <c r="K189" s="4" t="inlineStr"/>
       <c r="L189" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>27 938</t>
         </is>
       </c>
       <c r="M189" s="4" t="inlineStr">
         <is>
-          <t>27 938</t>
+          <t>4 500</t>
         </is>
       </c>
       <c r="N189" s="4" t="inlineStr">
         <is>
-          <t>4 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O189" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P189" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12898,25 +12061,20 @@
       <c r="K190" s="4" t="inlineStr"/>
       <c r="L190" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>32 035</t>
         </is>
       </c>
       <c r="M190" s="4" t="inlineStr">
         <is>
-          <t>32 035</t>
+          <t>4 500</t>
         </is>
       </c>
       <c r="N190" s="4" t="inlineStr">
         <is>
-          <t>4 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O190" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P190" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12966,21 +12124,16 @@
       </c>
       <c r="L191" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M191" s="4" t="inlineStr">
-        <is>
           <t>7 636</t>
         </is>
       </c>
-      <c r="N191" s="4" t="inlineStr"/>
+      <c r="M191" s="4" t="inlineStr"/>
+      <c r="N191" s="4" t="inlineStr">
+        <is>
+          <t>24 000</t>
+        </is>
+      </c>
       <c r="O191" s="4" t="inlineStr">
-        <is>
-          <t>24 000</t>
-        </is>
-      </c>
-      <c r="P191" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13030,25 +12183,20 @@
       </c>
       <c r="L192" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>7 636</t>
         </is>
       </c>
       <c r="M192" s="4" t="inlineStr">
         <is>
-          <t>7 636</t>
+          <t>4 500</t>
         </is>
       </c>
       <c r="N192" s="4" t="inlineStr">
         <is>
-          <t>4 500</t>
+          <t>24 000</t>
         </is>
       </c>
       <c r="O192" s="4" t="inlineStr">
-        <is>
-          <t>24 000</t>
-        </is>
-      </c>
-      <c r="P192" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13098,25 +12246,20 @@
       </c>
       <c r="L193" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>2 235</t>
         </is>
       </c>
       <c r="M193" s="4" t="inlineStr">
         <is>
-          <t>2 235</t>
+          <t>3 500</t>
         </is>
       </c>
       <c r="N193" s="4" t="inlineStr">
         <is>
-          <t>3 500</t>
+          <t>20 000</t>
         </is>
       </c>
       <c r="O193" s="4" t="inlineStr">
-        <is>
-          <t>20 000</t>
-        </is>
-      </c>
-      <c r="P193" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13166,25 +12309,20 @@
       </c>
       <c r="L194" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>5 215</t>
         </is>
       </c>
       <c r="M194" s="4" t="inlineStr">
         <is>
-          <t>5 215</t>
+          <t>3 500</t>
         </is>
       </c>
       <c r="N194" s="4" t="inlineStr">
         <is>
-          <t>3 500</t>
+          <t>20 000</t>
         </is>
       </c>
       <c r="O194" s="4" t="inlineStr">
-        <is>
-          <t>20 000</t>
-        </is>
-      </c>
-      <c r="P194" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13234,25 +12372,20 @@
       </c>
       <c r="L195" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>3 390</t>
         </is>
       </c>
       <c r="M195" s="4" t="inlineStr">
         <is>
-          <t>3 390</t>
+          <t>3 000</t>
         </is>
       </c>
       <c r="N195" s="4" t="inlineStr">
         <is>
-          <t>3 000</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O195" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P195" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13298,25 +12431,20 @@
       <c r="K196" s="4" t="inlineStr"/>
       <c r="L196" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>931</t>
         </is>
       </c>
       <c r="M196" s="4" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>2 500</t>
         </is>
       </c>
       <c r="N196" s="4" t="inlineStr">
         <is>
-          <t>2 500</t>
+          <t>по согласованию</t>
         </is>
       </c>
       <c r="O196" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P196" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13342,7 +12470,6 @@
       <c r="M197" s="23" t="n"/>
       <c r="N197" s="23" t="n"/>
       <c r="O197" s="23" t="n"/>
-      <c r="P197" s="23" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="18" t="n">
@@ -13380,25 +12507,20 @@
       <c r="K198" s="4" t="inlineStr"/>
       <c r="L198" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
+          <t>10 244</t>
         </is>
       </c>
       <c r="M198" s="4" t="inlineStr">
         <is>
-          <t>10 244</t>
+          <t>4 000</t>
         </is>
       </c>
       <c r="N198" s="4" t="inlineStr">
         <is>
-          <t>4 000</t>
+          <t>30 000</t>
         </is>
       </c>
       <c r="O198" s="4" t="inlineStr">
-        <is>
-          <t>30 000</t>
-        </is>
-      </c>
-      <c r="P198" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13440,21 +12562,16 @@
       <c r="K199" s="4" t="inlineStr"/>
       <c r="L199" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M199" s="4" t="inlineStr">
-        <is>
           <t>10 244</t>
         </is>
       </c>
-      <c r="N199" s="4" t="inlineStr"/>
+      <c r="M199" s="4" t="inlineStr"/>
+      <c r="N199" s="4" t="inlineStr">
+        <is>
+          <t>30 000</t>
+        </is>
+      </c>
       <c r="O199" s="4" t="inlineStr">
-        <is>
-          <t>30 000</t>
-        </is>
-      </c>
-      <c r="P199" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13480,7 +12597,6 @@
       <c r="M200" s="23" t="n"/>
       <c r="N200" s="23" t="n"/>
       <c r="O200" s="23" t="n"/>
-      <c r="P200" s="23" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="18" t="n">
@@ -13526,21 +12642,16 @@
       </c>
       <c r="L201" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M201" s="4" t="inlineStr">
-        <is>
           <t>4 656</t>
         </is>
       </c>
-      <c r="N201" s="4" t="inlineStr"/>
+      <c r="M201" s="4" t="inlineStr"/>
+      <c r="N201" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O201" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P201" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13590,21 +12701,16 @@
       </c>
       <c r="L202" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M202" s="4" t="inlineStr">
-        <is>
           <t>3 166</t>
         </is>
       </c>
-      <c r="N202" s="4" t="inlineStr"/>
+      <c r="M202" s="4" t="inlineStr"/>
+      <c r="N202" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O202" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P202" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13654,21 +12760,16 @@
       </c>
       <c r="L203" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M203" s="4" t="inlineStr">
-        <is>
           <t>2 794</t>
         </is>
       </c>
-      <c r="N203" s="4" t="inlineStr"/>
+      <c r="M203" s="4" t="inlineStr"/>
+      <c r="N203" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O203" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P203" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13718,21 +12819,16 @@
       </c>
       <c r="L204" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M204" s="4" t="inlineStr">
-        <is>
           <t>1 118</t>
         </is>
       </c>
-      <c r="N204" s="4" t="inlineStr"/>
+      <c r="M204" s="4" t="inlineStr"/>
+      <c r="N204" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O204" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P204" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13758,7 +12854,6 @@
       <c r="M205" s="23" t="n"/>
       <c r="N205" s="23" t="n"/>
       <c r="O205" s="23" t="n"/>
-      <c r="P205" s="23" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="18" t="n">
@@ -13798,19 +12893,18 @@
       </c>
       <c r="J206" s="18" t="inlineStr"/>
       <c r="K206" s="4" t="inlineStr"/>
-      <c r="L206" s="4" t="inlineStr"/>
-      <c r="M206" s="4" t="inlineStr">
+      <c r="L206" s="4" t="inlineStr">
         <is>
           <t>35 000</t>
         </is>
       </c>
-      <c r="N206" s="4" t="inlineStr"/>
+      <c r="M206" s="4" t="inlineStr"/>
+      <c r="N206" s="4" t="inlineStr">
+        <is>
+          <t>120 000</t>
+        </is>
+      </c>
       <c r="O206" s="4" t="inlineStr">
-        <is>
-          <t>120 000</t>
-        </is>
-      </c>
-      <c r="P206" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13854,19 +12948,18 @@
       </c>
       <c r="J207" s="18" t="inlineStr"/>
       <c r="K207" s="4" t="inlineStr"/>
-      <c r="L207" s="4" t="inlineStr"/>
-      <c r="M207" s="4" t="inlineStr">
+      <c r="L207" s="4" t="inlineStr">
         <is>
           <t>35 000</t>
         </is>
       </c>
-      <c r="N207" s="4" t="inlineStr"/>
+      <c r="M207" s="4" t="inlineStr"/>
+      <c r="N207" s="4" t="inlineStr">
+        <is>
+          <t>120 000</t>
+        </is>
+      </c>
       <c r="O207" s="4" t="inlineStr">
-        <is>
-          <t>120 000</t>
-        </is>
-      </c>
-      <c r="P207" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13910,19 +13003,18 @@
       </c>
       <c r="J208" s="18" t="inlineStr"/>
       <c r="K208" s="4" t="inlineStr"/>
-      <c r="L208" s="4" t="inlineStr"/>
-      <c r="M208" s="4" t="inlineStr">
+      <c r="L208" s="4" t="inlineStr">
         <is>
           <t>15 000</t>
         </is>
       </c>
-      <c r="N208" s="4" t="inlineStr"/>
+      <c r="M208" s="4" t="inlineStr"/>
+      <c r="N208" s="4" t="inlineStr">
+        <is>
+          <t>45 000</t>
+        </is>
+      </c>
       <c r="O208" s="4" t="inlineStr">
-        <is>
-          <t>45 000</t>
-        </is>
-      </c>
-      <c r="P208" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13966,19 +13058,18 @@
       </c>
       <c r="J209" s="18" t="inlineStr"/>
       <c r="K209" s="4" t="inlineStr"/>
-      <c r="L209" s="4" t="inlineStr"/>
-      <c r="M209" s="4" t="inlineStr">
+      <c r="L209" s="4" t="inlineStr">
         <is>
           <t>15 000</t>
         </is>
       </c>
-      <c r="N209" s="4" t="inlineStr"/>
+      <c r="M209" s="4" t="inlineStr"/>
+      <c r="N209" s="4" t="inlineStr">
+        <is>
+          <t>45 000</t>
+        </is>
+      </c>
       <c r="O209" s="4" t="inlineStr">
-        <is>
-          <t>45 000</t>
-        </is>
-      </c>
-      <c r="P209" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14004,7 +13095,6 @@
       <c r="M210" s="23" t="n"/>
       <c r="N210" s="23" t="n"/>
       <c r="O210" s="23" t="n"/>
-      <c r="P210" s="23" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="25" t="n">
@@ -14040,19 +13130,18 @@
       </c>
       <c r="J211" s="25" t="inlineStr"/>
       <c r="K211" s="12" t="inlineStr"/>
-      <c r="L211" s="12" t="inlineStr"/>
-      <c r="M211" s="12" t="inlineStr">
+      <c r="L211" s="12" t="inlineStr">
         <is>
           <t>цена отдельно</t>
         </is>
       </c>
-      <c r="N211" s="12" t="inlineStr"/>
+      <c r="M211" s="12" t="inlineStr"/>
+      <c r="N211" s="12" t="inlineStr">
+        <is>
+          <t>55 000</t>
+        </is>
+      </c>
       <c r="O211" s="12" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="P211" s="12" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14090,19 +13179,18 @@
       </c>
       <c r="J212" s="25" t="inlineStr"/>
       <c r="K212" s="12" t="inlineStr"/>
-      <c r="L212" s="12" t="inlineStr"/>
-      <c r="M212" s="12" t="inlineStr">
+      <c r="L212" s="12" t="inlineStr">
         <is>
           <t>цена отдельно</t>
         </is>
       </c>
-      <c r="N212" s="12" t="inlineStr"/>
+      <c r="M212" s="12" t="inlineStr"/>
+      <c r="N212" s="12" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O212" s="12" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P212" s="12" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14146,19 +13234,18 @@
       </c>
       <c r="J213" s="18" t="inlineStr"/>
       <c r="K213" s="4" t="inlineStr"/>
-      <c r="L213" s="4" t="inlineStr"/>
-      <c r="M213" s="4" t="inlineStr">
+      <c r="L213" s="4" t="inlineStr">
         <is>
           <t>30 000</t>
         </is>
       </c>
-      <c r="N213" s="4" t="inlineStr"/>
+      <c r="M213" s="4" t="inlineStr"/>
+      <c r="N213" s="4" t="inlineStr">
+        <is>
+          <t>70 000</t>
+        </is>
+      </c>
       <c r="O213" s="4" t="inlineStr">
-        <is>
-          <t>70 000</t>
-        </is>
-      </c>
-      <c r="P213" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14202,19 +13289,18 @@
       </c>
       <c r="J214" s="18" t="inlineStr"/>
       <c r="K214" s="4" t="inlineStr"/>
-      <c r="L214" s="4" t="inlineStr"/>
-      <c r="M214" s="4" t="inlineStr">
+      <c r="L214" s="4" t="inlineStr">
         <is>
           <t>25 000</t>
         </is>
       </c>
-      <c r="N214" s="4" t="inlineStr"/>
+      <c r="M214" s="4" t="inlineStr"/>
+      <c r="N214" s="4" t="inlineStr">
+        <is>
+          <t>65 000</t>
+        </is>
+      </c>
       <c r="O214" s="4" t="inlineStr">
-        <is>
-          <t>65 000</t>
-        </is>
-      </c>
-      <c r="P214" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14258,19 +13344,18 @@
       </c>
       <c r="J215" s="25" t="inlineStr"/>
       <c r="K215" s="12" t="inlineStr"/>
-      <c r="L215" s="12" t="inlineStr"/>
-      <c r="M215" s="12" t="inlineStr">
+      <c r="L215" s="12" t="inlineStr">
         <is>
           <t>цена отдельно</t>
         </is>
       </c>
-      <c r="N215" s="12" t="inlineStr"/>
+      <c r="M215" s="12" t="inlineStr"/>
+      <c r="N215" s="12" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O215" s="12" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P215" s="12" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14310,21 +13395,16 @@
       <c r="K216" s="4" t="inlineStr"/>
       <c r="L216" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M216" s="4" t="inlineStr">
-        <is>
           <t>12 665</t>
         </is>
       </c>
-      <c r="N216" s="4" t="inlineStr"/>
+      <c r="M216" s="4" t="inlineStr"/>
+      <c r="N216" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O216" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P216" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14364,21 +13444,16 @@
       <c r="K217" s="4" t="inlineStr"/>
       <c r="L217" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M217" s="4" t="inlineStr">
-        <is>
           <t>4 470</t>
         </is>
       </c>
-      <c r="N217" s="4" t="inlineStr"/>
+      <c r="M217" s="4" t="inlineStr"/>
+      <c r="N217" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O217" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P217" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14416,19 +13491,18 @@
       </c>
       <c r="J218" s="25" t="inlineStr"/>
       <c r="K218" s="12" t="inlineStr"/>
-      <c r="L218" s="12" t="inlineStr"/>
-      <c r="M218" s="12" t="inlineStr">
+      <c r="L218" s="12" t="inlineStr">
         <is>
           <t>цена отдельно</t>
         </is>
       </c>
-      <c r="N218" s="12" t="inlineStr"/>
+      <c r="M218" s="12" t="inlineStr"/>
+      <c r="N218" s="12" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O218" s="12" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P218" s="12" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14466,19 +13540,18 @@
       </c>
       <c r="J219" s="25" t="inlineStr"/>
       <c r="K219" s="12" t="inlineStr"/>
-      <c r="L219" s="12" t="inlineStr"/>
-      <c r="M219" s="12" t="inlineStr">
+      <c r="L219" s="12" t="inlineStr">
         <is>
           <t>цена отдельно</t>
         </is>
       </c>
-      <c r="N219" s="12" t="inlineStr"/>
+      <c r="M219" s="12" t="inlineStr"/>
+      <c r="N219" s="12" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O219" s="12" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P219" s="12" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14504,7 +13577,6 @@
       <c r="M220" s="23" t="n"/>
       <c r="N220" s="23" t="n"/>
       <c r="O220" s="23" t="n"/>
-      <c r="P220" s="23" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="18" t="n">
@@ -14550,21 +13622,16 @@
       </c>
       <c r="L221" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M221" s="4" t="inlineStr">
-        <is>
           <t>2 794</t>
         </is>
       </c>
-      <c r="N221" s="4" t="inlineStr"/>
+      <c r="M221" s="4" t="inlineStr"/>
+      <c r="N221" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O221" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P221" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14590,7 +13657,6 @@
       <c r="M222" s="23" t="n"/>
       <c r="N222" s="23" t="n"/>
       <c r="O222" s="23" t="n"/>
-      <c r="P222" s="23" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="18" t="n">
@@ -14628,21 +13694,16 @@
       <c r="K223" s="4" t="inlineStr"/>
       <c r="L223" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M223" s="4" t="inlineStr">
-        <is>
           <t>7 450</t>
         </is>
       </c>
-      <c r="N223" s="4" t="inlineStr"/>
+      <c r="M223" s="4" t="inlineStr"/>
+      <c r="N223" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O223" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P223" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14668,7 +13729,6 @@
       <c r="M224" s="23" t="n"/>
       <c r="N224" s="23" t="n"/>
       <c r="O224" s="23" t="n"/>
-      <c r="P224" s="23" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="24" t="n">
@@ -14704,19 +13764,18 @@
       </c>
       <c r="J225" s="24" t="inlineStr"/>
       <c r="K225" s="14" t="inlineStr"/>
-      <c r="L225" s="14" t="inlineStr"/>
-      <c r="M225" s="14" t="inlineStr">
+      <c r="L225" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N225" s="14" t="inlineStr"/>
+      <c r="M225" s="14" t="inlineStr"/>
+      <c r="N225" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O225" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P225" s="14" t="inlineStr">
         <is>
           <t>алюминий</t>
         </is>
@@ -14756,19 +13815,18 @@
       </c>
       <c r="J226" s="24" t="inlineStr"/>
       <c r="K226" s="14" t="inlineStr"/>
-      <c r="L226" s="14" t="inlineStr"/>
-      <c r="M226" s="14" t="inlineStr">
+      <c r="L226" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N226" s="14" t="inlineStr"/>
+      <c r="M226" s="14" t="inlineStr"/>
+      <c r="N226" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O226" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P226" s="14" t="inlineStr">
         <is>
           <t>алюминий</t>
         </is>
@@ -14808,19 +13866,18 @@
       </c>
       <c r="J227" s="24" t="inlineStr"/>
       <c r="K227" s="14" t="inlineStr"/>
-      <c r="L227" s="14" t="inlineStr"/>
-      <c r="M227" s="14" t="inlineStr">
+      <c r="L227" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N227" s="14" t="inlineStr"/>
+      <c r="M227" s="14" t="inlineStr"/>
+      <c r="N227" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O227" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P227" s="14" t="inlineStr">
         <is>
           <t>алюминий</t>
         </is>
@@ -14860,19 +13917,18 @@
       </c>
       <c r="J228" s="24" t="inlineStr"/>
       <c r="K228" s="14" t="inlineStr"/>
-      <c r="L228" s="14" t="inlineStr"/>
-      <c r="M228" s="14" t="inlineStr">
+      <c r="L228" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N228" s="14" t="inlineStr"/>
+      <c r="M228" s="14" t="inlineStr"/>
+      <c r="N228" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O228" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P228" s="14" t="inlineStr">
         <is>
           <t>алюминий</t>
         </is>
@@ -14914,21 +13970,16 @@
       <c r="K229" s="4" t="inlineStr"/>
       <c r="L229" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M229" s="4" t="inlineStr">
-        <is>
           <t>33 898</t>
         </is>
       </c>
-      <c r="N229" s="4" t="inlineStr"/>
+      <c r="M229" s="4" t="inlineStr"/>
+      <c r="N229" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O229" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P229" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14970,21 +14021,16 @@
       <c r="K230" s="4" t="inlineStr"/>
       <c r="L230" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M230" s="4" t="inlineStr">
-        <is>
           <t>20 860</t>
         </is>
       </c>
-      <c r="N230" s="4" t="inlineStr"/>
+      <c r="M230" s="4" t="inlineStr"/>
+      <c r="N230" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O230" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P230" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -15026,21 +14072,16 @@
       <c r="K231" s="4" t="inlineStr"/>
       <c r="L231" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M231" s="4" t="inlineStr">
-        <is>
           <t>2 794</t>
         </is>
       </c>
-      <c r="N231" s="4" t="inlineStr"/>
+      <c r="M231" s="4" t="inlineStr"/>
+      <c r="N231" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O231" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P231" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -15082,21 +14123,16 @@
       <c r="K232" s="4" t="inlineStr"/>
       <c r="L232" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M232" s="4" t="inlineStr">
-        <is>
           <t>2 980</t>
         </is>
       </c>
-      <c r="N232" s="4" t="inlineStr"/>
+      <c r="M232" s="4" t="inlineStr"/>
+      <c r="N232" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O232" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P232" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -15122,7 +14158,6 @@
       <c r="M233" s="23" t="n"/>
       <c r="N233" s="23" t="n"/>
       <c r="O233" s="23" t="n"/>
-      <c r="P233" s="23" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="18" t="n">
@@ -15160,21 +14195,16 @@
       <c r="K234" s="4" t="inlineStr"/>
       <c r="L234" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M234" s="4" t="inlineStr">
-        <is>
           <t>20 115</t>
         </is>
       </c>
-      <c r="N234" s="4" t="inlineStr"/>
+      <c r="M234" s="4" t="inlineStr"/>
+      <c r="N234" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O234" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P234" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -15216,21 +14246,16 @@
       <c r="K235" s="4" t="inlineStr"/>
       <c r="L235" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M235" s="4" t="inlineStr">
-        <is>
           <t>25 144</t>
         </is>
       </c>
-      <c r="N235" s="4" t="inlineStr"/>
+      <c r="M235" s="4" t="inlineStr"/>
+      <c r="N235" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O235" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P235" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -15270,21 +14295,16 @@
       <c r="K236" s="4" t="inlineStr"/>
       <c r="L236" s="4" t="inlineStr">
         <is>
-          <t>1 862</t>
-        </is>
-      </c>
-      <c r="M236" s="4" t="inlineStr">
-        <is>
           <t>6 332</t>
         </is>
       </c>
-      <c r="N236" s="4" t="inlineStr"/>
+      <c r="M236" s="4" t="inlineStr"/>
+      <c r="N236" s="4" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O236" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P236" s="4" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -15310,7 +14330,6 @@
       <c r="M237" s="23" t="n"/>
       <c r="N237" s="23" t="n"/>
       <c r="O237" s="23" t="n"/>
-      <c r="P237" s="23" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="24" t="n">
@@ -15350,19 +14369,18 @@
       </c>
       <c r="J238" s="24" t="inlineStr"/>
       <c r="K238" s="14" t="inlineStr"/>
-      <c r="L238" s="14" t="inlineStr"/>
-      <c r="M238" s="14" t="inlineStr">
+      <c r="L238" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N238" s="14" t="inlineStr"/>
+      <c r="M238" s="14" t="inlineStr"/>
+      <c r="N238" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O238" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P238" s="14" t="inlineStr">
         <is>
           <t>сталь</t>
         </is>
@@ -15408,19 +14426,18 @@
         <v>1</v>
       </c>
       <c r="K239" s="14" t="inlineStr"/>
-      <c r="L239" s="14" t="inlineStr"/>
-      <c r="M239" s="14" t="inlineStr">
+      <c r="L239" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N239" s="14" t="inlineStr"/>
+      <c r="M239" s="14" t="inlineStr"/>
+      <c r="N239" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O239" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P239" s="14" t="inlineStr">
         <is>
           <t>сталь</t>
         </is>
@@ -15466,19 +14483,18 @@
         <v>1</v>
       </c>
       <c r="K240" s="14" t="inlineStr"/>
-      <c r="L240" s="14" t="inlineStr"/>
-      <c r="M240" s="14" t="inlineStr">
+      <c r="L240" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N240" s="14" t="inlineStr"/>
+      <c r="M240" s="14" t="inlineStr"/>
+      <c r="N240" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O240" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P240" s="14" t="inlineStr">
         <is>
           <t>сталь</t>
         </is>
@@ -15504,7 +14520,6 @@
       <c r="M241" s="23" t="n"/>
       <c r="N241" s="23" t="n"/>
       <c r="O241" s="23" t="n"/>
-      <c r="P241" s="23" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="24" t="n">
@@ -15540,19 +14555,18 @@
       </c>
       <c r="J242" s="24" t="inlineStr"/>
       <c r="K242" s="14" t="inlineStr"/>
-      <c r="L242" s="14" t="inlineStr"/>
-      <c r="M242" s="14" t="inlineStr">
+      <c r="L242" s="14" t="inlineStr">
         <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N242" s="14" t="inlineStr"/>
+      <c r="M242" s="14" t="inlineStr"/>
+      <c r="N242" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="O242" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P242" s="14" t="inlineStr">
         <is>
           <t>сталь</t>
         </is>
@@ -15578,7 +14592,6 @@
       <c r="M243" s="23" t="n"/>
       <c r="N243" s="23" t="n"/>
       <c r="O243" s="23" t="n"/>
-      <c r="P243" s="23" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="24" t="n">
@@ -15614,23 +14627,22 @@
       </c>
       <c r="J244" s="24" t="inlineStr"/>
       <c r="K244" s="14" t="inlineStr"/>
-      <c r="L244" s="14" t="inlineStr"/>
+      <c r="L244" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="M244" s="14" t="inlineStr">
         <is>
+          <t>6 000</t>
+        </is>
+      </c>
+      <c r="N244" s="14" t="inlineStr">
+        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N244" s="14" t="inlineStr">
-        <is>
-          <t>6 000</t>
-        </is>
-      </c>
       <c r="O244" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P244" s="14" t="inlineStr">
         <is>
           <t>сталь</t>
         </is>
@@ -15670,23 +14682,22 @@
       </c>
       <c r="J245" s="24" t="inlineStr"/>
       <c r="K245" s="14" t="inlineStr"/>
-      <c r="L245" s="14" t="inlineStr"/>
+      <c r="L245" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
       <c r="M245" s="14" t="inlineStr">
         <is>
+          <t>4 500</t>
+        </is>
+      </c>
+      <c r="N245" s="14" t="inlineStr">
+        <is>
           <t>по согласованию</t>
         </is>
       </c>
-      <c r="N245" s="14" t="inlineStr">
-        <is>
-          <t>4 500</t>
-        </is>
-      </c>
       <c r="O245" s="14" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="P245" s="14" t="inlineStr">
         <is>
           <t>сталь</t>
         </is>
@@ -15712,7 +14723,6 @@
       <c r="M246" s="23" t="n"/>
       <c r="N246" s="23" t="n"/>
       <c r="O246" s="23" t="n"/>
-      <c r="P246" s="23" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="18" t="n">
@@ -15756,19 +14766,18 @@
           <t>коробка №7</t>
         </is>
       </c>
-      <c r="L247" s="4" t="inlineStr"/>
-      <c r="M247" s="4" t="inlineStr">
+      <c r="L247" s="4" t="inlineStr">
         <is>
           <t>55 000</t>
         </is>
       </c>
-      <c r="N247" s="4" t="inlineStr"/>
+      <c r="M247" s="4" t="inlineStr"/>
+      <c r="N247" s="4" t="inlineStr">
+        <is>
+          <t>140 000</t>
+        </is>
+      </c>
       <c r="O247" s="4" t="inlineStr">
-        <is>
-          <t>140 000</t>
-        </is>
-      </c>
-      <c r="P247" s="4" t="inlineStr">
         <is>
           <t>титан</t>
         </is>
@@ -15816,54 +14825,53 @@
           <t>коробка №6</t>
         </is>
       </c>
-      <c r="L248" s="4" t="inlineStr"/>
-      <c r="M248" s="4" t="inlineStr">
+      <c r="L248" s="4" t="inlineStr">
         <is>
           <t>35 000</t>
         </is>
       </c>
-      <c r="N248" s="4" t="inlineStr"/>
+      <c r="M248" s="4" t="inlineStr"/>
+      <c r="N248" s="4" t="inlineStr">
+        <is>
+          <t>100 000</t>
+        </is>
+      </c>
       <c r="O248" s="4" t="inlineStr">
         <is>
-          <t>100 000</t>
-        </is>
-      </c>
-      <c r="P248" s="4" t="inlineStr">
-        <is>
           <t>титан</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P248"/>
+  <autoFilter ref="A4:O248"/>
   <mergeCells count="27">
-    <mergeCell ref="A5:P5"/>
-    <mergeCell ref="A17:P17"/>
-    <mergeCell ref="A126:P126"/>
-    <mergeCell ref="A200:P200"/>
-    <mergeCell ref="A224:P224"/>
-    <mergeCell ref="A134:P134"/>
-    <mergeCell ref="A112:P112"/>
-    <mergeCell ref="A220:P220"/>
-    <mergeCell ref="A92:P92"/>
-    <mergeCell ref="A186:P186"/>
-    <mergeCell ref="A49:P49"/>
-    <mergeCell ref="A103:P103"/>
-    <mergeCell ref="A222:P222"/>
-    <mergeCell ref="A132:P132"/>
-    <mergeCell ref="A197:P197"/>
-    <mergeCell ref="A241:P241"/>
-    <mergeCell ref="A168:P168"/>
-    <mergeCell ref="A237:P237"/>
-    <mergeCell ref="A205:P205"/>
-    <mergeCell ref="A87:P87"/>
-    <mergeCell ref="A243:P243"/>
-    <mergeCell ref="A246:P246"/>
-    <mergeCell ref="A118:P118"/>
-    <mergeCell ref="A233:P233"/>
-    <mergeCell ref="A136:P136"/>
-    <mergeCell ref="A210:P210"/>
-    <mergeCell ref="A57:P57"/>
+    <mergeCell ref="A87:O87"/>
+    <mergeCell ref="A205:O205"/>
+    <mergeCell ref="A243:O243"/>
+    <mergeCell ref="A118:O118"/>
+    <mergeCell ref="A233:O233"/>
+    <mergeCell ref="A246:O246"/>
+    <mergeCell ref="A136:O136"/>
+    <mergeCell ref="A57:O57"/>
+    <mergeCell ref="A210:O210"/>
+    <mergeCell ref="A5:O5"/>
+    <mergeCell ref="A126:O126"/>
+    <mergeCell ref="A17:O17"/>
+    <mergeCell ref="A224:O224"/>
+    <mergeCell ref="A200:O200"/>
+    <mergeCell ref="A134:O134"/>
+    <mergeCell ref="A112:O112"/>
+    <mergeCell ref="A220:O220"/>
+    <mergeCell ref="A92:O92"/>
+    <mergeCell ref="A186:O186"/>
+    <mergeCell ref="A222:O222"/>
+    <mergeCell ref="A49:O49"/>
+    <mergeCell ref="A103:O103"/>
+    <mergeCell ref="A132:O132"/>
+    <mergeCell ref="A241:O241"/>
+    <mergeCell ref="A168:O168"/>
+    <mergeCell ref="A197:O197"/>
+    <mergeCell ref="A237:O237"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>

--- a/outputs/marine_equipment/Контейнер_погрузка.xlsx
+++ b/outputs/marine_equipment/Контейнер_погрузка.xlsx
@@ -762,7 +762,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>3. Реализация</t>
+          <t>3. Продажная цена</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -964,7 +964,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Порядок групп — как грузим. Нарастающий вес показывает, сколько тонн уже в контейнере к концу каждой группы. Три колонки денег — это цепочка: закуп по Договору (мы продаем компании), ремонт по прайсу мастерской, реализация (продаем вместе конечному покупателю).</t>
+          <t>Порядок групп — как грузим. Нарастающий вес показывает, сколько тонн уже в контейнере к концу каждой группы. Три колонки денег — это цепочка: закуп по Договору (мы продаем компании), ремонт по прайсу мастерской, продажная цена (продаем вместе конечному покупателю).</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>3. Реализация, руб</t>
+          <t>3. Продажная цена, руб</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>3. Реализация за ед., руб</t>
+          <t>3. Продажная цена за ед., руб</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -14902,14 +14902,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Три цены: закуп, ремонт, реализация</t>
+          <t>Три цены: закуп, ремонт, продажная цена</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Закуп по Договору — по этой цене мы продаем арматуру ПКФ «АРМА». Дальше компания приводит товар в порядок и при необходимости ремонтирует, ремонт считается по прайсу мастерской. Потом мы вместе с ней продаем арматуру конечному покупателю — это цена реализации. Оранжевым — то, у чего закуп от металла не считается.</t>
+          <t>Закуп по Договору — по этой цене мы продаем арматуру ПКФ «АРМА». Дальше компания приводит товар в порядок и при необходимости ремонтирует, ремонт считается по прайсу мастерской. Потом мы вместе с ней продаем арматуру конечному покупателю — это продажная цена, в Договоре она называется ценой реализации. Оранжевым — то, у чего закуп от металла не считается.</t>
         </is>
       </c>
     </row>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>3. Реализация, руб</t>
+          <t>3. Продажная цена, руб</t>
         </is>
       </c>
     </row>
@@ -15572,7 +15572,7 @@
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t>— Реализация — ориентир, а не согласованная цена: по пункту 3.2 Договора конкретную цену согласуют письменно до передачи товара конечному покупателю.</t>
+          <t>— Продажная цена — ориентир, а не согласованная: по пункту 3.2 Договора конкретную цену согласуют письменно до передачи товара конечному покупателю.</t>
         </is>
       </c>
     </row>

--- a/outputs/marine_equipment/Контейнер_погрузка.xlsx
+++ b/outputs/marine_equipment/Контейнер_погрузка.xlsx
@@ -127,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -196,6 +196,9 @@
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -573,7 +576,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Погрузка контейнера в Санкт-Петербург</t>
+          <t>Погрузка контейнера в Санкт-Петербург, сорокафутовый</t>
         </is>
       </c>
     </row>
@@ -660,12 +663,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>468 кг</t>
+          <t>700 кг</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>сырая необрезная, 0,035 куб. м на тонну груза</t>
+          <t>сырая необрезная, цифра собственника на эту погрузку</t>
         </is>
       </c>
     </row>
@@ -677,7 +680,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>19 559 кг</t>
+          <t>19 791 кг</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -694,12 +697,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>25 000 кг</t>
+          <t>26 000 кг</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>решение собственника</t>
+          <t>сорокафутовый контейнер, решение собственника</t>
         </is>
       </c>
     </row>
@@ -711,7 +714,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>5 441 кг (22%)</t>
+          <t>6 209 кг (24%)</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -15607,7 +15610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15678,11 +15681,11 @@
       <c r="C5" s="18" t="inlineStr"/>
       <c r="D5" s="18" t="inlineStr"/>
       <c r="E5" s="4" t="n">
-        <v>468</v>
+        <v>700</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>468 кг доски на всю укладку, 0,035 куб. м на тонну груза</t>
+          <t>700 кг доски на всю укладку</t>
         </is>
       </c>
     </row>
@@ -15806,36 +15809,326 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Пол контейнера: сорокафутовый, 12.03 м в длину</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Ду</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Штук</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Поперек, шт</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Рядов</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Глубина, м</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Высота стопки, м</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>Ду350</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>Ду300</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>Ду250</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="n">
+        <v>21</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>Ду200</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>Ду125</t>
+        </is>
+      </c>
+      <c r="B18" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F18" s="25" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>Ду100</t>
+        </is>
+      </c>
+      <c r="B19" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="25" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F19" s="25" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>Ду80</t>
+        </is>
+      </c>
+      <c r="B20" s="25" t="n">
+        <v>36</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="D20" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" s="25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F20" s="25" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>Ду60</t>
+        </is>
+      </c>
+      <c r="B21" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F21" s="25" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>Ду50</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F22" s="25" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Крупные от Ду200</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr"/>
+      <c r="C23" s="20" t="inlineStr"/>
+      <c r="D23" s="20" t="inlineStr"/>
+      <c r="E23" s="20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F23" s="20" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Свободный пол</t>
+        </is>
+      </c>
+      <c r="B24" s="27" t="inlineStr"/>
+      <c r="C24" s="27" t="inlineStr"/>
+      <c r="D24" s="27" t="inlineStr"/>
+      <c r="E24" s="27" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>2 мест под ящики на полу</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>— Задвижки от Ду200 просят 9.80 м пола при длине 12.03 м. Они ложатся В ОДИН СЛОЙ, и остается 2.23 м свободного пола.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>— Мелкие задвижки Ду125 и ниже заняли бы еще 2.48 м пола. Их на пол не кладем: они легкие, идут в ящики и наверх. Желтым они и помечены.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>— Габариты справочные, по типовым судовым бронзовым клинкетам. Замерить на первых рядах в день погрузки: справочник уже ошибся на массах почти вдвое.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Чего делать нельзя</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>— Класть фланец на фланец. Ломается не корпус — бронза держит 200 МПа при наших 0,01 — а шток, маховик и привалочная поверхность фланца.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>— Ставить арматуру на арматуру ярусами. Задвижки и тяжелое лежат на полу в один слой, ящики стоят рядом, на ящики идут только фильтры.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>— Класть прокладку под ящик над пустотой: доска 200х25 на пролете 600 мм дает 10,6 МПа изгиба при расчетных 10 для сырой необрезной с сучками. Шаг 300-400 мм и над корпусами.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>— Грузить маховики россыпью. Снимаем в ящик с биркой, иначе задвижка приедет неполной и это станет претензией.</t>
         </is>
@@ -15999,7 +16292,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Заказать доску: 468 кг сырой необрезной</t>
+          <t>Заказать доску: 700 кг сырой необрезной</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">

--- a/outputs/marine_equipment/Контейнер_погрузка.xlsx
+++ b/outputs/marine_equipment/Контейнер_погрузка.xlsx
@@ -127,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -198,6 +198,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -736,7 +739,7 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>34 819 624 руб</t>
+          <t>26 868 206 руб</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -787,7 +790,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>20 757 376 руб</t>
+          <t>28 708 794 руб</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -826,7 +829,7 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>28 позиций, 521 кг</t>
+          <t>91 позиций, 4 623 кг</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
@@ -860,7 +863,7 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>54 позиций, 1 244 кг</t>
+          <t>99 позиций, 4 771 кг</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
@@ -1075,7 +1078,7 @@
         <v>10482</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>5919559</v>
+        <v>3662239</v>
       </c>
       <c r="H6" s="19" t="n">
         <v>570000</v>
@@ -1141,7 +1144,7 @@
         <v>13390</v>
       </c>
       <c r="G8" s="19" t="n">
-        <v>2371037</v>
+        <v>1946758</v>
       </c>
       <c r="H8" s="19" t="n">
         <v>351500</v>
@@ -1174,7 +1177,7 @@
         <v>13428</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>70590</v>
+        <v>39672</v>
       </c>
       <c r="H9" s="19" t="n">
         <v>11000</v>
@@ -1273,7 +1276,7 @@
         <v>15501</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>187370</v>
+        <v>116594</v>
       </c>
       <c r="H12" s="19" t="n">
         <v>0</v>
@@ -1306,7 +1309,7 @@
         <v>15675</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>323518</v>
+        <v>0</v>
       </c>
       <c r="H13" s="19" t="n">
         <v>0</v>
@@ -1339,7 +1342,7 @@
         <v>15692</v>
       </c>
       <c r="G14" s="19" t="n">
-        <v>36763</v>
+        <v>13038</v>
       </c>
       <c r="H14" s="19" t="n">
         <v>5000</v>
@@ -1405,7 +1408,7 @@
         <v>15727</v>
       </c>
       <c r="G16" s="19" t="n">
-        <v>60718</v>
+        <v>0</v>
       </c>
       <c r="H16" s="19" t="n">
         <v>0</v>
@@ -1438,7 +1441,7 @@
         <v>16190</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>582150</v>
+        <v>211890</v>
       </c>
       <c r="H17" s="19" t="n">
         <v>190500</v>
@@ -1471,7 +1474,7 @@
         <v>17427</v>
       </c>
       <c r="G18" s="19" t="n">
-        <v>2046757</v>
+        <v>210820</v>
       </c>
       <c r="H18" s="19" t="n">
         <v>426500</v>
@@ -1504,7 +1507,7 @@
         <v>17520</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>173920</v>
+        <v>158648</v>
       </c>
       <c r="H19" s="19" t="n">
         <v>76000</v>
@@ -1537,7 +1540,7 @@
         <v>17867</v>
       </c>
       <c r="G20" s="19" t="n">
-        <v>645372</v>
+        <v>10244</v>
       </c>
       <c r="H20" s="19" t="n">
         <v>4000</v>
@@ -1570,7 +1573,7 @@
         <v>17919</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>97044</v>
+        <v>0</v>
       </c>
       <c r="H21" s="19" t="n">
         <v>0</v>
@@ -1603,7 +1606,7 @@
         <v>18178</v>
       </c>
       <c r="G22" s="19" t="n">
-        <v>345000</v>
+        <v>0</v>
       </c>
       <c r="H22" s="19" t="n">
         <v>0</v>
@@ -1636,7 +1639,7 @@
         <v>18424</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>441075</v>
+        <v>0</v>
       </c>
       <c r="H23" s="19" t="n">
         <v>0</v>
@@ -1735,7 +1738,7 @@
         <v>18837</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>631950</v>
+        <v>0</v>
       </c>
       <c r="H26" s="19" t="n">
         <v>0</v>
@@ -1768,7 +1771,7 @@
         <v>18923</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>158498</v>
+        <v>0</v>
       </c>
       <c r="H27" s="19" t="n">
         <v>0</v>
@@ -1900,7 +1903,7 @@
         <v>19091</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>230000</v>
+        <v>0</v>
       </c>
       <c r="H31" s="19" t="n">
         <v>0</v>
@@ -1933,7 +1936,7 @@
         <v>19091</v>
       </c>
       <c r="G32" s="21" t="n">
-        <v>34819624</v>
+        <v>26868206</v>
       </c>
       <c r="H32" s="21" t="n">
         <v>3267000</v>
@@ -3176,153 +3179,153 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="24" t="n">
         <v>19</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>Клапан невозвратный Ду 100</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>522-03.205</t>
         </is>
       </c>
-      <c r="D25" s="18" t="n">
+      <c r="D25" s="24" t="n">
         <v>100</v>
       </c>
-      <c r="E25" s="18" t="inlineStr"/>
-      <c r="F25" s="18" t="inlineStr">
+      <c r="E25" s="24" t="inlineStr"/>
+      <c r="F25" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G25" s="18" t="n">
+      <c r="G25" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="H25" s="18" t="n">
+      <c r="H25" s="24" t="n">
         <v>28.8</v>
       </c>
-      <c r="I25" s="18" t="n">
+      <c r="I25" s="24" t="n">
         <v>115</v>
       </c>
-      <c r="J25" s="18" t="inlineStr"/>
-      <c r="K25" s="4" t="inlineStr"/>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>53 640</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr"/>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="O25" s="4" t="inlineStr">
+      <c r="J25" s="24" t="inlineStr"/>
+      <c r="K25" s="14" t="inlineStr"/>
+      <c r="L25" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M25" s="14" t="inlineStr"/>
+      <c r="N25" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O25" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>Клапан невозвратный Ду 100</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>522-01.168</t>
         </is>
       </c>
-      <c r="D26" s="18" t="n">
+      <c r="D26" s="24" t="n">
         <v>100</v>
       </c>
-      <c r="E26" s="18" t="inlineStr"/>
-      <c r="F26" s="18" t="inlineStr">
+      <c r="E26" s="24" t="inlineStr"/>
+      <c r="F26" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G26" s="18" t="n">
+      <c r="G26" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="18" t="n">
+      <c r="H26" s="24" t="n">
         <v>28.8</v>
       </c>
-      <c r="I26" s="18" t="n">
+      <c r="I26" s="24" t="n">
         <v>29</v>
       </c>
-      <c r="J26" s="18" t="inlineStr"/>
-      <c r="K26" s="4" t="inlineStr"/>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>53 640</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr"/>
-      <c r="N26" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="O26" s="4" t="inlineStr">
+      <c r="J26" s="24" t="inlineStr"/>
+      <c r="K26" s="14" t="inlineStr"/>
+      <c r="L26" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M26" s="14" t="inlineStr"/>
+      <c r="N26" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O26" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="24" t="n">
         <v>21</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>Клапан фланцевый проходной Ду50</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>521-35.3442</t>
         </is>
       </c>
-      <c r="D27" s="18" t="n">
+      <c r="D27" s="24" t="n">
         <v>50</v>
       </c>
-      <c r="E27" s="18" t="inlineStr"/>
-      <c r="F27" s="18" t="inlineStr">
+      <c r="E27" s="24" t="inlineStr"/>
+      <c r="F27" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G27" s="18" t="n">
+      <c r="G27" s="24" t="n">
         <v>60</v>
       </c>
-      <c r="H27" s="18" t="n">
+      <c r="H27" s="24" t="n">
         <v>17.8</v>
       </c>
-      <c r="I27" s="18" t="n">
+      <c r="I27" s="24" t="n">
         <v>1068</v>
       </c>
-      <c r="J27" s="18" t="inlineStr"/>
-      <c r="K27" s="4" t="inlineStr"/>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>33 152</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr"/>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="J27" s="24" t="inlineStr"/>
+      <c r="K27" s="14" t="inlineStr"/>
+      <c r="L27" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M27" s="14" t="inlineStr"/>
+      <c r="N27" s="14" t="inlineStr">
         <is>
           <t>55 000</t>
         </is>
       </c>
-      <c r="O27" s="4" t="inlineStr">
+      <c r="O27" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5507,51 +5510,51 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="18" t="n">
+      <c r="A68" s="24" t="n">
         <v>60</v>
       </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="B68" s="15" t="inlineStr">
         <is>
           <t>Клапан фланцевый угловой Ду80</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C68" s="14" t="inlineStr">
         <is>
           <t>522-01.244</t>
         </is>
       </c>
-      <c r="D68" s="18" t="n">
+      <c r="D68" s="24" t="n">
         <v>80</v>
       </c>
-      <c r="E68" s="18" t="inlineStr"/>
-      <c r="F68" s="18" t="inlineStr">
+      <c r="E68" s="24" t="inlineStr"/>
+      <c r="F68" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G68" s="18" t="n">
+      <c r="G68" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H68" s="18" t="n">
+      <c r="H68" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="I68" s="18" t="n">
+      <c r="I68" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="J68" s="18" t="inlineStr"/>
-      <c r="K68" s="4" t="inlineStr"/>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>37 250</t>
-        </is>
-      </c>
-      <c r="M68" s="4" t="inlineStr"/>
-      <c r="N68" s="4" t="inlineStr">
+      <c r="J68" s="24" t="inlineStr"/>
+      <c r="K68" s="14" t="inlineStr"/>
+      <c r="L68" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M68" s="14" t="inlineStr"/>
+      <c r="N68" s="14" t="inlineStr">
         <is>
           <t>70 000</t>
         </is>
       </c>
-      <c r="O68" s="4" t="inlineStr">
+      <c r="O68" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5613,51 +5616,51 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="18" t="n">
+      <c r="A70" s="24" t="n">
         <v>62</v>
       </c>
-      <c r="B70" s="5" t="inlineStr">
+      <c r="B70" s="15" t="inlineStr">
         <is>
           <t>Клапан фланцевый угловой Ду80</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C70" s="14" t="inlineStr">
         <is>
           <t>522-03.196</t>
         </is>
       </c>
-      <c r="D70" s="18" t="n">
+      <c r="D70" s="24" t="n">
         <v>80</v>
       </c>
-      <c r="E70" s="18" t="inlineStr"/>
-      <c r="F70" s="18" t="inlineStr">
+      <c r="E70" s="24" t="inlineStr"/>
+      <c r="F70" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G70" s="18" t="n">
+      <c r="G70" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="H70" s="18" t="n">
+      <c r="H70" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="I70" s="18" t="n">
+      <c r="I70" s="24" t="n">
         <v>80</v>
       </c>
-      <c r="J70" s="18" t="inlineStr"/>
-      <c r="K70" s="4" t="inlineStr"/>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>37 250</t>
-        </is>
-      </c>
-      <c r="M70" s="4" t="inlineStr"/>
-      <c r="N70" s="4" t="inlineStr">
+      <c r="J70" s="24" t="inlineStr"/>
+      <c r="K70" s="14" t="inlineStr"/>
+      <c r="L70" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M70" s="14" t="inlineStr"/>
+      <c r="N70" s="14" t="inlineStr">
         <is>
           <t>70 000</t>
         </is>
       </c>
-      <c r="O70" s="4" t="inlineStr">
+      <c r="O70" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5723,110 +5726,110 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="18" t="n">
+      <c r="A72" s="24" t="n">
         <v>64</v>
       </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B72" s="15" t="inlineStr">
         <is>
           <t>Клапан фланцевый угловой Ду80</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C72" s="14" t="inlineStr">
         <is>
           <t>521-01.150</t>
         </is>
       </c>
-      <c r="D72" s="18" t="n">
+      <c r="D72" s="24" t="n">
         <v>80</v>
       </c>
-      <c r="E72" s="18" t="inlineStr">
+      <c r="E72" s="24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F72" s="18" t="inlineStr">
+      <c r="F72" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G72" s="18" t="n">
+      <c r="G72" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H72" s="18" t="n">
+      <c r="H72" s="24" t="n">
         <v>18.7</v>
       </c>
-      <c r="I72" s="18" t="n">
+      <c r="I72" s="24" t="n">
         <v>19</v>
       </c>
-      <c r="J72" s="18" t="inlineStr"/>
-      <c r="K72" s="4" t="inlineStr"/>
-      <c r="L72" s="4" t="inlineStr">
-        <is>
-          <t>34 829</t>
-        </is>
-      </c>
-      <c r="M72" s="4" t="inlineStr"/>
-      <c r="N72" s="4" t="inlineStr">
+      <c r="J72" s="24" t="inlineStr"/>
+      <c r="K72" s="14" t="inlineStr"/>
+      <c r="L72" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M72" s="14" t="inlineStr"/>
+      <c r="N72" s="14" t="inlineStr">
         <is>
           <t>70 000</t>
         </is>
       </c>
-      <c r="O72" s="4" t="inlineStr">
+      <c r="O72" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="18" t="n">
+      <c r="A73" s="24" t="n">
         <v>65</v>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B73" s="15" t="inlineStr">
         <is>
           <t>Клапан фланцевый угловой Ду80</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C73" s="14" t="inlineStr">
         <is>
           <t>521-01.150-02</t>
         </is>
       </c>
-      <c r="D73" s="18" t="n">
+      <c r="D73" s="24" t="n">
         <v>80</v>
       </c>
-      <c r="E73" s="18" t="inlineStr">
+      <c r="E73" s="24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F73" s="18" t="inlineStr">
+      <c r="F73" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G73" s="18" t="n">
+      <c r="G73" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="H73" s="18" t="n">
+      <c r="H73" s="24" t="n">
         <v>18.7</v>
       </c>
-      <c r="I73" s="18" t="n">
+      <c r="I73" s="24" t="n">
         <v>37</v>
       </c>
-      <c r="J73" s="18" t="inlineStr"/>
-      <c r="K73" s="4" t="inlineStr"/>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>34 829</t>
-        </is>
-      </c>
-      <c r="M73" s="4" t="inlineStr"/>
-      <c r="N73" s="4" t="inlineStr">
+      <c r="J73" s="24" t="inlineStr"/>
+      <c r="K73" s="14" t="inlineStr"/>
+      <c r="L73" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M73" s="14" t="inlineStr"/>
+      <c r="N73" s="14" t="inlineStr">
         <is>
           <t>70 000</t>
         </is>
       </c>
-      <c r="O73" s="4" t="inlineStr">
+      <c r="O73" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -5892,55 +5895,55 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="18" t="n">
+      <c r="A75" s="24" t="n">
         <v>67</v>
       </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B75" s="15" t="inlineStr">
         <is>
           <t>Клапан фланцевый угловой Ду80</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C75" s="14" t="inlineStr">
         <is>
           <t>521-35.011</t>
         </is>
       </c>
-      <c r="D75" s="18" t="n">
+      <c r="D75" s="24" t="n">
         <v>80</v>
       </c>
-      <c r="E75" s="18" t="inlineStr">
+      <c r="E75" s="24" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F75" s="18" t="inlineStr">
+      <c r="F75" s="24" t="inlineStr">
         <is>
           <t>новая</t>
         </is>
       </c>
-      <c r="G75" s="18" t="n">
+      <c r="G75" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H75" s="18" t="n">
+      <c r="H75" s="24" t="n">
         <v>25.5</v>
       </c>
-      <c r="I75" s="18" t="n">
+      <c r="I75" s="24" t="n">
         <v>26</v>
       </c>
-      <c r="J75" s="18" t="inlineStr"/>
-      <c r="K75" s="4" t="inlineStr"/>
-      <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t>47 494</t>
-        </is>
-      </c>
-      <c r="M75" s="4" t="inlineStr"/>
-      <c r="N75" s="4" t="inlineStr">
+      <c r="J75" s="24" t="inlineStr"/>
+      <c r="K75" s="14" t="inlineStr"/>
+      <c r="L75" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M75" s="14" t="inlineStr"/>
+      <c r="N75" s="14" t="inlineStr">
         <is>
           <t>70 000</t>
         </is>
       </c>
-      <c r="O75" s="4" t="inlineStr">
+      <c r="O75" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6120,55 +6123,55 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="18" t="n">
+      <c r="A79" s="24" t="n">
         <v>71</v>
       </c>
-      <c r="B79" s="5" t="inlineStr">
+      <c r="B79" s="15" t="inlineStr">
         <is>
           <t>Клапан фланцевый угловой Ду65 Ру40</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C79" s="14" t="inlineStr">
         <is>
           <t>521-03.230</t>
         </is>
       </c>
-      <c r="D79" s="18" t="n">
+      <c r="D79" s="24" t="n">
         <v>65</v>
       </c>
-      <c r="E79" s="18" t="inlineStr">
+      <c r="E79" s="24" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="F79" s="18" t="inlineStr">
+      <c r="F79" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G79" s="18" t="n">
+      <c r="G79" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H79" s="18" t="n">
+      <c r="H79" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="I79" s="18" t="n">
+      <c r="I79" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="J79" s="18" t="inlineStr"/>
-      <c r="K79" s="4" t="inlineStr"/>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>37 250</t>
-        </is>
-      </c>
-      <c r="M79" s="4" t="inlineStr"/>
-      <c r="N79" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="O79" s="4" t="inlineStr">
+      <c r="J79" s="24" t="inlineStr"/>
+      <c r="K79" s="14" t="inlineStr"/>
+      <c r="L79" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M79" s="14" t="inlineStr"/>
+      <c r="N79" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O79" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6344,55 +6347,55 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="18" t="n">
+      <c r="A83" s="24" t="n">
         <v>75</v>
       </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="B83" s="15" t="inlineStr">
         <is>
           <t>Клапан фланцевый угловой Ду40 РУ 25</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C83" s="14" t="inlineStr">
         <is>
           <t>522-35.446</t>
         </is>
       </c>
-      <c r="D83" s="18" t="n">
+      <c r="D83" s="24" t="n">
         <v>40</v>
       </c>
-      <c r="E83" s="18" t="inlineStr">
+      <c r="E83" s="24" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F83" s="18" t="inlineStr">
+      <c r="F83" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G83" s="18" t="n">
+      <c r="G83" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="H83" s="18" t="n">
+      <c r="H83" s="24" t="n">
         <v>13.1</v>
       </c>
-      <c r="I83" s="18" t="n">
+      <c r="I83" s="24" t="n">
         <v>26</v>
       </c>
-      <c r="J83" s="18" t="inlineStr"/>
-      <c r="K83" s="4" t="inlineStr"/>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>24 399</t>
-        </is>
-      </c>
-      <c r="M83" s="4" t="inlineStr"/>
-      <c r="N83" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="O83" s="4" t="inlineStr">
+      <c r="J83" s="24" t="inlineStr"/>
+      <c r="K83" s="14" t="inlineStr"/>
+      <c r="L83" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M83" s="14" t="inlineStr"/>
+      <c r="N83" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O83" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -6589,110 +6592,110 @@
       <c r="O87" s="23" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="18" t="n">
+      <c r="A88" s="24" t="n">
         <v>79</v>
       </c>
-      <c r="B88" s="5" t="inlineStr">
+      <c r="B88" s="15" t="inlineStr">
         <is>
           <t>Клапан фланц.  пожарный угловой Ду32 Ру10</t>
         </is>
       </c>
-      <c r="C88" s="4" t="inlineStr">
+      <c r="C88" s="14" t="inlineStr">
         <is>
           <t>595-03-006</t>
         </is>
       </c>
-      <c r="D88" s="18" t="n">
+      <c r="D88" s="24" t="n">
         <v>32</v>
       </c>
-      <c r="E88" s="18" t="inlineStr">
+      <c r="E88" s="24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F88" s="18" t="inlineStr">
+      <c r="F88" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G88" s="18" t="n">
+      <c r="G88" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H88" s="18" t="n">
+      <c r="H88" s="24" t="n">
         <v>5.8</v>
       </c>
-      <c r="I88" s="18" t="n">
+      <c r="I88" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="J88" s="18" t="inlineStr"/>
-      <c r="K88" s="4" t="inlineStr"/>
-      <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t>10 802</t>
-        </is>
-      </c>
-      <c r="M88" s="4" t="inlineStr"/>
-      <c r="N88" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="O88" s="4" t="inlineStr">
+      <c r="J88" s="24" t="inlineStr"/>
+      <c r="K88" s="14" t="inlineStr"/>
+      <c r="L88" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M88" s="14" t="inlineStr"/>
+      <c r="N88" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O88" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="18" t="n">
+      <c r="A89" s="24" t="n">
         <v>80</v>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B89" s="15" t="inlineStr">
         <is>
           <t>Клапан фланц. пожарный угловой Ду32 Ру16</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
+      <c r="C89" s="14" t="inlineStr">
         <is>
           <t>595-01-010</t>
         </is>
       </c>
-      <c r="D89" s="18" t="n">
+      <c r="D89" s="24" t="n">
         <v>32</v>
       </c>
-      <c r="E89" s="18" t="inlineStr">
+      <c r="E89" s="24" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F89" s="18" t="inlineStr">
+      <c r="F89" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G89" s="18" t="n">
+      <c r="G89" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="H89" s="18" t="n">
+      <c r="H89" s="24" t="n">
         <v>5.4</v>
       </c>
-      <c r="I89" s="18" t="n">
+      <c r="I89" s="24" t="n">
         <v>11</v>
       </c>
-      <c r="J89" s="18" t="inlineStr"/>
-      <c r="K89" s="4" t="inlineStr"/>
-      <c r="L89" s="4" t="inlineStr">
-        <is>
-          <t>10 058</t>
-        </is>
-      </c>
-      <c r="M89" s="4" t="inlineStr"/>
-      <c r="N89" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="O89" s="4" t="inlineStr">
+      <c r="J89" s="24" t="inlineStr"/>
+      <c r="K89" s="14" t="inlineStr"/>
+      <c r="L89" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M89" s="14" t="inlineStr"/>
+      <c r="N89" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O89" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -7834,55 +7837,55 @@
       <c r="O112" s="23" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="18" t="n">
+      <c r="A113" s="24" t="n">
         <v>101</v>
       </c>
-      <c r="B113" s="5" t="inlineStr">
+      <c r="B113" s="15" t="inlineStr">
         <is>
           <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
         </is>
       </c>
-      <c r="C113" s="4" t="inlineStr">
+      <c r="C113" s="14" t="inlineStr">
         <is>
           <t>527-03.055</t>
         </is>
       </c>
-      <c r="D113" s="18" t="n">
+      <c r="D113" s="24" t="n">
         <v>80</v>
       </c>
-      <c r="E113" s="18" t="inlineStr">
+      <c r="E113" s="24" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F113" s="18" t="inlineStr">
+      <c r="F113" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G113" s="18" t="n">
+      <c r="G113" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="H113" s="18" t="n">
+      <c r="H113" s="24" t="n">
         <v>19</v>
       </c>
-      <c r="I113" s="18" t="n">
+      <c r="I113" s="24" t="n">
         <v>38</v>
       </c>
-      <c r="J113" s="18" t="inlineStr"/>
-      <c r="K113" s="4" t="inlineStr"/>
-      <c r="L113" s="4" t="inlineStr">
-        <is>
-          <t>35 388</t>
-        </is>
-      </c>
-      <c r="M113" s="4" t="inlineStr"/>
-      <c r="N113" s="4" t="inlineStr">
+      <c r="J113" s="24" t="inlineStr"/>
+      <c r="K113" s="14" t="inlineStr"/>
+      <c r="L113" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M113" s="14" t="inlineStr"/>
+      <c r="N113" s="14" t="inlineStr">
         <is>
           <t>95 000</t>
         </is>
       </c>
-      <c r="O113" s="4" t="inlineStr">
+      <c r="O113" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8130,403 +8133,403 @@
       <c r="O118" s="23" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="18" t="n">
+      <c r="A119" s="24" t="n">
         <v>106</v>
       </c>
-      <c r="B119" s="5" t="inlineStr">
+      <c r="B119" s="15" t="inlineStr">
         <is>
           <t>Клапан запорн.с присоед.под дюрит прох. Ду65</t>
         </is>
       </c>
-      <c r="C119" s="4" t="inlineStr">
+      <c r="C119" s="14" t="inlineStr">
         <is>
           <t>ИШТЛ.491112-003.04</t>
         </is>
       </c>
-      <c r="D119" s="18" t="n">
+      <c r="D119" s="24" t="n">
         <v>65</v>
       </c>
-      <c r="E119" s="18" t="inlineStr">
+      <c r="E119" s="24" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F119" s="18" t="inlineStr">
+      <c r="F119" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G119" s="18" t="n">
+      <c r="G119" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="H119" s="18" t="n">
+      <c r="H119" s="24" t="n">
         <v>5.7</v>
       </c>
-      <c r="I119" s="18" t="n">
+      <c r="I119" s="24" t="n">
         <v>28</v>
       </c>
-      <c r="J119" s="18" t="n">
+      <c r="J119" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="K119" s="4" t="inlineStr"/>
-      <c r="L119" s="4" t="inlineStr">
-        <is>
-          <t>10 616</t>
-        </is>
-      </c>
-      <c r="M119" s="4" t="inlineStr"/>
-      <c r="N119" s="4" t="inlineStr">
+      <c r="K119" s="14" t="inlineStr"/>
+      <c r="L119" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M119" s="14" t="inlineStr"/>
+      <c r="N119" s="14" t="inlineStr">
         <is>
           <t>75 000</t>
         </is>
       </c>
-      <c r="O119" s="4" t="inlineStr">
+      <c r="O119" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="18" t="n">
+      <c r="A120" s="24" t="n">
         <v>107</v>
       </c>
-      <c r="B120" s="5" t="inlineStr">
+      <c r="B120" s="15" t="inlineStr">
         <is>
           <t>Клапан запорн.с присоед.под дюрит прох. Ду65</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr">
+      <c r="C120" s="14" t="inlineStr">
         <is>
           <t>521-03.442-04</t>
         </is>
       </c>
-      <c r="D120" s="18" t="n">
+      <c r="D120" s="24" t="n">
         <v>65</v>
       </c>
-      <c r="E120" s="18" t="inlineStr">
+      <c r="E120" s="24" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F120" s="18" t="inlineStr">
+      <c r="F120" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G120" s="18" t="n">
+      <c r="G120" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="H120" s="18" t="n">
+      <c r="H120" s="24" t="n">
         <v>5.7</v>
       </c>
-      <c r="I120" s="18" t="n">
+      <c r="I120" s="24" t="n">
         <v>28</v>
       </c>
-      <c r="J120" s="18" t="n">
+      <c r="J120" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="K120" s="4" t="inlineStr"/>
-      <c r="L120" s="4" t="inlineStr">
-        <is>
-          <t>10 616</t>
-        </is>
-      </c>
-      <c r="M120" s="4" t="inlineStr"/>
-      <c r="N120" s="4" t="inlineStr">
+      <c r="K120" s="14" t="inlineStr"/>
+      <c r="L120" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M120" s="14" t="inlineStr"/>
+      <c r="N120" s="14" t="inlineStr">
         <is>
           <t>75 000</t>
         </is>
       </c>
-      <c r="O120" s="4" t="inlineStr">
+      <c r="O120" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="18" t="n">
+      <c r="A121" s="24" t="n">
         <v>108</v>
       </c>
-      <c r="B121" s="5" t="inlineStr">
+      <c r="B121" s="15" t="inlineStr">
         <is>
           <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50</t>
         </is>
       </c>
-      <c r="C121" s="4" t="inlineStr">
+      <c r="C121" s="14" t="inlineStr">
         <is>
           <t>521-03.442-03</t>
         </is>
       </c>
-      <c r="D121" s="18" t="n">
+      <c r="D121" s="24" t="n">
         <v>50</v>
       </c>
-      <c r="E121" s="18" t="inlineStr">
+      <c r="E121" s="24" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F121" s="18" t="inlineStr">
+      <c r="F121" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G121" s="18" t="n">
+      <c r="G121" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="H121" s="18" t="n">
+      <c r="H121" s="24" t="n">
         <v>5.5</v>
       </c>
-      <c r="I121" s="18" t="n">
+      <c r="I121" s="24" t="n">
         <v>55</v>
       </c>
-      <c r="J121" s="18" t="n">
+      <c r="J121" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="K121" s="4" t="inlineStr"/>
-      <c r="L121" s="4" t="inlineStr">
-        <is>
-          <t>10 244</t>
-        </is>
-      </c>
-      <c r="M121" s="4" t="inlineStr"/>
-      <c r="N121" s="4" t="inlineStr">
+      <c r="K121" s="14" t="inlineStr"/>
+      <c r="L121" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M121" s="14" t="inlineStr"/>
+      <c r="N121" s="14" t="inlineStr">
         <is>
           <t>55 000</t>
         </is>
       </c>
-      <c r="O121" s="4" t="inlineStr">
+      <c r="O121" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="18" t="n">
+      <c r="A122" s="24" t="n">
         <v>109</v>
       </c>
-      <c r="B122" s="5" t="inlineStr">
+      <c r="B122" s="15" t="inlineStr">
         <is>
           <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50</t>
         </is>
       </c>
-      <c r="C122" s="4" t="inlineStr">
+      <c r="C122" s="14" t="inlineStr">
         <is>
           <t>ИШТЛ.491912-002.04</t>
         </is>
       </c>
-      <c r="D122" s="18" t="n">
+      <c r="D122" s="24" t="n">
         <v>50</v>
       </c>
-      <c r="E122" s="18" t="inlineStr">
+      <c r="E122" s="24" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F122" s="18" t="inlineStr">
+      <c r="F122" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G122" s="18" t="n">
+      <c r="G122" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="H122" s="18" t="n">
+      <c r="H122" s="24" t="n">
         <v>5.5</v>
       </c>
-      <c r="I122" s="18" t="n">
+      <c r="I122" s="24" t="n">
         <v>28</v>
       </c>
-      <c r="J122" s="18" t="n">
+      <c r="J122" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="K122" s="4" t="inlineStr"/>
-      <c r="L122" s="4" t="inlineStr">
-        <is>
-          <t>10 244</t>
-        </is>
-      </c>
-      <c r="M122" s="4" t="inlineStr"/>
-      <c r="N122" s="4" t="inlineStr">
+      <c r="K122" s="14" t="inlineStr"/>
+      <c r="L122" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M122" s="14" t="inlineStr"/>
+      <c r="N122" s="14" t="inlineStr">
         <is>
           <t>55 000</t>
         </is>
       </c>
-      <c r="O122" s="4" t="inlineStr">
+      <c r="O122" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="18" t="n">
+      <c r="A123" s="24" t="n">
         <v>110</v>
       </c>
-      <c r="B123" s="5" t="inlineStr">
+      <c r="B123" s="15" t="inlineStr">
         <is>
           <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50</t>
         </is>
       </c>
-      <c r="C123" s="4" t="inlineStr">
+      <c r="C123" s="14" t="inlineStr">
         <is>
           <t>ИШТЛ.491112-003.03</t>
         </is>
       </c>
-      <c r="D123" s="18" t="n">
+      <c r="D123" s="24" t="n">
         <v>50</v>
       </c>
-      <c r="E123" s="18" t="inlineStr">
+      <c r="E123" s="24" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F123" s="18" t="inlineStr">
+      <c r="F123" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G123" s="18" t="n">
+      <c r="G123" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="H123" s="18" t="n">
+      <c r="H123" s="24" t="n">
         <v>5.5</v>
       </c>
-      <c r="I123" s="18" t="n">
+      <c r="I123" s="24" t="n">
         <v>28</v>
       </c>
-      <c r="J123" s="18" t="n">
+      <c r="J123" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="K123" s="4" t="inlineStr"/>
-      <c r="L123" s="4" t="inlineStr">
-        <is>
-          <t>10 244</t>
-        </is>
-      </c>
-      <c r="M123" s="4" t="inlineStr"/>
-      <c r="N123" s="4" t="inlineStr">
+      <c r="K123" s="14" t="inlineStr"/>
+      <c r="L123" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M123" s="14" t="inlineStr"/>
+      <c r="N123" s="14" t="inlineStr">
         <is>
           <t>55 000</t>
         </is>
       </c>
-      <c r="O123" s="4" t="inlineStr">
+      <c r="O123" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="18" t="n">
+      <c r="A124" s="24" t="n">
         <v>111</v>
       </c>
-      <c r="B124" s="5" t="inlineStr">
+      <c r="B124" s="15" t="inlineStr">
         <is>
           <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50 Ру6</t>
         </is>
       </c>
-      <c r="C124" s="4" t="inlineStr">
+      <c r="C124" s="14" t="inlineStr">
         <is>
           <t>522-03.124-04</t>
         </is>
       </c>
-      <c r="D124" s="18" t="n">
+      <c r="D124" s="24" t="n">
         <v>50</v>
       </c>
-      <c r="E124" s="18" t="inlineStr">
+      <c r="E124" s="24" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F124" s="18" t="inlineStr">
+      <c r="F124" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G124" s="18" t="n">
+      <c r="G124" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H124" s="18" t="n">
+      <c r="H124" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="I124" s="18" t="n">
+      <c r="I124" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J124" s="18" t="inlineStr"/>
-      <c r="K124" s="4" t="inlineStr">
+      <c r="J124" s="24" t="inlineStr"/>
+      <c r="K124" s="14" t="inlineStr">
         <is>
           <t>коробка №7</t>
         </is>
       </c>
-      <c r="L124" s="4" t="inlineStr">
-        <is>
-          <t>2 794</t>
-        </is>
-      </c>
-      <c r="M124" s="4" t="inlineStr"/>
-      <c r="N124" s="4" t="inlineStr">
+      <c r="L124" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M124" s="14" t="inlineStr"/>
+      <c r="N124" s="14" t="inlineStr">
         <is>
           <t>45 000</t>
         </is>
       </c>
-      <c r="O124" s="4" t="inlineStr">
+      <c r="O124" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="18" t="n">
+      <c r="A125" s="24" t="n">
         <v>112</v>
       </c>
-      <c r="B125" s="5" t="inlineStr">
+      <c r="B125" s="15" t="inlineStr">
         <is>
           <t>Клапан угловой с присоединением под дюрит Ду50Ру4</t>
         </is>
       </c>
-      <c r="C125" s="4" t="inlineStr">
+      <c r="C125" s="14" t="inlineStr">
         <is>
           <t>521-03.445-04</t>
         </is>
       </c>
-      <c r="D125" s="18" t="n">
+      <c r="D125" s="24" t="n">
         <v>50</v>
       </c>
-      <c r="E125" s="18" t="inlineStr">
+      <c r="E125" s="24" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F125" s="18" t="inlineStr">
+      <c r="F125" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G125" s="18" t="n">
+      <c r="G125" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="H125" s="18" t="n">
+      <c r="H125" s="24" t="n">
         <v>1.3</v>
       </c>
-      <c r="I125" s="18" t="n">
+      <c r="I125" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="J125" s="18" t="inlineStr"/>
-      <c r="K125" s="4" t="inlineStr">
+      <c r="J125" s="24" t="inlineStr"/>
+      <c r="K125" s="14" t="inlineStr">
         <is>
           <t>коробка №7</t>
         </is>
       </c>
-      <c r="L125" s="4" t="inlineStr">
-        <is>
-          <t>2 421</t>
-        </is>
-      </c>
-      <c r="M125" s="4" t="inlineStr"/>
-      <c r="N125" s="4" t="inlineStr">
+      <c r="L125" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M125" s="14" t="inlineStr"/>
+      <c r="N125" s="14" t="inlineStr">
         <is>
           <t>40 000</t>
         </is>
       </c>
-      <c r="O125" s="4" t="inlineStr">
+      <c r="O125" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8554,177 +8557,177 @@
       <c r="O126" s="23" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="18" t="n">
+      <c r="A127" s="24" t="n">
         <v>113</v>
       </c>
-      <c r="B127" s="5" t="inlineStr">
+      <c r="B127" s="15" t="inlineStr">
         <is>
           <t>Клапан предохранительный штуцерный сигнальный Ду10Ру1,3-6,5</t>
         </is>
       </c>
-      <c r="C127" s="4" t="inlineStr">
+      <c r="C127" s="14" t="inlineStr">
         <is>
           <t>524-03.174</t>
         </is>
       </c>
-      <c r="D127" s="18" t="n">
+      <c r="D127" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="E127" s="18" t="inlineStr">
+      <c r="E127" s="24" t="inlineStr">
         <is>
           <t>1,3-6,5</t>
         </is>
       </c>
-      <c r="F127" s="18" t="inlineStr">
+      <c r="F127" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G127" s="18" t="n">
+      <c r="G127" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H127" s="18" t="n">
+      <c r="H127" s="24" t="n">
         <v>0.8</v>
       </c>
-      <c r="I127" s="18" t="n">
+      <c r="I127" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J127" s="18" t="inlineStr"/>
-      <c r="K127" s="4" t="inlineStr">
+      <c r="J127" s="24" t="inlineStr"/>
+      <c r="K127" s="14" t="inlineStr">
         <is>
           <t>коробка №5</t>
         </is>
       </c>
-      <c r="L127" s="4" t="inlineStr">
-        <is>
-          <t>1 490</t>
-        </is>
-      </c>
-      <c r="M127" s="4" t="inlineStr"/>
-      <c r="N127" s="4" t="inlineStr">
+      <c r="L127" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M127" s="14" t="inlineStr"/>
+      <c r="N127" s="14" t="inlineStr">
         <is>
           <t>15 000</t>
         </is>
       </c>
-      <c r="O127" s="4" t="inlineStr">
+      <c r="O127" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="18" t="n">
+      <c r="A128" s="24" t="n">
         <v>114</v>
       </c>
-      <c r="B128" s="5" t="inlineStr">
+      <c r="B128" s="15" t="inlineStr">
         <is>
           <t>Клапан предохранительный штуцерный сигнальный Ду10Ру2,5-6,5</t>
         </is>
       </c>
-      <c r="C128" s="4" t="inlineStr">
+      <c r="C128" s="14" t="inlineStr">
         <is>
           <t>524-03.173</t>
         </is>
       </c>
-      <c r="D128" s="18" t="n">
+      <c r="D128" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="E128" s="18" t="inlineStr">
+      <c r="E128" s="24" t="inlineStr">
         <is>
           <t>2,5-6,5</t>
         </is>
       </c>
-      <c r="F128" s="18" t="inlineStr">
+      <c r="F128" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G128" s="18" t="n">
+      <c r="G128" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H128" s="18" t="n">
+      <c r="H128" s="24" t="n">
         <v>1.2</v>
       </c>
-      <c r="I128" s="18" t="n">
+      <c r="I128" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J128" s="18" t="inlineStr"/>
-      <c r="K128" s="4" t="inlineStr">
+      <c r="J128" s="24" t="inlineStr"/>
+      <c r="K128" s="14" t="inlineStr">
         <is>
           <t>коробка №5</t>
         </is>
       </c>
-      <c r="L128" s="4" t="inlineStr">
-        <is>
-          <t>2 235</t>
-        </is>
-      </c>
-      <c r="M128" s="4" t="inlineStr"/>
-      <c r="N128" s="4" t="inlineStr">
+      <c r="L128" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M128" s="14" t="inlineStr"/>
+      <c r="N128" s="14" t="inlineStr">
         <is>
           <t>15 000</t>
         </is>
       </c>
-      <c r="O128" s="4" t="inlineStr">
+      <c r="O128" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="18" t="n">
+      <c r="A129" s="24" t="n">
         <v>115</v>
       </c>
-      <c r="B129" s="5" t="inlineStr">
+      <c r="B129" s="15" t="inlineStr">
         <is>
           <t>Клапан предохранительный штуцерный сигнальный Ду6 Ру100-230</t>
         </is>
       </c>
-      <c r="C129" s="4" t="inlineStr">
+      <c r="C129" s="14" t="inlineStr">
         <is>
           <t>524-35.2423-01</t>
         </is>
       </c>
-      <c r="D129" s="18" t="n">
+      <c r="D129" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="E129" s="18" t="inlineStr">
+      <c r="E129" s="24" t="inlineStr">
         <is>
           <t>100-230</t>
         </is>
       </c>
-      <c r="F129" s="18" t="inlineStr">
+      <c r="F129" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G129" s="18" t="n">
+      <c r="G129" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H129" s="18" t="n">
+      <c r="H129" s="24" t="n">
         <v>3.5</v>
       </c>
-      <c r="I129" s="18" t="n">
+      <c r="I129" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="J129" s="18" t="inlineStr"/>
-      <c r="K129" s="4" t="inlineStr">
+      <c r="J129" s="24" t="inlineStr"/>
+      <c r="K129" s="14" t="inlineStr">
         <is>
           <t>коробка №5</t>
         </is>
       </c>
-      <c r="L129" s="4" t="inlineStr">
-        <is>
-          <t>20 000</t>
-        </is>
-      </c>
-      <c r="M129" s="4" t="inlineStr"/>
-      <c r="N129" s="4" t="inlineStr">
+      <c r="L129" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M129" s="14" t="inlineStr"/>
+      <c r="N129" s="14" t="inlineStr">
         <is>
           <t>55 000</t>
         </is>
       </c>
-      <c r="O129" s="4" t="inlineStr">
+      <c r="O129" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -8950,55 +8953,55 @@
       <c r="O134" s="23" t="n"/>
     </row>
     <row r="135">
-      <c r="A135" s="18" t="n">
+      <c r="A135" s="24" t="n">
         <v>119</v>
       </c>
-      <c r="B135" s="5" t="inlineStr">
+      <c r="B135" s="15" t="inlineStr">
         <is>
           <t>Клапан паровой Ду65Ру10</t>
         </is>
       </c>
-      <c r="C135" s="4" t="inlineStr">
+      <c r="C135" s="14" t="inlineStr">
         <is>
           <t>581-03.034</t>
         </is>
       </c>
-      <c r="D135" s="18" t="n">
+      <c r="D135" s="24" t="n">
         <v>65</v>
       </c>
-      <c r="E135" s="18" t="inlineStr">
+      <c r="E135" s="24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F135" s="18" t="inlineStr">
+      <c r="F135" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G135" s="18" t="n">
+      <c r="G135" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H135" s="18" t="n">
+      <c r="H135" s="24" t="n">
         <v>32.6</v>
       </c>
-      <c r="I135" s="18" t="n">
+      <c r="I135" s="24" t="n">
         <v>33</v>
       </c>
-      <c r="J135" s="18" t="inlineStr"/>
-      <c r="K135" s="4" t="inlineStr"/>
-      <c r="L135" s="4" t="inlineStr">
-        <is>
-          <t>60 718</t>
-        </is>
-      </c>
-      <c r="M135" s="4" t="inlineStr"/>
-      <c r="N135" s="4" t="inlineStr">
+      <c r="J135" s="24" t="inlineStr"/>
+      <c r="K135" s="14" t="inlineStr"/>
+      <c r="L135" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M135" s="14" t="inlineStr"/>
+      <c r="N135" s="14" t="inlineStr">
         <is>
           <t>160 000</t>
         </is>
       </c>
-      <c r="O135" s="4" t="inlineStr">
+      <c r="O135" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9136,240 +9139,240 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="18" t="n">
+      <c r="A139" s="24" t="n">
         <v>122</v>
       </c>
-      <c r="B139" s="5" t="inlineStr">
+      <c r="B139" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный угловой Ду32 Ру100</t>
         </is>
       </c>
-      <c r="C139" s="4" t="inlineStr">
+      <c r="C139" s="14" t="inlineStr">
         <is>
           <t>521-01.468-07</t>
         </is>
       </c>
-      <c r="D139" s="18" t="n">
+      <c r="D139" s="24" t="n">
         <v>32</v>
       </c>
-      <c r="E139" s="18" t="inlineStr">
+      <c r="E139" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F139" s="18" t="inlineStr">
+      <c r="F139" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G139" s="18" t="n">
+      <c r="G139" s="24" t="n">
         <v>31</v>
       </c>
-      <c r="H139" s="18" t="n">
+      <c r="H139" s="24" t="n">
         <v>3.3</v>
       </c>
-      <c r="I139" s="18" t="n">
+      <c r="I139" s="24" t="n">
         <v>102</v>
       </c>
-      <c r="J139" s="18" t="n">
+      <c r="J139" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="K139" s="4" t="inlineStr">
+      <c r="K139" s="14" t="inlineStr">
         <is>
           <t>ящик №1</t>
         </is>
       </c>
-      <c r="L139" s="4" t="inlineStr">
-        <is>
-          <t>6 500</t>
-        </is>
-      </c>
-      <c r="M139" s="4" t="inlineStr"/>
-      <c r="N139" s="4" t="inlineStr">
+      <c r="L139" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M139" s="14" t="inlineStr"/>
+      <c r="N139" s="14" t="inlineStr">
         <is>
           <t>22 000</t>
         </is>
       </c>
-      <c r="O139" s="4" t="inlineStr">
+      <c r="O139" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="18" t="n">
+      <c r="A140" s="24" t="n">
         <v>123</v>
       </c>
-      <c r="B140" s="5" t="inlineStr">
+      <c r="B140" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный угловой Ду32Ру100</t>
         </is>
       </c>
-      <c r="C140" s="4" t="inlineStr">
+      <c r="C140" s="14" t="inlineStr">
         <is>
           <t>521-01.464-07</t>
         </is>
       </c>
-      <c r="D140" s="18" t="n">
+      <c r="D140" s="24" t="n">
         <v>32</v>
       </c>
-      <c r="E140" s="18" t="inlineStr">
+      <c r="E140" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F140" s="18" t="inlineStr">
+      <c r="F140" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G140" s="18" t="n">
+      <c r="G140" s="24" t="n">
         <v>14</v>
       </c>
-      <c r="H140" s="18" t="n">
+      <c r="H140" s="24" t="n">
         <v>3.3</v>
       </c>
-      <c r="I140" s="18" t="n">
+      <c r="I140" s="24" t="n">
         <v>46</v>
       </c>
-      <c r="J140" s="18" t="n">
+      <c r="J140" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="K140" s="4" t="inlineStr">
+      <c r="K140" s="14" t="inlineStr">
         <is>
           <t>ящик №1</t>
         </is>
       </c>
-      <c r="L140" s="4" t="inlineStr">
-        <is>
-          <t>6 500</t>
-        </is>
-      </c>
-      <c r="M140" s="4" t="inlineStr"/>
-      <c r="N140" s="4" t="inlineStr">
+      <c r="L140" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M140" s="14" t="inlineStr"/>
+      <c r="N140" s="14" t="inlineStr">
         <is>
           <t>22 000</t>
         </is>
       </c>
-      <c r="O140" s="4" t="inlineStr">
+      <c r="O140" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="18" t="n">
+      <c r="A141" s="24" t="n">
         <v>124</v>
       </c>
-      <c r="B141" s="5" t="inlineStr">
+      <c r="B141" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный угловой Ду32Ру100</t>
         </is>
       </c>
-      <c r="C141" s="4" t="inlineStr">
+      <c r="C141" s="14" t="inlineStr">
         <is>
           <t>521-01.464-06</t>
         </is>
       </c>
-      <c r="D141" s="18" t="n">
+      <c r="D141" s="24" t="n">
         <v>32</v>
       </c>
-      <c r="E141" s="18" t="inlineStr">
+      <c r="E141" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F141" s="18" t="inlineStr">
+      <c r="F141" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G141" s="18" t="n">
+      <c r="G141" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H141" s="18" t="n">
+      <c r="H141" s="24" t="n">
         <v>3.3</v>
       </c>
-      <c r="I141" s="18" t="n">
+      <c r="I141" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J141" s="18" t="inlineStr"/>
-      <c r="K141" s="4" t="inlineStr">
+      <c r="J141" s="24" t="inlineStr"/>
+      <c r="K141" s="14" t="inlineStr">
         <is>
           <t>ящик №1</t>
         </is>
       </c>
-      <c r="L141" s="4" t="inlineStr">
-        <is>
-          <t>6 500</t>
-        </is>
-      </c>
-      <c r="M141" s="4" t="inlineStr"/>
-      <c r="N141" s="4" t="inlineStr">
+      <c r="L141" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M141" s="14" t="inlineStr"/>
+      <c r="N141" s="14" t="inlineStr">
         <is>
           <t>22 000</t>
         </is>
       </c>
-      <c r="O141" s="4" t="inlineStr">
+      <c r="O141" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="18" t="n">
+      <c r="A142" s="24" t="n">
         <v>125</v>
       </c>
-      <c r="B142" s="5" t="inlineStr">
+      <c r="B142" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный угловой Ду32Ру100</t>
         </is>
       </c>
-      <c r="C142" s="4" t="inlineStr">
+      <c r="C142" s="14" t="inlineStr">
         <is>
           <t>522-01.500-07</t>
         </is>
       </c>
-      <c r="D142" s="18" t="n">
+      <c r="D142" s="24" t="n">
         <v>32</v>
       </c>
-      <c r="E142" s="18" t="inlineStr">
+      <c r="E142" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F142" s="18" t="inlineStr">
+      <c r="F142" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G142" s="18" t="n">
+      <c r="G142" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H142" s="18" t="n">
+      <c r="H142" s="24" t="n">
         <v>3.3</v>
       </c>
-      <c r="I142" s="18" t="n">
+      <c r="I142" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J142" s="18" t="inlineStr"/>
-      <c r="K142" s="4" t="inlineStr">
+      <c r="J142" s="24" t="inlineStr"/>
+      <c r="K142" s="14" t="inlineStr">
         <is>
           <t>ящик №1</t>
         </is>
       </c>
-      <c r="L142" s="4" t="inlineStr">
-        <is>
-          <t>6 500</t>
-        </is>
-      </c>
-      <c r="M142" s="4" t="inlineStr"/>
-      <c r="N142" s="4" t="inlineStr">
+      <c r="L142" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M142" s="14" t="inlineStr"/>
+      <c r="N142" s="14" t="inlineStr">
         <is>
           <t>22 000</t>
         </is>
       </c>
-      <c r="O142" s="4" t="inlineStr">
+      <c r="O142" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9486,59 +9489,59 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="18" t="n">
+      <c r="A145" s="24" t="n">
         <v>128</v>
       </c>
-      <c r="B145" s="5" t="inlineStr">
+      <c r="B145" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный угловой Ду25 Ру 100</t>
         </is>
       </c>
-      <c r="C145" s="4" t="inlineStr">
+      <c r="C145" s="14" t="inlineStr">
         <is>
           <t>521--35.3363</t>
         </is>
       </c>
-      <c r="D145" s="18" t="n">
+      <c r="D145" s="24" t="n">
         <v>25</v>
       </c>
-      <c r="E145" s="18" t="inlineStr">
+      <c r="E145" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F145" s="18" t="inlineStr">
+      <c r="F145" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G145" s="18" t="n">
+      <c r="G145" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H145" s="18" t="n">
+      <c r="H145" s="24" t="n">
         <v>2.9</v>
       </c>
-      <c r="I145" s="18" t="n">
+      <c r="I145" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J145" s="18" t="inlineStr"/>
-      <c r="K145" s="4" t="inlineStr">
+      <c r="J145" s="24" t="inlineStr"/>
+      <c r="K145" s="14" t="inlineStr">
         <is>
           <t>коробка №8</t>
         </is>
       </c>
-      <c r="L145" s="4" t="inlineStr">
-        <is>
-          <t>5 000</t>
-        </is>
-      </c>
-      <c r="M145" s="4" t="inlineStr"/>
-      <c r="N145" s="4" t="inlineStr">
+      <c r="L145" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M145" s="14" t="inlineStr"/>
+      <c r="N145" s="14" t="inlineStr">
         <is>
           <t>20 000</t>
         </is>
       </c>
-      <c r="O145" s="4" t="inlineStr">
+      <c r="O145" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -9958,118 +9961,118 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="18" t="n">
+      <c r="A153" s="24" t="n">
         <v>136</v>
       </c>
-      <c r="B153" s="5" t="inlineStr">
+      <c r="B153" s="15" t="inlineStr">
         <is>
           <t>Клапан невозв-запор.цапковый угловой  под дюрит Ду20Ру6</t>
         </is>
       </c>
-      <c r="C153" s="4" t="inlineStr">
+      <c r="C153" s="14" t="inlineStr">
         <is>
           <t>522-03.123</t>
         </is>
       </c>
-      <c r="D153" s="18" t="n">
+      <c r="D153" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="E153" s="18" t="inlineStr">
+      <c r="E153" s="24" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F153" s="18" t="inlineStr">
+      <c r="F153" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G153" s="18" t="n">
+      <c r="G153" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="H153" s="18" t="n">
+      <c r="H153" s="24" t="n">
         <v>1.8</v>
       </c>
-      <c r="I153" s="18" t="n">
+      <c r="I153" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="J153" s="18" t="inlineStr"/>
-      <c r="K153" s="4" t="inlineStr">
+      <c r="J153" s="24" t="inlineStr"/>
+      <c r="K153" s="14" t="inlineStr">
         <is>
           <t>коробка  № 5</t>
         </is>
       </c>
-      <c r="L153" s="4" t="inlineStr">
-        <is>
-          <t>3 352</t>
-        </is>
-      </c>
-      <c r="M153" s="4" t="inlineStr"/>
-      <c r="N153" s="4" t="inlineStr">
+      <c r="L153" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M153" s="14" t="inlineStr"/>
+      <c r="N153" s="14" t="inlineStr">
         <is>
           <t>25 000</t>
         </is>
       </c>
-      <c r="O153" s="4" t="inlineStr">
+      <c r="O153" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="18" t="n">
+      <c r="A154" s="24" t="n">
         <v>137</v>
       </c>
-      <c r="B154" s="5" t="inlineStr">
+      <c r="B154" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный угловой Ду20 Ру160</t>
         </is>
       </c>
-      <c r="C154" s="4" t="inlineStr">
+      <c r="C154" s="14" t="inlineStr">
         <is>
           <t>521-03.479</t>
         </is>
       </c>
-      <c r="D154" s="18" t="n">
+      <c r="D154" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="E154" s="18" t="inlineStr">
+      <c r="E154" s="24" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="F154" s="18" t="inlineStr">
+      <c r="F154" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G154" s="18" t="n">
+      <c r="G154" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H154" s="18" t="n">
+      <c r="H154" s="24" t="n">
         <v>1.8</v>
       </c>
-      <c r="I154" s="18" t="n">
+      <c r="I154" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J154" s="18" t="inlineStr"/>
-      <c r="K154" s="4" t="inlineStr">
+      <c r="J154" s="24" t="inlineStr"/>
+      <c r="K154" s="14" t="inlineStr">
         <is>
           <t>коробка  № 5</t>
         </is>
       </c>
-      <c r="L154" s="4" t="inlineStr">
-        <is>
-          <t>4 500</t>
-        </is>
-      </c>
-      <c r="M154" s="4" t="inlineStr"/>
-      <c r="N154" s="4" t="inlineStr">
+      <c r="L154" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M154" s="14" t="inlineStr"/>
+      <c r="N154" s="14" t="inlineStr">
         <is>
           <t>22 000</t>
         </is>
       </c>
-      <c r="O154" s="4" t="inlineStr">
+      <c r="O154" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10249,55 +10252,55 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="18" t="n">
+      <c r="A158" s="24" t="n">
         <v>141</v>
       </c>
-      <c r="B158" s="5" t="inlineStr">
+      <c r="B158" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный угловой Ду15</t>
         </is>
       </c>
-      <c r="C158" s="4" t="inlineStr">
+      <c r="C158" s="14" t="inlineStr">
         <is>
           <t>521-01.468-08</t>
         </is>
       </c>
-      <c r="D158" s="18" t="n">
+      <c r="D158" s="24" t="n">
         <v>15</v>
       </c>
-      <c r="E158" s="18" t="inlineStr"/>
-      <c r="F158" s="18" t="inlineStr">
+      <c r="E158" s="24" t="inlineStr"/>
+      <c r="F158" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G158" s="18" t="n">
+      <c r="G158" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H158" s="18" t="n">
+      <c r="H158" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="I158" s="18" t="n">
+      <c r="I158" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J158" s="18" t="inlineStr"/>
-      <c r="K158" s="4" t="inlineStr">
+      <c r="J158" s="24" t="inlineStr"/>
+      <c r="K158" s="14" t="inlineStr">
         <is>
           <t>коробка №8</t>
         </is>
       </c>
-      <c r="L158" s="4" t="inlineStr">
-        <is>
-          <t>3 725</t>
-        </is>
-      </c>
-      <c r="M158" s="4" t="inlineStr"/>
-      <c r="N158" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="O158" s="4" t="inlineStr">
+      <c r="L158" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M158" s="14" t="inlineStr"/>
+      <c r="N158" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O158" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10644,177 +10647,177 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="18" t="n">
+      <c r="A165" s="24" t="n">
         <v>148</v>
       </c>
-      <c r="B165" s="5" t="inlineStr">
+      <c r="B165" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный угловой Ду10 Р160</t>
         </is>
       </c>
-      <c r="C165" s="4" t="inlineStr">
+      <c r="C165" s="14" t="inlineStr">
         <is>
           <t>522-03.149</t>
         </is>
       </c>
-      <c r="D165" s="18" t="n">
+      <c r="D165" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="E165" s="18" t="inlineStr">
+      <c r="E165" s="24" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="F165" s="18" t="inlineStr">
+      <c r="F165" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G165" s="18" t="n">
+      <c r="G165" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="H165" s="18" t="n">
+      <c r="H165" s="24" t="n">
         <v>0.7</v>
       </c>
-      <c r="I165" s="18" t="n">
+      <c r="I165" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="J165" s="18" t="inlineStr"/>
-      <c r="K165" s="4" t="inlineStr">
+      <c r="J165" s="24" t="inlineStr"/>
+      <c r="K165" s="14" t="inlineStr">
         <is>
           <t>коробка №5</t>
         </is>
       </c>
-      <c r="L165" s="4" t="inlineStr">
-        <is>
-          <t>3 000</t>
-        </is>
-      </c>
-      <c r="M165" s="4" t="inlineStr"/>
-      <c r="N165" s="4" t="inlineStr">
+      <c r="L165" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M165" s="14" t="inlineStr"/>
+      <c r="N165" s="14" t="inlineStr">
         <is>
           <t>15 000</t>
         </is>
       </c>
-      <c r="O165" s="4" t="inlineStr">
+      <c r="O165" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="18" t="n">
+      <c r="A166" s="24" t="n">
         <v>149</v>
       </c>
-      <c r="B166" s="5" t="inlineStr">
+      <c r="B166" s="15" t="inlineStr">
         <is>
           <t>Клапан предохранительный штуцерный угловой Ду10 ру 6,5-9</t>
         </is>
       </c>
-      <c r="C166" s="4" t="inlineStr">
+      <c r="C166" s="14" t="inlineStr">
         <is>
           <t>524-03.004</t>
         </is>
       </c>
-      <c r="D166" s="18" t="n">
+      <c r="D166" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="E166" s="18" t="inlineStr">
+      <c r="E166" s="24" t="inlineStr">
         <is>
           <t>6,5-9</t>
         </is>
       </c>
-      <c r="F166" s="18" t="inlineStr">
+      <c r="F166" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G166" s="18" t="n">
+      <c r="G166" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H166" s="18" t="n">
+      <c r="H166" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="I166" s="18" t="n">
+      <c r="I166" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J166" s="18" t="inlineStr"/>
-      <c r="K166" s="4" t="inlineStr">
+      <c r="J166" s="24" t="inlineStr"/>
+      <c r="K166" s="14" t="inlineStr">
         <is>
           <t>коробка №5</t>
         </is>
       </c>
-      <c r="L166" s="4" t="inlineStr">
-        <is>
-          <t>2 831</t>
-        </is>
-      </c>
-      <c r="M166" s="4" t="inlineStr"/>
-      <c r="N166" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="O166" s="4" t="inlineStr">
+      <c r="L166" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M166" s="14" t="inlineStr"/>
+      <c r="N166" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O166" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="18" t="n">
+      <c r="A167" s="24" t="n">
         <v>150</v>
       </c>
-      <c r="B167" s="5" t="inlineStr">
+      <c r="B167" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный угловой Рр150/10</t>
         </is>
       </c>
-      <c r="C167" s="4" t="inlineStr">
+      <c r="C167" s="14" t="inlineStr">
         <is>
           <t>521-ц22п</t>
         </is>
       </c>
-      <c r="D167" s="18" t="inlineStr"/>
-      <c r="E167" s="18" t="inlineStr">
+      <c r="D167" s="24" t="inlineStr"/>
+      <c r="E167" s="24" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="F167" s="18" t="inlineStr">
+      <c r="F167" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G167" s="18" t="n">
+      <c r="G167" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="H167" s="18" t="n">
+      <c r="H167" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="I167" s="18" t="n">
+      <c r="I167" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="J167" s="18" t="n">
+      <c r="J167" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="K167" s="4" t="inlineStr">
+      <c r="K167" s="14" t="inlineStr">
         <is>
           <t>коробка №8</t>
         </is>
       </c>
-      <c r="L167" s="4" t="inlineStr">
-        <is>
-          <t>3 000</t>
-        </is>
-      </c>
-      <c r="M167" s="4" t="inlineStr"/>
-      <c r="N167" s="4" t="inlineStr">
+      <c r="L167" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M167" s="14" t="inlineStr"/>
+      <c r="N167" s="14" t="inlineStr">
         <is>
           <t>12 000</t>
         </is>
       </c>
-      <c r="O167" s="4" t="inlineStr">
+      <c r="O167" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -10901,59 +10904,59 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="18" t="n">
+      <c r="A170" s="24" t="n">
         <v>152</v>
       </c>
-      <c r="B170" s="5" t="inlineStr">
+      <c r="B170" s="15" t="inlineStr">
         <is>
           <t>Клапан невозвратный штуцерный проходной Ду20 Ру40</t>
         </is>
       </c>
-      <c r="C170" s="4" t="inlineStr">
+      <c r="C170" s="14" t="inlineStr">
         <is>
           <t>522-3м-9</t>
         </is>
       </c>
-      <c r="D170" s="18" t="n">
+      <c r="D170" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="E170" s="18" t="inlineStr">
+      <c r="E170" s="24" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="F170" s="18" t="inlineStr">
+      <c r="F170" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G170" s="18" t="n">
+      <c r="G170" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H170" s="18" t="n">
+      <c r="H170" s="24" t="n">
         <v>1.9</v>
       </c>
-      <c r="I170" s="18" t="n">
+      <c r="I170" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="J170" s="18" t="inlineStr"/>
-      <c r="K170" s="4" t="inlineStr">
+      <c r="J170" s="24" t="inlineStr"/>
+      <c r="K170" s="14" t="inlineStr">
         <is>
           <t>коробка №9</t>
         </is>
       </c>
-      <c r="L170" s="4" t="inlineStr">
-        <is>
-          <t>3 539</t>
-        </is>
-      </c>
-      <c r="M170" s="4" t="inlineStr"/>
-      <c r="N170" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="O170" s="4" t="inlineStr">
+      <c r="L170" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M170" s="14" t="inlineStr"/>
+      <c r="N170" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O170" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -11552,228 +11555,228 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="18" t="n">
+      <c r="A181" s="24" t="n">
         <v>163</v>
       </c>
-      <c r="B181" s="5" t="inlineStr">
+      <c r="B181" s="15" t="inlineStr">
         <is>
           <t>(Кнопка)Клапан самозакрывающий проходной муфтовый Ду15Ру3</t>
         </is>
       </c>
-      <c r="C181" s="4" t="inlineStr">
+      <c r="C181" s="14" t="inlineStr">
         <is>
           <t>528-35.176</t>
         </is>
       </c>
-      <c r="D181" s="18" t="n">
+      <c r="D181" s="24" t="n">
         <v>15</v>
       </c>
-      <c r="E181" s="18" t="inlineStr">
+      <c r="E181" s="24" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F181" s="18" t="inlineStr">
+      <c r="F181" s="24" t="inlineStr">
         <is>
           <t>новая</t>
         </is>
       </c>
-      <c r="G181" s="18" t="n">
+      <c r="G181" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H181" s="18" t="n">
+      <c r="H181" s="24" t="n">
         <v>0.8</v>
       </c>
-      <c r="I181" s="18" t="n">
+      <c r="I181" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="J181" s="18" t="inlineStr"/>
-      <c r="K181" s="4" t="inlineStr">
+      <c r="J181" s="24" t="inlineStr"/>
+      <c r="K181" s="14" t="inlineStr">
         <is>
           <t>коробка №5</t>
         </is>
       </c>
-      <c r="L181" s="4" t="inlineStr">
-        <is>
-          <t>1 490</t>
-        </is>
-      </c>
-      <c r="M181" s="4" t="inlineStr"/>
-      <c r="N181" s="4" t="inlineStr">
+      <c r="L181" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M181" s="14" t="inlineStr"/>
+      <c r="N181" s="14" t="inlineStr">
         <is>
           <t>15 000</t>
         </is>
       </c>
-      <c r="O181" s="4" t="inlineStr">
+      <c r="O181" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="18" t="n">
+      <c r="A182" s="24" t="n">
         <v>164</v>
       </c>
-      <c r="B182" s="5" t="inlineStr">
+      <c r="B182" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный проходной бессальниковый  Ду15/1</t>
         </is>
       </c>
-      <c r="C182" s="4" t="inlineStr">
+      <c r="C182" s="14" t="inlineStr">
         <is>
           <t>521-35.2608-01</t>
         </is>
       </c>
-      <c r="D182" s="18" t="n">
+      <c r="D182" s="24" t="n">
         <v>15</v>
       </c>
-      <c r="E182" s="18" t="inlineStr"/>
-      <c r="F182" s="18" t="inlineStr">
+      <c r="E182" s="24" t="inlineStr"/>
+      <c r="F182" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G182" s="18" t="n">
+      <c r="G182" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="H182" s="18" t="n">
+      <c r="H182" s="24" t="n">
         <v>5.7</v>
       </c>
-      <c r="I182" s="18" t="n">
+      <c r="I182" s="24" t="n">
         <v>17</v>
       </c>
-      <c r="J182" s="18" t="inlineStr"/>
-      <c r="K182" s="4" t="inlineStr">
+      <c r="J182" s="24" t="inlineStr"/>
+      <c r="K182" s="14" t="inlineStr">
         <is>
           <t>коробка  № 4</t>
         </is>
       </c>
-      <c r="L182" s="4" t="inlineStr">
-        <is>
-          <t>10 616</t>
-        </is>
-      </c>
-      <c r="M182" s="4" t="inlineStr"/>
-      <c r="N182" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="O182" s="4" t="inlineStr">
+      <c r="L182" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M182" s="14" t="inlineStr"/>
+      <c r="N182" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O182" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="18" t="n">
+      <c r="A183" s="24" t="n">
         <v>165</v>
       </c>
-      <c r="B183" s="5" t="inlineStr">
+      <c r="B183" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный проходной Ду 10 Ру40</t>
         </is>
       </c>
-      <c r="C183" s="4" t="inlineStr">
+      <c r="C183" s="14" t="inlineStr">
         <is>
           <t>521-01.471-01</t>
         </is>
       </c>
-      <c r="D183" s="18" t="n">
+      <c r="D183" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="E183" s="18" t="inlineStr">
+      <c r="E183" s="24" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="F183" s="18" t="inlineStr">
+      <c r="F183" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G183" s="18" t="n">
+      <c r="G183" s="24" t="n">
         <v>796</v>
       </c>
-      <c r="H183" s="18" t="n">
+      <c r="H183" s="24" t="n">
         <v>1.2</v>
       </c>
-      <c r="I183" s="18" t="n">
+      <c r="I183" s="24" t="n">
         <v>955</v>
       </c>
-      <c r="J183" s="18" t="inlineStr"/>
-      <c r="K183" s="4" t="inlineStr"/>
-      <c r="L183" s="4" t="inlineStr">
-        <is>
-          <t>2 235</t>
-        </is>
-      </c>
-      <c r="M183" s="4" t="inlineStr"/>
-      <c r="N183" s="4" t="inlineStr">
+      <c r="J183" s="24" t="inlineStr"/>
+      <c r="K183" s="14" t="inlineStr"/>
+      <c r="L183" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M183" s="14" t="inlineStr"/>
+      <c r="N183" s="14" t="inlineStr">
         <is>
           <t>14 000</t>
         </is>
       </c>
-      <c r="O183" s="4" t="inlineStr">
+      <c r="O183" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="18" t="n">
+      <c r="A184" s="24" t="n">
         <v>166</v>
       </c>
-      <c r="B184" s="5" t="inlineStr">
+      <c r="B184" s="15" t="inlineStr">
         <is>
           <t>Клапан штуцерный проходной Ду 10 Ру400</t>
         </is>
       </c>
-      <c r="C184" s="4" t="inlineStr">
+      <c r="C184" s="14" t="inlineStr">
         <is>
           <t>521-35.3238</t>
         </is>
       </c>
-      <c r="D184" s="18" t="n">
+      <c r="D184" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="E184" s="18" t="inlineStr">
+      <c r="E184" s="24" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="F184" s="18" t="inlineStr">
+      <c r="F184" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G184" s="18" t="n">
+      <c r="G184" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H184" s="18" t="n">
+      <c r="H184" s="24" t="n">
         <v>3.8</v>
       </c>
-      <c r="I184" s="18" t="n">
+      <c r="I184" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="J184" s="18" t="inlineStr"/>
-      <c r="K184" s="4" t="inlineStr">
+      <c r="J184" s="24" t="inlineStr"/>
+      <c r="K184" s="14" t="inlineStr">
         <is>
           <t>коробка  № 5</t>
         </is>
       </c>
-      <c r="L184" s="4" t="inlineStr">
-        <is>
-          <t>20 000</t>
-        </is>
-      </c>
-      <c r="M184" s="4" t="inlineStr"/>
-      <c r="N184" s="4" t="inlineStr">
+      <c r="L184" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M184" s="14" t="inlineStr"/>
+      <c r="N184" s="14" t="inlineStr">
         <is>
           <t>65 000</t>
         </is>
       </c>
-      <c r="O184" s="4" t="inlineStr">
+      <c r="O184" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12084,59 +12087,59 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="18" t="n">
+      <c r="A191" s="24" t="n">
         <v>172</v>
       </c>
-      <c r="B191" s="5" t="inlineStr">
+      <c r="B191" s="15" t="inlineStr">
         <is>
           <t>Кран трехходовой штуцерный Ду32 Ру10</t>
         </is>
       </c>
-      <c r="C191" s="4" t="inlineStr">
+      <c r="C191" s="14" t="inlineStr">
         <is>
           <t>536-35.696</t>
         </is>
       </c>
-      <c r="D191" s="18" t="n">
+      <c r="D191" s="24" t="n">
         <v>32</v>
       </c>
-      <c r="E191" s="18" t="inlineStr">
+      <c r="E191" s="24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F191" s="18" t="inlineStr">
+      <c r="F191" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G191" s="18" t="n">
+      <c r="G191" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="H191" s="18" t="n">
+      <c r="H191" s="24" t="n">
         <v>4.1</v>
       </c>
-      <c r="I191" s="18" t="n">
+      <c r="I191" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="J191" s="18" t="inlineStr"/>
-      <c r="K191" s="4" t="inlineStr">
+      <c r="J191" s="24" t="inlineStr"/>
+      <c r="K191" s="14" t="inlineStr">
         <is>
           <t>коробка  № 3</t>
         </is>
       </c>
-      <c r="L191" s="4" t="inlineStr">
-        <is>
-          <t>7 636</t>
-        </is>
-      </c>
-      <c r="M191" s="4" t="inlineStr"/>
-      <c r="N191" s="4" t="inlineStr">
+      <c r="L191" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M191" s="14" t="inlineStr"/>
+      <c r="N191" s="14" t="inlineStr">
         <is>
           <t>24 000</t>
         </is>
       </c>
-      <c r="O191" s="4" t="inlineStr">
+      <c r="O191" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12530,51 +12533,51 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="18" t="n">
+      <c r="A199" s="24" t="n">
         <v>179</v>
       </c>
-      <c r="B199" s="5" t="inlineStr">
+      <c r="B199" s="15" t="inlineStr">
         <is>
           <t>Клапан педальный Ду25</t>
         </is>
       </c>
-      <c r="C199" s="4" t="inlineStr">
+      <c r="C199" s="14" t="inlineStr">
         <is>
           <t>М528-03.001</t>
         </is>
       </c>
-      <c r="D199" s="18" t="n">
+      <c r="D199" s="24" t="n">
         <v>25</v>
       </c>
-      <c r="E199" s="18" t="inlineStr"/>
-      <c r="F199" s="18" t="inlineStr">
+      <c r="E199" s="24" t="inlineStr"/>
+      <c r="F199" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G199" s="18" t="n">
+      <c r="G199" s="24" t="n">
         <v>62</v>
       </c>
-      <c r="H199" s="18" t="n">
+      <c r="H199" s="24" t="n">
         <v>5.5</v>
       </c>
-      <c r="I199" s="18" t="n">
+      <c r="I199" s="24" t="n">
         <v>341</v>
       </c>
-      <c r="J199" s="18" t="inlineStr"/>
-      <c r="K199" s="4" t="inlineStr"/>
-      <c r="L199" s="4" t="inlineStr">
-        <is>
-          <t>10 244</t>
-        </is>
-      </c>
-      <c r="M199" s="4" t="inlineStr"/>
-      <c r="N199" s="4" t="inlineStr">
+      <c r="J199" s="24" t="inlineStr"/>
+      <c r="K199" s="14" t="inlineStr"/>
+      <c r="L199" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M199" s="14" t="inlineStr"/>
+      <c r="N199" s="14" t="inlineStr">
         <is>
           <t>30 000</t>
         </is>
       </c>
-      <c r="O199" s="4" t="inlineStr">
+      <c r="O199" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12602,236 +12605,236 @@
       <c r="O200" s="23" t="n"/>
     </row>
     <row r="201">
-      <c r="A201" s="18" t="n">
+      <c r="A201" s="24" t="n">
         <v>180</v>
       </c>
-      <c r="B201" s="5" t="inlineStr">
+      <c r="B201" s="15" t="inlineStr">
         <is>
           <t>Стакан переборочный Ду25Ру100</t>
         </is>
       </c>
-      <c r="C201" s="4" t="inlineStr">
+      <c r="C201" s="14" t="inlineStr">
         <is>
           <t>554-35.156</t>
         </is>
       </c>
-      <c r="D201" s="18" t="n">
+      <c r="D201" s="24" t="n">
         <v>25</v>
       </c>
-      <c r="E201" s="18" t="inlineStr">
+      <c r="E201" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F201" s="18" t="inlineStr">
+      <c r="F201" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G201" s="18" t="n">
+      <c r="G201" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="H201" s="18" t="n">
+      <c r="H201" s="24" t="n">
         <v>2.5</v>
       </c>
-      <c r="I201" s="18" t="n">
+      <c r="I201" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="J201" s="18" t="inlineStr"/>
-      <c r="K201" s="4" t="inlineStr">
+      <c r="J201" s="24" t="inlineStr"/>
+      <c r="K201" s="14" t="inlineStr">
         <is>
           <t>коробка  № 2</t>
         </is>
       </c>
-      <c r="L201" s="4" t="inlineStr">
-        <is>
-          <t>4 656</t>
-        </is>
-      </c>
-      <c r="M201" s="4" t="inlineStr"/>
-      <c r="N201" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="O201" s="4" t="inlineStr">
+      <c r="L201" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M201" s="14" t="inlineStr"/>
+      <c r="N201" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O201" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="18" t="n">
+      <c r="A202" s="24" t="n">
         <v>181</v>
       </c>
-      <c r="B202" s="5" t="inlineStr">
+      <c r="B202" s="15" t="inlineStr">
         <is>
           <t>Стакан переборочный Ду20Ру100</t>
         </is>
       </c>
-      <c r="C202" s="4" t="inlineStr">
+      <c r="C202" s="14" t="inlineStr">
         <is>
           <t>554-03.909-03</t>
         </is>
       </c>
-      <c r="D202" s="18" t="n">
+      <c r="D202" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="E202" s="18" t="inlineStr">
+      <c r="E202" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F202" s="18" t="inlineStr">
+      <c r="F202" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G202" s="18" t="n">
+      <c r="G202" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="H202" s="18" t="n">
+      <c r="H202" s="24" t="n">
         <v>1.7</v>
       </c>
-      <c r="I202" s="18" t="n">
+      <c r="I202" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="J202" s="18" t="inlineStr"/>
-      <c r="K202" s="4" t="inlineStr">
+      <c r="J202" s="24" t="inlineStr"/>
+      <c r="K202" s="14" t="inlineStr">
         <is>
           <t>коробка  № 2</t>
         </is>
       </c>
-      <c r="L202" s="4" t="inlineStr">
-        <is>
-          <t>3 166</t>
-        </is>
-      </c>
-      <c r="M202" s="4" t="inlineStr"/>
-      <c r="N202" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="O202" s="4" t="inlineStr">
+      <c r="L202" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M202" s="14" t="inlineStr"/>
+      <c r="N202" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O202" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="18" t="n">
+      <c r="A203" s="24" t="n">
         <v>182</v>
       </c>
-      <c r="B203" s="5" t="inlineStr">
+      <c r="B203" s="15" t="inlineStr">
         <is>
           <t>Стакан переборочный Ду20Ру100</t>
         </is>
       </c>
-      <c r="C203" s="4" t="inlineStr">
+      <c r="C203" s="14" t="inlineStr">
         <is>
           <t>554-03.905-06</t>
         </is>
       </c>
-      <c r="D203" s="18" t="n">
+      <c r="D203" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="E203" s="18" t="inlineStr">
+      <c r="E203" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F203" s="18" t="inlineStr">
+      <c r="F203" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G203" s="18" t="n">
+      <c r="G203" s="24" t="n">
         <v>26</v>
       </c>
-      <c r="H203" s="18" t="n">
+      <c r="H203" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="I203" s="18" t="n">
+      <c r="I203" s="24" t="n">
         <v>39</v>
       </c>
-      <c r="J203" s="18" t="inlineStr"/>
-      <c r="K203" s="4" t="inlineStr">
+      <c r="J203" s="24" t="inlineStr"/>
+      <c r="K203" s="14" t="inlineStr">
         <is>
           <t>коробка  № 2</t>
         </is>
       </c>
-      <c r="L203" s="4" t="inlineStr">
-        <is>
-          <t>2 794</t>
-        </is>
-      </c>
-      <c r="M203" s="4" t="inlineStr"/>
-      <c r="N203" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="O203" s="4" t="inlineStr">
+      <c r="L203" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M203" s="14" t="inlineStr"/>
+      <c r="N203" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O203" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="18" t="n">
+      <c r="A204" s="24" t="n">
         <v>183</v>
       </c>
-      <c r="B204" s="5" t="inlineStr">
+      <c r="B204" s="15" t="inlineStr">
         <is>
           <t>Стакан переборочный Ду10Ру100</t>
         </is>
       </c>
-      <c r="C204" s="4" t="inlineStr">
+      <c r="C204" s="14" t="inlineStr">
         <is>
           <t>554-35.265</t>
         </is>
       </c>
-      <c r="D204" s="18" t="n">
+      <c r="D204" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="E204" s="18" t="inlineStr">
+      <c r="E204" s="24" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="F204" s="18" t="inlineStr">
+      <c r="F204" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G204" s="18" t="n">
+      <c r="G204" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="H204" s="18" t="n">
+      <c r="H204" s="24" t="n">
         <v>0.6</v>
       </c>
-      <c r="I204" s="18" t="n">
+      <c r="I204" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J204" s="18" t="inlineStr"/>
-      <c r="K204" s="4" t="inlineStr">
+      <c r="J204" s="24" t="inlineStr"/>
+      <c r="K204" s="14" t="inlineStr">
         <is>
           <t>коробка  № 2</t>
         </is>
       </c>
-      <c r="L204" s="4" t="inlineStr">
-        <is>
-          <t>1 118</t>
-        </is>
-      </c>
-      <c r="M204" s="4" t="inlineStr"/>
-      <c r="N204" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="O204" s="4" t="inlineStr">
+      <c r="L204" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M204" s="14" t="inlineStr"/>
+      <c r="N204" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O204" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -12859,220 +12862,220 @@
       <c r="O205" s="23" t="n"/>
     </row>
     <row r="206">
-      <c r="A206" s="18" t="n">
+      <c r="A206" s="24" t="n">
         <v>184</v>
       </c>
-      <c r="B206" s="5" t="inlineStr">
+      <c r="B206" s="15" t="inlineStr">
         <is>
           <t>Клапан редукционный штуц.проход.односедельный Ду20Ру400 у входа</t>
         </is>
       </c>
-      <c r="C206" s="4" t="inlineStr">
+      <c r="C206" s="14" t="inlineStr">
         <is>
           <t>525-03.044</t>
         </is>
       </c>
-      <c r="D206" s="18" t="n">
+      <c r="D206" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="E206" s="18" t="inlineStr">
+      <c r="E206" s="24" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="F206" s="18" t="inlineStr">
+      <c r="F206" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G206" s="18" t="n">
+      <c r="G206" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="H206" s="18" t="n">
+      <c r="H206" s="24" t="n">
         <v>27</v>
       </c>
-      <c r="I206" s="18" t="n">
+      <c r="I206" s="24" t="n">
         <v>216</v>
       </c>
-      <c r="J206" s="18" t="inlineStr"/>
-      <c r="K206" s="4" t="inlineStr"/>
-      <c r="L206" s="4" t="inlineStr">
-        <is>
-          <t>35 000</t>
-        </is>
-      </c>
-      <c r="M206" s="4" t="inlineStr"/>
-      <c r="N206" s="4" t="inlineStr">
+      <c r="J206" s="24" t="inlineStr"/>
+      <c r="K206" s="14" t="inlineStr"/>
+      <c r="L206" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M206" s="14" t="inlineStr"/>
+      <c r="N206" s="14" t="inlineStr">
         <is>
           <t>120 000</t>
         </is>
       </c>
-      <c r="O206" s="4" t="inlineStr">
+      <c r="O206" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="18" t="n">
+      <c r="A207" s="24" t="n">
         <v>185</v>
       </c>
-      <c r="B207" s="5" t="inlineStr">
+      <c r="B207" s="15" t="inlineStr">
         <is>
           <t>Клапан редукционный штуц.проход.односедельный Ду20Ру400 у входа</t>
         </is>
       </c>
-      <c r="C207" s="4" t="inlineStr">
+      <c r="C207" s="14" t="inlineStr">
         <is>
           <t>525-03.044-01</t>
         </is>
       </c>
-      <c r="D207" s="18" t="n">
+      <c r="D207" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="E207" s="18" t="inlineStr">
+      <c r="E207" s="24" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="F207" s="18" t="inlineStr">
+      <c r="F207" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G207" s="18" t="n">
+      <c r="G207" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H207" s="18" t="n">
+      <c r="H207" s="24" t="n">
         <v>27</v>
       </c>
-      <c r="I207" s="18" t="n">
+      <c r="I207" s="24" t="n">
         <v>27</v>
       </c>
-      <c r="J207" s="18" t="inlineStr"/>
-      <c r="K207" s="4" t="inlineStr"/>
-      <c r="L207" s="4" t="inlineStr">
-        <is>
-          <t>35 000</t>
-        </is>
-      </c>
-      <c r="M207" s="4" t="inlineStr"/>
-      <c r="N207" s="4" t="inlineStr">
+      <c r="J207" s="24" t="inlineStr"/>
+      <c r="K207" s="14" t="inlineStr"/>
+      <c r="L207" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M207" s="14" t="inlineStr"/>
+      <c r="N207" s="14" t="inlineStr">
         <is>
           <t>120 000</t>
         </is>
       </c>
-      <c r="O207" s="4" t="inlineStr">
+      <c r="O207" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="18" t="n">
+      <c r="A208" s="24" t="n">
         <v>186</v>
       </c>
-      <c r="B208" s="5" t="inlineStr">
+      <c r="B208" s="15" t="inlineStr">
         <is>
           <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
         </is>
       </c>
-      <c r="C208" s="4" t="inlineStr">
+      <c r="C208" s="14" t="inlineStr">
         <is>
           <t>525-35.2634</t>
         </is>
       </c>
-      <c r="D208" s="18" t="n">
+      <c r="D208" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="E208" s="18" t="inlineStr">
+      <c r="E208" s="24" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="F208" s="18" t="inlineStr">
+      <c r="F208" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G208" s="18" t="n">
+      <c r="G208" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H208" s="18" t="n">
+      <c r="H208" s="24" t="n">
         <v>7.5</v>
       </c>
-      <c r="I208" s="18" t="n">
+      <c r="I208" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="J208" s="18" t="inlineStr"/>
-      <c r="K208" s="4" t="inlineStr"/>
-      <c r="L208" s="4" t="inlineStr">
-        <is>
-          <t>15 000</t>
-        </is>
-      </c>
-      <c r="M208" s="4" t="inlineStr"/>
-      <c r="N208" s="4" t="inlineStr">
+      <c r="J208" s="24" t="inlineStr"/>
+      <c r="K208" s="14" t="inlineStr"/>
+      <c r="L208" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M208" s="14" t="inlineStr"/>
+      <c r="N208" s="14" t="inlineStr">
         <is>
           <t>45 000</t>
         </is>
       </c>
-      <c r="O208" s="4" t="inlineStr">
+      <c r="O208" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="18" t="n">
+      <c r="A209" s="24" t="n">
         <v>187</v>
       </c>
-      <c r="B209" s="5" t="inlineStr">
+      <c r="B209" s="15" t="inlineStr">
         <is>
           <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
         </is>
       </c>
-      <c r="C209" s="4" t="inlineStr">
+      <c r="C209" s="14" t="inlineStr">
         <is>
           <t>525-35.2634-04</t>
         </is>
       </c>
-      <c r="D209" s="18" t="n">
+      <c r="D209" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="E209" s="18" t="inlineStr">
+      <c r="E209" s="24" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="F209" s="18" t="inlineStr">
+      <c r="F209" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G209" s="18" t="n">
+      <c r="G209" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H209" s="18" t="n">
+      <c r="H209" s="24" t="n">
         <v>7.5</v>
       </c>
-      <c r="I209" s="18" t="n">
+      <c r="I209" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="J209" s="18" t="inlineStr"/>
-      <c r="K209" s="4" t="inlineStr"/>
-      <c r="L209" s="4" t="inlineStr">
-        <is>
-          <t>15 000</t>
-        </is>
-      </c>
-      <c r="M209" s="4" t="inlineStr"/>
-      <c r="N209" s="4" t="inlineStr">
+      <c r="J209" s="24" t="inlineStr"/>
+      <c r="K209" s="14" t="inlineStr"/>
+      <c r="L209" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M209" s="14" t="inlineStr"/>
+      <c r="N209" s="14" t="inlineStr">
         <is>
           <t>45 000</t>
         </is>
       </c>
-      <c r="O209" s="4" t="inlineStr">
+      <c r="O209" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13200,110 +13203,110 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="18" t="n">
+      <c r="A213" s="24" t="n">
         <v>190</v>
       </c>
-      <c r="B213" s="5" t="inlineStr">
+      <c r="B213" s="15" t="inlineStr">
         <is>
           <t>Клапан пусковой Ду32Ру125</t>
         </is>
       </c>
-      <c r="C213" s="4" t="inlineStr">
+      <c r="C213" s="14" t="inlineStr">
         <is>
           <t>587-03.082</t>
         </is>
       </c>
-      <c r="D213" s="18" t="n">
+      <c r="D213" s="24" t="n">
         <v>32</v>
       </c>
-      <c r="E213" s="18" t="inlineStr">
+      <c r="E213" s="24" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="F213" s="18" t="inlineStr">
+      <c r="F213" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G213" s="18" t="n">
+      <c r="G213" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="H213" s="18" t="n">
+      <c r="H213" s="24" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="I213" s="18" t="n">
+      <c r="I213" s="24" t="n">
         <v>70</v>
       </c>
-      <c r="J213" s="18" t="inlineStr"/>
-      <c r="K213" s="4" t="inlineStr"/>
-      <c r="L213" s="4" t="inlineStr">
-        <is>
-          <t>30 000</t>
-        </is>
-      </c>
-      <c r="M213" s="4" t="inlineStr"/>
-      <c r="N213" s="4" t="inlineStr">
+      <c r="J213" s="24" t="inlineStr"/>
+      <c r="K213" s="14" t="inlineStr"/>
+      <c r="L213" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M213" s="14" t="inlineStr"/>
+      <c r="N213" s="14" t="inlineStr">
         <is>
           <t>70 000</t>
         </is>
       </c>
-      <c r="O213" s="4" t="inlineStr">
+      <c r="O213" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="18" t="n">
+      <c r="A214" s="24" t="n">
         <v>191</v>
       </c>
-      <c r="B214" s="5" t="inlineStr">
+      <c r="B214" s="15" t="inlineStr">
         <is>
           <t>Клапан пусковой Ду20Ру125</t>
         </is>
       </c>
-      <c r="C214" s="4" t="inlineStr">
+      <c r="C214" s="14" t="inlineStr">
         <is>
           <t>587-03.080</t>
         </is>
       </c>
-      <c r="D214" s="18" t="n">
+      <c r="D214" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="E214" s="18" t="inlineStr">
+      <c r="E214" s="24" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="F214" s="18" t="inlineStr">
+      <c r="F214" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G214" s="18" t="n">
+      <c r="G214" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="H214" s="18" t="n">
+      <c r="H214" s="24" t="n">
         <v>5.6</v>
       </c>
-      <c r="I214" s="18" t="n">
+      <c r="I214" s="24" t="n">
         <v>39</v>
       </c>
-      <c r="J214" s="18" t="inlineStr"/>
-      <c r="K214" s="4" t="inlineStr"/>
-      <c r="L214" s="4" t="inlineStr">
-        <is>
-          <t>25 000</t>
-        </is>
-      </c>
-      <c r="M214" s="4" t="inlineStr"/>
-      <c r="N214" s="4" t="inlineStr">
+      <c r="J214" s="24" t="inlineStr"/>
+      <c r="K214" s="14" t="inlineStr"/>
+      <c r="L214" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M214" s="14" t="inlineStr"/>
+      <c r="N214" s="14" t="inlineStr">
         <is>
           <t>65 000</t>
         </is>
       </c>
-      <c r="O214" s="4" t="inlineStr">
+      <c r="O214" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13365,98 +13368,98 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="18" t="n">
+      <c r="A216" s="24" t="n">
         <v>193</v>
       </c>
-      <c r="B216" s="5" t="inlineStr">
+      <c r="B216" s="15" t="inlineStr">
         <is>
           <t>Кланан Рр18-2 45/25</t>
         </is>
       </c>
-      <c r="C216" s="4" t="inlineStr">
+      <c r="C216" s="14" t="inlineStr">
         <is>
           <t>2619802305</t>
         </is>
       </c>
-      <c r="D216" s="18" t="inlineStr"/>
-      <c r="E216" s="18" t="inlineStr"/>
-      <c r="F216" s="18" t="inlineStr">
+      <c r="D216" s="24" t="inlineStr"/>
+      <c r="E216" s="24" t="inlineStr"/>
+      <c r="F216" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G216" s="18" t="n">
+      <c r="G216" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H216" s="18" t="n">
+      <c r="H216" s="24" t="n">
         <v>6.8</v>
       </c>
-      <c r="I216" s="18" t="n">
+      <c r="I216" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="J216" s="18" t="inlineStr"/>
-      <c r="K216" s="4" t="inlineStr"/>
-      <c r="L216" s="4" t="inlineStr">
-        <is>
-          <t>12 665</t>
-        </is>
-      </c>
-      <c r="M216" s="4" t="inlineStr"/>
-      <c r="N216" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="O216" s="4" t="inlineStr">
+      <c r="J216" s="24" t="inlineStr"/>
+      <c r="K216" s="14" t="inlineStr"/>
+      <c r="L216" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M216" s="14" t="inlineStr"/>
+      <c r="N216" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O216" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="18" t="n">
+      <c r="A217" s="24" t="n">
         <v>194</v>
       </c>
-      <c r="B217" s="5" t="inlineStr">
+      <c r="B217" s="15" t="inlineStr">
         <is>
           <t>Клапан Ду20/10</t>
         </is>
       </c>
-      <c r="C217" s="4" t="inlineStr">
+      <c r="C217" s="14" t="inlineStr">
         <is>
           <t>581-С673-3</t>
         </is>
       </c>
-      <c r="D217" s="18" t="inlineStr"/>
-      <c r="E217" s="18" t="inlineStr"/>
-      <c r="F217" s="18" t="inlineStr">
+      <c r="D217" s="24" t="inlineStr"/>
+      <c r="E217" s="24" t="inlineStr"/>
+      <c r="F217" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G217" s="18" t="n">
+      <c r="G217" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="H217" s="18" t="n">
+      <c r="H217" s="24" t="n">
         <v>2.4</v>
       </c>
-      <c r="I217" s="18" t="n">
+      <c r="I217" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="J217" s="18" t="inlineStr"/>
-      <c r="K217" s="4" t="inlineStr"/>
-      <c r="L217" s="4" t="inlineStr">
-        <is>
-          <t>4 470</t>
-        </is>
-      </c>
-      <c r="M217" s="4" t="inlineStr"/>
-      <c r="N217" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="O217" s="4" t="inlineStr">
+      <c r="J217" s="24" t="inlineStr"/>
+      <c r="K217" s="14" t="inlineStr"/>
+      <c r="L217" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M217" s="14" t="inlineStr"/>
+      <c r="N217" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O217" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -13938,204 +13941,204 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="18" t="n">
+      <c r="A229" s="24" t="n">
         <v>203</v>
       </c>
-      <c r="B229" s="5" t="inlineStr">
+      <c r="B229" s="15" t="inlineStr">
         <is>
           <t>Головка воздушно-квадрат.(поплавковая) Ду125 (без поплавка)</t>
         </is>
       </c>
-      <c r="C229" s="4" t="inlineStr">
+      <c r="C229" s="14" t="inlineStr">
         <is>
           <t>(541-03.220)</t>
         </is>
       </c>
-      <c r="D229" s="18" t="n">
+      <c r="D229" s="24" t="n">
         <v>125</v>
       </c>
-      <c r="E229" s="18" t="inlineStr"/>
-      <c r="F229" s="18" t="inlineStr">
+      <c r="E229" s="24" t="inlineStr"/>
+      <c r="F229" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G229" s="18" t="n">
+      <c r="G229" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="H229" s="18" t="n">
+      <c r="H229" s="24" t="n">
         <v>18.2</v>
       </c>
-      <c r="I229" s="18" t="n">
+      <c r="I229" s="24" t="n">
         <v>109</v>
       </c>
-      <c r="J229" s="18" t="inlineStr"/>
-      <c r="K229" s="4" t="inlineStr"/>
-      <c r="L229" s="4" t="inlineStr">
-        <is>
-          <t>33 898</t>
-        </is>
-      </c>
-      <c r="M229" s="4" t="inlineStr"/>
-      <c r="N229" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="O229" s="4" t="inlineStr">
+      <c r="J229" s="24" t="inlineStr"/>
+      <c r="K229" s="14" t="inlineStr"/>
+      <c r="L229" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M229" s="14" t="inlineStr"/>
+      <c r="N229" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O229" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="18" t="n">
+      <c r="A230" s="24" t="n">
         <v>204</v>
       </c>
-      <c r="B230" s="5" t="inlineStr">
+      <c r="B230" s="15" t="inlineStr">
         <is>
           <t>Головка воздушно-квадрат.(поплавковая) Ду80</t>
         </is>
       </c>
-      <c r="C230" s="4" t="inlineStr">
+      <c r="C230" s="14" t="inlineStr">
         <is>
           <t>(541-03.218)</t>
         </is>
       </c>
-      <c r="D230" s="18" t="n">
+      <c r="D230" s="24" t="n">
         <v>80</v>
       </c>
-      <c r="E230" s="18" t="inlineStr"/>
-      <c r="F230" s="18" t="inlineStr">
+      <c r="E230" s="24" t="inlineStr"/>
+      <c r="F230" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G230" s="18" t="n">
+      <c r="G230" s="24" t="n">
         <v>19</v>
       </c>
-      <c r="H230" s="18" t="n">
+      <c r="H230" s="24" t="n">
         <v>11.2</v>
       </c>
-      <c r="I230" s="18" t="n">
+      <c r="I230" s="24" t="n">
         <v>213</v>
       </c>
-      <c r="J230" s="18" t="inlineStr"/>
-      <c r="K230" s="4" t="inlineStr"/>
-      <c r="L230" s="4" t="inlineStr">
-        <is>
-          <t>20 860</t>
-        </is>
-      </c>
-      <c r="M230" s="4" t="inlineStr"/>
-      <c r="N230" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="O230" s="4" t="inlineStr">
+      <c r="J230" s="24" t="inlineStr"/>
+      <c r="K230" s="14" t="inlineStr"/>
+      <c r="L230" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M230" s="14" t="inlineStr"/>
+      <c r="N230" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O230" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="18" t="n">
+      <c r="A231" s="24" t="n">
         <v>205</v>
       </c>
-      <c r="B231" s="5" t="inlineStr">
+      <c r="B231" s="15" t="inlineStr">
         <is>
           <t>Головка воздушно-квадрат.(поплавковая) Ду32</t>
         </is>
       </c>
-      <c r="C231" s="4" t="inlineStr">
+      <c r="C231" s="14" t="inlineStr">
         <is>
           <t>541-03.224</t>
         </is>
       </c>
-      <c r="D231" s="18" t="n">
+      <c r="D231" s="24" t="n">
         <v>32</v>
       </c>
-      <c r="E231" s="18" t="inlineStr"/>
-      <c r="F231" s="18" t="inlineStr">
+      <c r="E231" s="24" t="inlineStr"/>
+      <c r="F231" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G231" s="18" t="n">
+      <c r="G231" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="H231" s="18" t="n">
+      <c r="H231" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="I231" s="18" t="n">
+      <c r="I231" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="J231" s="18" t="inlineStr"/>
-      <c r="K231" s="4" t="inlineStr"/>
-      <c r="L231" s="4" t="inlineStr">
-        <is>
-          <t>2 794</t>
-        </is>
-      </c>
-      <c r="M231" s="4" t="inlineStr"/>
-      <c r="N231" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="O231" s="4" t="inlineStr">
+      <c r="J231" s="24" t="inlineStr"/>
+      <c r="K231" s="14" t="inlineStr"/>
+      <c r="L231" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M231" s="14" t="inlineStr"/>
+      <c r="N231" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O231" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="18" t="n">
+      <c r="A232" s="24" t="n">
         <v>206</v>
       </c>
-      <c r="B232" s="5" t="inlineStr">
+      <c r="B232" s="15" t="inlineStr">
         <is>
           <t>Головка воздушно-квадрат.(поплавковая) Ду25</t>
         </is>
       </c>
-      <c r="C232" s="4" t="inlineStr">
+      <c r="C232" s="14" t="inlineStr">
         <is>
           <t>(541-03.232)</t>
         </is>
       </c>
-      <c r="D232" s="18" t="n">
+      <c r="D232" s="24" t="n">
         <v>25</v>
       </c>
-      <c r="E232" s="18" t="inlineStr"/>
-      <c r="F232" s="18" t="inlineStr">
+      <c r="E232" s="24" t="inlineStr"/>
+      <c r="F232" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G232" s="18" t="n">
+      <c r="G232" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="H232" s="18" t="n">
+      <c r="H232" s="24" t="n">
         <v>1.6</v>
       </c>
-      <c r="I232" s="18" t="n">
+      <c r="I232" s="24" t="n">
         <v>13</v>
       </c>
-      <c r="J232" s="18" t="inlineStr"/>
-      <c r="K232" s="4" t="inlineStr"/>
-      <c r="L232" s="4" t="inlineStr">
-        <is>
-          <t>2 980</t>
-        </is>
-      </c>
-      <c r="M232" s="4" t="inlineStr"/>
-      <c r="N232" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="O232" s="4" t="inlineStr">
+      <c r="J232" s="24" t="inlineStr"/>
+      <c r="K232" s="14" t="inlineStr"/>
+      <c r="L232" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M232" s="14" t="inlineStr"/>
+      <c r="N232" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O232" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14163,151 +14166,151 @@
       <c r="O233" s="23" t="n"/>
     </row>
     <row r="234">
-      <c r="A234" s="18" t="n">
+      <c r="A234" s="24" t="n">
         <v>207</v>
       </c>
-      <c r="B234" s="5" t="inlineStr">
+      <c r="B234" s="15" t="inlineStr">
         <is>
           <t>Клапан невозвратно -приемный Ду 50</t>
         </is>
       </c>
-      <c r="C234" s="4" t="inlineStr">
+      <c r="C234" s="14" t="inlineStr">
         <is>
           <t>522-35.4043-01</t>
         </is>
       </c>
-      <c r="D234" s="18" t="n">
+      <c r="D234" s="24" t="n">
         <v>50</v>
       </c>
-      <c r="E234" s="18" t="inlineStr"/>
-      <c r="F234" s="18" t="inlineStr">
+      <c r="E234" s="24" t="inlineStr"/>
+      <c r="F234" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G234" s="18" t="n">
+      <c r="G234" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="H234" s="18" t="n">
+      <c r="H234" s="24" t="n">
         <v>10.8</v>
       </c>
-      <c r="I234" s="18" t="n">
+      <c r="I234" s="24" t="n">
         <v>65</v>
       </c>
-      <c r="J234" s="18" t="inlineStr"/>
-      <c r="K234" s="4" t="inlineStr"/>
-      <c r="L234" s="4" t="inlineStr">
-        <is>
-          <t>20 115</t>
-        </is>
-      </c>
-      <c r="M234" s="4" t="inlineStr"/>
-      <c r="N234" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="O234" s="4" t="inlineStr">
+      <c r="J234" s="24" t="inlineStr"/>
+      <c r="K234" s="14" t="inlineStr"/>
+      <c r="L234" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M234" s="14" t="inlineStr"/>
+      <c r="N234" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O234" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="18" t="n">
+      <c r="A235" s="24" t="n">
         <v>208</v>
       </c>
-      <c r="B235" s="5" t="inlineStr">
+      <c r="B235" s="15" t="inlineStr">
         <is>
           <t>Клапан невозвратно -приемный Ду 65</t>
         </is>
       </c>
-      <c r="C235" s="4" t="inlineStr">
+      <c r="C235" s="14" t="inlineStr">
         <is>
           <t>522-35.4044-01</t>
         </is>
       </c>
-      <c r="D235" s="18" t="n">
+      <c r="D235" s="24" t="n">
         <v>65</v>
       </c>
-      <c r="E235" s="18" t="inlineStr"/>
-      <c r="F235" s="18" t="inlineStr">
+      <c r="E235" s="24" t="inlineStr"/>
+      <c r="F235" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G235" s="18" t="n">
+      <c r="G235" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H235" s="18" t="n">
+      <c r="H235" s="24" t="n">
         <v>13.5</v>
       </c>
-      <c r="I235" s="18" t="n">
+      <c r="I235" s="24" t="n">
         <v>14</v>
       </c>
-      <c r="J235" s="18" t="inlineStr"/>
-      <c r="K235" s="4" t="inlineStr"/>
-      <c r="L235" s="4" t="inlineStr">
-        <is>
-          <t>25 144</t>
-        </is>
-      </c>
-      <c r="M235" s="4" t="inlineStr"/>
-      <c r="N235" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="O235" s="4" t="inlineStr">
+      <c r="J235" s="24" t="inlineStr"/>
+      <c r="K235" s="14" t="inlineStr"/>
+      <c r="L235" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M235" s="14" t="inlineStr"/>
+      <c r="N235" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O235" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="18" t="n">
+      <c r="A236" s="24" t="n">
         <v>209</v>
       </c>
-      <c r="B236" s="5" t="inlineStr">
+      <c r="B236" s="15" t="inlineStr">
         <is>
           <t>клапан</t>
         </is>
       </c>
-      <c r="C236" s="4" t="inlineStr">
+      <c r="C236" s="14" t="inlineStr">
         <is>
           <t>552-03.023</t>
         </is>
       </c>
-      <c r="D236" s="18" t="inlineStr"/>
-      <c r="E236" s="18" t="inlineStr"/>
-      <c r="F236" s="18" t="inlineStr">
+      <c r="D236" s="24" t="inlineStr"/>
+      <c r="E236" s="24" t="inlineStr"/>
+      <c r="F236" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G236" s="18" t="n">
+      <c r="G236" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="H236" s="18" t="n">
+      <c r="H236" s="24" t="n">
         <v>3.4</v>
       </c>
-      <c r="I236" s="18" t="n">
+      <c r="I236" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="J236" s="18" t="inlineStr"/>
-      <c r="K236" s="4" t="inlineStr"/>
-      <c r="L236" s="4" t="inlineStr">
-        <is>
-          <t>6 332</t>
-        </is>
-      </c>
-      <c r="M236" s="4" t="inlineStr"/>
-      <c r="N236" s="4" t="inlineStr">
-        <is>
-          <t>по согласованию</t>
-        </is>
-      </c>
-      <c r="O236" s="4" t="inlineStr">
+      <c r="J236" s="24" t="inlineStr"/>
+      <c r="K236" s="14" t="inlineStr"/>
+      <c r="L236" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M236" s="14" t="inlineStr"/>
+      <c r="N236" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="O236" s="14" t="inlineStr">
         <is>
           <t>бронза</t>
         </is>
@@ -14728,118 +14731,118 @@
       <c r="O246" s="23" t="n"/>
     </row>
     <row r="247">
-      <c r="A247" s="18" t="n">
+      <c r="A247" s="24" t="n">
         <v>216</v>
       </c>
-      <c r="B247" s="5" t="inlineStr">
+      <c r="B247" s="15" t="inlineStr">
         <is>
           <t>Клапан фланцевый проходной титановые Ду100Ру10</t>
         </is>
       </c>
-      <c r="C247" s="4" t="inlineStr">
+      <c r="C247" s="14" t="inlineStr">
         <is>
           <t>521-182.116</t>
         </is>
       </c>
-      <c r="D247" s="18" t="n">
+      <c r="D247" s="24" t="n">
         <v>100</v>
       </c>
-      <c r="E247" s="18" t="inlineStr">
+      <c r="E247" s="24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F247" s="18" t="inlineStr">
+      <c r="F247" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G247" s="18" t="n">
+      <c r="G247" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H247" s="18" t="n">
+      <c r="H247" s="24" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="I247" s="18" t="n">
+      <c r="I247" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="J247" s="18" t="inlineStr"/>
-      <c r="K247" s="4" t="inlineStr">
+      <c r="J247" s="24" t="inlineStr"/>
+      <c r="K247" s="14" t="inlineStr">
         <is>
           <t>коробка №7</t>
         </is>
       </c>
-      <c r="L247" s="4" t="inlineStr">
-        <is>
-          <t>55 000</t>
-        </is>
-      </c>
-      <c r="M247" s="4" t="inlineStr"/>
-      <c r="N247" s="4" t="inlineStr">
+      <c r="L247" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M247" s="14" t="inlineStr"/>
+      <c r="N247" s="14" t="inlineStr">
         <is>
           <t>140 000</t>
         </is>
       </c>
-      <c r="O247" s="4" t="inlineStr">
+      <c r="O247" s="14" t="inlineStr">
         <is>
           <t>титан</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="18" t="n">
+      <c r="A248" s="24" t="n">
         <v>217</v>
       </c>
-      <c r="B248" s="5" t="inlineStr">
+      <c r="B248" s="15" t="inlineStr">
         <is>
           <t>Клапан фланцевый проходной титановые Ду50Ру10</t>
         </is>
       </c>
-      <c r="C248" s="4" t="inlineStr">
+      <c r="C248" s="14" t="inlineStr">
         <is>
           <t>521-182.110</t>
         </is>
       </c>
-      <c r="D248" s="18" t="n">
+      <c r="D248" s="24" t="n">
         <v>50</v>
       </c>
-      <c r="E248" s="18" t="inlineStr">
+      <c r="E248" s="24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F248" s="18" t="inlineStr">
+      <c r="F248" s="24" t="inlineStr">
         <is>
           <t>новый</t>
         </is>
       </c>
-      <c r="G248" s="18" t="n">
+      <c r="G248" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="H248" s="18" t="n">
+      <c r="H248" s="24" t="n">
         <v>3.5</v>
       </c>
-      <c r="I248" s="18" t="n">
+      <c r="I248" s="24" t="n">
         <v>18</v>
       </c>
-      <c r="J248" s="18" t="inlineStr"/>
-      <c r="K248" s="4" t="inlineStr">
+      <c r="J248" s="24" t="inlineStr"/>
+      <c r="K248" s="14" t="inlineStr">
         <is>
           <t>коробка №6</t>
         </is>
       </c>
-      <c r="L248" s="4" t="inlineStr">
-        <is>
-          <t>35 000</t>
-        </is>
-      </c>
-      <c r="M248" s="4" t="inlineStr"/>
-      <c r="N248" s="4" t="inlineStr">
+      <c r="L248" s="14" t="inlineStr">
+        <is>
+          <t>по согласованию</t>
+        </is>
+      </c>
+      <c r="M248" s="14" t="inlineStr"/>
+      <c r="N248" s="14" t="inlineStr">
         <is>
           <t>100 000</t>
         </is>
       </c>
-      <c r="O248" s="4" t="inlineStr">
+      <c r="O248" s="14" t="inlineStr">
         <is>
           <t>титан</t>
         </is>
@@ -14887,7 +14890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14975,13 +14978,13 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>163</v>
+        <v>118</v>
       </c>
       <c r="C5" s="18" t="n">
-        <v>1519</v>
+        <v>445</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>17847</v>
+        <v>14320</v>
       </c>
       <c r="E5" s="19" t="n">
         <v>745</v>
@@ -14995,29 +14998,29 @@
         <v>1862.5</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>33386124</v>
+        <v>26821706</v>
       </c>
       <c r="I5" s="19" t="n">
         <v>2946000</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>54398000</v>
+        <v>34916000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>высокое давление, Ру от 100</t>
+          <t>новое, цена согласовывается отдельно</t>
         </is>
       </c>
       <c r="B6" s="24" t="n">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="C6" s="24" t="n">
-        <v>206</v>
+        <v>1234</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>633</v>
+        <v>4466</v>
       </c>
       <c r="E6" s="26" t="inlineStr">
         <is>
@@ -15034,30 +15037,34 @@
           <t>цену согласовываем</t>
         </is>
       </c>
-      <c r="H6" s="26" t="n">
-        <v>858500</v>
-      </c>
-      <c r="I6" s="26" t="n">
-        <v>310500</v>
+      <c r="H6" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J6" s="26" t="n">
-        <v>2581000</v>
+        <v>23744000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>редукционный, цена в редукторе</t>
+          <t>высокое давление, Ру от 100</t>
         </is>
       </c>
       <c r="B7" s="24" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C7" s="24" t="n">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>259</v>
+        <v>194</v>
       </c>
       <c r="E7" s="26" t="inlineStr">
         <is>
@@ -15075,31 +15082,29 @@
         </is>
       </c>
       <c r="H7" s="26" t="n">
-        <v>345000</v>
-      </c>
-      <c r="I7" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>46500</v>
+      </c>
+      <c r="I7" s="26" t="n">
+        <v>310500</v>
       </c>
       <c r="J7" s="26" t="n">
-        <v>1170000</v>
+        <v>184000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>сталь, цена не от массы металла</t>
+          <t>электромагнитный, цена в приводе и катушке</t>
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C8" s="24" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D8" s="26" t="n">
-        <v>140</v>
+        <v>56</v>
       </c>
       <c r="E8" s="26" t="inlineStr">
         <is>
@@ -15121,8 +15126,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I8" s="26" t="n">
-        <v>10500</v>
+      <c r="I8" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J8" s="26" t="inlineStr">
         <is>
@@ -15133,17 +15140,17 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>электромагнитный, цена в приводе и катушке</t>
+          <t>сталь, цена не от массы металла</t>
         </is>
       </c>
       <c r="B9" s="24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" s="24" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D9" s="26" t="n">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="E9" s="26" t="inlineStr">
         <is>
@@ -15165,330 +15172,268 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I9" s="26" t="inlineStr">
+      <c r="I9" s="26" t="n">
+        <v>10500</v>
+      </c>
+      <c r="J9" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" s="26" t="n">
-        <v>55000</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>алюминий, цена не от массы металла</t>
-        </is>
-      </c>
-      <c r="B10" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="C10" s="24" t="n">
-        <v>17</v>
-      </c>
-      <c r="D10" s="26" t="n">
-        <v>61</v>
-      </c>
-      <c r="E10" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="15" t="inlineStr">
-        <is>
-          <t>цену согласовываем</t>
-        </is>
-      </c>
-      <c r="H10" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I10" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J10" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>титан, цена не от массы металла</t>
-        </is>
-      </c>
-      <c r="B11" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" s="24" t="n">
-        <v>6</v>
-      </c>
-      <c r="D11" s="26" t="n">
-        <v>28</v>
-      </c>
-      <c r="E11" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="15" t="inlineStr">
-        <is>
-          <t>цену согласовываем</t>
-        </is>
-      </c>
-      <c r="H11" s="26" t="n">
-        <v>230000</v>
-      </c>
-      <c r="I11" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J11" s="26" t="n">
-        <v>640000</v>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="n">
+        <v>217</v>
+      </c>
+      <c r="C10" s="20" t="n">
+        <v>1773</v>
+      </c>
+      <c r="D10" s="21" t="n">
+        <v>19091</v>
+      </c>
+      <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="21" t="n">
+        <v>26868206</v>
+      </c>
+      <c r="I10" s="21" t="n">
+        <v>3267000</v>
+      </c>
+      <c r="J10" s="21" t="n">
+        <v>58844000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="n">
-        <v>217</v>
-      </c>
-      <c r="C12" s="20" t="n">
-        <v>1773</v>
-      </c>
-      <c r="D12" s="21" t="n">
-        <v>19091</v>
-      </c>
-      <c r="E12" s="6" t="inlineStr"/>
-      <c r="F12" s="6" t="inlineStr"/>
-      <c r="G12" s="6" t="inlineStr"/>
-      <c r="H12" s="21" t="n">
-        <v>34819624</v>
-      </c>
-      <c r="I12" s="21" t="n">
-        <v>3267000</v>
-      </c>
-      <c r="J12" s="21" t="n">
-        <v>58844000</v>
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Откуда берется ставка закупа</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>— Закупочная цена = цена металлолома * 2,5. Договоренность с Антоном Бурыкиным от 25.10.2026.</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>Откуда берется ставка закупа</t>
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>— Бронза: 745 * 2,5 = 1 862,50 руб за килограмм. Это и есть ставка, по которой посчитана вся бронза в спецификации.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
-          <t>— Закупочная цена = цена металлолома * 2,5. Договоренность с Антоном Бурыкиным от 25.10.2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>— Бронза: 745 * 2,5 = 1 862,50 руб за килограмм. Это и есть ставка, по которой посчитана вся бронза в спецификации.</t>
+          <t>— Уточнится вес при замере — цена пересчитается сама. Поменяет приемка цены — пересчитается и ставка.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>— Уточнится вес при замере — цена пересчитается сама. Поменяет приемка цены — пересчитается и ставка.</t>
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Прайс приемки на 13.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Металл</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Лом, руб за кг</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Закуп, руб за кг</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>Прайс приемки на 13.10.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Металл</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Лом, руб за кг</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Закуп, руб за кг</t>
-        </is>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>нихром</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="n">
+        <v>1342</v>
+      </c>
+      <c r="C19" s="19" t="n">
+        <v>3355</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>медь</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>945</v>
+      </c>
+      <c r="C20" s="19" t="n">
+        <v>2362.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>нихром</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="B21" s="19" t="n">
-        <v>1342</v>
+        <v>745</v>
       </c>
       <c r="C21" s="19" t="n">
-        <v>3355</v>
+        <v>1862.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>медь</t>
+          <t>латунь</t>
         </is>
       </c>
       <c r="B22" s="19" t="n">
-        <v>945</v>
+        <v>635</v>
       </c>
       <c r="C22" s="19" t="n">
-        <v>2362.5</v>
+        <v>1587.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>бронза</t>
+          <t>алюминий</t>
         </is>
       </c>
       <c r="B23" s="19" t="n">
-        <v>745</v>
+        <v>260</v>
       </c>
       <c r="C23" s="19" t="n">
-        <v>1862.5</v>
+        <v>650</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>латунь</t>
+          <t>титан</t>
         </is>
       </c>
       <c r="B24" s="19" t="n">
-        <v>635</v>
+        <v>130</v>
       </c>
       <c r="C24" s="19" t="n">
-        <v>1587.5</v>
+        <v>325</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>алюминий</t>
+          <t>цам</t>
         </is>
       </c>
       <c r="B25" s="19" t="n">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="C25" s="19" t="n">
-        <v>650</v>
+        <v>325</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>титан</t>
+          <t>свинец</t>
         </is>
       </c>
       <c r="B26" s="19" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="C26" s="19" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>цам</t>
+          <t>нержавейка</t>
         </is>
       </c>
       <c r="B27" s="19" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="C27" s="19" t="n">
-        <v>325</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>свинец</t>
+          <t>аккумуляторы</t>
         </is>
       </c>
       <c r="B28" s="19" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="C28" s="19" t="n">
-        <v>175</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>нержавейка</t>
+          <t>трансформаторы</t>
         </is>
       </c>
       <c r="B29" s="19" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C29" s="19" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>аккумуляторы</t>
+          <t>черный металл</t>
         </is>
       </c>
       <c r="B30" s="19" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C30" s="19" t="n">
-        <v>87.5</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>трансформаторы</t>
+          <t>чугун</t>
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C31" s="19" t="n">
-        <v>50</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>черный металл</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="B32" s="19" t="n">
@@ -15501,86 +15446,60 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>чугун</t>
+          <t>электродвигатели</t>
         </is>
       </c>
       <c r="B33" s="19" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C33" s="19" t="n">
-        <v>47.5</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>сталь</t>
-        </is>
-      </c>
-      <c r="B34" s="19" t="n">
-        <v>19</v>
-      </c>
-      <c r="C34" s="19" t="n">
-        <v>47.5</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>электродвигатели</t>
-        </is>
-      </c>
-      <c r="B35" s="19" t="n">
-        <v>15</v>
-      </c>
-      <c r="C35" s="19" t="n">
         <v>37.5</v>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>— Лом — это нижняя граница цены. Любая позиция стоит хотя бы как металл, и ниже продавать незачем: сдать быстрее и без споров по состоянию.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>— Вся арматура бронзовая, 745 руб за кг: на море ставят бронзу, латунь идет на реки. Из этого и выходит ставка 1 862,50.</t>
+        </is>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="17" t="inlineStr">
         <is>
-          <t>— Лом — это нижняя граница цены. Любая позиция стоит хотя бы как металл, и ниже продавать незачем: сдать быстрее и без споров по состоянию.</t>
+          <t>— Сталь, титан, алюминий и нержавейка от лома не считаются вовсе: множитель дал бы по стали 47,50 руб за кг, а у конкурента стальная задвижка Ду200 стоит 40 000 руб. Цену по ним согласовываем отдельно.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>— Вся арматура бронзовая, 745 руб за кг: на море ставят бронзу, латунь идет на реки. Из этого и выходит ставка 1 862,50.</t>
+          <t>— Так же не считаются электромагнитные и редукционные клапаны и клапаны на высокое давление Ру от 100: корпус у них та же бронза, но платят не за нее.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>— Сталь, титан, алюминий и нержавейка от лома не считаются вовсе: множитель дал бы по стали 47,50 руб за кг, а у конкурента стальная задвижка Ду200 стоит 40 000 руб. Цену по ним согласовываем отдельно.</t>
+          <t>— Ремонт в цену закупа не входит — это следующий шаг цепочки, его делает компания после покупки. Новое не ремонтируем.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>— Так же не считаются электромагнитные и редукционные клапаны и клапаны на высокое давление Ру от 100: корпус у них та же бронза, но платят не за нее.</t>
+          <t>— Продажная цена — ориентир, а не согласованная: по пункту 3.2 Договора конкретную цену согласуют письменно до передачи товара конечному покупателю.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
-        <is>
-          <t>— Ремонт в цену закупа не входит — это следующий шаг цепочки, его делает компания после покупки. Новое не ремонтируем.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>— Продажная цена — ориентир, а не согласованная: по пункту 3.2 Договора конкретную цену согласуют письменно до передачи товара конечному покупателю.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>— Если приемка поменяет цены, пересчитывается и ставка: она считается из прайса, а не вписана руками.</t>
         </is>
@@ -15589,15 +15508,15 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A14:J14"/>
     <mergeCell ref="A40:J40"/>
     <mergeCell ref="A39:J39"/>
     <mergeCell ref="A15:J15"/>
-    <mergeCell ref="A43:J43"/>
+    <mergeCell ref="A35:J35"/>
     <mergeCell ref="A38:J38"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A42:J42"/>
     <mergeCell ref="A41:J41"/>
+    <mergeCell ref="A13:J13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
@@ -15610,7 +15529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15631,7 +15550,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Порядок ярусов и правила сохранности. Главный риск не вес сам по себе, а что лежит поверх нижнего ряда задвижек.</t>
+          <t>Пол в контейнере деревянный, настил под низ не нужен. Задвижки кладем прямо на пол, поверх них доску, и уже на доску остальную арматуру — чтобы металл не бился о металл. Доска идет МЕЖДУ ярусами, а не под низ.</t>
         </is>
       </c>
     </row>
@@ -15670,52 +15589,52 @@
     <row r="5" ht="46" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Настил</t>
+          <t>1 ярус</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>сырая необрезная доска по полу</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr"/>
-      <c r="D5" s="18" t="inlineStr"/>
-      <c r="E5" s="4" t="n">
-        <v>700</v>
+          <t>задвижки клинкетные НА ПОЛ</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>7 304</t>
+        </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>700 кг доски на всю укладку</t>
+          <t>пол деревянный, настил не нужен. Штоком ГОРИЗОНТАЛЬНО, фланец на фланец не кладем никогда, съемные маховики снимаем в ящик с биркой</t>
         </is>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>1 ярус</t>
+          <t>Доска</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>задвижки клинкетные</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="n">
-        <v>11</v>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>7 304</t>
-        </is>
+          <t>перекладочная доска поверх задвижек</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr"/>
+      <c r="D6" s="18" t="inlineStr"/>
+      <c r="E6" s="4" t="n">
+        <v>700</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>штоком ГОРИЗОНТАЛЬНО, фланец на фланец не кладем никогда, съемные маховики снимаем в ящик с биркой</t>
+          <t>700 кг на всю укладку. Кладется МЕЖДУ ярусами, чтобы арматура не билась друг о друга. Прокладки с шагом 300-400 мм и строго над корпусами задвижек, под угол ящика над пустотой — брус 50х50</t>
         </is>
       </c>
     </row>
@@ -15745,289 +15664,289 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>рядом с задвижками на полу, а не сверху</t>
+          <t>на доску поверх задвижек, либо рядом на свободном полу</t>
         </is>
       </c>
     </row>
     <row r="8" ht="46" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>3 ярус</t>
+          <t>Доска</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>ящики и коробки с мелочью</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="n">
-        <v>191</v>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>1 642</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>8 820</t>
-        </is>
+          <t>еще слой доски</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr"/>
+      <c r="D8" s="18" t="inlineStr"/>
+      <c r="E8" s="4" t="n">
+        <v>700</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>на доску поверх задвижек, прокладки с шагом 300-400 мм и строго над корпусами, под угол ящика над пустотой — брус 50х50</t>
+          <t>между тяжелой арматурой и ящиками, по тому же правилу</t>
         </is>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>3 ярус</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>ящики и коробки с мелочью</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>191</v>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>1 642</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>8 820</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>на доску. Мелочь едет в ящиках, россыпью не кладем</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
           <t>Верх</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>фильтры забортной воды</t>
         </is>
       </c>
-      <c r="C9" s="18" t="n">
+      <c r="C10" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>1 741</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>наверх идет только легкое; крупные фильтры Ду200 ставим на пол, а не на ящики</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>наверх идет только легкое; крупные фильтры Ду200 ставим на свободный пол, а не на ящики</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Пол контейнера: сорокафутовый, 12.03 м в длину</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Ду</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Штук</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Поперек, шт</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Рядов</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Глубина, м</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Высота стопки, м</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>Ду350</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>0.52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>Ду300</t>
+          <t>Ду350</t>
         </is>
       </c>
       <c r="B15" s="18" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C15" s="18" t="n">
         <v>2</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>3.15</v>
+        <v>0.5</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>Ду250</t>
+          <t>Ду300</t>
         </is>
       </c>
       <c r="B16" s="18" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C16" s="18" t="n">
         <v>2</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>4.4</v>
+        <v>3.15</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>0.41</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="18" t="inlineStr">
         <is>
+          <t>Ду250</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="n">
+        <v>21</v>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
           <t>Ду200</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n">
+      <c r="B18" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="18" t="n">
+      <c r="C18" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D18" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E17" s="18" t="n">
+      <c r="E18" s="18" t="n">
         <v>1.75</v>
       </c>
-      <c r="F17" s="18" t="n">
+      <c r="F18" s="18" t="n">
         <v>0.34</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="25" t="inlineStr">
-        <is>
-          <t>Ду125</t>
-        </is>
-      </c>
-      <c r="B18" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="D18" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="25" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F18" s="25" t="n">
-        <v>0.25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="25" t="inlineStr">
         <is>
-          <t>Ду100</t>
+          <t>Ду125</t>
         </is>
       </c>
       <c r="B19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="25" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="F19" s="25" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="25" t="inlineStr">
         <is>
-          <t>Ду80</t>
+          <t>Ду100</t>
         </is>
       </c>
       <c r="B20" s="25" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="C20" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20" s="25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E20" s="25" t="n">
-        <v>1.2</v>
+        <v>0.23</v>
       </c>
       <c r="F20" s="25" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="25" t="inlineStr">
         <is>
-          <t>Ду60</t>
+          <t>Ду80</t>
         </is>
       </c>
       <c r="B21" s="25" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="C21" s="25" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E21" s="25" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="F21" s="25" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="25" t="inlineStr">
         <is>
-          <t>Ду50</t>
+          <t>Ду60</t>
         </is>
       </c>
       <c r="B22" s="25" t="n">
@@ -16047,88 +15966,128 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>Ду50</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F23" s="25" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Крупные от Ду200</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr"/>
-      <c r="C23" s="20" t="inlineStr"/>
-      <c r="D23" s="20" t="inlineStr"/>
-      <c r="E23" s="20" t="n">
+      <c r="B24" s="20" t="inlineStr"/>
+      <c r="C24" s="20" t="inlineStr"/>
+      <c r="D24" s="20" t="inlineStr"/>
+      <c r="E24" s="20" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="F23" s="20" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Свободный пол</t>
         </is>
       </c>
-      <c r="B24" s="27" t="inlineStr"/>
-      <c r="C24" s="27" t="inlineStr"/>
-      <c r="D24" s="27" t="inlineStr"/>
-      <c r="E24" s="27" t="n">
+      <c r="B25" s="27" t="inlineStr"/>
+      <c r="C25" s="27" t="inlineStr"/>
+      <c r="D25" s="27" t="inlineStr"/>
+      <c r="E25" s="27" t="n">
         <v>2.23</v>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>2 мест под ящики на полу</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>— Задвижки от Ду200 просят 9.80 м пола при длине 12.03 м. Они ложатся В ОДИН СЛОЙ, и остается 2.23 м свободного пола.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>— Мелкие задвижки Ду125 и ниже заняли бы еще 2.48 м пола. Их на пол не кладем: они легкие, идут в ящики и наверх. Желтым они и помечены.</t>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Высота под вторым ярусом</t>
+        </is>
+      </c>
+      <c r="B26" s="28" t="inlineStr"/>
+      <c r="C26" s="28" t="inlineStr"/>
+      <c r="D26" s="28" t="inlineStr"/>
+      <c r="E26" s="28" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>задвижка на боку плюс доска — с этой отметки начинается второй ярус арматуры</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
         <is>
+          <t>— Задвижки от Ду200 просят 9.80 м пола при длине 12.03 м. Они ложатся В ОДИН СЛОЙ, и остается 2.23 м свободного пола.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>— Мелкие задвижки Ду125 и ниже заняли бы еще 2.48 м пола. Их на пол не кладем: они легкие, идут в ящики и наверх. Желтым они и помечены.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
           <t>— Габариты справочные, по типовым судовым бронзовым клинкетам. Замерить на первых рядах в день погрузки: справочник уже ошибся на массах почти вдвое.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Чего делать нельзя</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>— Класть фланец на фланец. Ломается не корпус — бронза держит 200 МПа при наших 0,01 — а шток, маховик и привалочная поверхность фланца.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="17" t="inlineStr">
-        <is>
-          <t>— Ставить арматуру на арматуру ярусами. Задвижки и тяжелое лежат на полу в один слой, ящики стоят рядом, на ящики идут только фильтры.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="17" t="inlineStr">
         <is>
-          <t>— Класть прокладку под ящик над пустотой: доска 200х25 на пролете 600 мм дает 10,6 МПа изгиба при расчетных 10 для сырой необрезной с сучками. Шаг 300-400 мм и над корпусами.</t>
+          <t>— Класть фланец на фланец. Ломается не корпус — бронза держит 200 МПа при наших 0,01 — а шток, маховик и привалочная поверхность фланца.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>— Класть арматуру на арматуру БЕЗ ДОСКИ между ярусами. Металл о металл в дороге разбивает фланцы и штоки. Между каждым ярусом — слой доски.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>— Класть прокладку под ящик над пустотой: доска 200х25 на пролете 600 мм дает 10,6 МПа изгиба при расчетных 10 для сырой необрезной с сучками. Шаг 300-400 мм и над корпусами.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>— Грузить маховики россыпью. Снимаем в ящик с биркой, иначе задвижка приедет неполной и это станет претензией.</t>
         </is>
@@ -16196,7 +16155,7 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Согласовать письменно цену по 28 позициям «по согласованию» (521 кг)</t>
+          <t>Согласовать письменно цену по 91 позициям «по согласованию» (4 623 кг)</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
